--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-05 07:13</t>
+          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-06 07:25</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-05 07:13</t>
+          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-06 07:25</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-05 07:13</t>
+          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-06 07:25</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-06 07:25</t>
+          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-07 07:41</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1011,24 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>33.55</v>
+        <v>71.5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>34.73</v>
+        <v>74.02</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>3.52</v>
@@ -1037,24 +1037,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>71.5</v>
+        <v>33.55</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>74.02</v>
+        <v>34.73</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>3.52</v>
@@ -2077,12 +2077,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>107.89</v>
+        <v>516.39</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>109.51</v>
+        <v>524.14</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>1.5</v>
@@ -2103,12 +2103,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>516.39</v>
+        <v>107.89</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>524.14</v>
+        <v>109.51</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>1.5</v>
@@ -2415,24 +2415,24 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Smurfit Westrock</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>201.9</v>
+        <v>45.26</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>204.45</v>
+        <v>45.83</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>1.26</v>
@@ -2441,24 +2441,24 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Smurfit Westrock</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>45.26</v>
+        <v>201.9</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>45.83</v>
+        <v>204.45</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>1.26</v>
@@ -2519,12 +2519,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Idexx Laboratories</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>529.29</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>535.38</v>
+        <v>94.17</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>1.15</v>
@@ -2545,24 +2545,24 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>386.08</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>94.17</v>
+        <v>390.53</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>1.15</v>
@@ -2597,24 +2597,24 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>Idexx Laboratories</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>386.08</v>
+        <v>529.29</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>390.53</v>
+        <v>535.38</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>1.15</v>
@@ -2805,24 +2805,24 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>610.6799999999999</v>
+        <v>155.56</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>616.77</v>
+        <v>157.12</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>1</v>
@@ -2831,24 +2831,24 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>155.56</v>
+        <v>610.6799999999999</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>157.12</v>
+        <v>616.77</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>1</v>
@@ -2987,12 +2987,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>96.5</v>
+        <v>187.13</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>97.36</v>
+        <v>188.8</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>0.89</v>
@@ -3013,12 +3013,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>W. W. Grainger</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>187.13</v>
+        <v>1312.84</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>188.8</v>
+        <v>1324.49</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0.89</v>
@@ -3039,12 +3039,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>W. W. Grainger</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>1312.84</v>
+        <v>96.5</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>1324.49</v>
+        <v>97.36</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>0.89</v>
@@ -3065,24 +3065,24 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>82.06999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>82.78</v>
+        <v>89.97</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>0.87</v>
@@ -3091,24 +3091,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>89.19</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>89.97</v>
+        <v>82.78</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>0.87</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>91.77</v>
+        <v>228.45</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>92.54000000000001</v>
+        <v>230.36</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>0.84</v>
@@ -3195,24 +3195,24 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>228.45</v>
+        <v>91.77</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>230.36</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>0.84</v>
@@ -3221,24 +3221,24 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>56.3</v>
+        <v>210.51</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>56.77</v>
+        <v>212.25</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>0.83</v>
@@ -3247,24 +3247,24 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>210.51</v>
+        <v>56.3</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>212.25</v>
+        <v>56.77</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>0.83</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>52.73</v>
+        <v>2968.04</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>53</v>
+        <v>2983.29</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>0.51</v>
@@ -3585,24 +3585,24 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>2968.04</v>
+        <v>52.73</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2983.29</v>
+        <v>53</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>0.51</v>
@@ -3689,12 +3689,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>35.71</v>
+        <v>33.58</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>35.86</v>
+        <v>33.72</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>0.42</v>
@@ -3715,12 +3715,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>33.58</v>
+        <v>35.71</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>33.72</v>
+        <v>35.86</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0.42</v>
@@ -3741,24 +3741,24 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>331.94</v>
+        <v>151.38</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>333.26</v>
+        <v>151.99</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>0.4</v>
@@ -3767,24 +3767,24 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>151.38</v>
+        <v>331.94</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>151.99</v>
+        <v>333.26</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0.4</v>
@@ -3871,24 +3871,24 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>60.02</v>
+        <v>187.79</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>60.21</v>
+        <v>188.39</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>0.32</v>
@@ -3897,24 +3897,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>187.79</v>
+        <v>60.02</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>188.39</v>
+        <v>60.21</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>0.32</v>
@@ -4027,24 +4027,24 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>Host Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>22.12</v>
+        <v>21.99</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>22.18</v>
+        <v>22.05</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0.27</v>
@@ -4053,24 +4053,24 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Host Hotels &amp; Resorts</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>21.99</v>
+        <v>317.49</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>22.05</v>
+        <v>318.36</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>0.27</v>
@@ -4079,24 +4079,24 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>317.49</v>
+        <v>22.12</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>318.36</v>
+        <v>22.18</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>0.27</v>
@@ -4131,24 +4131,24 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>214.13</v>
+        <v>169.21</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>214.69</v>
+        <v>169.65</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>0.26</v>
@@ -4157,24 +4157,24 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>164.01</v>
+        <v>214.13</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>164.44</v>
+        <v>214.69</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>0.26</v>
@@ -4183,24 +4183,24 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>169.21</v>
+        <v>217.15</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>169.65</v>
+        <v>217.72</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>0.26</v>
@@ -4209,24 +4209,24 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>217.15</v>
+        <v>164.01</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>217.72</v>
+        <v>164.44</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>0.26</v>
@@ -4313,12 +4313,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>254.66</v>
+        <v>57.41</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>255.09</v>
+        <v>57.51</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>0.17</v>
@@ -4339,24 +4339,24 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>245.18</v>
+        <v>254.66</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>245.6</v>
+        <v>255.09</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>0.17</v>
@@ -4365,24 +4365,24 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>57.41</v>
+        <v>245.18</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>57.51</v>
+        <v>245.6</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>0.17</v>
@@ -4391,24 +4391,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>289.15</v>
+        <v>193.94</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>289.62</v>
+        <v>194.26</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>0.16</v>
@@ -4417,24 +4417,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>193.94</v>
+        <v>289.15</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>194.26</v>
+        <v>289.62</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>0.16</v>
@@ -4495,24 +4495,24 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>58.51</v>
+        <v>74.05</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>58.59</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>0.14</v>
@@ -4521,24 +4521,24 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>74.05</v>
+        <v>58.51</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>74.15000000000001</v>
+        <v>58.59</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>0.14</v>
@@ -4547,24 +4547,24 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>89.78</v>
+        <v>23.48</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>23.51</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>0.13</v>
@@ -4599,24 +4599,24 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>23.48</v>
+        <v>89.78</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>23.51</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>0.13</v>
@@ -4651,24 +4651,24 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>185.38</v>
+        <v>124.31</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>185.59</v>
+        <v>124.45</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>0.11</v>
@@ -4677,24 +4677,24 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>124.31</v>
+        <v>278.97</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>124.45</v>
+        <v>279.28</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>0.11</v>
@@ -4703,24 +4703,24 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>278.97</v>
+        <v>185.38</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>279.28</v>
+        <v>185.59</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>0.11</v>
@@ -4755,24 +4755,24 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Synchrony Financial</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>79.84999999999999</v>
+        <v>105.6</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>79.92</v>
+        <v>105.69</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>0.09</v>
@@ -4781,24 +4781,24 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Synchrony Financial</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>105.6</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>105.69</v>
+        <v>79.92</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>0.09</v>
@@ -4807,24 +4807,24 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Truist Financial</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>51.61</v>
+        <v>234.71</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>51.65</v>
+        <v>234.89</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0.08</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Truist Financial</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>234.71</v>
+        <v>51.61</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>234.89</v>
+        <v>51.65</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>0.08</v>
@@ -4859,24 +4859,24 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>1037.93</v>
+        <v>14.78</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1038.61</v>
+        <v>14.79</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -4885,24 +4885,24 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
-        <v>14.78</v>
+        <v>1037.93</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>14.79</v>
+        <v>1038.61</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -4911,24 +4911,24 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>106.41</v>
+        <v>185.75</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>106.47</v>
+        <v>185.87</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>0.06</v>
@@ -4937,24 +4937,24 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>185.75</v>
+        <v>106.41</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>185.87</v>
+        <v>106.47</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>0.06</v>
@@ -5015,24 +5015,24 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>89.79000000000001</v>
+        <v>370.69</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>89.8</v>
+        <v>370.72</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0.01</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>370.69</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>370.72</v>
+        <v>89.8</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>0.01</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>68</v>
+        <v>298.5</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>67.97</v>
+        <v>298.38</v>
       </c>
       <c r="F183" s="7" t="n">
         <v>-0.04</v>
@@ -5197,24 +5197,24 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>98.59</v>
+        <v>156.36</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>98.55</v>
+        <v>156.29</v>
       </c>
       <c r="F184" s="7" t="n">
         <v>-0.04</v>
@@ -5223,24 +5223,24 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>298.5</v>
+        <v>98.59</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>298.38</v>
+        <v>98.55</v>
       </c>
       <c r="F185" s="7" t="n">
         <v>-0.04</v>
@@ -5249,24 +5249,24 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>156.36</v>
+        <v>68</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>156.29</v>
+        <v>67.97</v>
       </c>
       <c r="F186" s="7" t="n">
         <v>-0.04</v>
@@ -5379,24 +5379,24 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate Equities</t>
+          <t>A. O. Smith</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>52.69</v>
+        <v>60.53</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>52.65</v>
+        <v>60.48</v>
       </c>
       <c r="F191" s="7" t="n">
         <v>-0.08</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Alexandria Real Estate Equities</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>132.19</v>
+        <v>52.69</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>132.08</v>
+        <v>52.65</v>
       </c>
       <c r="F192" s="7" t="n">
         <v>-0.08</v>
@@ -5431,24 +5431,24 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>A. O. Smith</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
-        <v>60.53</v>
+        <v>132.19</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>60.48</v>
+        <v>132.08</v>
       </c>
       <c r="F193" s="7" t="n">
         <v>-0.08</v>
@@ -5457,24 +5457,24 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>240.06</v>
+        <v>23.04</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>239.84</v>
+        <v>23.02</v>
       </c>
       <c r="F194" s="7" t="n">
         <v>-0.09</v>
@@ -5483,24 +5483,24 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>23.04</v>
+        <v>240.06</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>23.02</v>
+        <v>239.84</v>
       </c>
       <c r="F195" s="7" t="n">
         <v>-0.09</v>
@@ -5535,24 +5535,24 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
-        <v>694.41</v>
+        <v>15.59</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>693.53</v>
+        <v>15.57</v>
       </c>
       <c r="F197" s="7" t="n">
         <v>-0.13</v>
@@ -5587,24 +5587,24 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
-        <v>15.59</v>
+        <v>694.41</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>15.57</v>
+        <v>693.53</v>
       </c>
       <c r="F199" s="7" t="n">
         <v>-0.13</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>40.57</v>
+        <v>124.71</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>40.5</v>
+        <v>124.5</v>
       </c>
       <c r="F204" s="7" t="n">
         <v>-0.17</v>
@@ -5743,24 +5743,24 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Molson Coors Beverage Company</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>124.71</v>
+        <v>40.57</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>124.5</v>
+        <v>40.5</v>
       </c>
       <c r="F205" s="7" t="n">
         <v>-0.17</v>
@@ -5769,12 +5769,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Huntington Bancshares</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D206" s="5" t="n">
-        <v>54.97</v>
+        <v>17.06</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>54.87</v>
+        <v>17.03</v>
       </c>
       <c r="F206" s="7" t="n">
         <v>-0.18</v>
@@ -5795,12 +5795,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Huntington Bancshares</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>17.06</v>
+        <v>54.97</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>17.03</v>
+        <v>54.87</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>-0.18</v>
@@ -5821,24 +5821,24 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>128.56</v>
+        <v>68.59</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>128.32</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="F208" s="7" t="n">
         <v>-0.19</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>68.59</v>
+        <v>128.56</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>68.45999999999999</v>
+        <v>128.32</v>
       </c>
       <c r="F209" s="7" t="n">
         <v>-0.19</v>
@@ -6133,24 +6133,24 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>44.51</v>
+        <v>384.19</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>44.37</v>
+        <v>383</v>
       </c>
       <c r="F220" s="7" t="n">
         <v>-0.31</v>
@@ -6159,24 +6159,24 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>384.19</v>
+        <v>130.63</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>383</v>
+        <v>130.22</v>
       </c>
       <c r="F221" s="7" t="n">
         <v>-0.31</v>
@@ -6211,24 +6211,24 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>130.63</v>
+        <v>44.51</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>130.22</v>
+        <v>44.37</v>
       </c>
       <c r="F223" s="7" t="n">
         <v>-0.31</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>92.95</v>
+        <v>209.41</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>92.62</v>
+        <v>208.65</v>
       </c>
       <c r="F228" s="7" t="n">
         <v>-0.36</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>209.41</v>
+        <v>92.95</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>208.65</v>
+        <v>92.62</v>
       </c>
       <c r="F229" s="7" t="n">
         <v>-0.36</v>
@@ -6419,12 +6419,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>71.48</v>
+        <v>79.37</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="F231" s="7" t="n">
         <v>-0.38</v>
@@ -6471,12 +6471,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>79.37</v>
+        <v>71.48</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>79.06999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F233" s="7" t="n">
         <v>-0.38</v>
@@ -6497,24 +6497,24 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>62.93</v>
+        <v>508.13</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>62.67</v>
+        <v>506.03</v>
       </c>
       <c r="F234" s="7" t="n">
         <v>-0.41</v>
@@ -6549,24 +6549,24 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D236" s="5" t="n">
-        <v>508.13</v>
+        <v>62.93</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>506.03</v>
+        <v>62.67</v>
       </c>
       <c r="F236" s="7" t="n">
         <v>-0.41</v>
@@ -6575,24 +6575,24 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>28.37</v>
+        <v>108.79</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>28.25</v>
+        <v>108.33</v>
       </c>
       <c r="F237" s="7" t="n">
         <v>-0.42</v>
@@ -6601,24 +6601,24 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Ross Stores</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>108.79</v>
+        <v>231.67</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>108.33</v>
+        <v>230.69</v>
       </c>
       <c r="F238" s="7" t="n">
         <v>-0.42</v>
@@ -6627,24 +6627,24 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Ross Stores</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>231.67</v>
+        <v>28.37</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>230.69</v>
+        <v>28.25</v>
       </c>
       <c r="F239" s="7" t="n">
         <v>-0.42</v>
@@ -6653,12 +6653,12 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>293.35</v>
+        <v>392.15</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>292.08</v>
+        <v>390.47</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>-0.43</v>
@@ -6679,12 +6679,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>392.15</v>
+        <v>293.35</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>390.47</v>
+        <v>292.08</v>
       </c>
       <c r="F241" s="7" t="n">
         <v>-0.43</v>
@@ -6783,24 +6783,24 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>97.2</v>
+        <v>1040.83</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>1035.98</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>-0.47</v>
@@ -6809,24 +6809,24 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>1040.83</v>
+        <v>97.2</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>1035.98</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="F246" s="7" t="n">
         <v>-0.47</v>
@@ -6939,24 +6939,24 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>262.47</v>
+        <v>218.04</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>261.07</v>
+        <v>216.88</v>
       </c>
       <c r="F251" s="7" t="n">
         <v>-0.53</v>
@@ -6991,24 +6991,24 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>218.04</v>
+        <v>262.47</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>216.88</v>
+        <v>261.07</v>
       </c>
       <c r="F253" s="7" t="n">
         <v>-0.53</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>63.04</v>
+        <v>47.04</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>62.68</v>
+        <v>46.77</v>
       </c>
       <c r="F256" s="7" t="n">
         <v>-0.57</v>
@@ -7095,24 +7095,24 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>47.04</v>
+        <v>63.04</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>46.77</v>
+        <v>62.68</v>
       </c>
       <c r="F257" s="7" t="n">
         <v>-0.57</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>71.47</v>
+        <v>37.29</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>71.05</v>
+        <v>37.07</v>
       </c>
       <c r="F259" s="7" t="n">
         <v>-0.59</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>37.29</v>
+        <v>71.47</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>37.07</v>
+        <v>71.05</v>
       </c>
       <c r="F261" s="7" t="n">
         <v>-0.59</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>84.56999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>84.04000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="F265" s="7" t="n">
         <v>-0.63</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>76.29000000000001</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>75.81</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="F266" s="7" t="n">
         <v>-0.63</v>
@@ -7407,24 +7407,24 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
-        <v>51.76</v>
+        <v>202.13</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>51.42</v>
+        <v>200.79</v>
       </c>
       <c r="F269" s="7" t="n">
         <v>-0.66</v>
@@ -7433,24 +7433,24 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>202.13</v>
+        <v>51.76</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>200.79</v>
+        <v>51.42</v>
       </c>
       <c r="F270" s="7" t="n">
         <v>-0.66</v>
@@ -7589,24 +7589,24 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>138.35</v>
+        <v>83.37</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>137.34</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F276" s="7" t="n">
         <v>-0.73</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>83.37</v>
+        <v>138.35</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>82.76000000000001</v>
+        <v>137.34</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>-0.73</v>
@@ -7771,24 +7771,24 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>419.68</v>
+        <v>68.23</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>416.37</v>
+        <v>67.69</v>
       </c>
       <c r="F283" s="7" t="n">
         <v>-0.79</v>
@@ -7823,24 +7823,24 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
-        <v>55.61</v>
+        <v>419.68</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>55.17</v>
+        <v>416.37</v>
       </c>
       <c r="F285" s="7" t="n">
         <v>-0.79</v>
@@ -7849,24 +7849,24 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>68.23</v>
+        <v>55.61</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>67.69</v>
+        <v>55.17</v>
       </c>
       <c r="F286" s="7" t="n">
         <v>-0.79</v>
@@ -7901,12 +7901,12 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>342.73</v>
+        <v>1356.23</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>339.97</v>
+        <v>1345.26</v>
       </c>
       <c r="F288" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7927,12 +7927,12 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D289" s="5" t="n">
-        <v>1356.23</v>
+        <v>92.44</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>1345.26</v>
+        <v>91.69</v>
       </c>
       <c r="F289" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7953,24 +7953,24 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D290" s="5" t="n">
-        <v>76.34</v>
+        <v>342.73</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>75.72</v>
+        <v>339.97</v>
       </c>
       <c r="F290" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7979,24 +7979,24 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>92.44</v>
+        <v>76.34</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>91.69</v>
+        <v>75.72</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>214.76</v>
+        <v>369.83</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>212.93</v>
+        <v>366.7</v>
       </c>
       <c r="F293" s="7" t="n">
         <v>-0.85</v>
@@ -8083,24 +8083,24 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>369.83</v>
+        <v>214.76</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>366.7</v>
+        <v>212.93</v>
       </c>
       <c r="F295" s="7" t="n">
         <v>-0.85</v>
@@ -8109,24 +8109,24 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Corteva</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D296" s="5" t="n">
-        <v>98.92</v>
+        <v>88.62</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>87.86</v>
       </c>
       <c r="F296" s="7" t="n">
         <v>-0.86</v>
@@ -8135,24 +8135,24 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Corteva</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
-        <v>88.62</v>
+        <v>98.92</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>87.86</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F297" s="7" t="n">
         <v>-0.86</v>
@@ -8161,24 +8161,24 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>75.92</v>
+        <v>214.97</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>213.1</v>
       </c>
       <c r="F298" s="7" t="n">
         <v>-0.87</v>
@@ -8187,24 +8187,24 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>214.97</v>
+        <v>75.92</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>213.1</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F299" s="7" t="n">
         <v>-0.87</v>
@@ -8213,24 +8213,24 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D300" s="5" t="n">
-        <v>1159.6</v>
+        <v>32.88</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>1149.36</v>
+        <v>32.59</v>
       </c>
       <c r="F300" s="7" t="n">
         <v>-0.88</v>
@@ -8265,24 +8265,24 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>32.88</v>
+        <v>1159.6</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>32.59</v>
+        <v>1149.36</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>-0.88</v>
@@ -8291,24 +8291,24 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>147.54</v>
+        <v>50.59</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>146.23</v>
+        <v>50.14</v>
       </c>
       <c r="F303" s="7" t="n">
         <v>-0.89</v>
@@ -8317,24 +8317,24 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>50.59</v>
+        <v>147.54</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>50.14</v>
+        <v>146.23</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>-0.89</v>
@@ -8447,24 +8447,24 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Occidental Petroleum</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>195.13</v>
+        <v>60.61</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>193.29</v>
+        <v>60.04</v>
       </c>
       <c r="F309" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8499,24 +8499,24 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>362.06</v>
+        <v>195.13</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>358.64</v>
+        <v>193.29</v>
       </c>
       <c r="F311" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8525,24 +8525,24 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Occidental Petroleum</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>60.61</v>
+        <v>362.06</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>60.04</v>
+        <v>358.64</v>
       </c>
       <c r="F312" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8551,24 +8551,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>38.77</v>
+        <v>52.58</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>38.4</v>
+        <v>52.08</v>
       </c>
       <c r="F313" s="7" t="n">
         <v>-0.95</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>52.58</v>
+        <v>38.77</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>52.08</v>
+        <v>38.4</v>
       </c>
       <c r="F314" s="7" t="n">
         <v>-0.95</v>
@@ -8707,24 +8707,24 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>141.52</v>
+        <v>121.4</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>140.15</v>
+        <v>120.22</v>
       </c>
       <c r="F319" s="7" t="n">
         <v>-0.97</v>
@@ -8733,12 +8733,12 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>378.75</v>
+        <v>141.52</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>375.07</v>
+        <v>140.15</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>-0.97</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>121.4</v>
+        <v>378.75</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>120.22</v>
+        <v>375.07</v>
       </c>
       <c r="F321" s="7" t="n">
         <v>-0.97</v>
@@ -8811,24 +8811,24 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>128</v>
+        <v>211.52</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>126.75</v>
+        <v>209.44</v>
       </c>
       <c r="F323" s="7" t="n">
         <v>-0.98</v>
@@ -8837,24 +8837,24 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>211.52</v>
+        <v>128</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>209.44</v>
+        <v>126.75</v>
       </c>
       <c r="F324" s="7" t="n">
         <v>-0.98</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>110.88</v>
+        <v>226.83</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>109.78</v>
+        <v>224.59</v>
       </c>
       <c r="F327" s="7" t="n">
         <v>-0.99</v>
@@ -8941,24 +8941,24 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>226.83</v>
+        <v>110.88</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>224.59</v>
+        <v>109.78</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>-0.99</v>
@@ -8993,24 +8993,24 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>314.35</v>
+        <v>413.56</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>311.18</v>
+        <v>409.38</v>
       </c>
       <c r="F330" s="7" t="n">
         <v>-1.01</v>
@@ -9019,24 +9019,24 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>413.56</v>
+        <v>314.35</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>409.38</v>
+        <v>311.18</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>-1.01</v>
@@ -9045,24 +9045,24 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>409.2</v>
+        <v>84.45</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>405</v>
+        <v>83.58</v>
       </c>
       <c r="F332" s="7" t="n">
         <v>-1.03</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>84.45</v>
+        <v>409.2</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>83.58</v>
+        <v>405</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-1.03</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>177.75</v>
+        <v>225.12</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>175.85</v>
+        <v>222.71</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-1.07</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>225.12</v>
+        <v>177.75</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>222.71</v>
+        <v>175.85</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-1.07</v>
@@ -9253,24 +9253,24 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D340" s="5" t="n">
-        <v>175.06</v>
+        <v>57.57</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>173.15</v>
+        <v>56.94</v>
       </c>
       <c r="F340" s="7" t="n">
         <v>-1.09</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>57.57</v>
+        <v>175.06</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>56.94</v>
+        <v>173.15</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-1.09</v>
@@ -9305,24 +9305,24 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D342" s="5" t="n">
-        <v>585.71</v>
+        <v>366.5</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>579.21</v>
+        <v>362.42</v>
       </c>
       <c r="F342" s="7" t="n">
         <v>-1.11</v>
@@ -9331,24 +9331,24 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>339.08</v>
+        <v>18.95</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>335.31</v>
+        <v>18.74</v>
       </c>
       <c r="F343" s="7" t="n">
         <v>-1.11</v>
@@ -9383,24 +9383,24 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>137.68</v>
+        <v>339.08</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>136.15</v>
+        <v>335.31</v>
       </c>
       <c r="F345" s="7" t="n">
         <v>-1.11</v>
@@ -9409,24 +9409,24 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>366.5</v>
+        <v>137.68</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>362.42</v>
+        <v>136.15</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>-1.11</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>18.95</v>
+        <v>585.71</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>18.74</v>
+        <v>579.21</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-1.11</v>
@@ -9487,24 +9487,24 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>278.43</v>
+        <v>99.05</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>275.23</v>
+        <v>97.91</v>
       </c>
       <c r="F349" s="7" t="n">
         <v>-1.15</v>
@@ -9513,24 +9513,24 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>99.05</v>
+        <v>278.43</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>97.91</v>
+        <v>275.23</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>-1.15</v>
@@ -9591,24 +9591,24 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Bunge Global</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>342.48</v>
+        <v>120.12</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>338.46</v>
+        <v>118.71</v>
       </c>
       <c r="F353" s="7" t="n">
         <v>-1.17</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Bunge Global</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>120.12</v>
+        <v>342.48</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>118.71</v>
+        <v>338.46</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-1.17</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>108.42</v>
+        <v>6373.95</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>107.14</v>
+        <v>6298.85</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-1.18</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>6373.95</v>
+        <v>108.42</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>6298.85</v>
+        <v>107.14</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-1.18</v>
@@ -9721,24 +9721,24 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>26.81</v>
+        <v>293.54</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>26.49</v>
+        <v>290.05</v>
       </c>
       <c r="F358" s="7" t="n">
         <v>-1.19</v>
@@ -9747,24 +9747,24 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>293.54</v>
+        <v>26.81</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>290.05</v>
+        <v>26.49</v>
       </c>
       <c r="F359" s="7" t="n">
         <v>-1.19</v>
@@ -10423,24 +10423,24 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>532.95</v>
+        <v>188.46</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>525.28</v>
+        <v>185.74</v>
       </c>
       <c r="F385" s="7" t="n">
         <v>-1.44</v>
@@ -10449,12 +10449,12 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>68.02</v>
+        <v>260.21</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>67.04000000000001</v>
+        <v>256.46</v>
       </c>
       <c r="F386" s="7" t="n">
         <v>-1.44</v>
@@ -10475,12 +10475,12 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>260.21</v>
+        <v>68.02</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>256.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-1.44</v>
@@ -10501,24 +10501,24 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>188.46</v>
+        <v>532.95</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>185.74</v>
+        <v>525.28</v>
       </c>
       <c r="F388" s="7" t="n">
         <v>-1.44</v>
@@ -10683,24 +10683,24 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Principal Financial Group</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>118.51</v>
+        <v>187.62</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>116.68</v>
+        <v>184.74</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-1.54</v>
@@ -10709,24 +10709,24 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Principal Financial Group</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D396" s="5" t="n">
-        <v>187.62</v>
+        <v>118.51</v>
       </c>
       <c r="E396" s="5" t="n">
-        <v>184.74</v>
+        <v>116.68</v>
       </c>
       <c r="F396" s="7" t="n">
         <v>-1.54</v>
@@ -10735,24 +10735,24 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>444.12</v>
+        <v>181.1</v>
       </c>
       <c r="E397" s="5" t="n">
-        <v>437.23</v>
+        <v>178.29</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>-1.55</v>
@@ -10761,24 +10761,24 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D398" s="5" t="n">
-        <v>181.1</v>
+        <v>444.12</v>
       </c>
       <c r="E398" s="5" t="n">
-        <v>178.29</v>
+        <v>437.23</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>-1.55</v>
@@ -10787,12 +10787,12 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>450.58</v>
+        <v>72.56</v>
       </c>
       <c r="E399" s="5" t="n">
-        <v>443.51</v>
+        <v>71.42</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>-1.57</v>
@@ -10813,12 +10813,12 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="D400" s="5" t="n">
-        <v>72.56</v>
+        <v>450.58</v>
       </c>
       <c r="E400" s="5" t="n">
-        <v>71.42</v>
+        <v>443.51</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>-1.57</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>37.57</v>
+        <v>168.37</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>36.96</v>
+        <v>165.64</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-1.62</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>99.23</v>
+        <v>37.57</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>97.62</v>
+        <v>36.96</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-1.62</v>
@@ -11021,12 +11021,12 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
@@ -11035,10 +11035,10 @@
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>168.37</v>
+        <v>99.23</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>165.64</v>
+        <v>97.62</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>-1.62</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>347.03</v>
+        <v>140.02</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>341.08</v>
+        <v>137.63</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-1.71</v>
@@ -11229,24 +11229,24 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D416" s="5" t="n">
-        <v>140.02</v>
+        <v>347.03</v>
       </c>
       <c r="E416" s="5" t="n">
-        <v>137.63</v>
+        <v>341.08</v>
       </c>
       <c r="F416" s="7" t="n">
         <v>-1.71</v>
@@ -11359,24 +11359,24 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>185.25</v>
+        <v>130.43</v>
       </c>
       <c r="E421" s="5" t="n">
-        <v>181.94</v>
+        <v>128.09</v>
       </c>
       <c r="F421" s="7" t="n">
         <v>-1.79</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>130.43</v>
+        <v>185.25</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>128.09</v>
+        <v>181.94</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-1.79</v>
@@ -11437,24 +11437,24 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>Healthpeak Properties</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D424" s="5" t="n">
-        <v>21.03</v>
+        <v>30.95</v>
       </c>
       <c r="E424" s="5" t="n">
-        <v>20.65</v>
+        <v>30.39</v>
       </c>
       <c r="F424" s="7" t="n">
         <v>-1.81</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>Healthpeak Properties</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>30.95</v>
+        <v>21.03</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>30.39</v>
+        <v>20.65</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-1.81</v>
@@ -11541,24 +11541,24 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Crown Castle</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>98.70999999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>96.88</v>
+        <v>75.83</v>
       </c>
       <c r="F428" s="7" t="n">
         <v>-1.85</v>
@@ -11567,24 +11567,24 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Crown Castle</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>77.26000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>75.83</v>
+        <v>96.88</v>
       </c>
       <c r="F429" s="7" t="n">
         <v>-1.85</v>
@@ -11619,12 +11619,12 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C431" s="4" t="inlineStr">
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>843.47</v>
+        <v>68.09</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>827.72</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F431" s="7" t="n">
         <v>-1.87</v>
@@ -11645,12 +11645,12 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C432" s="4" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D432" s="5" t="n">
-        <v>68.09</v>
+        <v>843.47</v>
       </c>
       <c r="E432" s="5" t="n">
-        <v>66.81999999999999</v>
+        <v>827.72</v>
       </c>
       <c r="F432" s="7" t="n">
         <v>-1.87</v>
@@ -11827,24 +11827,24 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>92.11</v>
+        <v>44.53</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>90.27</v>
+        <v>43.64</v>
       </c>
       <c r="F439" s="7" t="n">
         <v>-2</v>
@@ -11853,24 +11853,24 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D440" s="5" t="n">
-        <v>44.53</v>
+        <v>92.11</v>
       </c>
       <c r="E440" s="5" t="n">
-        <v>43.64</v>
+        <v>90.27</v>
       </c>
       <c r="F440" s="7" t="n">
         <v>-2</v>
@@ -12763,24 +12763,24 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>284.38</v>
+        <v>56.82</v>
       </c>
       <c r="E475" s="5" t="n">
-        <v>275.09</v>
+        <v>54.96</v>
       </c>
       <c r="F475" s="7" t="n">
         <v>-3.27</v>
@@ -12789,24 +12789,24 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D476" s="5" t="n">
-        <v>56.82</v>
+        <v>284.38</v>
       </c>
       <c r="E476" s="5" t="n">
-        <v>54.96</v>
+        <v>275.09</v>
       </c>
       <c r="F476" s="7" t="n">
         <v>-3.27</v>
@@ -13101,24 +13101,24 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D488" s="5" t="n">
-        <v>192.7</v>
+        <v>538.15</v>
       </c>
       <c r="E488" s="5" t="n">
-        <v>184.64</v>
+        <v>515.67</v>
       </c>
       <c r="F488" s="7" t="n">
         <v>-4.18</v>
@@ -13127,24 +13127,24 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>538.15</v>
+        <v>192.7</v>
       </c>
       <c r="E489" s="5" t="n">
-        <v>515.67</v>
+        <v>184.64</v>
       </c>
       <c r="F489" s="7" t="n">
         <v>-4.18</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-06 07:25</t>
+          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-07 07:41</t>
         </is>
       </c>
     </row>
@@ -14795,30 +14795,30 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>794.1900000000001</v>
+        <v>250.5</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>827.72</v>
+        <v>261.07</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>852.03</v>
+        <v>263.97</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>794.1900000000001</v>
+        <v>249.64</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>4.22</v>
@@ -14827,30 +14827,30 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>250.5</v>
+        <v>794.1900000000001</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>261.07</v>
+        <v>827.72</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>263.97</v>
+        <v>852.03</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>249.64</v>
+        <v>794.1900000000001</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>4.22</v>
@@ -15691,30 +15691,30 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>322.03</v>
+        <v>164.19</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>330.95</v>
+        <v>168.74</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>337.22</v>
+        <v>170.48</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>322.03</v>
+        <v>164.19</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>2.77</v>
@@ -15723,30 +15723,30 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>164.19</v>
+        <v>322.03</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>168.74</v>
+        <v>330.95</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>170.48</v>
+        <v>337.22</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>164.19</v>
+        <v>322.03</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>2.77</v>
@@ -15851,30 +15851,30 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>36.18</v>
+        <v>128.26</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>37.07</v>
+        <v>131.42</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>37.63</v>
+        <v>131.91</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>36.18</v>
+        <v>126.59</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>2.46</v>
@@ -15883,30 +15883,30 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>128.26</v>
+        <v>36.18</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>131.42</v>
+        <v>37.07</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>131.91</v>
+        <v>37.63</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>126.59</v>
+        <v>36.18</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>2.46</v>
@@ -16331,12 +16331,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -16345,16 +16345,16 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>45.88</v>
+        <v>81.84</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>46.77</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>47.04</v>
+        <v>84.06</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>45.86</v>
+        <v>81.84</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>1.94</v>
@@ -16363,12 +16363,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -16377,16 +16377,16 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>81.84</v>
+        <v>45.88</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>83.43000000000001</v>
+        <v>46.77</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>84.06</v>
+        <v>47.04</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>81.84</v>
+        <v>45.86</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>1.94</v>
@@ -16779,30 +16779,30 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>27.96</v>
+        <v>62.41</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>28.45</v>
+        <v>63.5</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>29.02</v>
+        <v>64.63</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>27.96</v>
+        <v>62.41</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>1.75</v>
@@ -16811,30 +16811,30 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>62.41</v>
+        <v>27.96</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>63.5</v>
+        <v>28.45</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>64.63</v>
+        <v>29.02</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>62.41</v>
+        <v>27.96</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>1.75</v>
@@ -17291,30 +17291,30 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>105.75</v>
+        <v>162.5</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>107.27</v>
+        <v>164.84</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>107.78</v>
+        <v>164.84</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>105.75</v>
+        <v>160.51</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>1.44</v>
@@ -17355,30 +17355,30 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>162.5</v>
+        <v>105.75</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>164.84</v>
+        <v>107.27</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>164.84</v>
+        <v>107.78</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>160.51</v>
+        <v>105.75</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>1.44</v>
@@ -17771,12 +17771,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -17785,16 +17785,16 @@
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>39.24</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>39.67</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>39.98</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>39.24</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H132" s="6" t="n">
         <v>1.1</v>
@@ -17803,30 +17803,30 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>128.8</v>
+        <v>54.57</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>130.22</v>
+        <v>55.17</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>130.94</v>
+        <v>55.75</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>126.59</v>
+        <v>54.18</v>
       </c>
       <c r="H133" s="6" t="n">
         <v>1.1</v>
@@ -17835,30 +17835,30 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>54.57</v>
+        <v>39.24</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>55.17</v>
+        <v>39.67</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>55.75</v>
+        <v>39.98</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>54.18</v>
+        <v>39.24</v>
       </c>
       <c r="H134" s="6" t="n">
         <v>1.1</v>
@@ -17867,30 +17867,30 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>80.65000000000001</v>
+        <v>128.8</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>130.22</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>81.93000000000001</v>
+        <v>130.94</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>80.65000000000001</v>
+        <v>126.59</v>
       </c>
       <c r="H135" s="6" t="n">
         <v>1.1</v>
@@ -17931,30 +17931,30 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>392.95</v>
+        <v>237.29</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>397.14</v>
+        <v>239.84</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>400.94</v>
+        <v>240.06</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>389.41</v>
+        <v>232.02</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>1.07</v>
@@ -17963,12 +17963,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -17977,16 +17977,16 @@
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>218.5</v>
+        <v>392.95</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>220.83</v>
+        <v>397.14</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>224.51</v>
+        <v>400.94</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>216.04</v>
+        <v>389.41</v>
       </c>
       <c r="H138" s="6" t="n">
         <v>1.07</v>
@@ -17995,30 +17995,30 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>237.29</v>
+        <v>218.5</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>239.84</v>
+        <v>220.83</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>240.06</v>
+        <v>224.51</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>232.02</v>
+        <v>216.04</v>
       </c>
       <c r="H139" s="6" t="n">
         <v>1.07</v>
@@ -18187,12 +18187,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Globe Life</t>
+          <t>Everest Group</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -18201,16 +18201,16 @@
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>172.79</v>
+        <v>377.61</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>174.27</v>
+        <v>380.87</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>176.52</v>
+        <v>386.25</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>172.3</v>
+        <v>374.65</v>
       </c>
       <c r="H145" s="6" t="n">
         <v>0.86</v>
@@ -18219,12 +18219,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Everest Group</t>
+          <t>Globe Life</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -18233,16 +18233,16 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>377.61</v>
+        <v>172.79</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>380.87</v>
+        <v>174.27</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>386.25</v>
+        <v>176.52</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>374.65</v>
+        <v>172.3</v>
       </c>
       <c r="H146" s="6" t="n">
         <v>0.86</v>
@@ -18283,30 +18283,30 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>197.67</v>
+        <v>34.72</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>199.22</v>
+        <v>34.99</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>203.42</v>
+        <v>34.99</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>197.67</v>
+        <v>34.6</v>
       </c>
       <c r="H148" s="6" t="n">
         <v>0.78</v>
@@ -18315,30 +18315,30 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>34.72</v>
+        <v>197.67</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>34.99</v>
+        <v>199.22</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>34.99</v>
+        <v>203.42</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>34.6</v>
+        <v>197.67</v>
       </c>
       <c r="H149" s="6" t="n">
         <v>0.78</v>
@@ -18379,30 +18379,30 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>163.18</v>
+        <v>287.82</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>164.44</v>
+        <v>290.05</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>164.44</v>
+        <v>296.06</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>160.88</v>
+        <v>287.82</v>
       </c>
       <c r="H151" s="6" t="n">
         <v>0.77</v>
@@ -18411,30 +18411,30 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>287.82</v>
+        <v>163.18</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>290.05</v>
+        <v>164.44</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>296.06</v>
+        <v>164.44</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>287.82</v>
+        <v>160.88</v>
       </c>
       <c r="H152" s="6" t="n">
         <v>0.77</v>
@@ -18443,30 +18443,30 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Carvana</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>184.64</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>186.01</v>
+        <v>74.59</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>189.79</v>
+        <v>74.59</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>182.27</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="H153" s="6" t="n">
         <v>0.74</v>
@@ -18475,30 +18475,30 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>337.47</v>
+        <v>184.64</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>339.97</v>
+        <v>186.01</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>342.73</v>
+        <v>189.79</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>337.47</v>
+        <v>182.27</v>
       </c>
       <c r="H154" s="6" t="n">
         <v>0.74</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Carvana</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>74.04000000000001</v>
+        <v>337.47</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>74.59</v>
+        <v>339.97</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>74.59</v>
+        <v>342.73</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>72.18000000000001</v>
+        <v>337.47</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>0.74</v>
@@ -18923,30 +18923,30 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>215.63</v>
+        <v>62.32</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>216.88</v>
+        <v>62.68</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>220.03</v>
+        <v>63.04</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>214.26</v>
+        <v>61.94</v>
       </c>
       <c r="H168" s="6" t="n">
         <v>0.58</v>
@@ -18955,30 +18955,30 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>62.32</v>
+        <v>354.97</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>62.68</v>
+        <v>357.03</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>63.04</v>
+        <v>357.03</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>61.94</v>
+        <v>335.46</v>
       </c>
       <c r="H169" s="6" t="n">
         <v>0.58</v>
@@ -18987,30 +18987,30 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>354.97</v>
+        <v>215.63</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>357.03</v>
+        <v>216.88</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>357.03</v>
+        <v>220.03</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>335.46</v>
+        <v>214.26</v>
       </c>
       <c r="H170" s="6" t="n">
         <v>0.58</v>
@@ -19595,30 +19595,30 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>26.41</v>
+        <v>30.33</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>26.49</v>
+        <v>30.42</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>27.06</v>
+        <v>30.44</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>26.3</v>
+        <v>29.29</v>
       </c>
       <c r="H189" s="6" t="n">
         <v>0.3</v>
@@ -19627,30 +19627,30 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>30.33</v>
+        <v>26.41</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>30.42</v>
+        <v>26.49</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>30.44</v>
+        <v>27.06</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>29.29</v>
+        <v>26.3</v>
       </c>
       <c r="H190" s="6" t="n">
         <v>0.3</v>
@@ -19787,30 +19787,30 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>459.66</v>
+        <v>34.65</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>460.72</v>
+        <v>34.73</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>460.72</v>
+        <v>34.73</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>443.31</v>
+        <v>33.01</v>
       </c>
       <c r="H195" s="6" t="n">
         <v>0.23</v>
@@ -19819,30 +19819,30 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D196" s="5" t="n">
-        <v>34.65</v>
+        <v>459.66</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>34.73</v>
+        <v>460.72</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>34.73</v>
+        <v>460.72</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>33.01</v>
+        <v>443.31</v>
       </c>
       <c r="H196" s="6" t="n">
         <v>0.23</v>
@@ -20011,12 +20011,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -20025,16 +20025,16 @@
         </is>
       </c>
       <c r="D202" s="5" t="n">
-        <v>218.64</v>
+        <v>442.89</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>218.95</v>
+        <v>443.51</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>223.87</v>
+        <v>450.58</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>218.08</v>
+        <v>431.71</v>
       </c>
       <c r="H202" s="6" t="n">
         <v>0.14</v>
@@ -20043,12 +20043,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -20057,16 +20057,16 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>442.89</v>
+        <v>218.64</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>443.51</v>
+        <v>218.95</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>450.58</v>
+        <v>223.87</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>431.71</v>
+        <v>218.08</v>
       </c>
       <c r="H203" s="6" t="n">
         <v>0.14</v>
@@ -20203,30 +20203,30 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>50.1</v>
+        <v>755.47</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>50.14</v>
+        <v>756.09</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>50.59</v>
+        <v>766.91</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>50.02</v>
+        <v>752.21</v>
       </c>
       <c r="H208" s="6" t="n">
         <v>0.08</v>
@@ -20235,30 +20235,30 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>755.47</v>
+        <v>319.7</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>756.09</v>
+        <v>319.97</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>766.91</v>
+        <v>328.21</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>752.21</v>
+        <v>316.85</v>
       </c>
       <c r="H209" s="6" t="n">
         <v>0.08</v>
@@ -20267,30 +20267,30 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>319.7</v>
+        <v>181.37</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>319.97</v>
+        <v>181.52</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>328.21</v>
+        <v>188.02</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>316.85</v>
+        <v>180.44</v>
       </c>
       <c r="H210" s="6" t="n">
         <v>0.08</v>
@@ -20299,12 +20299,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -20313,16 +20313,16 @@
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>181.37</v>
+        <v>50.1</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>181.52</v>
+        <v>50.14</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>188.02</v>
+        <v>50.59</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>180.44</v>
+        <v>50.02</v>
       </c>
       <c r="H211" s="6" t="n">
         <v>0.08</v>
@@ -20555,30 +20555,30 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Northern Trust</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>68.03</v>
+        <v>186.79</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>67.97</v>
+        <v>186.63</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>68.03</v>
+        <v>187.45</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>67.73999999999999</v>
+        <v>182.68</v>
       </c>
       <c r="H219" s="7" t="n">
         <v>-0.09</v>
@@ -20587,30 +20587,30 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Northern Trust</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>186.79</v>
+        <v>68.03</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>186.63</v>
+        <v>67.97</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>187.45</v>
+        <v>68.03</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>182.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H220" s="7" t="n">
         <v>-0.09</v>
@@ -20907,30 +20907,30 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>LyondellBasell</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D230" s="5" t="n">
-        <v>448.96</v>
+        <v>63.67</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>447.9</v>
+        <v>63.52</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>448.96</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="G230" s="5" t="n">
-        <v>439.02</v>
+        <v>63.52</v>
       </c>
       <c r="H230" s="7" t="n">
         <v>-0.24</v>
@@ -20939,30 +20939,30 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>LyondellBasell</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>63.67</v>
+        <v>448.96</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>63.52</v>
+        <v>447.9</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>66.56999999999999</v>
+        <v>448.96</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>63.52</v>
+        <v>439.02</v>
       </c>
       <c r="H231" s="7" t="n">
         <v>-0.24</v>
@@ -21163,30 +21163,30 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>90.20999999999999</v>
+        <v>53.18</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>53</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>90.81999999999999</v>
+        <v>53.31</v>
       </c>
       <c r="G238" s="5" t="n">
-        <v>89.78</v>
+        <v>51.67</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>-0.34</v>
@@ -21195,30 +21195,30 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>75.52</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>76.06</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="G239" s="5" t="n">
-        <v>74.77</v>
+        <v>89.78</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>-0.34</v>
@@ -21227,30 +21227,30 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>53.18</v>
+        <v>75.52</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>53.31</v>
+        <v>76.06</v>
       </c>
       <c r="G240" s="5" t="n">
-        <v>51.67</v>
+        <v>74.77</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>-0.34</v>
@@ -21451,30 +21451,30 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>Paccar</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
-        <v>171.97</v>
+        <v>125.34</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>171.1</v>
+        <v>124.7</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>174.72</v>
+        <v>125.34</v>
       </c>
       <c r="G247" s="5" t="n">
-        <v>169.9</v>
+        <v>122.13</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>-0.51</v>
@@ -21483,30 +21483,30 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D248" s="5" t="n">
-        <v>31.56</v>
+        <v>171.97</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>31.4</v>
+        <v>171.1</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>32.24</v>
+        <v>174.72</v>
       </c>
       <c r="G248" s="5" t="n">
-        <v>31.4</v>
+        <v>169.9</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>-0.51</v>
@@ -21515,30 +21515,30 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Paccar</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>125.34</v>
+        <v>31.56</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>124.7</v>
+        <v>31.4</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>125.34</v>
+        <v>32.24</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>122.13</v>
+        <v>31.4</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>-0.51</v>
@@ -21707,30 +21707,30 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>109.93</v>
+        <v>43.93</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>109.2</v>
+        <v>43.64</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>110.49</v>
+        <v>44.53</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>108.61</v>
+        <v>43.64</v>
       </c>
       <c r="H255" s="7" t="n">
         <v>-0.66</v>
@@ -21739,30 +21739,30 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>43.93</v>
+        <v>162.33</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>43.64</v>
+        <v>161.26</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>44.53</v>
+        <v>164.59</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>43.64</v>
+        <v>157.85</v>
       </c>
       <c r="H256" s="7" t="n">
         <v>-0.66</v>
@@ -21771,30 +21771,30 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>162.33</v>
+        <v>109.93</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>161.26</v>
+        <v>109.2</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>164.59</v>
+        <v>110.49</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>157.85</v>
+        <v>108.61</v>
       </c>
       <c r="H257" s="7" t="n">
         <v>-0.66</v>
@@ -21835,12 +21835,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -21849,16 +21849,16 @@
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>393.39</v>
+        <v>564.85</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>390.53</v>
+        <v>560.75</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>393.39</v>
+        <v>564.85</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>374</v>
+        <v>545.5</v>
       </c>
       <c r="H259" s="7" t="n">
         <v>-0.73</v>
@@ -21867,12 +21867,12 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -21881,16 +21881,16 @@
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>564.85</v>
+        <v>393.39</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>560.75</v>
+        <v>390.53</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>564.85</v>
+        <v>393.39</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>545.5</v>
+        <v>374</v>
       </c>
       <c r="H260" s="7" t="n">
         <v>-0.73</v>
@@ -23083,30 +23083,30 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>461.67</v>
+        <v>177.75</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>454.71</v>
+        <v>175.06</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>461.67</v>
+        <v>177.75</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>435.91</v>
+        <v>173.03</v>
       </c>
       <c r="H298" s="7" t="n">
         <v>-1.51</v>
@@ -23115,30 +23115,30 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>177.75</v>
+        <v>461.67</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>175.06</v>
+        <v>454.71</v>
       </c>
       <c r="F299" s="5" t="n">
-        <v>177.75</v>
+        <v>461.67</v>
       </c>
       <c r="G299" s="5" t="n">
-        <v>173.03</v>
+        <v>435.91</v>
       </c>
       <c r="H299" s="7" t="n">
         <v>-1.51</v>
@@ -23179,30 +23179,30 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>6396.27</v>
+        <v>189.61</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>6298.85</v>
+        <v>186.72</v>
       </c>
       <c r="F301" s="5" t="n">
-        <v>6396.27</v>
+        <v>193.12</v>
       </c>
       <c r="G301" s="5" t="n">
-        <v>6275.82</v>
+        <v>186.72</v>
       </c>
       <c r="H301" s="7" t="n">
         <v>-1.52</v>
@@ -23211,30 +23211,30 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>189.61</v>
+        <v>6396.27</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>186.72</v>
+        <v>6298.85</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>193.12</v>
+        <v>6396.27</v>
       </c>
       <c r="G302" s="5" t="n">
-        <v>186.72</v>
+        <v>6275.82</v>
       </c>
       <c r="H302" s="7" t="n">
         <v>-1.52</v>
@@ -23371,30 +23371,30 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>142.53</v>
+        <v>95.86</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>140.15</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="F307" s="5" t="n">
-        <v>143.17</v>
+        <v>95.86</v>
       </c>
       <c r="G307" s="5" t="n">
-        <v>138.06</v>
+        <v>91.2</v>
       </c>
       <c r="H307" s="7" t="n">
         <v>-1.67</v>
@@ -23403,30 +23403,30 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>95.86</v>
+        <v>142.53</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>94.26000000000001</v>
+        <v>140.15</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>95.86</v>
+        <v>143.17</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>91.2</v>
+        <v>138.06</v>
       </c>
       <c r="H308" s="7" t="n">
         <v>-1.67</v>
@@ -23531,30 +23531,30 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>62.36</v>
+        <v>208.05</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>61.28</v>
+        <v>204.45</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>62.45</v>
+        <v>208.05</v>
       </c>
       <c r="G312" s="5" t="n">
-        <v>61.28</v>
+        <v>199.84</v>
       </c>
       <c r="H312" s="7" t="n">
         <v>-1.73</v>
@@ -23563,30 +23563,30 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>208.05</v>
+        <v>62.36</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>204.45</v>
+        <v>61.28</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>208.05</v>
+        <v>62.45</v>
       </c>
       <c r="G313" s="5" t="n">
-        <v>199.84</v>
+        <v>61.28</v>
       </c>
       <c r="H313" s="7" t="n">
         <v>-1.73</v>
@@ -23755,30 +23755,30 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>204.18</v>
+        <v>621.96</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>200.47</v>
+        <v>610.65</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>204.18</v>
+        <v>621.96</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>198.09</v>
+        <v>606.36</v>
       </c>
       <c r="H319" s="7" t="n">
         <v>-1.82</v>
@@ -23787,30 +23787,30 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>87.95</v>
+        <v>267.56</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>86.34999999999999</v>
+        <v>262.69</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>87.95</v>
+        <v>267.56</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>85.78</v>
+        <v>262</v>
       </c>
       <c r="H320" s="7" t="n">
         <v>-1.82</v>
@@ -23819,30 +23819,30 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>International Flavors &amp; Fragrances</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>621.96</v>
+        <v>87.95</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>610.65</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>621.96</v>
+        <v>87.95</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>606.36</v>
+        <v>85.78</v>
       </c>
       <c r="H321" s="7" t="n">
         <v>-1.82</v>
@@ -23851,30 +23851,30 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>267.56</v>
+        <v>204.18</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>262.69</v>
+        <v>200.47</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>267.56</v>
+        <v>204.18</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>262</v>
+        <v>198.09</v>
       </c>
       <c r="H322" s="7" t="n">
         <v>-1.82</v>
@@ -23979,30 +23979,30 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>324.59</v>
+        <v>130.69</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>318.36</v>
+        <v>128.18</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>324.59</v>
+        <v>130.69</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>314.4</v>
+        <v>128.18</v>
       </c>
       <c r="H326" s="7" t="n">
         <v>-1.92</v>
@@ -24011,30 +24011,30 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>130.69</v>
+        <v>324.59</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>128.18</v>
+        <v>318.36</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>130.69</v>
+        <v>324.59</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>128.18</v>
+        <v>314.4</v>
       </c>
       <c r="H327" s="7" t="n">
         <v>-1.92</v>
@@ -24267,30 +24267,30 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>105.62</v>
+        <v>107.47</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>103.41</v>
+        <v>105.22</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>106.7</v>
+        <v>108.62</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>103.41</v>
+        <v>105.09</v>
       </c>
       <c r="H335" s="7" t="n">
         <v>-2.09</v>
@@ -24299,30 +24299,30 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>107.47</v>
+        <v>105.62</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>105.22</v>
+        <v>103.41</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>108.62</v>
+        <v>106.7</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>105.09</v>
+        <v>103.41</v>
       </c>
       <c r="H336" s="7" t="n">
         <v>-2.09</v>
@@ -24523,30 +24523,30 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>71.17</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>69.59</v>
+        <v>85.81</v>
       </c>
       <c r="F343" s="5" t="n">
-        <v>71.17</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>69.28</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="H343" s="7" t="n">
         <v>-2.22</v>
@@ -24555,30 +24555,30 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>85.81</v>
+        <v>69.59</v>
       </c>
       <c r="F344" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="G344" s="5" t="n">
-        <v>83.76000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="H344" s="7" t="n">
         <v>-2.22</v>
@@ -24779,30 +24779,30 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Molson Coors Beverage Company</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>242.76</v>
+        <v>41.46</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>237.14</v>
+        <v>40.5</v>
       </c>
       <c r="F351" s="5" t="n">
-        <v>242.76</v>
+        <v>41.46</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>236.22</v>
+        <v>39.76</v>
       </c>
       <c r="H351" s="7" t="n">
         <v>-2.32</v>
@@ -24811,30 +24811,30 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>41.46</v>
+        <v>242.76</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>40.5</v>
+        <v>237.14</v>
       </c>
       <c r="F352" s="5" t="n">
-        <v>41.46</v>
+        <v>242.76</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>39.76</v>
+        <v>236.22</v>
       </c>
       <c r="H352" s="7" t="n">
         <v>-2.32</v>
@@ -24843,30 +24843,30 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>346.59</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>338.46</v>
+        <v>67.69</v>
       </c>
       <c r="F353" s="5" t="n">
-        <v>346.59</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>335.02</v>
+        <v>67.06</v>
       </c>
       <c r="H353" s="7" t="n">
         <v>-2.35</v>
@@ -24875,30 +24875,30 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>346.59</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>67.69</v>
+        <v>338.46</v>
       </c>
       <c r="F354" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>346.59</v>
       </c>
       <c r="G354" s="5" t="n">
-        <v>67.06</v>
+        <v>335.02</v>
       </c>
       <c r="H354" s="7" t="n">
         <v>-2.35</v>
@@ -24971,12 +24971,12 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -24985,16 +24985,16 @@
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>214.56</v>
+        <v>140.7</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>209.44</v>
+        <v>137.34</v>
       </c>
       <c r="F357" s="5" t="n">
-        <v>214.56</v>
+        <v>140.7</v>
       </c>
       <c r="G357" s="5" t="n">
-        <v>209.44</v>
+        <v>136.59</v>
       </c>
       <c r="H357" s="7" t="n">
         <v>-2.39</v>
@@ -25003,12 +25003,12 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
@@ -25017,16 +25017,16 @@
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>140.7</v>
+        <v>214.56</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>137.34</v>
+        <v>209.44</v>
       </c>
       <c r="F358" s="5" t="n">
-        <v>140.7</v>
+        <v>214.56</v>
       </c>
       <c r="G358" s="5" t="n">
-        <v>136.59</v>
+        <v>209.44</v>
       </c>
       <c r="H358" s="7" t="n">
         <v>-2.39</v>
@@ -25451,30 +25451,30 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>73.31</v>
+        <v>108.1</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>71.42</v>
+        <v>105.31</v>
       </c>
       <c r="F372" s="5" t="n">
-        <v>73.31</v>
+        <v>108.1</v>
       </c>
       <c r="G372" s="5" t="n">
-        <v>71.42</v>
+        <v>105.31</v>
       </c>
       <c r="H372" s="7" t="n">
         <v>-2.58</v>
@@ -25483,30 +25483,30 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>108.1</v>
+        <v>1256.26</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>105.31</v>
+        <v>1223.86</v>
       </c>
       <c r="F373" s="5" t="n">
-        <v>108.1</v>
+        <v>1267.77</v>
       </c>
       <c r="G373" s="5" t="n">
-        <v>105.31</v>
+        <v>1213.65</v>
       </c>
       <c r="H373" s="7" t="n">
         <v>-2.58</v>
@@ -25515,30 +25515,30 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>1256.26</v>
+        <v>73.31</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>1223.86</v>
+        <v>71.42</v>
       </c>
       <c r="F374" s="5" t="n">
-        <v>1267.77</v>
+        <v>73.31</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>1213.65</v>
+        <v>71.42</v>
       </c>
       <c r="H374" s="7" t="n">
         <v>-2.58</v>
@@ -25579,30 +25579,30 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D376" s="5" t="n">
-        <v>343.75</v>
+        <v>23.64</v>
       </c>
       <c r="E376" s="5" t="n">
-        <v>334.74</v>
+        <v>23.02</v>
       </c>
       <c r="F376" s="5" t="n">
-        <v>343.75</v>
+        <v>23.64</v>
       </c>
       <c r="G376" s="5" t="n">
-        <v>334.47</v>
+        <v>23.02</v>
       </c>
       <c r="H376" s="7" t="n">
         <v>-2.62</v>
@@ -25611,30 +25611,30 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>23.64</v>
+        <v>343.75</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>23.02</v>
+        <v>334.74</v>
       </c>
       <c r="F377" s="5" t="n">
-        <v>23.64</v>
+        <v>343.75</v>
       </c>
       <c r="G377" s="5" t="n">
-        <v>23.02</v>
+        <v>334.47</v>
       </c>
       <c r="H377" s="7" t="n">
         <v>-2.62</v>
@@ -25867,30 +25867,30 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>100.91</v>
+        <v>38.03</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="F385" s="5" t="n">
-        <v>100.91</v>
+        <v>38.52</v>
       </c>
       <c r="G385" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="H385" s="7" t="n">
         <v>-2.81</v>
@@ -25899,30 +25899,30 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>38.03</v>
+        <v>100.91</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>36.96</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F386" s="5" t="n">
-        <v>38.52</v>
+        <v>100.91</v>
       </c>
       <c r="G386" s="5" t="n">
-        <v>36.96</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="H386" s="7" t="n">
         <v>-2.81</v>
@@ -26155,30 +26155,30 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D394" s="5" t="n">
-        <v>198.68</v>
+        <v>260.4</v>
       </c>
       <c r="E394" s="5" t="n">
-        <v>192.88</v>
+        <v>252.8</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>198.68</v>
+        <v>260.4</v>
       </c>
       <c r="G394" s="5" t="n">
-        <v>188.9</v>
+        <v>252.8</v>
       </c>
       <c r="H394" s="7" t="n">
         <v>-2.92</v>
@@ -26187,30 +26187,30 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>260.4</v>
+        <v>198.68</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>252.8</v>
+        <v>192.88</v>
       </c>
       <c r="F395" s="5" t="n">
-        <v>260.4</v>
+        <v>198.68</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>252.8</v>
+        <v>188.9</v>
       </c>
       <c r="H395" s="7" t="n">
         <v>-2.92</v>
@@ -26731,30 +26731,30 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>235.09</v>
+        <v>46.67</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>227.42</v>
+        <v>45.15</v>
       </c>
       <c r="F412" s="5" t="n">
-        <v>235.09</v>
+        <v>46.68</v>
       </c>
       <c r="G412" s="5" t="n">
-        <v>221.72</v>
+        <v>45.15</v>
       </c>
       <c r="H412" s="7" t="n">
         <v>-3.26</v>
@@ -26763,30 +26763,30 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>46.67</v>
+        <v>235.09</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>45.15</v>
+        <v>227.42</v>
       </c>
       <c r="F413" s="5" t="n">
-        <v>46.68</v>
+        <v>235.09</v>
       </c>
       <c r="G413" s="5" t="n">
-        <v>45.15</v>
+        <v>221.72</v>
       </c>
       <c r="H413" s="7" t="n">
         <v>-3.26</v>
@@ -27275,30 +27275,30 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>377.94</v>
+        <v>112.47</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>364.03</v>
+        <v>108.33</v>
       </c>
       <c r="F429" s="5" t="n">
-        <v>379.27</v>
+        <v>112.47</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>364.03</v>
+        <v>108.33</v>
       </c>
       <c r="H429" s="7" t="n">
         <v>-3.68</v>
@@ -27307,30 +27307,30 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>112.47</v>
+        <v>377.94</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>108.33</v>
+        <v>364.03</v>
       </c>
       <c r="F430" s="5" t="n">
-        <v>112.47</v>
+        <v>379.27</v>
       </c>
       <c r="G430" s="5" t="n">
-        <v>108.33</v>
+        <v>364.03</v>
       </c>
       <c r="H430" s="7" t="n">
         <v>-3.68</v>
@@ -27563,30 +27563,30 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>136.98</v>
+        <v>233.78</v>
       </c>
       <c r="E438" s="5" t="n">
-        <v>131.59</v>
+        <v>224.59</v>
       </c>
       <c r="F438" s="5" t="n">
-        <v>136.98</v>
+        <v>233.78</v>
       </c>
       <c r="G438" s="5" t="n">
-        <v>131.13</v>
+        <v>224.59</v>
       </c>
       <c r="H438" s="7" t="n">
         <v>-3.93</v>
@@ -27595,30 +27595,30 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>233.78</v>
+        <v>136.98</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>224.59</v>
+        <v>131.59</v>
       </c>
       <c r="F439" s="5" t="n">
-        <v>233.78</v>
+        <v>136.98</v>
       </c>
       <c r="G439" s="5" t="n">
-        <v>224.59</v>
+        <v>131.13</v>
       </c>
       <c r="H439" s="7" t="n">
         <v>-3.93</v>
@@ -28299,30 +28299,30 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D461" s="5" t="n">
-        <v>111.31</v>
+        <v>24.76</v>
       </c>
       <c r="E461" s="5" t="n">
-        <v>105.69</v>
+        <v>23.51</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>111.31</v>
+        <v>24.76</v>
       </c>
       <c r="G461" s="5" t="n">
-        <v>105.69</v>
+        <v>23.23</v>
       </c>
       <c r="H461" s="7" t="n">
         <v>-5.05</v>
@@ -28331,30 +28331,30 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D462" s="5" t="n">
-        <v>24.76</v>
+        <v>111.31</v>
       </c>
       <c r="E462" s="5" t="n">
-        <v>23.51</v>
+        <v>105.69</v>
       </c>
       <c r="F462" s="5" t="n">
-        <v>24.76</v>
+        <v>111.31</v>
       </c>
       <c r="G462" s="5" t="n">
-        <v>23.23</v>
+        <v>105.69</v>
       </c>
       <c r="H462" s="7" t="n">
         <v>-5.05</v>
@@ -28843,30 +28843,30 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D478" s="5" t="n">
-        <v>186.29</v>
+        <v>198.63</v>
       </c>
       <c r="E478" s="5" t="n">
-        <v>174.33</v>
+        <v>185.87</v>
       </c>
       <c r="F478" s="5" t="n">
-        <v>186.38</v>
+        <v>199.96</v>
       </c>
       <c r="G478" s="5" t="n">
-        <v>169.46</v>
+        <v>185.75</v>
       </c>
       <c r="H478" s="7" t="n">
         <v>-6.42</v>
@@ -28875,30 +28875,30 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D479" s="5" t="n">
-        <v>198.63</v>
+        <v>186.29</v>
       </c>
       <c r="E479" s="5" t="n">
-        <v>185.87</v>
+        <v>174.33</v>
       </c>
       <c r="F479" s="5" t="n">
-        <v>199.96</v>
+        <v>186.38</v>
       </c>
       <c r="G479" s="5" t="n">
-        <v>185.75</v>
+        <v>169.46</v>
       </c>
       <c r="H479" s="7" t="n">
         <v>-6.42</v>
@@ -28907,30 +28907,30 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>16.65</v>
+        <v>46.86</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>15.57</v>
+        <v>43.82</v>
       </c>
       <c r="F480" s="5" t="n">
-        <v>16.65</v>
+        <v>46.86</v>
       </c>
       <c r="G480" s="5" t="n">
-        <v>15.43</v>
+        <v>43.82</v>
       </c>
       <c r="H480" s="7" t="n">
         <v>-6.49</v>
@@ -28939,30 +28939,30 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>46.86</v>
+        <v>16.65</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>43.82</v>
+        <v>15.57</v>
       </c>
       <c r="F481" s="5" t="n">
-        <v>46.86</v>
+        <v>16.65</v>
       </c>
       <c r="G481" s="5" t="n">
-        <v>43.82</v>
+        <v>15.43</v>
       </c>
       <c r="H481" s="7" t="n">
         <v>-6.49</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-06 07:25</t>
+          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-07 07:41</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-07 07:41</t>
+          <t>Sep 03 close to Sep 04 close  |  503 companies  |  updated 2026-09-08 07:34</t>
         </is>
       </c>
     </row>
@@ -1011,24 +1011,24 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>71.5</v>
+        <v>33.55</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>74.02</v>
+        <v>34.73</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>3.52</v>
@@ -1037,24 +1037,24 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>33.55</v>
+        <v>71.5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>34.73</v>
+        <v>74.02</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>3.52</v>
@@ -2077,12 +2077,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>516.39</v>
+        <v>107.89</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>524.14</v>
+        <v>109.51</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>1.5</v>
@@ -2103,12 +2103,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>107.89</v>
+        <v>516.39</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>109.51</v>
+        <v>524.14</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>1.5</v>
@@ -2415,24 +2415,24 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Smurfit Westrock</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>45.26</v>
+        <v>201.9</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>45.83</v>
+        <v>204.45</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>1.26</v>
@@ -2441,24 +2441,24 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Smurfit Westrock</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>201.9</v>
+        <v>45.26</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>204.45</v>
+        <v>45.83</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>1.26</v>
@@ -2519,12 +2519,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>IDXX</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Idexx Laboratories</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>529.29</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>94.17</v>
+        <v>535.38</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>1.15</v>
@@ -2545,24 +2545,24 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>386.08</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>390.53</v>
+        <v>94.17</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>1.15</v>
@@ -2597,24 +2597,24 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Idexx Laboratories</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>529.29</v>
+        <v>386.08</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>535.38</v>
+        <v>390.53</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>1.15</v>
@@ -2805,24 +2805,24 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>155.56</v>
+        <v>610.6799999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>157.12</v>
+        <v>616.77</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>1</v>
@@ -2831,24 +2831,24 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>610.6799999999999</v>
+        <v>155.56</v>
       </c>
       <c r="E93" s="5" t="n">
-        <v>616.77</v>
+        <v>157.12</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>1</v>
@@ -2987,12 +2987,12 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>187.13</v>
+        <v>96.5</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>188.8</v>
+        <v>97.36</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>0.89</v>
@@ -3013,12 +3013,12 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>W. W. Grainger</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>1312.84</v>
+        <v>187.13</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1324.49</v>
+        <v>188.8</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>0.89</v>
@@ -3039,12 +3039,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>W. W. Grainger</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>96.5</v>
+        <v>1312.84</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>97.36</v>
+        <v>1324.49</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>0.89</v>
@@ -3065,24 +3065,24 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Amphenol</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>89.19</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>89.97</v>
+        <v>82.78</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>0.87</v>
@@ -3091,24 +3091,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>APH</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>82.06999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>82.78</v>
+        <v>89.97</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>0.87</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>228.45</v>
+        <v>91.77</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>230.36</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>0.84</v>
@@ -3195,24 +3195,24 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>91.77</v>
+        <v>228.45</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>92.54000000000001</v>
+        <v>230.36</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>0.84</v>
@@ -3221,24 +3221,24 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>210.51</v>
+        <v>56.3</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>212.25</v>
+        <v>56.77</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>0.83</v>
@@ -3247,24 +3247,24 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>56.3</v>
+        <v>210.51</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>56.77</v>
+        <v>212.25</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>0.83</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>2968.04</v>
+        <v>52.73</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2983.29</v>
+        <v>53</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>0.51</v>
@@ -3585,24 +3585,24 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>52.73</v>
+        <v>2968.04</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>53</v>
+        <v>2983.29</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>0.51</v>
@@ -3689,12 +3689,12 @@
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>CPRT</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Copart</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="D126" s="5" t="n">
-        <v>33.58</v>
+        <v>35.71</v>
       </c>
       <c r="E126" s="5" t="n">
-        <v>33.72</v>
+        <v>35.86</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>0.42</v>
@@ -3715,12 +3715,12 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>CPRT</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Copart</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>35.71</v>
+        <v>33.58</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>35.86</v>
+        <v>33.72</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>0.42</v>
@@ -3741,24 +3741,24 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>CHTR</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Charter Communications</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>151.38</v>
+        <v>331.94</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>151.99</v>
+        <v>333.26</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>0.4</v>
@@ -3767,24 +3767,24 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>CHTR</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Charter Communications</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>331.94</v>
+        <v>151.38</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>333.26</v>
+        <v>151.99</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>0.4</v>
@@ -3871,24 +3871,24 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>187.79</v>
+        <v>60.02</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>188.39</v>
+        <v>60.21</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>0.32</v>
@@ -3897,24 +3897,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>60.02</v>
+        <v>187.79</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>60.21</v>
+        <v>188.39</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>0.32</v>
@@ -4027,24 +4027,24 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>KEY</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Host Hotels &amp; Resorts</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>21.99</v>
+        <v>22.12</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>22.05</v>
+        <v>22.18</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>0.27</v>
@@ -4053,24 +4053,24 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Host Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>317.49</v>
+        <v>21.99</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>318.36</v>
+        <v>22.05</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>0.27</v>
@@ -4079,24 +4079,24 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>KEY</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>22.12</v>
+        <v>317.49</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>22.18</v>
+        <v>318.36</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>0.27</v>
@@ -4131,24 +4131,24 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>169.21</v>
+        <v>214.13</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>169.65</v>
+        <v>214.69</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>0.26</v>
@@ -4157,24 +4157,24 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>214.13</v>
+        <v>164.01</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>214.69</v>
+        <v>164.44</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>0.26</v>
@@ -4183,24 +4183,24 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>217.15</v>
+        <v>169.21</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>217.72</v>
+        <v>169.65</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>0.26</v>
@@ -4209,24 +4209,24 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>164.01</v>
+        <v>217.15</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>164.44</v>
+        <v>217.72</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>0.26</v>
@@ -4313,12 +4313,12 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>57.41</v>
+        <v>254.66</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>57.51</v>
+        <v>255.09</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>0.17</v>
@@ -4339,24 +4339,24 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>254.66</v>
+        <v>245.18</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>255.09</v>
+        <v>245.6</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>0.17</v>
@@ -4365,24 +4365,24 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>245.18</v>
+        <v>57.41</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>245.6</v>
+        <v>57.51</v>
       </c>
       <c r="F152" s="6" t="n">
         <v>0.17</v>
@@ -4391,24 +4391,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>193.94</v>
+        <v>289.15</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>194.26</v>
+        <v>289.62</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>0.16</v>
@@ -4417,24 +4417,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>289.15</v>
+        <v>193.94</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>289.62</v>
+        <v>194.26</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>0.16</v>
@@ -4495,24 +4495,24 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>74.05</v>
+        <v>58.51</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>74.15000000000001</v>
+        <v>58.59</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>0.14</v>
@@ -4521,24 +4521,24 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>58.51</v>
+        <v>74.05</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>58.59</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>0.14</v>
@@ -4547,24 +4547,24 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>23.48</v>
+        <v>89.78</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>23.51</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>0.13</v>
@@ -4599,24 +4599,24 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>89.78</v>
+        <v>23.48</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>23.51</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>0.13</v>
@@ -4651,24 +4651,24 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>PulteGroup</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>124.31</v>
+        <v>185.38</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>124.45</v>
+        <v>185.59</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>0.11</v>
@@ -4677,24 +4677,24 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>PHM</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>278.97</v>
+        <v>124.31</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>279.28</v>
+        <v>124.45</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>0.11</v>
@@ -4703,24 +4703,24 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>185.38</v>
+        <v>278.97</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>185.59</v>
+        <v>279.28</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>0.11</v>
@@ -4755,24 +4755,24 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>SYF</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Synchrony Financial</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>105.6</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>105.69</v>
+        <v>79.92</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>0.09</v>
@@ -4781,24 +4781,24 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>SYF</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Synchrony Financial</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>79.84999999999999</v>
+        <v>105.6</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>79.92</v>
+        <v>105.69</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>0.09</v>
@@ -4807,24 +4807,24 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>TFC</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Truist Financial</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>234.71</v>
+        <v>51.61</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>234.89</v>
+        <v>51.65</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0.08</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Truist Financial</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>51.61</v>
+        <v>234.71</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>51.65</v>
+        <v>234.89</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>0.08</v>
@@ -4859,24 +4859,24 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>14.78</v>
+        <v>1037.93</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>14.79</v>
+        <v>1038.61</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -4885,24 +4885,24 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
-        <v>1037.93</v>
+        <v>14.78</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1038.61</v>
+        <v>14.79</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -4911,24 +4911,24 @@
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>185.75</v>
+        <v>106.41</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>185.87</v>
+        <v>106.47</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>0.06</v>
@@ -4937,24 +4937,24 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>106.41</v>
+        <v>185.75</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>106.47</v>
+        <v>185.87</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>0.06</v>
@@ -5015,24 +5015,24 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>370.69</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>370.72</v>
+        <v>89.8</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0.01</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>89.79000000000001</v>
+        <v>370.69</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>89.8</v>
+        <v>370.72</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>0.01</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>CBOE</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>298.5</v>
+        <v>68</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>298.38</v>
+        <v>67.97</v>
       </c>
       <c r="F183" s="7" t="n">
         <v>-0.04</v>
@@ -5197,24 +5197,24 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>156.36</v>
+        <v>98.59</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>156.29</v>
+        <v>98.55</v>
       </c>
       <c r="F184" s="7" t="n">
         <v>-0.04</v>
@@ -5223,24 +5223,24 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>CBOE</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>98.59</v>
+        <v>298.5</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>98.55</v>
+        <v>298.38</v>
       </c>
       <c r="F185" s="7" t="n">
         <v>-0.04</v>
@@ -5249,24 +5249,24 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>68</v>
+        <v>156.36</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>67.97</v>
+        <v>156.29</v>
       </c>
       <c r="F186" s="7" t="n">
         <v>-0.04</v>
@@ -5379,24 +5379,24 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>A. O. Smith</t>
+          <t>Alexandria Real Estate Equities</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>60.53</v>
+        <v>52.69</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>60.48</v>
+        <v>52.65</v>
       </c>
       <c r="F191" s="7" t="n">
         <v>-0.08</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Alexandria Real Estate Equities</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>52.69</v>
+        <v>132.19</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>52.65</v>
+        <v>132.08</v>
       </c>
       <c r="F192" s="7" t="n">
         <v>-0.08</v>
@@ -5431,24 +5431,24 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>A. O. Smith</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
-        <v>132.19</v>
+        <v>60.53</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>132.08</v>
+        <v>60.48</v>
       </c>
       <c r="F193" s="7" t="n">
         <v>-0.08</v>
@@ -5457,24 +5457,24 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>23.04</v>
+        <v>240.06</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>23.02</v>
+        <v>239.84</v>
       </c>
       <c r="F194" s="7" t="n">
         <v>-0.09</v>
@@ -5483,24 +5483,24 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>240.06</v>
+        <v>23.04</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>239.84</v>
+        <v>23.02</v>
       </c>
       <c r="F195" s="7" t="n">
         <v>-0.09</v>
@@ -5535,24 +5535,24 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
-        <v>15.59</v>
+        <v>694.41</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>15.57</v>
+        <v>693.53</v>
       </c>
       <c r="F197" s="7" t="n">
         <v>-0.13</v>
@@ -5587,24 +5587,24 @@
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D199" s="5" t="n">
-        <v>694.41</v>
+        <v>15.59</v>
       </c>
       <c r="E199" s="5" t="n">
-        <v>693.53</v>
+        <v>15.57</v>
       </c>
       <c r="F199" s="7" t="n">
         <v>-0.13</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Molson Coors Beverage Company</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>124.71</v>
+        <v>40.57</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>124.5</v>
+        <v>40.5</v>
       </c>
       <c r="F204" s="7" t="n">
         <v>-0.17</v>
@@ -5743,24 +5743,24 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>40.57</v>
+        <v>124.71</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>40.5</v>
+        <v>124.5</v>
       </c>
       <c r="F205" s="7" t="n">
         <v>-0.17</v>
@@ -5769,12 +5769,12 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Huntington Bancshares</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -5783,10 +5783,10 @@
         </is>
       </c>
       <c r="D206" s="5" t="n">
-        <v>17.06</v>
+        <v>54.97</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>17.03</v>
+        <v>54.87</v>
       </c>
       <c r="F206" s="7" t="n">
         <v>-0.18</v>
@@ -5795,12 +5795,12 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Huntington Bancshares</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>54.97</v>
+        <v>17.06</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>54.87</v>
+        <v>17.03</v>
       </c>
       <c r="F207" s="7" t="n">
         <v>-0.18</v>
@@ -5821,24 +5821,24 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>68.59</v>
+        <v>128.56</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>68.45999999999999</v>
+        <v>128.32</v>
       </c>
       <c r="F208" s="7" t="n">
         <v>-0.19</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>128.56</v>
+        <v>68.59</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>128.32</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="F209" s="7" t="n">
         <v>-0.19</v>
@@ -6133,24 +6133,24 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>384.19</v>
+        <v>44.51</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>383</v>
+        <v>44.37</v>
       </c>
       <c r="F220" s="7" t="n">
         <v>-0.31</v>
@@ -6159,24 +6159,24 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>130.63</v>
+        <v>384.19</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>130.22</v>
+        <v>383</v>
       </c>
       <c r="F221" s="7" t="n">
         <v>-0.31</v>
@@ -6211,24 +6211,24 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>44.51</v>
+        <v>130.63</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>44.37</v>
+        <v>130.22</v>
       </c>
       <c r="F223" s="7" t="n">
         <v>-0.31</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>TEL</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>TE Connectivity</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>209.41</v>
+        <v>92.95</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>208.65</v>
+        <v>92.62</v>
       </c>
       <c r="F228" s="7" t="n">
         <v>-0.36</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>TEL</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>TE Connectivity</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>92.95</v>
+        <v>209.41</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>92.62</v>
+        <v>208.65</v>
       </c>
       <c r="F229" s="7" t="n">
         <v>-0.36</v>
@@ -6419,12 +6419,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>79.37</v>
+        <v>71.48</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>79.06999999999999</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F231" s="7" t="n">
         <v>-0.38</v>
@@ -6471,12 +6471,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>71.48</v>
+        <v>79.37</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>71.20999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="F233" s="7" t="n">
         <v>-0.38</v>
@@ -6497,24 +6497,24 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>508.13</v>
+        <v>62.93</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>506.03</v>
+        <v>62.67</v>
       </c>
       <c r="F234" s="7" t="n">
         <v>-0.41</v>
@@ -6549,24 +6549,24 @@
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D236" s="5" t="n">
-        <v>62.93</v>
+        <v>508.13</v>
       </c>
       <c r="E236" s="5" t="n">
-        <v>62.67</v>
+        <v>506.03</v>
       </c>
       <c r="F236" s="7" t="n">
         <v>-0.41</v>
@@ -6575,24 +6575,24 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>108.79</v>
+        <v>28.37</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>108.33</v>
+        <v>28.25</v>
       </c>
       <c r="F237" s="7" t="n">
         <v>-0.42</v>
@@ -6601,24 +6601,24 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Ross Stores</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>231.67</v>
+        <v>108.79</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>230.69</v>
+        <v>108.33</v>
       </c>
       <c r="F238" s="7" t="n">
         <v>-0.42</v>
@@ -6627,24 +6627,24 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Ross Stores</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>28.37</v>
+        <v>231.67</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>28.25</v>
+        <v>230.69</v>
       </c>
       <c r="F239" s="7" t="n">
         <v>-0.42</v>
@@ -6653,12 +6653,12 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>F5, Inc.</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>392.15</v>
+        <v>293.35</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>390.47</v>
+        <v>292.08</v>
       </c>
       <c r="F240" s="7" t="n">
         <v>-0.43</v>
@@ -6679,12 +6679,12 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>FFIV</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>F5, Inc.</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>293.35</v>
+        <v>392.15</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>292.08</v>
+        <v>390.47</v>
       </c>
       <c r="F241" s="7" t="n">
         <v>-0.43</v>
@@ -6783,24 +6783,24 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Equinix</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>1040.83</v>
+        <v>97.2</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>1035.98</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="F245" s="7" t="n">
         <v>-0.47</v>
@@ -6809,24 +6809,24 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>EQIX</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equinix</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>97.2</v>
+        <v>1040.83</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>96.73999999999999</v>
+        <v>1035.98</v>
       </c>
       <c r="F246" s="7" t="n">
         <v>-0.47</v>
@@ -6939,24 +6939,24 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>218.04</v>
+        <v>262.47</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>216.88</v>
+        <v>261.07</v>
       </c>
       <c r="F251" s="7" t="n">
         <v>-0.53</v>
@@ -6991,24 +6991,24 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>262.47</v>
+        <v>218.04</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>261.07</v>
+        <v>216.88</v>
       </c>
       <c r="F253" s="7" t="n">
         <v>-0.53</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>47.04</v>
+        <v>63.04</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>46.77</v>
+        <v>62.68</v>
       </c>
       <c r="F256" s="7" t="n">
         <v>-0.57</v>
@@ -7095,24 +7095,24 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>63.04</v>
+        <v>47.04</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>62.68</v>
+        <v>46.77</v>
       </c>
       <c r="F257" s="7" t="n">
         <v>-0.57</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>37.29</v>
+        <v>71.47</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>37.07</v>
+        <v>71.05</v>
       </c>
       <c r="F259" s="7" t="n">
         <v>-0.59</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>71.47</v>
+        <v>37.29</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>71.05</v>
+        <v>37.07</v>
       </c>
       <c r="F261" s="7" t="n">
         <v>-0.59</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>76.29000000000001</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>75.81</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="F265" s="7" t="n">
         <v>-0.63</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>84.56999999999999</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>84.04000000000001</v>
+        <v>75.81</v>
       </c>
       <c r="F266" s="7" t="n">
         <v>-0.63</v>
@@ -7407,24 +7407,24 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
-        <v>202.13</v>
+        <v>51.76</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>200.79</v>
+        <v>51.42</v>
       </c>
       <c r="F269" s="7" t="n">
         <v>-0.66</v>
@@ -7433,24 +7433,24 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>51.76</v>
+        <v>202.13</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>51.42</v>
+        <v>200.79</v>
       </c>
       <c r="F270" s="7" t="n">
         <v>-0.66</v>
@@ -7589,24 +7589,24 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>83.37</v>
+        <v>138.35</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>82.76000000000001</v>
+        <v>137.34</v>
       </c>
       <c r="F276" s="7" t="n">
         <v>-0.73</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>138.35</v>
+        <v>83.37</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>137.34</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="F277" s="7" t="n">
         <v>-0.73</v>
@@ -7771,24 +7771,24 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>68.23</v>
+        <v>419.68</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>67.69</v>
+        <v>416.37</v>
       </c>
       <c r="F283" s="7" t="n">
         <v>-0.79</v>
@@ -7823,24 +7823,24 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
-        <v>419.68</v>
+        <v>55.61</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>416.37</v>
+        <v>55.17</v>
       </c>
       <c r="F285" s="7" t="n">
         <v>-0.79</v>
@@ -7849,24 +7849,24 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>55.61</v>
+        <v>68.23</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>55.17</v>
+        <v>67.69</v>
       </c>
       <c r="F286" s="7" t="n">
         <v>-0.79</v>
@@ -7901,12 +7901,12 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
@@ -7915,10 +7915,10 @@
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>1356.23</v>
+        <v>342.73</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>1345.26</v>
+        <v>339.97</v>
       </c>
       <c r="F288" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7927,12 +7927,12 @@
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="D289" s="5" t="n">
-        <v>92.44</v>
+        <v>1356.23</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>91.69</v>
+        <v>1345.26</v>
       </c>
       <c r="F289" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7953,24 +7953,24 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D290" s="5" t="n">
-        <v>342.73</v>
+        <v>76.34</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>339.97</v>
+        <v>75.72</v>
       </c>
       <c r="F290" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -7979,24 +7979,24 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>76.34</v>
+        <v>92.44</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>75.72</v>
+        <v>91.69</v>
       </c>
       <c r="F291" s="7" t="n">
         <v>-0.8100000000000001</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>DDOG</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>369.83</v>
+        <v>214.76</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>366.7</v>
+        <v>212.93</v>
       </c>
       <c r="F293" s="7" t="n">
         <v>-0.85</v>
@@ -8083,24 +8083,24 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Datadog</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>214.76</v>
+        <v>369.83</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>212.93</v>
+        <v>366.7</v>
       </c>
       <c r="F295" s="7" t="n">
         <v>-0.85</v>
@@ -8109,24 +8109,24 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>CTVA</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Corteva</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D296" s="5" t="n">
-        <v>88.62</v>
+        <v>98.92</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>87.86</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F296" s="7" t="n">
         <v>-0.86</v>
@@ -8135,24 +8135,24 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>CTVA</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Corteva</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
-        <v>98.92</v>
+        <v>88.62</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>87.86</v>
       </c>
       <c r="F297" s="7" t="n">
         <v>-0.86</v>
@@ -8161,24 +8161,24 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>214.97</v>
+        <v>75.92</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>213.1</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F298" s="7" t="n">
         <v>-0.87</v>
@@ -8187,24 +8187,24 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>CRWD</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>75.92</v>
+        <v>214.97</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>213.1</v>
       </c>
       <c r="F299" s="7" t="n">
         <v>-0.87</v>
@@ -8213,24 +8213,24 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D300" s="5" t="n">
-        <v>32.88</v>
+        <v>1159.6</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>32.59</v>
+        <v>1149.36</v>
       </c>
       <c r="F300" s="7" t="n">
         <v>-0.88</v>
@@ -8265,24 +8265,24 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>1159.6</v>
+        <v>32.88</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>1149.36</v>
+        <v>32.59</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>-0.88</v>
@@ -8291,24 +8291,24 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>50.59</v>
+        <v>147.54</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>50.14</v>
+        <v>146.23</v>
       </c>
       <c r="F303" s="7" t="n">
         <v>-0.89</v>
@@ -8317,24 +8317,24 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>147.54</v>
+        <v>50.59</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>146.23</v>
+        <v>50.14</v>
       </c>
       <c r="F304" s="7" t="n">
         <v>-0.89</v>
@@ -8447,24 +8447,24 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Occidental Petroleum</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>60.61</v>
+        <v>195.13</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>60.04</v>
+        <v>193.29</v>
       </c>
       <c r="F309" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8499,24 +8499,24 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>JPM</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>JPMorgan Chase</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>195.13</v>
+        <v>362.06</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>193.29</v>
+        <v>358.64</v>
       </c>
       <c r="F311" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8525,24 +8525,24 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>JPM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>JPMorgan Chase</t>
+          <t>Occidental Petroleum</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>362.06</v>
+        <v>60.61</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>358.64</v>
+        <v>60.04</v>
       </c>
       <c r="F312" s="7" t="n">
         <v>-0.9399999999999999</v>
@@ -8551,24 +8551,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>52.58</v>
+        <v>38.77</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>52.08</v>
+        <v>38.4</v>
       </c>
       <c r="F313" s="7" t="n">
         <v>-0.95</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>38.77</v>
+        <v>52.58</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>38.4</v>
+        <v>52.08</v>
       </c>
       <c r="F314" s="7" t="n">
         <v>-0.95</v>
@@ -8707,24 +8707,24 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>121.4</v>
+        <v>141.52</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>120.22</v>
+        <v>140.15</v>
       </c>
       <c r="F319" s="7" t="n">
         <v>-0.97</v>
@@ -8733,12 +8733,12 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -8747,10 +8747,10 @@
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>141.52</v>
+        <v>378.75</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>140.15</v>
+        <v>375.07</v>
       </c>
       <c r="F320" s="7" t="n">
         <v>-0.97</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>378.75</v>
+        <v>121.4</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>375.07</v>
+        <v>120.22</v>
       </c>
       <c r="F321" s="7" t="n">
         <v>-0.97</v>
@@ -8811,24 +8811,24 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>211.52</v>
+        <v>128</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>209.44</v>
+        <v>126.75</v>
       </c>
       <c r="F323" s="7" t="n">
         <v>-0.98</v>
@@ -8837,24 +8837,24 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Incyte</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>128</v>
+        <v>211.52</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>126.75</v>
+        <v>209.44</v>
       </c>
       <c r="F324" s="7" t="n">
         <v>-0.98</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>226.83</v>
+        <v>110.88</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>224.59</v>
+        <v>109.78</v>
       </c>
       <c r="F327" s="7" t="n">
         <v>-0.99</v>
@@ -8941,24 +8941,24 @@
     <row r="328">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D328" s="5" t="n">
-        <v>110.88</v>
+        <v>226.83</v>
       </c>
       <c r="E328" s="5" t="n">
-        <v>109.78</v>
+        <v>224.59</v>
       </c>
       <c r="F328" s="7" t="n">
         <v>-0.99</v>
@@ -8993,24 +8993,24 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>413.56</v>
+        <v>314.35</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>409.38</v>
+        <v>311.18</v>
       </c>
       <c r="F330" s="7" t="n">
         <v>-1.01</v>
@@ -9019,24 +9019,24 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>314.35</v>
+        <v>413.56</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>311.18</v>
+        <v>409.38</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>-1.01</v>
@@ -9045,24 +9045,24 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>84.45</v>
+        <v>409.2</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>83.58</v>
+        <v>405</v>
       </c>
       <c r="F332" s="7" t="n">
         <v>-1.03</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>409.2</v>
+        <v>84.45</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>405</v>
+        <v>83.58</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-1.03</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>AMT</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>225.12</v>
+        <v>177.75</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>222.71</v>
+        <v>175.85</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-1.07</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>AMT</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>177.75</v>
+        <v>225.12</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>175.85</v>
+        <v>222.71</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-1.07</v>
@@ -9253,24 +9253,24 @@
     <row r="340">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B340" s="4" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D340" s="5" t="n">
-        <v>57.57</v>
+        <v>175.06</v>
       </c>
       <c r="E340" s="5" t="n">
-        <v>56.94</v>
+        <v>173.15</v>
       </c>
       <c r="F340" s="7" t="n">
         <v>-1.09</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>175.06</v>
+        <v>57.57</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>173.15</v>
+        <v>56.94</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-1.09</v>
@@ -9305,24 +9305,24 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D342" s="5" t="n">
-        <v>366.5</v>
+        <v>585.71</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>362.42</v>
+        <v>579.21</v>
       </c>
       <c r="F342" s="7" t="n">
         <v>-1.11</v>
@@ -9331,24 +9331,24 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>18.95</v>
+        <v>339.08</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>18.74</v>
+        <v>335.31</v>
       </c>
       <c r="F343" s="7" t="n">
         <v>-1.11</v>
@@ -9383,24 +9383,24 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>339.08</v>
+        <v>137.68</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>335.31</v>
+        <v>136.15</v>
       </c>
       <c r="F345" s="7" t="n">
         <v>-1.11</v>
@@ -9409,24 +9409,24 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>137.68</v>
+        <v>366.5</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>136.15</v>
+        <v>362.42</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>-1.11</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>585.71</v>
+        <v>18.95</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>579.21</v>
+        <v>18.74</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-1.11</v>
@@ -9487,24 +9487,24 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>99.05</v>
+        <v>278.43</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>97.91</v>
+        <v>275.23</v>
       </c>
       <c r="F349" s="7" t="n">
         <v>-1.15</v>
@@ -9513,24 +9513,24 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>278.43</v>
+        <v>99.05</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>275.23</v>
+        <v>97.91</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>-1.15</v>
@@ -9591,24 +9591,24 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Bunge Global</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>120.12</v>
+        <v>342.48</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>118.71</v>
+        <v>338.46</v>
       </c>
       <c r="F353" s="7" t="n">
         <v>-1.17</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Bunge Global</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>342.48</v>
+        <v>120.12</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>338.46</v>
+        <v>118.71</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-1.17</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>6373.95</v>
+        <v>108.42</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>6298.85</v>
+        <v>107.14</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-1.18</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>108.42</v>
+        <v>6373.95</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>107.14</v>
+        <v>6298.85</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-1.18</v>
@@ -9721,24 +9721,24 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>293.54</v>
+        <v>26.81</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>290.05</v>
+        <v>26.49</v>
       </c>
       <c r="F358" s="7" t="n">
         <v>-1.19</v>
@@ -9747,24 +9747,24 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>26.81</v>
+        <v>293.54</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>26.49</v>
+        <v>290.05</v>
       </c>
       <c r="F359" s="7" t="n">
         <v>-1.19</v>
@@ -10423,24 +10423,24 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>188.46</v>
+        <v>532.95</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>185.74</v>
+        <v>525.28</v>
       </c>
       <c r="F385" s="7" t="n">
         <v>-1.44</v>
@@ -10449,12 +10449,12 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
@@ -10463,10 +10463,10 @@
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>260.21</v>
+        <v>68.02</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>256.46</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="F386" s="7" t="n">
         <v>-1.44</v>
@@ -10475,12 +10475,12 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
@@ -10489,10 +10489,10 @@
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>68.02</v>
+        <v>260.21</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>67.04000000000001</v>
+        <v>256.46</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-1.44</v>
@@ -10501,24 +10501,24 @@
     <row r="388">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D388" s="5" t="n">
-        <v>532.95</v>
+        <v>188.46</v>
       </c>
       <c r="E388" s="5" t="n">
-        <v>525.28</v>
+        <v>185.74</v>
       </c>
       <c r="F388" s="7" t="n">
         <v>-1.44</v>
@@ -10683,24 +10683,24 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>PFG</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Principal Financial Group</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>187.62</v>
+        <v>118.51</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>184.74</v>
+        <v>116.68</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-1.54</v>
@@ -10709,24 +10709,24 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>PFG</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>Principal Financial Group</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D396" s="5" t="n">
-        <v>118.51</v>
+        <v>187.62</v>
       </c>
       <c r="E396" s="5" t="n">
-        <v>116.68</v>
+        <v>184.74</v>
       </c>
       <c r="F396" s="7" t="n">
         <v>-1.54</v>
@@ -10735,24 +10735,24 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>181.1</v>
+        <v>444.12</v>
       </c>
       <c r="E397" s="5" t="n">
-        <v>178.29</v>
+        <v>437.23</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>-1.55</v>
@@ -10761,24 +10761,24 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D398" s="5" t="n">
-        <v>444.12</v>
+        <v>181.1</v>
       </c>
       <c r="E398" s="5" t="n">
-        <v>437.23</v>
+        <v>178.29</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>-1.55</v>
@@ -10787,12 +10787,12 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
@@ -10801,10 +10801,10 @@
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>72.56</v>
+        <v>450.58</v>
       </c>
       <c r="E399" s="5" t="n">
-        <v>71.42</v>
+        <v>443.51</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>-1.57</v>
@@ -10813,12 +10813,12 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="D400" s="5" t="n">
-        <v>450.58</v>
+        <v>72.56</v>
       </c>
       <c r="E400" s="5" t="n">
-        <v>443.51</v>
+        <v>71.42</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>-1.57</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>168.37</v>
+        <v>37.57</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>165.64</v>
+        <v>36.96</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-1.62</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>37.57</v>
+        <v>99.23</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>36.96</v>
+        <v>97.62</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-1.62</v>
@@ -11021,12 +11021,12 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
@@ -11035,10 +11035,10 @@
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>99.23</v>
+        <v>168.37</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>97.62</v>
+        <v>165.64</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>-1.62</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>140.02</v>
+        <v>347.03</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>137.63</v>
+        <v>341.08</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-1.71</v>
@@ -11229,24 +11229,24 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D416" s="5" t="n">
-        <v>347.03</v>
+        <v>140.02</v>
       </c>
       <c r="E416" s="5" t="n">
-        <v>341.08</v>
+        <v>137.63</v>
       </c>
       <c r="F416" s="7" t="n">
         <v>-1.71</v>
@@ -11359,24 +11359,24 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>130.43</v>
+        <v>185.25</v>
       </c>
       <c r="E421" s="5" t="n">
-        <v>128.09</v>
+        <v>181.94</v>
       </c>
       <c r="F421" s="7" t="n">
         <v>-1.79</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>185.25</v>
+        <v>130.43</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>181.94</v>
+        <v>128.09</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-1.79</v>
@@ -11437,24 +11437,24 @@
     <row r="424">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>DOC</t>
         </is>
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>Healthpeak Properties</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D424" s="5" t="n">
-        <v>30.95</v>
+        <v>21.03</v>
       </c>
       <c r="E424" s="5" t="n">
-        <v>30.39</v>
+        <v>20.65</v>
       </c>
       <c r="F424" s="7" t="n">
         <v>-1.81</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>DOC</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Healthpeak Properties</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>21.03</v>
+        <v>30.95</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>20.65</v>
+        <v>30.39</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-1.81</v>
@@ -11541,24 +11541,24 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>CCI</t>
+          <t>NDAQ</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>Crown Castle</t>
+          <t>Nasdaq, Inc.</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>77.26000000000001</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>75.83</v>
+        <v>96.88</v>
       </c>
       <c r="F428" s="7" t="n">
         <v>-1.85</v>
@@ -11567,24 +11567,24 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>CCI</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Nasdaq, Inc.</t>
+          <t>Crown Castle</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>98.70999999999999</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>96.88</v>
+        <v>75.83</v>
       </c>
       <c r="F429" s="7" t="n">
         <v>-1.85</v>
@@ -11619,12 +11619,12 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C431" s="4" t="inlineStr">
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>68.09</v>
+        <v>843.47</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>66.81999999999999</v>
+        <v>827.72</v>
       </c>
       <c r="F431" s="7" t="n">
         <v>-1.87</v>
@@ -11645,12 +11645,12 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C432" s="4" t="inlineStr">
@@ -11659,10 +11659,10 @@
         </is>
       </c>
       <c r="D432" s="5" t="n">
-        <v>843.47</v>
+        <v>68.09</v>
       </c>
       <c r="E432" s="5" t="n">
-        <v>827.72</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F432" s="7" t="n">
         <v>-1.87</v>
@@ -11827,24 +11827,24 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>44.53</v>
+        <v>92.11</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>43.64</v>
+        <v>90.27</v>
       </c>
       <c r="F439" s="7" t="n">
         <v>-2</v>
@@ -11853,24 +11853,24 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D440" s="5" t="n">
-        <v>92.11</v>
+        <v>44.53</v>
       </c>
       <c r="E440" s="5" t="n">
-        <v>90.27</v>
+        <v>43.64</v>
       </c>
       <c r="F440" s="7" t="n">
         <v>-2</v>
@@ -12763,24 +12763,24 @@
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D475" s="5" t="n">
-        <v>56.82</v>
+        <v>284.38</v>
       </c>
       <c r="E475" s="5" t="n">
-        <v>54.96</v>
+        <v>275.09</v>
       </c>
       <c r="F475" s="7" t="n">
         <v>-3.27</v>
@@ -12789,24 +12789,24 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D476" s="5" t="n">
-        <v>284.38</v>
+        <v>56.82</v>
       </c>
       <c r="E476" s="5" t="n">
-        <v>275.09</v>
+        <v>54.96</v>
       </c>
       <c r="F476" s="7" t="n">
         <v>-3.27</v>
@@ -13101,24 +13101,24 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D488" s="5" t="n">
-        <v>538.15</v>
+        <v>192.7</v>
       </c>
       <c r="E488" s="5" t="n">
-        <v>515.67</v>
+        <v>184.64</v>
       </c>
       <c r="F488" s="7" t="n">
         <v>-4.18</v>
@@ -13127,24 +13127,24 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>192.7</v>
+        <v>538.15</v>
       </c>
       <c r="E489" s="5" t="n">
-        <v>184.64</v>
+        <v>515.67</v>
       </c>
       <c r="F489" s="7" t="n">
         <v>-4.18</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-07 07:41</t>
+          <t>Aug 28 close to Sep 04 close  |  503 companies  |  updated 2026-09-08 07:34</t>
         </is>
       </c>
     </row>
@@ -14795,30 +14795,30 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>250.5</v>
+        <v>794.1900000000001</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>261.07</v>
+        <v>827.72</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>263.97</v>
+        <v>852.03</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>249.64</v>
+        <v>794.1900000000001</v>
       </c>
       <c r="H39" s="6" t="n">
         <v>4.22</v>
@@ -14827,30 +14827,30 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Regeneron Pharmaceuticals</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>794.1900000000001</v>
+        <v>250.5</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>827.72</v>
+        <v>261.07</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>852.03</v>
+        <v>263.97</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>794.1900000000001</v>
+        <v>249.64</v>
       </c>
       <c r="H40" s="6" t="n">
         <v>4.22</v>
@@ -15691,30 +15691,30 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COR</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Cencora</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>164.19</v>
+        <v>322.03</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>168.74</v>
+        <v>330.95</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>170.48</v>
+        <v>337.22</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>164.19</v>
+        <v>322.03</v>
       </c>
       <c r="H67" s="6" t="n">
         <v>2.77</v>
@@ -15723,30 +15723,30 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>COR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Cencora</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>322.03</v>
+        <v>164.19</v>
       </c>
       <c r="E68" s="5" t="n">
-        <v>330.95</v>
+        <v>168.74</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>337.22</v>
+        <v>170.48</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>322.03</v>
+        <v>164.19</v>
       </c>
       <c r="H68" s="6" t="n">
         <v>2.77</v>
@@ -15851,30 +15851,30 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>128.26</v>
+        <v>36.18</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>131.42</v>
+        <v>37.07</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>131.91</v>
+        <v>37.63</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>126.59</v>
+        <v>36.18</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>2.46</v>
@@ -15883,30 +15883,30 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>36.18</v>
+        <v>128.26</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>37.07</v>
+        <v>131.42</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>37.63</v>
+        <v>131.91</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>36.18</v>
+        <v>126.59</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>2.46</v>
@@ -16331,12 +16331,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -16345,16 +16345,16 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>81.84</v>
+        <v>45.88</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>83.43000000000001</v>
+        <v>46.77</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>84.06</v>
+        <v>47.04</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>81.84</v>
+        <v>45.86</v>
       </c>
       <c r="H87" s="6" t="n">
         <v>1.94</v>
@@ -16363,12 +16363,12 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
@@ -16377,16 +16377,16 @@
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>45.88</v>
+        <v>81.84</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>46.77</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>47.04</v>
+        <v>84.06</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>45.86</v>
+        <v>81.84</v>
       </c>
       <c r="H88" s="6" t="n">
         <v>1.94</v>
@@ -16779,30 +16779,30 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>62.41</v>
+        <v>27.96</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>63.5</v>
+        <v>28.45</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>64.63</v>
+        <v>29.02</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>62.41</v>
+        <v>27.96</v>
       </c>
       <c r="H101" s="6" t="n">
         <v>1.75</v>
@@ -16811,30 +16811,30 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>27.96</v>
+        <v>62.41</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>28.45</v>
+        <v>63.5</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>29.02</v>
+        <v>64.63</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>27.96</v>
+        <v>62.41</v>
       </c>
       <c r="H102" s="6" t="n">
         <v>1.75</v>
@@ -17291,30 +17291,30 @@
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D117" s="5" t="n">
-        <v>162.5</v>
+        <v>105.75</v>
       </c>
       <c r="E117" s="5" t="n">
-        <v>164.84</v>
+        <v>107.27</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>164.84</v>
+        <v>107.78</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>160.51</v>
+        <v>105.75</v>
       </c>
       <c r="H117" s="6" t="n">
         <v>1.44</v>
@@ -17355,30 +17355,30 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>105.75</v>
+        <v>162.5</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>107.27</v>
+        <v>164.84</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>107.78</v>
+        <v>164.84</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>105.75</v>
+        <v>160.51</v>
       </c>
       <c r="H119" s="6" t="n">
         <v>1.44</v>
@@ -17771,12 +17771,12 @@
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -17785,16 +17785,16 @@
         </is>
       </c>
       <c r="D132" s="5" t="n">
-        <v>80.65000000000001</v>
+        <v>39.24</v>
       </c>
       <c r="E132" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>39.67</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>81.93000000000001</v>
+        <v>39.98</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>80.65000000000001</v>
+        <v>39.24</v>
       </c>
       <c r="H132" s="6" t="n">
         <v>1.1</v>
@@ -17803,30 +17803,30 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>54.57</v>
+        <v>128.8</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>55.17</v>
+        <v>130.22</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>55.75</v>
+        <v>130.94</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>54.18</v>
+        <v>126.59</v>
       </c>
       <c r="H133" s="6" t="n">
         <v>1.1</v>
@@ -17835,30 +17835,30 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>39.24</v>
+        <v>54.57</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>39.67</v>
+        <v>55.17</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>39.98</v>
+        <v>55.75</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>39.24</v>
+        <v>54.18</v>
       </c>
       <c r="H134" s="6" t="n">
         <v>1.1</v>
@@ -17867,30 +17867,30 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>128.8</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>130.22</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>130.94</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>126.59</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H135" s="6" t="n">
         <v>1.1</v>
@@ -17931,30 +17931,30 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>237.29</v>
+        <v>392.95</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>239.84</v>
+        <v>397.14</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>240.06</v>
+        <v>400.94</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>232.02</v>
+        <v>389.41</v>
       </c>
       <c r="H137" s="6" t="n">
         <v>1.07</v>
@@ -17963,12 +17963,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -17977,16 +17977,16 @@
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>392.95</v>
+        <v>218.5</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>397.14</v>
+        <v>220.83</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>400.94</v>
+        <v>224.51</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>389.41</v>
+        <v>216.04</v>
       </c>
       <c r="H138" s="6" t="n">
         <v>1.07</v>
@@ -17995,30 +17995,30 @@
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D139" s="5" t="n">
-        <v>218.5</v>
+        <v>237.29</v>
       </c>
       <c r="E139" s="5" t="n">
-        <v>220.83</v>
+        <v>239.84</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>224.51</v>
+        <v>240.06</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>216.04</v>
+        <v>232.02</v>
       </c>
       <c r="H139" s="6" t="n">
         <v>1.07</v>
@@ -18187,12 +18187,12 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Everest Group</t>
+          <t>Globe Life</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -18201,16 +18201,16 @@
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>377.61</v>
+        <v>172.79</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>380.87</v>
+        <v>174.27</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>386.25</v>
+        <v>176.52</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>374.65</v>
+        <v>172.3</v>
       </c>
       <c r="H145" s="6" t="n">
         <v>0.86</v>
@@ -18219,12 +18219,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Globe Life</t>
+          <t>Everest Group</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -18233,16 +18233,16 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>172.79</v>
+        <v>377.61</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>174.27</v>
+        <v>380.87</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>176.52</v>
+        <v>386.25</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>172.3</v>
+        <v>374.65</v>
       </c>
       <c r="H146" s="6" t="n">
         <v>0.86</v>
@@ -18283,30 +18283,30 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>34.72</v>
+        <v>197.67</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>34.99</v>
+        <v>199.22</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>34.99</v>
+        <v>203.42</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>34.6</v>
+        <v>197.67</v>
       </c>
       <c r="H148" s="6" t="n">
         <v>0.78</v>
@@ -18315,30 +18315,30 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>197.67</v>
+        <v>34.72</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>199.22</v>
+        <v>34.99</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>203.42</v>
+        <v>34.99</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>197.67</v>
+        <v>34.6</v>
       </c>
       <c r="H149" s="6" t="n">
         <v>0.78</v>
@@ -18379,30 +18379,30 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>287.82</v>
+        <v>163.18</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>290.05</v>
+        <v>164.44</v>
       </c>
       <c r="F151" s="5" t="n">
-        <v>296.06</v>
+        <v>164.44</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>287.82</v>
+        <v>160.88</v>
       </c>
       <c r="H151" s="6" t="n">
         <v>0.77</v>
@@ -18411,30 +18411,30 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>163.18</v>
+        <v>287.82</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>164.44</v>
+        <v>290.05</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>164.44</v>
+        <v>296.06</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>160.88</v>
+        <v>287.82</v>
       </c>
       <c r="H152" s="6" t="n">
         <v>0.77</v>
@@ -18443,30 +18443,30 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Carvana</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>74.04000000000001</v>
+        <v>184.64</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>74.59</v>
+        <v>186.01</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>74.59</v>
+        <v>189.79</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>72.18000000000001</v>
+        <v>182.27</v>
       </c>
       <c r="H153" s="6" t="n">
         <v>0.74</v>
@@ -18475,30 +18475,30 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>184.64</v>
+        <v>337.47</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>186.01</v>
+        <v>339.97</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>189.79</v>
+        <v>342.73</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>182.27</v>
+        <v>337.47</v>
       </c>
       <c r="H154" s="6" t="n">
         <v>0.74</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Carvana</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>337.47</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>339.97</v>
+        <v>74.59</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>342.73</v>
+        <v>74.59</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>337.47</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>0.74</v>
@@ -18923,30 +18923,30 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>62.32</v>
+        <v>215.63</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>62.68</v>
+        <v>216.88</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>63.04</v>
+        <v>220.03</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>61.94</v>
+        <v>214.26</v>
       </c>
       <c r="H168" s="6" t="n">
         <v>0.58</v>
@@ -18955,30 +18955,30 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>354.97</v>
+        <v>62.32</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>357.03</v>
+        <v>62.68</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>357.03</v>
+        <v>63.04</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>335.46</v>
+        <v>61.94</v>
       </c>
       <c r="H169" s="6" t="n">
         <v>0.58</v>
@@ -18987,30 +18987,30 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>215.63</v>
+        <v>354.97</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>216.88</v>
+        <v>357.03</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>220.03</v>
+        <v>357.03</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>214.26</v>
+        <v>335.46</v>
       </c>
       <c r="H170" s="6" t="n">
         <v>0.58</v>
@@ -19595,30 +19595,30 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>30.33</v>
+        <v>26.41</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>30.42</v>
+        <v>26.49</v>
       </c>
       <c r="F189" s="5" t="n">
-        <v>30.44</v>
+        <v>27.06</v>
       </c>
       <c r="G189" s="5" t="n">
-        <v>29.29</v>
+        <v>26.3</v>
       </c>
       <c r="H189" s="6" t="n">
         <v>0.3</v>
@@ -19627,30 +19627,30 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>26.41</v>
+        <v>30.33</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>26.49</v>
+        <v>30.42</v>
       </c>
       <c r="F190" s="5" t="n">
-        <v>27.06</v>
+        <v>30.44</v>
       </c>
       <c r="G190" s="5" t="n">
-        <v>26.3</v>
+        <v>29.29</v>
       </c>
       <c r="H190" s="6" t="n">
         <v>0.3</v>
@@ -19787,30 +19787,30 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>34.65</v>
+        <v>459.66</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>34.73</v>
+        <v>460.72</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>34.73</v>
+        <v>460.72</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>33.01</v>
+        <v>443.31</v>
       </c>
       <c r="H195" s="6" t="n">
         <v>0.23</v>
@@ -19819,30 +19819,30 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D196" s="5" t="n">
-        <v>459.66</v>
+        <v>34.65</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>460.72</v>
+        <v>34.73</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>460.72</v>
+        <v>34.73</v>
       </c>
       <c r="G196" s="5" t="n">
-        <v>443.31</v>
+        <v>33.01</v>
       </c>
       <c r="H196" s="6" t="n">
         <v>0.23</v>
@@ -20011,12 +20011,12 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -20025,16 +20025,16 @@
         </is>
       </c>
       <c r="D202" s="5" t="n">
-        <v>442.89</v>
+        <v>218.64</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>443.51</v>
+        <v>218.95</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>450.58</v>
+        <v>223.87</v>
       </c>
       <c r="G202" s="5" t="n">
-        <v>431.71</v>
+        <v>218.08</v>
       </c>
       <c r="H202" s="6" t="n">
         <v>0.14</v>
@@ -20043,12 +20043,12 @@
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -20057,16 +20057,16 @@
         </is>
       </c>
       <c r="D203" s="5" t="n">
-        <v>218.64</v>
+        <v>442.89</v>
       </c>
       <c r="E203" s="5" t="n">
-        <v>218.95</v>
+        <v>443.51</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>223.87</v>
+        <v>450.58</v>
       </c>
       <c r="G203" s="5" t="n">
-        <v>218.08</v>
+        <v>431.71</v>
       </c>
       <c r="H203" s="6" t="n">
         <v>0.14</v>
@@ -20203,30 +20203,30 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>755.47</v>
+        <v>50.1</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>756.09</v>
+        <v>50.14</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>766.91</v>
+        <v>50.59</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>752.21</v>
+        <v>50.02</v>
       </c>
       <c r="H208" s="6" t="n">
         <v>0.08</v>
@@ -20235,30 +20235,30 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>319.7</v>
+        <v>755.47</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>319.97</v>
+        <v>756.09</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>328.21</v>
+        <v>766.91</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>316.85</v>
+        <v>752.21</v>
       </c>
       <c r="H209" s="6" t="n">
         <v>0.08</v>
@@ -20267,30 +20267,30 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>181.37</v>
+        <v>319.7</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>181.52</v>
+        <v>319.97</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>188.02</v>
+        <v>328.21</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>180.44</v>
+        <v>316.85</v>
       </c>
       <c r="H210" s="6" t="n">
         <v>0.08</v>
@@ -20299,12 +20299,12 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -20313,16 +20313,16 @@
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>50.1</v>
+        <v>181.37</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>50.14</v>
+        <v>181.52</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>50.59</v>
+        <v>188.02</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>50.02</v>
+        <v>180.44</v>
       </c>
       <c r="H211" s="6" t="n">
         <v>0.08</v>
@@ -20555,30 +20555,30 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Northern Trust</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>186.79</v>
+        <v>68.03</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>186.63</v>
+        <v>67.97</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>187.45</v>
+        <v>68.03</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>182.68</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H219" s="7" t="n">
         <v>-0.09</v>
@@ -20587,30 +20587,30 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Northern Trust</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>68.03</v>
+        <v>186.79</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>67.97</v>
+        <v>186.63</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>68.03</v>
+        <v>187.45</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>67.73999999999999</v>
+        <v>182.68</v>
       </c>
       <c r="H220" s="7" t="n">
         <v>-0.09</v>
@@ -20907,30 +20907,30 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>LYB</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>LyondellBasell</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D230" s="5" t="n">
-        <v>63.67</v>
+        <v>448.96</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>63.52</v>
+        <v>447.9</v>
       </c>
       <c r="F230" s="5" t="n">
-        <v>66.56999999999999</v>
+        <v>448.96</v>
       </c>
       <c r="G230" s="5" t="n">
-        <v>63.52</v>
+        <v>439.02</v>
       </c>
       <c r="H230" s="7" t="n">
         <v>-0.24</v>
@@ -20939,30 +20939,30 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>LYB</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>LyondellBasell</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>448.96</v>
+        <v>63.67</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>447.9</v>
+        <v>63.52</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>448.96</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>439.02</v>
+        <v>63.52</v>
       </c>
       <c r="H231" s="7" t="n">
         <v>-0.24</v>
@@ -21163,30 +21163,30 @@
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>EW</t>
         </is>
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D238" s="5" t="n">
-        <v>53.18</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="E238" s="5" t="n">
-        <v>53</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="F238" s="5" t="n">
-        <v>53.31</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="G238" s="5" t="n">
-        <v>51.67</v>
+        <v>89.78</v>
       </c>
       <c r="H238" s="7" t="n">
         <v>-0.34</v>
@@ -21195,30 +21195,30 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>90.20999999999999</v>
+        <v>75.52</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>89.90000000000001</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>90.81999999999999</v>
+        <v>76.06</v>
       </c>
       <c r="G239" s="5" t="n">
-        <v>89.78</v>
+        <v>74.77</v>
       </c>
       <c r="H239" s="7" t="n">
         <v>-0.34</v>
@@ -21227,30 +21227,30 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>75.52</v>
+        <v>53.18</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>75.26000000000001</v>
+        <v>53</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>76.06</v>
+        <v>53.31</v>
       </c>
       <c r="G240" s="5" t="n">
-        <v>74.77</v>
+        <v>51.67</v>
       </c>
       <c r="H240" s="7" t="n">
         <v>-0.34</v>
@@ -21451,30 +21451,30 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Paccar</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
-        <v>125.34</v>
+        <v>171.97</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>124.7</v>
+        <v>171.1</v>
       </c>
       <c r="F247" s="5" t="n">
-        <v>125.34</v>
+        <v>174.72</v>
       </c>
       <c r="G247" s="5" t="n">
-        <v>122.13</v>
+        <v>169.9</v>
       </c>
       <c r="H247" s="7" t="n">
         <v>-0.51</v>
@@ -21483,30 +21483,30 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D248" s="5" t="n">
-        <v>171.97</v>
+        <v>31.56</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>171.1</v>
+        <v>31.4</v>
       </c>
       <c r="F248" s="5" t="n">
-        <v>174.72</v>
+        <v>32.24</v>
       </c>
       <c r="G248" s="5" t="n">
-        <v>169.9</v>
+        <v>31.4</v>
       </c>
       <c r="H248" s="7" t="n">
         <v>-0.51</v>
@@ -21515,30 +21515,30 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Paccar</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>31.56</v>
+        <v>125.34</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>31.4</v>
+        <v>124.7</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>32.24</v>
+        <v>125.34</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>31.4</v>
+        <v>122.13</v>
       </c>
       <c r="H249" s="7" t="n">
         <v>-0.51</v>
@@ -21707,30 +21707,30 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>43.93</v>
+        <v>109.93</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>43.64</v>
+        <v>109.2</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>44.53</v>
+        <v>110.49</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>43.64</v>
+        <v>108.61</v>
       </c>
       <c r="H255" s="7" t="n">
         <v>-0.66</v>
@@ -21739,30 +21739,30 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>162.33</v>
+        <v>43.93</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>161.26</v>
+        <v>43.64</v>
       </c>
       <c r="F256" s="5" t="n">
-        <v>164.59</v>
+        <v>44.53</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>157.85</v>
+        <v>43.64</v>
       </c>
       <c r="H256" s="7" t="n">
         <v>-0.66</v>
@@ -21771,30 +21771,30 @@
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D257" s="5" t="n">
-        <v>109.93</v>
+        <v>162.33</v>
       </c>
       <c r="E257" s="5" t="n">
-        <v>109.2</v>
+        <v>161.26</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>110.49</v>
+        <v>164.59</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>108.61</v>
+        <v>157.85</v>
       </c>
       <c r="H257" s="7" t="n">
         <v>-0.66</v>
@@ -21835,12 +21835,12 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -21849,16 +21849,16 @@
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>564.85</v>
+        <v>393.39</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>560.75</v>
+        <v>390.53</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>564.85</v>
+        <v>393.39</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>545.5</v>
+        <v>374</v>
       </c>
       <c r="H259" s="7" t="n">
         <v>-0.73</v>
@@ -21867,12 +21867,12 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -21881,16 +21881,16 @@
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>393.39</v>
+        <v>564.85</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>390.53</v>
+        <v>560.75</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>393.39</v>
+        <v>564.85</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>374</v>
+        <v>545.5</v>
       </c>
       <c r="H260" s="7" t="n">
         <v>-0.73</v>
@@ -23083,30 +23083,30 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>AVY</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Avery Dennison</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>177.75</v>
+        <v>461.67</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>175.06</v>
+        <v>454.71</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>177.75</v>
+        <v>461.67</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>173.03</v>
+        <v>435.91</v>
       </c>
       <c r="H298" s="7" t="n">
         <v>-1.51</v>
@@ -23115,30 +23115,30 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AVY</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>461.67</v>
+        <v>177.75</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>454.71</v>
+        <v>175.06</v>
       </c>
       <c r="F299" s="5" t="n">
-        <v>461.67</v>
+        <v>177.75</v>
       </c>
       <c r="G299" s="5" t="n">
-        <v>435.91</v>
+        <v>173.03</v>
       </c>
       <c r="H299" s="7" t="n">
         <v>-1.51</v>
@@ -23179,30 +23179,30 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>189.61</v>
+        <v>6396.27</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>186.72</v>
+        <v>6298.85</v>
       </c>
       <c r="F301" s="5" t="n">
-        <v>193.12</v>
+        <v>6396.27</v>
       </c>
       <c r="G301" s="5" t="n">
-        <v>186.72</v>
+        <v>6275.82</v>
       </c>
       <c r="H301" s="7" t="n">
         <v>-1.52</v>
@@ -23211,30 +23211,30 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>6396.27</v>
+        <v>189.61</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>6298.85</v>
+        <v>186.72</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>6396.27</v>
+        <v>193.12</v>
       </c>
       <c r="G302" s="5" t="n">
-        <v>6275.82</v>
+        <v>186.72</v>
       </c>
       <c r="H302" s="7" t="n">
         <v>-1.52</v>
@@ -23371,30 +23371,30 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>95.86</v>
+        <v>142.53</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>94.26000000000001</v>
+        <v>140.15</v>
       </c>
       <c r="F307" s="5" t="n">
-        <v>95.86</v>
+        <v>143.17</v>
       </c>
       <c r="G307" s="5" t="n">
-        <v>91.2</v>
+        <v>138.06</v>
       </c>
       <c r="H307" s="7" t="n">
         <v>-1.67</v>
@@ -23403,30 +23403,30 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>142.53</v>
+        <v>95.86</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>140.15</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>143.17</v>
+        <v>95.86</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>138.06</v>
+        <v>91.2</v>
       </c>
       <c r="H308" s="7" t="n">
         <v>-1.67</v>
@@ -23531,30 +23531,30 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>208.05</v>
+        <v>62.36</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>204.45</v>
+        <v>61.28</v>
       </c>
       <c r="F312" s="5" t="n">
-        <v>208.05</v>
+        <v>62.45</v>
       </c>
       <c r="G312" s="5" t="n">
-        <v>199.84</v>
+        <v>61.28</v>
       </c>
       <c r="H312" s="7" t="n">
         <v>-1.73</v>
@@ -23563,30 +23563,30 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>62.36</v>
+        <v>208.05</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>61.28</v>
+        <v>204.45</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>62.45</v>
+        <v>208.05</v>
       </c>
       <c r="G313" s="5" t="n">
-        <v>61.28</v>
+        <v>199.84</v>
       </c>
       <c r="H313" s="7" t="n">
         <v>-1.73</v>
@@ -23755,30 +23755,30 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>621.96</v>
+        <v>204.18</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>610.65</v>
+        <v>200.47</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>621.96</v>
+        <v>204.18</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>606.36</v>
+        <v>198.09</v>
       </c>
       <c r="H319" s="7" t="n">
         <v>-1.82</v>
@@ -23787,30 +23787,30 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>International Flavors &amp; Fragrances</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>267.56</v>
+        <v>87.95</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>262.69</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>267.56</v>
+        <v>87.95</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>262</v>
+        <v>85.78</v>
       </c>
       <c r="H320" s="7" t="n">
         <v>-1.82</v>
@@ -23819,30 +23819,30 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>87.95</v>
+        <v>621.96</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>86.34999999999999</v>
+        <v>610.65</v>
       </c>
       <c r="F321" s="5" t="n">
-        <v>87.95</v>
+        <v>621.96</v>
       </c>
       <c r="G321" s="5" t="n">
-        <v>85.78</v>
+        <v>606.36</v>
       </c>
       <c r="H321" s="7" t="n">
         <v>-1.82</v>
@@ -23851,30 +23851,30 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>204.18</v>
+        <v>267.56</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>200.47</v>
+        <v>262.69</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>204.18</v>
+        <v>267.56</v>
       </c>
       <c r="G322" s="5" t="n">
-        <v>198.09</v>
+        <v>262</v>
       </c>
       <c r="H322" s="7" t="n">
         <v>-1.82</v>
@@ -23979,30 +23979,30 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>130.69</v>
+        <v>324.59</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>128.18</v>
+        <v>318.36</v>
       </c>
       <c r="F326" s="5" t="n">
-        <v>130.69</v>
+        <v>324.59</v>
       </c>
       <c r="G326" s="5" t="n">
-        <v>128.18</v>
+        <v>314.4</v>
       </c>
       <c r="H326" s="7" t="n">
         <v>-1.92</v>
@@ -24011,30 +24011,30 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>324.59</v>
+        <v>130.69</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>318.36</v>
+        <v>128.18</v>
       </c>
       <c r="F327" s="5" t="n">
-        <v>324.59</v>
+        <v>130.69</v>
       </c>
       <c r="G327" s="5" t="n">
-        <v>314.4</v>
+        <v>128.18</v>
       </c>
       <c r="H327" s="7" t="n">
         <v>-1.92</v>
@@ -24267,30 +24267,30 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>107.47</v>
+        <v>105.62</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>105.22</v>
+        <v>103.41</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>108.62</v>
+        <v>106.7</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>105.09</v>
+        <v>103.41</v>
       </c>
       <c r="H335" s="7" t="n">
         <v>-2.09</v>
@@ -24299,30 +24299,30 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>105.62</v>
+        <v>107.47</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>103.41</v>
+        <v>105.22</v>
       </c>
       <c r="F336" s="5" t="n">
-        <v>106.7</v>
+        <v>108.62</v>
       </c>
       <c r="G336" s="5" t="n">
-        <v>103.41</v>
+        <v>105.09</v>
       </c>
       <c r="H336" s="7" t="n">
         <v>-2.09</v>
@@ -24523,30 +24523,30 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>85.81</v>
+        <v>69.59</v>
       </c>
       <c r="F343" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>83.76000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="H343" s="7" t="n">
         <v>-2.22</v>
@@ -24555,30 +24555,30 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>71.17</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>69.59</v>
+        <v>85.81</v>
       </c>
       <c r="F344" s="5" t="n">
-        <v>71.17</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="G344" s="5" t="n">
-        <v>69.28</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="H344" s="7" t="n">
         <v>-2.22</v>
@@ -24779,30 +24779,30 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>TAP</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>Molson Coors Beverage Company</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>41.46</v>
+        <v>242.76</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>40.5</v>
+        <v>237.14</v>
       </c>
       <c r="F351" s="5" t="n">
-        <v>41.46</v>
+        <v>242.76</v>
       </c>
       <c r="G351" s="5" t="n">
-        <v>39.76</v>
+        <v>236.22</v>
       </c>
       <c r="H351" s="7" t="n">
         <v>-2.32</v>
@@ -24811,30 +24811,30 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>TAP</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Molson Coors Beverage Company</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>242.76</v>
+        <v>41.46</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>237.14</v>
+        <v>40.5</v>
       </c>
       <c r="F352" s="5" t="n">
-        <v>242.76</v>
+        <v>41.46</v>
       </c>
       <c r="G352" s="5" t="n">
-        <v>236.22</v>
+        <v>39.76</v>
       </c>
       <c r="H352" s="7" t="n">
         <v>-2.32</v>
@@ -24843,30 +24843,30 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>BXP</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>BXP, Inc.</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>346.59</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>67.69</v>
+        <v>338.46</v>
       </c>
       <c r="F353" s="5" t="n">
-        <v>69.31999999999999</v>
+        <v>346.59</v>
       </c>
       <c r="G353" s="5" t="n">
-        <v>67.06</v>
+        <v>335.02</v>
       </c>
       <c r="H353" s="7" t="n">
         <v>-2.35</v>
@@ -24875,30 +24875,30 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BXP</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>BXP, Inc.</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>346.59</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>338.46</v>
+        <v>67.69</v>
       </c>
       <c r="F354" s="5" t="n">
-        <v>346.59</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="G354" s="5" t="n">
-        <v>335.02</v>
+        <v>67.06</v>
       </c>
       <c r="H354" s="7" t="n">
         <v>-2.35</v>
@@ -24971,12 +24971,12 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -24985,16 +24985,16 @@
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>140.7</v>
+        <v>214.56</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>137.34</v>
+        <v>209.44</v>
       </c>
       <c r="F357" s="5" t="n">
-        <v>140.7</v>
+        <v>214.56</v>
       </c>
       <c r="G357" s="5" t="n">
-        <v>136.59</v>
+        <v>209.44</v>
       </c>
       <c r="H357" s="7" t="n">
         <v>-2.39</v>
@@ -25003,12 +25003,12 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
@@ -25017,16 +25017,16 @@
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>214.56</v>
+        <v>140.7</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>209.44</v>
+        <v>137.34</v>
       </c>
       <c r="F358" s="5" t="n">
-        <v>214.56</v>
+        <v>140.7</v>
       </c>
       <c r="G358" s="5" t="n">
-        <v>209.44</v>
+        <v>136.59</v>
       </c>
       <c r="H358" s="7" t="n">
         <v>-2.39</v>
@@ -25451,30 +25451,30 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>108.1</v>
+        <v>73.31</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>105.31</v>
+        <v>71.42</v>
       </c>
       <c r="F372" s="5" t="n">
-        <v>108.1</v>
+        <v>73.31</v>
       </c>
       <c r="G372" s="5" t="n">
-        <v>105.31</v>
+        <v>71.42</v>
       </c>
       <c r="H372" s="7" t="n">
         <v>-2.58</v>
@@ -25483,30 +25483,30 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>1256.26</v>
+        <v>108.1</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>1223.86</v>
+        <v>105.31</v>
       </c>
       <c r="F373" s="5" t="n">
-        <v>1267.77</v>
+        <v>108.1</v>
       </c>
       <c r="G373" s="5" t="n">
-        <v>1213.65</v>
+        <v>105.31</v>
       </c>
       <c r="H373" s="7" t="n">
         <v>-2.58</v>
@@ -25515,30 +25515,30 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>73.31</v>
+        <v>1256.26</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>71.42</v>
+        <v>1223.86</v>
       </c>
       <c r="F374" s="5" t="n">
-        <v>73.31</v>
+        <v>1267.77</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>71.42</v>
+        <v>1213.65</v>
       </c>
       <c r="H374" s="7" t="n">
         <v>-2.58</v>
@@ -25579,30 +25579,30 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D376" s="5" t="n">
-        <v>23.64</v>
+        <v>343.75</v>
       </c>
       <c r="E376" s="5" t="n">
-        <v>23.02</v>
+        <v>334.74</v>
       </c>
       <c r="F376" s="5" t="n">
-        <v>23.64</v>
+        <v>343.75</v>
       </c>
       <c r="G376" s="5" t="n">
-        <v>23.02</v>
+        <v>334.47</v>
       </c>
       <c r="H376" s="7" t="n">
         <v>-2.62</v>
@@ -25611,30 +25611,30 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>343.75</v>
+        <v>23.64</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>334.74</v>
+        <v>23.02</v>
       </c>
       <c r="F377" s="5" t="n">
-        <v>343.75</v>
+        <v>23.64</v>
       </c>
       <c r="G377" s="5" t="n">
-        <v>334.47</v>
+        <v>23.02</v>
       </c>
       <c r="H377" s="7" t="n">
         <v>-2.62</v>
@@ -25867,30 +25867,30 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>38.03</v>
+        <v>100.91</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>36.96</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F385" s="5" t="n">
-        <v>38.52</v>
+        <v>100.91</v>
       </c>
       <c r="G385" s="5" t="n">
-        <v>36.96</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="H385" s="7" t="n">
         <v>-2.81</v>
@@ -25899,30 +25899,30 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>100.91</v>
+        <v>38.03</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="F386" s="5" t="n">
-        <v>100.91</v>
+        <v>38.52</v>
       </c>
       <c r="G386" s="5" t="n">
-        <v>98.06999999999999</v>
+        <v>36.96</v>
       </c>
       <c r="H386" s="7" t="n">
         <v>-2.81</v>
@@ -26155,30 +26155,30 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D394" s="5" t="n">
-        <v>260.4</v>
+        <v>198.68</v>
       </c>
       <c r="E394" s="5" t="n">
-        <v>252.8</v>
+        <v>192.88</v>
       </c>
       <c r="F394" s="5" t="n">
-        <v>260.4</v>
+        <v>198.68</v>
       </c>
       <c r="G394" s="5" t="n">
-        <v>252.8</v>
+        <v>188.9</v>
       </c>
       <c r="H394" s="7" t="n">
         <v>-2.92</v>
@@ -26187,30 +26187,30 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>198.68</v>
+        <v>260.4</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>192.88</v>
+        <v>252.8</v>
       </c>
       <c r="F395" s="5" t="n">
-        <v>198.68</v>
+        <v>260.4</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>188.9</v>
+        <v>252.8</v>
       </c>
       <c r="H395" s="7" t="n">
         <v>-2.92</v>
@@ -26731,30 +26731,30 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>46.67</v>
+        <v>235.09</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>45.15</v>
+        <v>227.42</v>
       </c>
       <c r="F412" s="5" t="n">
-        <v>46.68</v>
+        <v>235.09</v>
       </c>
       <c r="G412" s="5" t="n">
-        <v>45.15</v>
+        <v>221.72</v>
       </c>
       <c r="H412" s="7" t="n">
         <v>-3.26</v>
@@ -26763,30 +26763,30 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>235.09</v>
+        <v>46.67</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>227.42</v>
+        <v>45.15</v>
       </c>
       <c r="F413" s="5" t="n">
-        <v>235.09</v>
+        <v>46.68</v>
       </c>
       <c r="G413" s="5" t="n">
-        <v>221.72</v>
+        <v>45.15</v>
       </c>
       <c r="H413" s="7" t="n">
         <v>-3.26</v>
@@ -27275,30 +27275,30 @@
     <row r="429">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D429" s="5" t="n">
-        <v>112.47</v>
+        <v>377.94</v>
       </c>
       <c r="E429" s="5" t="n">
-        <v>108.33</v>
+        <v>364.03</v>
       </c>
       <c r="F429" s="5" t="n">
-        <v>112.47</v>
+        <v>379.27</v>
       </c>
       <c r="G429" s="5" t="n">
-        <v>108.33</v>
+        <v>364.03</v>
       </c>
       <c r="H429" s="7" t="n">
         <v>-3.68</v>
@@ -27307,30 +27307,30 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>377.94</v>
+        <v>112.47</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>364.03</v>
+        <v>108.33</v>
       </c>
       <c r="F430" s="5" t="n">
-        <v>379.27</v>
+        <v>112.47</v>
       </c>
       <c r="G430" s="5" t="n">
-        <v>364.03</v>
+        <v>108.33</v>
       </c>
       <c r="H430" s="7" t="n">
         <v>-3.68</v>
@@ -27563,30 +27563,30 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>233.78</v>
+        <v>136.98</v>
       </c>
       <c r="E438" s="5" t="n">
-        <v>224.59</v>
+        <v>131.59</v>
       </c>
       <c r="F438" s="5" t="n">
-        <v>233.78</v>
+        <v>136.98</v>
       </c>
       <c r="G438" s="5" t="n">
-        <v>224.59</v>
+        <v>131.13</v>
       </c>
       <c r="H438" s="7" t="n">
         <v>-3.93</v>
@@ -27595,30 +27595,30 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>136.98</v>
+        <v>233.78</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>131.59</v>
+        <v>224.59</v>
       </c>
       <c r="F439" s="5" t="n">
-        <v>136.98</v>
+        <v>233.78</v>
       </c>
       <c r="G439" s="5" t="n">
-        <v>131.13</v>
+        <v>224.59</v>
       </c>
       <c r="H439" s="7" t="n">
         <v>-3.93</v>
@@ -28299,30 +28299,30 @@
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D461" s="5" t="n">
-        <v>24.76</v>
+        <v>111.31</v>
       </c>
       <c r="E461" s="5" t="n">
-        <v>23.51</v>
+        <v>105.69</v>
       </c>
       <c r="F461" s="5" t="n">
-        <v>24.76</v>
+        <v>111.31</v>
       </c>
       <c r="G461" s="5" t="n">
-        <v>23.23</v>
+        <v>105.69</v>
       </c>
       <c r="H461" s="7" t="n">
         <v>-5.05</v>
@@ -28331,30 +28331,30 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D462" s="5" t="n">
-        <v>111.31</v>
+        <v>24.76</v>
       </c>
       <c r="E462" s="5" t="n">
-        <v>105.69</v>
+        <v>23.51</v>
       </c>
       <c r="F462" s="5" t="n">
-        <v>111.31</v>
+        <v>24.76</v>
       </c>
       <c r="G462" s="5" t="n">
-        <v>105.69</v>
+        <v>23.23</v>
       </c>
       <c r="H462" s="7" t="n">
         <v>-5.05</v>
@@ -28843,30 +28843,30 @@
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D478" s="5" t="n">
-        <v>198.63</v>
+        <v>186.29</v>
       </c>
       <c r="E478" s="5" t="n">
-        <v>185.87</v>
+        <v>174.33</v>
       </c>
       <c r="F478" s="5" t="n">
-        <v>199.96</v>
+        <v>186.38</v>
       </c>
       <c r="G478" s="5" t="n">
-        <v>185.75</v>
+        <v>169.46</v>
       </c>
       <c r="H478" s="7" t="n">
         <v>-6.42</v>
@@ -28875,30 +28875,30 @@
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D479" s="5" t="n">
-        <v>186.29</v>
+        <v>198.63</v>
       </c>
       <c r="E479" s="5" t="n">
-        <v>174.33</v>
+        <v>185.87</v>
       </c>
       <c r="F479" s="5" t="n">
-        <v>186.38</v>
+        <v>199.96</v>
       </c>
       <c r="G479" s="5" t="n">
-        <v>169.46</v>
+        <v>185.75</v>
       </c>
       <c r="H479" s="7" t="n">
         <v>-6.42</v>
@@ -28907,30 +28907,30 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Norwegian Cruise Line Holdings</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>46.86</v>
+        <v>16.65</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>43.82</v>
+        <v>15.57</v>
       </c>
       <c r="F480" s="5" t="n">
-        <v>46.86</v>
+        <v>16.65</v>
       </c>
       <c r="G480" s="5" t="n">
-        <v>43.82</v>
+        <v>15.43</v>
       </c>
       <c r="H480" s="7" t="n">
         <v>-6.49</v>
@@ -28939,30 +28939,30 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Cruise Line Holdings</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>16.65</v>
+        <v>46.86</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>15.57</v>
+        <v>43.82</v>
       </c>
       <c r="F481" s="5" t="n">
-        <v>16.65</v>
+        <v>46.86</v>
       </c>
       <c r="G481" s="5" t="n">
-        <v>15.43</v>
+        <v>43.82</v>
       </c>
       <c r="H481" s="7" t="n">
         <v>-6.49</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-07 07:41</t>
+          <t>Daily (Sep 03-&gt;Sep 04) and rolling 5-day  |  updated 2026-09-08 07:34</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 10 close to Sep 11 close  |  503 companies  |  updated 2026-09-12 07:27</t>
+          <t>Sep 10 close to Sep 11 close  |  503 companies  |  updated 2026-09-13 07:48</t>
         </is>
       </c>
     </row>
@@ -1193,24 +1193,24 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>234.02</v>
+        <v>409.15</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>243.29</v>
+        <v>425.37</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>3.96</v>
@@ -1219,24 +1219,24 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>409.15</v>
+        <v>234.02</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>425.37</v>
+        <v>243.29</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>3.96</v>
@@ -2051,24 +2051,24 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>148.37</v>
+        <v>960.67</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>152.19</v>
+        <v>985.39</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>2.57</v>
@@ -2077,24 +2077,24 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Fair Isaac</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>960.67</v>
+        <v>148.37</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>985.39</v>
+        <v>152.19</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>2.57</v>
@@ -2467,24 +2467,24 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>77.90000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>79.59999999999999</v>
+        <v>91.37</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>2.18</v>
@@ -2493,24 +2493,24 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>89.42</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>91.37</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>2.18</v>
@@ -2597,24 +2597,24 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>535.63</v>
+        <v>367.56</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>546.78</v>
+        <v>375.2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>2.08</v>
@@ -2623,24 +2623,24 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>367.56</v>
+        <v>535.63</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>375.2</v>
+        <v>546.78</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>2.08</v>
@@ -2779,24 +2779,24 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>243</v>
+        <v>251.89</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>247.72</v>
+        <v>256.78</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>1.94</v>
@@ -2805,24 +2805,24 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>251.89</v>
+        <v>243</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>256.78</v>
+        <v>247.72</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>1.94</v>
@@ -2883,24 +2883,24 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
-        <v>317.44</v>
+        <v>344.01</v>
       </c>
       <c r="E95" s="5" t="n">
-        <v>323.31</v>
+        <v>350.37</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>1.85</v>
@@ -2909,24 +2909,24 @@
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>344.01</v>
+        <v>317.44</v>
       </c>
       <c r="E96" s="5" t="n">
-        <v>350.37</v>
+        <v>323.31</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>1.85</v>
@@ -2935,24 +2935,24 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>76.01000000000001</v>
+        <v>137.99</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>77.40000000000001</v>
+        <v>140.51</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>1.83</v>
@@ -2961,24 +2961,24 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>137.99</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>140.51</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>1.83</v>
@@ -3013,24 +3013,24 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>332.6</v>
+        <v>452.41</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>338.5</v>
+        <v>460.4</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>1.77</v>
@@ -3039,24 +3039,24 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D101" s="5" t="n">
-        <v>452.41</v>
+        <v>332.6</v>
       </c>
       <c r="E101" s="5" t="n">
-        <v>460.4</v>
+        <v>338.5</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>1.77</v>
@@ -3117,24 +3117,24 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>79.88</v>
+        <v>257.3</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>81.27</v>
+        <v>261.77</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>1.74</v>
@@ -3143,24 +3143,24 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>257.3</v>
+        <v>79.88</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>261.77</v>
+        <v>81.27</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>1.74</v>
@@ -3481,24 +3481,24 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>111.65</v>
+        <v>467.36</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>113.46</v>
+        <v>474.95</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>1.62</v>
@@ -3507,12 +3507,12 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>467.36</v>
+        <v>1062.4</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>474.95</v>
+        <v>1079.65</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>1.62</v>
@@ -3533,24 +3533,24 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>1062.4</v>
+        <v>111.65</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>1079.65</v>
+        <v>113.46</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>1.62</v>
@@ -3637,24 +3637,24 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>65.40000000000001</v>
+        <v>155.34</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>66.42</v>
+        <v>157.77</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>1.56</v>
@@ -3663,24 +3663,24 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>155.34</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>157.77</v>
+        <v>66.42</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>1.56</v>
@@ -3793,24 +3793,24 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>90.16</v>
+        <v>330.39</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>91.54000000000001</v>
+        <v>335.45</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>1.53</v>
@@ -3819,24 +3819,24 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>330.39</v>
+        <v>90.16</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>335.45</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>1.53</v>
@@ -3871,24 +3871,24 @@
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Martin Marietta Materials</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D133" s="5" t="n">
-        <v>306.96</v>
+        <v>502.47</v>
       </c>
       <c r="E133" s="5" t="n">
-        <v>311.54</v>
+        <v>509.96</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>1.49</v>
@@ -3897,24 +3897,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>502.47</v>
+        <v>306.96</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>509.96</v>
+        <v>311.54</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>1.49</v>
@@ -4157,24 +4157,24 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>105.73</v>
+        <v>288.85</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>107.15</v>
+        <v>292.71</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>1.34</v>
@@ -4183,24 +4183,24 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>288.85</v>
+        <v>105.73</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>292.71</v>
+        <v>107.15</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>1.34</v>
@@ -4209,12 +4209,12 @@
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>MMM</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>3M</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -4223,10 +4223,10 @@
         </is>
       </c>
       <c r="D146" s="5" t="n">
-        <v>162.86</v>
+        <v>67.64</v>
       </c>
       <c r="E146" s="5" t="n">
-        <v>164.97</v>
+        <v>68.52</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>1.3</v>
@@ -4235,12 +4235,12 @@
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>MMM</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>3M</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="D147" s="5" t="n">
-        <v>67.64</v>
+        <v>162.86</v>
       </c>
       <c r="E147" s="5" t="n">
-        <v>68.52</v>
+        <v>164.97</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>1.3</v>
@@ -4313,24 +4313,24 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>49.97</v>
+        <v>547.6</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>50.61</v>
+        <v>554.61</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>1.28</v>
@@ -4339,24 +4339,24 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>547.6</v>
+        <v>49.97</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>554.61</v>
+        <v>50.61</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>1.28</v>
@@ -4417,24 +4417,24 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>IDEX Corporation</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>221.46</v>
+        <v>320.71</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>224.21</v>
+        <v>324.69</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>1.24</v>
@@ -4443,24 +4443,24 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>IDEX Corporation</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>320.71</v>
+        <v>221.46</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>324.69</v>
+        <v>224.21</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>1.24</v>
@@ -4469,24 +4469,24 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>550.03</v>
+        <v>596.5</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>556.75</v>
+        <v>603.79</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>1.22</v>
@@ -4495,24 +4495,24 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>596.5</v>
+        <v>172.72</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>603.79</v>
+        <v>174.83</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>1.22</v>
@@ -4521,24 +4521,24 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>172.72</v>
+        <v>550.03</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>174.83</v>
+        <v>556.75</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>1.22</v>
@@ -4625,24 +4625,24 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>TransDigm Group</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>6088.28</v>
+        <v>1126.88</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>6160.76</v>
+        <v>1140.32</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>1.19</v>
@@ -4651,24 +4651,24 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>TransDigm Group</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>1126.88</v>
+        <v>6088.28</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1140.32</v>
+        <v>6160.76</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>1.19</v>
@@ -4729,24 +4729,24 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
-        <v>207.53</v>
+        <v>92.44</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>209.89</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>1.14</v>
@@ -4755,24 +4755,24 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>92.44</v>
+        <v>207.53</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>93.48999999999999</v>
+        <v>209.89</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>1.14</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>155.81</v>
+        <v>87.66</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>157.4</v>
+        <v>88.55</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>1.02</v>
@@ -5067,24 +5067,24 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
-        <v>87.66</v>
+        <v>155.81</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>88.55</v>
+        <v>157.4</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>1.02</v>
@@ -5119,24 +5119,24 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Home Depot (The)</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>305.69</v>
+        <v>134.41</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>308.74</v>
+        <v>135.75</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>1</v>
@@ -5145,24 +5145,24 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>134.41</v>
+        <v>461.62</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>135.75</v>
+        <v>466.22</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>1</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Home Depot (The)</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>461.62</v>
+        <v>305.69</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>466.22</v>
+        <v>308.74</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>1</v>
@@ -5275,24 +5275,24 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>140.53</v>
+        <v>89.45</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>141.85</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -5301,24 +5301,24 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Oneok</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D188" s="5" t="n">
-        <v>89.45</v>
+        <v>95.72</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>90.29000000000001</v>
+        <v>96.62</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -5327,24 +5327,24 @@
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Oneok</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D189" s="5" t="n">
-        <v>95.72</v>
+        <v>140.53</v>
       </c>
       <c r="E189" s="5" t="n">
-        <v>96.62</v>
+        <v>141.85</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -5379,24 +5379,24 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>187.37</v>
+        <v>147.05</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>189.05</v>
+        <v>148.38</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>0.9</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>207.17</v>
+        <v>187.37</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>209.03</v>
+        <v>189.05</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>0.9</v>
@@ -5431,24 +5431,24 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
-        <v>147.05</v>
+        <v>207.17</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>148.38</v>
+        <v>209.03</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>0.9</v>
@@ -5639,24 +5639,24 @@
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Palantir Technologies</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D201" s="5" t="n">
-        <v>165.86</v>
+        <v>255</v>
       </c>
       <c r="E201" s="5" t="n">
-        <v>167.23</v>
+        <v>257.12</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>0.83</v>
@@ -5665,24 +5665,24 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Palantir Technologies</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D202" s="5" t="n">
-        <v>255</v>
+        <v>165.86</v>
       </c>
       <c r="E202" s="5" t="n">
-        <v>257.12</v>
+        <v>167.23</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>0.83</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>212.66</v>
+        <v>176.42</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>214.38</v>
+        <v>177.85</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>0.8100000000000001</v>
@@ -5743,24 +5743,24 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>176.42</v>
+        <v>212.66</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>177.85</v>
+        <v>214.38</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>0.8100000000000001</v>
@@ -5769,24 +5769,24 @@
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Vivmark Residential</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D206" s="5" t="n">
-        <v>215.43</v>
+        <v>65.02</v>
       </c>
       <c r="E206" s="5" t="n">
-        <v>217.15</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="F206" s="6" t="n">
         <v>0.8</v>
@@ -5795,24 +5795,24 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Vivmark Residential</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>65.02</v>
+        <v>215.43</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>65.54000000000001</v>
+        <v>217.15</v>
       </c>
       <c r="F207" s="6" t="n">
         <v>0.8</v>
@@ -6081,24 +6081,24 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>RL</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Ralph Lauren Corporation</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D218" s="5" t="n">
-        <v>336.67</v>
+        <v>43.09</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>339.09</v>
+        <v>43.4</v>
       </c>
       <c r="F218" s="6" t="n">
         <v>0.72</v>
@@ -6107,24 +6107,24 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>Ralph Lauren Corporation</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>43.09</v>
+        <v>336.67</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>43.4</v>
+        <v>339.09</v>
       </c>
       <c r="F219" s="6" t="n">
         <v>0.72</v>
@@ -6133,24 +6133,24 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>FERG</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Ferguson Enterprises</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>220.97</v>
+        <v>114.47</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>222.54</v>
+        <v>115.28</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>0.71</v>
@@ -6159,24 +6159,24 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>FERG</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Ferguson Enterprises</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>114.47</v>
+        <v>220.97</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>115.28</v>
+        <v>222.54</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>0.71</v>
@@ -6211,24 +6211,24 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>105.82</v>
+        <v>62.41</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>106.55</v>
+        <v>62.84</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>0.6899999999999999</v>
@@ -6237,24 +6237,24 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>62.41</v>
+        <v>105.82</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>62.84</v>
+        <v>106.55</v>
       </c>
       <c r="F224" s="6" t="n">
         <v>0.6899999999999999</v>
@@ -6263,24 +6263,24 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D225" s="5" t="n">
-        <v>565.37</v>
+        <v>189.77</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>569.1900000000001</v>
+        <v>191.06</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>0.68</v>
@@ -6289,24 +6289,24 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D226" s="5" t="n">
-        <v>189.77</v>
+        <v>565.37</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>191.06</v>
+        <v>569.1900000000001</v>
       </c>
       <c r="F226" s="6" t="n">
         <v>0.68</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>GWW</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>W. W. Grainger</t>
+          <t>Fox Corporation (Class B)</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>1271.49</v>
+        <v>58.06</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>1280</v>
+        <v>58.45</v>
       </c>
       <c r="F228" s="6" t="n">
         <v>0.67</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>GWW</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Fox Corporation (Class B)</t>
+          <t>W. W. Grainger</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>58.06</v>
+        <v>1271.49</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>58.45</v>
+        <v>1280</v>
       </c>
       <c r="F229" s="6" t="n">
         <v>0.67</v>
@@ -6393,12 +6393,12 @@
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -6407,10 +6407,10 @@
         </is>
       </c>
       <c r="D230" s="5" t="n">
-        <v>216.19</v>
+        <v>507</v>
       </c>
       <c r="E230" s="5" t="n">
-        <v>217.62</v>
+        <v>510.37</v>
       </c>
       <c r="F230" s="6" t="n">
         <v>0.66</v>
@@ -6419,12 +6419,12 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>507</v>
+        <v>216.19</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>510.37</v>
+        <v>217.62</v>
       </c>
       <c r="F231" s="6" t="n">
         <v>0.66</v>
@@ -6497,24 +6497,24 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>PSA</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Public Storage</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>118.48</v>
+        <v>294.6</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>119.24</v>
+        <v>296.5</v>
       </c>
       <c r="F234" s="6" t="n">
         <v>0.64</v>
@@ -6523,24 +6523,24 @@
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Public Storage</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D235" s="5" t="n">
-        <v>294.6</v>
+        <v>118.48</v>
       </c>
       <c r="E235" s="5" t="n">
-        <v>296.5</v>
+        <v>119.24</v>
       </c>
       <c r="F235" s="6" t="n">
         <v>0.64</v>
@@ -6679,24 +6679,24 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>271.37</v>
+        <v>168.04</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>272.91</v>
+        <v>169</v>
       </c>
       <c r="F241" s="6" t="n">
         <v>0.57</v>
@@ -6705,24 +6705,24 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>207.11</v>
+        <v>271.37</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>208.3</v>
+        <v>272.91</v>
       </c>
       <c r="F242" s="6" t="n">
         <v>0.57</v>
@@ -6731,24 +6731,24 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>168.04</v>
+        <v>207.11</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>169</v>
+        <v>208.3</v>
       </c>
       <c r="F243" s="6" t="n">
         <v>0.57</v>
@@ -6809,24 +6809,24 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>CME Group</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>274.07</v>
+        <v>42.6</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>275.54</v>
+        <v>42.83</v>
       </c>
       <c r="F246" s="6" t="n">
         <v>0.54</v>
@@ -6861,24 +6861,24 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>CME</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>CME Group</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D248" s="5" t="n">
-        <v>260.98</v>
+        <v>274.07</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>262.4</v>
+        <v>275.54</v>
       </c>
       <c r="F248" s="6" t="n">
         <v>0.54</v>
@@ -6887,24 +6887,24 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>42.6</v>
+        <v>260.98</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>42.83</v>
+        <v>262.4</v>
       </c>
       <c r="F249" s="6" t="n">
         <v>0.54</v>
@@ -6913,24 +6913,24 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>126.14</v>
+        <v>54.43</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>126.81</v>
+        <v>54.72</v>
       </c>
       <c r="F250" s="6" t="n">
         <v>0.53</v>
@@ -6939,24 +6939,24 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>54.43</v>
+        <v>126.14</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>54.72</v>
+        <v>126.81</v>
       </c>
       <c r="F251" s="6" t="n">
         <v>0.53</v>
@@ -6991,24 +6991,24 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>242.98</v>
+        <v>363.56</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>244.24</v>
+        <v>365.44</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0.52</v>
@@ -7043,24 +7043,24 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>363.56</v>
+        <v>242.98</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>365.44</v>
+        <v>244.24</v>
       </c>
       <c r="F255" s="6" t="n">
         <v>0.52</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Occidental Petroleum</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>61.16</v>
+        <v>34.56</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>61.46</v>
+        <v>34.73</v>
       </c>
       <c r="F259" s="6" t="n">
         <v>0.49</v>
@@ -7173,24 +7173,24 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>NKE</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Nike, Inc.</t>
+          <t>Occidental Petroleum</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>36.62</v>
+        <v>61.16</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>36.8</v>
+        <v>61.46</v>
       </c>
       <c r="F260" s="6" t="n">
         <v>0.49</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>34.56</v>
+        <v>463.88</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>34.73</v>
+        <v>466.16</v>
       </c>
       <c r="F261" s="6" t="n">
         <v>0.49</v>
@@ -7225,24 +7225,24 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>NKE</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Nike, Inc.</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>463.88</v>
+        <v>36.62</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>466.16</v>
+        <v>36.8</v>
       </c>
       <c r="F262" s="6" t="n">
         <v>0.49</v>
@@ -7277,24 +7277,24 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>201.03</v>
+        <v>165.23</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>201.95</v>
+        <v>165.99</v>
       </c>
       <c r="F264" s="6" t="n">
         <v>0.46</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>165.23</v>
+        <v>201.03</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>165.99</v>
+        <v>201.95</v>
       </c>
       <c r="F265" s="6" t="n">
         <v>0.46</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>APA Corporation</t>
+          <t>Host Hotels &amp; Resorts</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>44.53</v>
+        <v>22.14</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>44.73</v>
+        <v>22.24</v>
       </c>
       <c r="F266" s="6" t="n">
         <v>0.45</v>
@@ -7355,24 +7355,24 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Host Hotels &amp; Resorts</t>
+          <t>APA Corporation</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>22.14</v>
+        <v>44.53</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>22.24</v>
+        <v>44.73</v>
       </c>
       <c r="F267" s="6" t="n">
         <v>0.45</v>
@@ -7407,24 +7407,24 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
-        <v>105.05</v>
+        <v>51.1</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>105.5</v>
+        <v>51.32</v>
       </c>
       <c r="F269" s="6" t="n">
         <v>0.43</v>
@@ -7433,24 +7433,24 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>51.1</v>
+        <v>105.05</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>51.32</v>
+        <v>105.5</v>
       </c>
       <c r="F270" s="6" t="n">
         <v>0.43</v>
@@ -7485,24 +7485,24 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>American International Group</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>24.73</v>
+        <v>75.03</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>24.83</v>
+        <v>75.33</v>
       </c>
       <c r="F272" s="6" t="n">
         <v>0.4</v>
@@ -7511,24 +7511,24 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>American International Group</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>75.03</v>
+        <v>24.73</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>75.33</v>
+        <v>24.83</v>
       </c>
       <c r="F273" s="6" t="n">
         <v>0.4</v>
@@ -7849,24 +7849,24 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>360.83</v>
+        <v>81.36</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>361.99</v>
+        <v>81.62</v>
       </c>
       <c r="F286" s="6" t="n">
         <v>0.32</v>
@@ -7901,24 +7901,24 @@
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>81.36</v>
+        <v>360.83</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>81.62</v>
+        <v>361.99</v>
       </c>
       <c r="F288" s="6" t="n">
         <v>0.32</v>
@@ -8161,24 +8161,24 @@
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Globe Life</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>93.94</v>
+        <v>170.8</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>94.15000000000001</v>
+        <v>171.17</v>
       </c>
       <c r="F298" s="6" t="n">
         <v>0.22</v>
@@ -8187,24 +8187,24 @@
     <row r="299">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Globe Life</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D299" s="5" t="n">
-        <v>170.8</v>
+        <v>93.94</v>
       </c>
       <c r="E299" s="5" t="n">
-        <v>171.17</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="F299" s="6" t="n">
         <v>0.22</v>
@@ -8317,24 +8317,24 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>CMG</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>36.13</v>
+        <v>175.86</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>36.2</v>
+        <v>176.2</v>
       </c>
       <c r="F304" s="6" t="n">
         <v>0.19</v>
@@ -8369,24 +8369,24 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>CMG</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>175.86</v>
+        <v>36.13</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>176.2</v>
+        <v>36.2</v>
       </c>
       <c r="F306" s="6" t="n">
         <v>0.19</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>196.59</v>
+        <v>75.41</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>196.82</v>
+        <v>75.5</v>
       </c>
       <c r="F314" s="6" t="n">
         <v>0.12</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>169.59</v>
+        <v>181.33</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>169.8</v>
+        <v>181.55</v>
       </c>
       <c r="F315" s="6" t="n">
         <v>0.12</v>
@@ -8629,24 +8629,24 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>75.41</v>
+        <v>196.59</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>75.5</v>
+        <v>196.82</v>
       </c>
       <c r="F316" s="6" t="n">
         <v>0.12</v>
@@ -8655,24 +8655,24 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>25.17</v>
+        <v>169.59</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>25.2</v>
+        <v>169.8</v>
       </c>
       <c r="F317" s="6" t="n">
         <v>0.12</v>
@@ -8681,24 +8681,24 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D318" s="5" t="n">
-        <v>181.33</v>
+        <v>25.17</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>181.55</v>
+        <v>25.2</v>
       </c>
       <c r="F318" s="6" t="n">
         <v>0.12</v>
@@ -8837,24 +8837,24 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>410.42</v>
+        <v>880.86</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>410.71</v>
+        <v>881.51</v>
       </c>
       <c r="F324" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8863,24 +8863,24 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D325" s="5" t="n">
-        <v>880.86</v>
+        <v>298.01</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>881.51</v>
+        <v>298.22</v>
       </c>
       <c r="F325" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8889,24 +8889,24 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>298.01</v>
+        <v>410.42</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>298.22</v>
+        <v>410.71</v>
       </c>
       <c r="F326" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>311.8</v>
+        <v>121.07</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>311.99</v>
+        <v>121.14</v>
       </c>
       <c r="F327" s="6" t="n">
         <v>0.06</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>315.41</v>
+        <v>155.73</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>315.61</v>
+        <v>155.83</v>
       </c>
       <c r="F329" s="6" t="n">
         <v>0.06</v>
@@ -8993,24 +8993,24 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>121.07</v>
+        <v>315.41</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>121.14</v>
+        <v>315.61</v>
       </c>
       <c r="F330" s="6" t="n">
         <v>0.06</v>
@@ -9019,24 +9019,24 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>155.73</v>
+        <v>311.8</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>155.83</v>
+        <v>311.99</v>
       </c>
       <c r="F331" s="6" t="n">
         <v>0.06</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>170.08</v>
+        <v>119.37</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>170.15</v>
+        <v>119.42</v>
       </c>
       <c r="F333" s="6" t="n">
         <v>0.04</v>
@@ -9097,24 +9097,24 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>BNY Mellon</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D334" s="5" t="n">
-        <v>119.37</v>
+        <v>162.59</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>119.42</v>
+        <v>162.66</v>
       </c>
       <c r="F334" s="6" t="n">
         <v>0.04</v>
@@ -9123,24 +9123,24 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>BNY Mellon</t>
+          <t>Williams Companies</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>162.59</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>162.66</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="F335" s="6" t="n">
         <v>0.04</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Williams Companies</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>72.81999999999999</v>
+        <v>170.08</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>72.84999999999999</v>
+        <v>170.15</v>
       </c>
       <c r="F336" s="6" t="n">
         <v>0.04</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>89.23</v>
+        <v>67.25</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>89.23999999999999</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F337" s="6" t="n">
         <v>0.01</v>
@@ -9201,24 +9201,24 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D338" s="5" t="n">
-        <v>67.25</v>
+        <v>89.23</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>67.26000000000001</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F338" s="6" t="n">
         <v>0.01</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>388.58</v>
+        <v>105.35</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>388.52</v>
+        <v>105.33</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-0.02</v>
@@ -9331,24 +9331,24 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>105.35</v>
+        <v>306.24</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>105.33</v>
+        <v>306.19</v>
       </c>
       <c r="F343" s="7" t="n">
         <v>-0.02</v>
@@ -9357,24 +9357,24 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>306.24</v>
+        <v>388.58</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>306.19</v>
+        <v>388.52</v>
       </c>
       <c r="F344" s="7" t="n">
         <v>-0.02</v>
@@ -9461,24 +9461,24 @@
     <row r="348">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B348" s="4" t="inlineStr">
         <is>
-          <t>Welltower</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D348" s="5" t="n">
-        <v>235.71</v>
+        <v>173.53</v>
       </c>
       <c r="E348" s="5" t="n">
-        <v>235.62</v>
+        <v>173.46</v>
       </c>
       <c r="F348" s="7" t="n">
         <v>-0.04</v>
@@ -9487,24 +9487,24 @@
     <row r="349">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B349" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Welltower</t>
         </is>
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D349" s="5" t="n">
-        <v>173.53</v>
+        <v>235.71</v>
       </c>
       <c r="E349" s="5" t="n">
-        <v>173.46</v>
+        <v>235.62</v>
       </c>
       <c r="F349" s="7" t="n">
         <v>-0.04</v>
@@ -9513,24 +9513,24 @@
     <row r="350">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>MDLZ</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B350" s="4" t="inlineStr">
         <is>
-          <t>Mondelez International</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D350" s="5" t="n">
-        <v>62.47</v>
+        <v>104.95</v>
       </c>
       <c r="E350" s="5" t="n">
-        <v>62.44</v>
+        <v>104.9</v>
       </c>
       <c r="F350" s="7" t="n">
         <v>-0.05</v>
@@ -9539,24 +9539,24 @@
     <row r="351">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>MDLZ</t>
         </is>
       </c>
       <c r="B351" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Mondelez International</t>
         </is>
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D351" s="5" t="n">
-        <v>104.95</v>
+        <v>62.47</v>
       </c>
       <c r="E351" s="5" t="n">
-        <v>104.9</v>
+        <v>62.44</v>
       </c>
       <c r="F351" s="7" t="n">
         <v>-0.05</v>
@@ -9591,24 +9591,24 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>KVUE</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Kenvue</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>17.79</v>
+        <v>408.47</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>17.78</v>
+        <v>408.22</v>
       </c>
       <c r="F353" s="7" t="n">
         <v>-0.06</v>
@@ -9617,24 +9617,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>KVUE</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>UDR, Inc.</t>
+          <t>Kenvue</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>35.14</v>
+        <v>17.79</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>35.12</v>
+        <v>17.78</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>-0.06</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>UDR, Inc.</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>408.47</v>
+        <v>35.14</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>408.22</v>
+        <v>35.12</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-0.06</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>14.8</v>
+        <v>27.56</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>14.79</v>
+        <v>27.54</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>107.33</v>
+        <v>14.8</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>107.25</v>
+        <v>14.79</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9747,24 +9747,24 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>27.56</v>
+        <v>107.33</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>27.54</v>
+        <v>107.25</v>
       </c>
       <c r="F359" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9773,24 +9773,24 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>ACGL</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>Arch Capital Group</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D360" s="5" t="n">
-        <v>96.2</v>
+        <v>123.47</v>
       </c>
       <c r="E360" s="5" t="n">
-        <v>96.09</v>
+        <v>123.33</v>
       </c>
       <c r="F360" s="7" t="n">
         <v>-0.11</v>
@@ -9799,24 +9799,24 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>ACGL</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Arch Capital Group</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>123.47</v>
+        <v>96.2</v>
       </c>
       <c r="E361" s="5" t="n">
-        <v>123.33</v>
+        <v>96.09</v>
       </c>
       <c r="F361" s="7" t="n">
         <v>-0.11</v>
@@ -9825,24 +9825,24 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>CB</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>Chubb Limited</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D362" s="5" t="n">
-        <v>338.67</v>
+        <v>59.57</v>
       </c>
       <c r="E362" s="5" t="n">
-        <v>338.25</v>
+        <v>59.5</v>
       </c>
       <c r="F362" s="7" t="n">
         <v>-0.12</v>
@@ -9851,24 +9851,24 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>59.57</v>
+        <v>72.48</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>59.5</v>
+        <v>72.39</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-0.12</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CB</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Chubb Limited</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>72.48</v>
+        <v>338.67</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>72.39</v>
+        <v>338.25</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-0.12</v>
@@ -10033,24 +10033,24 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>JKHY</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D370" s="5" t="n">
-        <v>200.53</v>
+        <v>161.42</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>200.14</v>
+        <v>161.12</v>
       </c>
       <c r="F370" s="7" t="n">
         <v>-0.19</v>
@@ -10059,24 +10059,24 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>JKHY</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>161.42</v>
+        <v>200.53</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>161.12</v>
+        <v>200.14</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>-0.19</v>
@@ -10163,24 +10163,24 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>News Corp (Class B)</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>70.05</v>
+        <v>32.78</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>69.90000000000001</v>
+        <v>32.71</v>
       </c>
       <c r="F375" s="7" t="n">
         <v>-0.21</v>
@@ -10215,24 +10215,24 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class B)</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>32.78</v>
+        <v>253.05</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>32.71</v>
+        <v>252.53</v>
       </c>
       <c r="F377" s="7" t="n">
         <v>-0.21</v>
@@ -10241,24 +10241,24 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D378" s="5" t="n">
-        <v>253.05</v>
+        <v>70.05</v>
       </c>
       <c r="E378" s="5" t="n">
-        <v>252.53</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F378" s="7" t="n">
         <v>-0.21</v>
@@ -10267,24 +10267,24 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>Archer Daniels Midland</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>86.91</v>
+        <v>198.12</v>
       </c>
       <c r="E379" s="5" t="n">
-        <v>86.72</v>
+        <v>197.68</v>
       </c>
       <c r="F379" s="7" t="n">
         <v>-0.22</v>
@@ -10293,24 +10293,24 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Archer Daniels Midland</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D380" s="5" t="n">
-        <v>73.09</v>
+        <v>86.91</v>
       </c>
       <c r="E380" s="5" t="n">
-        <v>72.93000000000001</v>
+        <v>86.72</v>
       </c>
       <c r="F380" s="7" t="n">
         <v>-0.22</v>
@@ -10345,24 +10345,24 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D382" s="5" t="n">
-        <v>31.46</v>
+        <v>73.09</v>
       </c>
       <c r="E382" s="5" t="n">
-        <v>31.39</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="F382" s="7" t="n">
         <v>-0.22</v>
@@ -10371,24 +10371,24 @@
     <row r="383">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D383" s="5" t="n">
-        <v>198.12</v>
+        <v>31.46</v>
       </c>
       <c r="E383" s="5" t="n">
-        <v>197.68</v>
+        <v>31.39</v>
       </c>
       <c r="F383" s="7" t="n">
         <v>-0.22</v>
@@ -10449,24 +10449,24 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>174.33</v>
+        <v>136.65</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>173.92</v>
+        <v>136.32</v>
       </c>
       <c r="F386" s="7" t="n">
         <v>-0.24</v>
@@ -10475,24 +10475,24 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>136.65</v>
+        <v>174.33</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>136.32</v>
+        <v>173.92</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-0.24</v>
@@ -10527,24 +10527,24 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>46.25</v>
+        <v>56.73</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>46.13</v>
+        <v>56.58</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>-0.26</v>
@@ -10553,24 +10553,24 @@
     <row r="390">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D390" s="5" t="n">
-        <v>56.73</v>
+        <v>46.25</v>
       </c>
       <c r="E390" s="5" t="n">
-        <v>56.58</v>
+        <v>46.13</v>
       </c>
       <c r="F390" s="7" t="n">
         <v>-0.26</v>
@@ -10657,24 +10657,24 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>KMI</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>Kinder Morgan</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D394" s="5" t="n">
-        <v>30.95</v>
+        <v>88.55</v>
       </c>
       <c r="E394" s="5" t="n">
-        <v>30.86</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F394" s="7" t="n">
         <v>-0.29</v>
@@ -10683,24 +10683,24 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>KMI</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Kinder Morgan</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>266.35</v>
+        <v>30.95</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>265.58</v>
+        <v>30.86</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-0.29</v>
@@ -10709,24 +10709,24 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D396" s="5" t="n">
-        <v>88.55</v>
+        <v>266.35</v>
       </c>
       <c r="E396" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>265.58</v>
       </c>
       <c r="F396" s="7" t="n">
         <v>-0.29</v>
@@ -10787,24 +10787,24 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>AKAM</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>107.13</v>
+        <v>126.42</v>
       </c>
       <c r="E399" s="5" t="n">
-        <v>106.79</v>
+        <v>126.02</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>-0.32</v>
@@ -10813,24 +10813,24 @@
     <row r="400">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D400" s="5" t="n">
-        <v>126.42</v>
+        <v>677.9400000000001</v>
       </c>
       <c r="E400" s="5" t="n">
-        <v>126.02</v>
+        <v>675.74</v>
       </c>
       <c r="F400" s="7" t="n">
         <v>-0.32</v>
@@ -10865,24 +10865,24 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>AKAM</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Akamai Technologies</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D402" s="5" t="n">
-        <v>677.9400000000001</v>
+        <v>107.13</v>
       </c>
       <c r="E402" s="5" t="n">
-        <v>675.74</v>
+        <v>106.79</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>-0.32</v>
@@ -11229,24 +11229,24 @@
     <row r="416">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B416" s="4" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D416" s="5" t="n">
-        <v>99.22</v>
+        <v>285.78</v>
       </c>
       <c r="E416" s="5" t="n">
-        <v>98.73999999999999</v>
+        <v>284.4</v>
       </c>
       <c r="F416" s="7" t="n">
         <v>-0.48</v>
@@ -11255,24 +11255,24 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>285.78</v>
+        <v>99.22</v>
       </c>
       <c r="E417" s="5" t="n">
-        <v>284.4</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F417" s="7" t="n">
         <v>-0.48</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>43.39</v>
+        <v>129.55</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>43.16</v>
+        <v>128.86</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-0.53</v>
@@ -11411,24 +11411,24 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>129.55</v>
+        <v>43.39</v>
       </c>
       <c r="E423" s="5" t="n">
-        <v>128.86</v>
+        <v>43.16</v>
       </c>
       <c r="F423" s="7" t="n">
         <v>-0.53</v>
@@ -11515,24 +11515,24 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>TRGP</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Targa Resources</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>291.91</v>
+        <v>28.2</v>
       </c>
       <c r="E427" s="5" t="n">
-        <v>290.25</v>
+        <v>28.04</v>
       </c>
       <c r="F427" s="7" t="n">
         <v>-0.57</v>
@@ -11541,24 +11541,24 @@
     <row r="428">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>TRGP</t>
         </is>
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Targa Resources</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D428" s="5" t="n">
-        <v>28.2</v>
+        <v>291.91</v>
       </c>
       <c r="E428" s="5" t="n">
-        <v>28.04</v>
+        <v>290.25</v>
       </c>
       <c r="F428" s="7" t="n">
         <v>-0.57</v>
@@ -12425,24 +12425,24 @@
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D462" s="5" t="n">
-        <v>88.77</v>
+        <v>248.37</v>
       </c>
       <c r="E462" s="5" t="n">
-        <v>87.76000000000001</v>
+        <v>245.54</v>
       </c>
       <c r="F462" s="7" t="n">
         <v>-1.14</v>
@@ -12451,24 +12451,24 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D463" s="5" t="n">
-        <v>248.37</v>
+        <v>88.77</v>
       </c>
       <c r="E463" s="5" t="n">
-        <v>245.54</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="F463" s="7" t="n">
         <v>-1.14</v>
@@ -12529,24 +12529,24 @@
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D466" s="5" t="n">
-        <v>243.31</v>
+        <v>72.56</v>
       </c>
       <c r="E466" s="5" t="n">
-        <v>240.32</v>
+        <v>71.67</v>
       </c>
       <c r="F466" s="7" t="n">
         <v>-1.23</v>
@@ -12555,24 +12555,24 @@
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D467" s="5" t="n">
-        <v>72.56</v>
+        <v>243.31</v>
       </c>
       <c r="E467" s="5" t="n">
-        <v>71.67</v>
+        <v>240.32</v>
       </c>
       <c r="F467" s="7" t="n">
         <v>-1.23</v>
@@ -13075,24 +13075,24 @@
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Bunge Global</t>
         </is>
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D487" s="5" t="n">
-        <v>84.51000000000001</v>
+        <v>124.59</v>
       </c>
       <c r="E487" s="5" t="n">
-        <v>83.03</v>
+        <v>122.41</v>
       </c>
       <c r="F487" s="7" t="n">
         <v>-1.75</v>
@@ -13101,24 +13101,24 @@
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>Fortinet</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D488" s="5" t="n">
-        <v>158.85</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="E488" s="5" t="n">
-        <v>156.07</v>
+        <v>83.03</v>
       </c>
       <c r="F488" s="7" t="n">
         <v>-1.75</v>
@@ -13127,24 +13127,24 @@
     <row r="489">
       <c r="A489" s="4" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>Bunge Global</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D489" s="5" t="n">
-        <v>124.59</v>
+        <v>158.85</v>
       </c>
       <c r="E489" s="5" t="n">
-        <v>122.41</v>
+        <v>156.07</v>
       </c>
       <c r="F489" s="7" t="n">
         <v>-1.75</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 03 close to Sep 11 close  |  503 companies  |  updated 2026-09-12 07:27</t>
+          <t>Sep 03 close to Sep 11 close  |  503 companies  |  updated 2026-09-13 07:48</t>
         </is>
       </c>
     </row>
@@ -15275,12 +15275,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -15289,16 +15289,16 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>81.08</v>
+        <v>186.17</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>83.20999999999999</v>
+        <v>191.06</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>83.20999999999999</v>
+        <v>191.06</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>79.84</v>
+        <v>182.53</v>
       </c>
       <c r="H54" s="6" t="n">
         <v>2.63</v>
@@ -15307,12 +15307,12 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -15321,16 +15321,16 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>186.17</v>
+        <v>81.08</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>191.06</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>191.06</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>182.53</v>
+        <v>79.84</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>2.63</v>
@@ -16139,12 +16139,12 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>EMR</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -16153,16 +16153,16 @@
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>38.73</v>
+        <v>150.21</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>39.24</v>
+        <v>152.19</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>39.62</v>
+        <v>152.82</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>38.67</v>
+        <v>148.37</v>
       </c>
       <c r="H81" s="6" t="n">
         <v>1.32</v>
@@ -16171,12 +16171,12 @@
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>EMR</t>
+          <t>LUV</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -16185,16 +16185,16 @@
         </is>
       </c>
       <c r="D82" s="5" t="n">
-        <v>150.21</v>
+        <v>38.73</v>
       </c>
       <c r="E82" s="5" t="n">
-        <v>152.19</v>
+        <v>39.24</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>152.82</v>
+        <v>39.62</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>148.37</v>
+        <v>38.67</v>
       </c>
       <c r="H82" s="6" t="n">
         <v>1.32</v>
@@ -18411,30 +18411,30 @@
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D152" s="5" t="n">
-        <v>41.66</v>
+        <v>445.19</v>
       </c>
       <c r="E152" s="5" t="n">
-        <v>41.41</v>
+        <v>442.52</v>
       </c>
       <c r="F152" s="5" t="n">
-        <v>41.9</v>
+        <v>447.9</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>41.39</v>
+        <v>439.83</v>
       </c>
       <c r="H152" s="7" t="n">
         <v>-0.6</v>
@@ -18443,30 +18443,30 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Trane Technologies</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>445.19</v>
+        <v>41.66</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>442.52</v>
+        <v>41.41</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>447.9</v>
+        <v>41.9</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>439.83</v>
+        <v>41.39</v>
       </c>
       <c r="H153" s="7" t="n">
         <v>-0.6</v>
@@ -18891,30 +18891,30 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>USB</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>68</v>
+        <v>63.53</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>67.26000000000001</v>
+        <v>62.84</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>68.61</v>
+        <v>63.53</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>67.25</v>
+        <v>62.11</v>
       </c>
       <c r="H167" s="7" t="n">
         <v>-1.09</v>
@@ -18923,30 +18923,30 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>USB</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>63.53</v>
+        <v>68</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>62.84</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>63.53</v>
+        <v>68.61</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>62.11</v>
+        <v>67.25</v>
       </c>
       <c r="H168" s="7" t="n">
         <v>-1.09</v>
@@ -19147,30 +19147,30 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>342.48</v>
+        <v>262.47</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>338.5</v>
+        <v>259.43</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>342.48</v>
+        <v>262.47</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>330.65</v>
+        <v>255.46</v>
       </c>
       <c r="H175" s="7" t="n">
         <v>-1.16</v>
@@ -19211,30 +19211,30 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>262.47</v>
+        <v>342.48</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>259.43</v>
+        <v>338.5</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>262.47</v>
+        <v>342.48</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>255.46</v>
+        <v>330.65</v>
       </c>
       <c r="H177" s="7" t="n">
         <v>-1.16</v>
@@ -19243,30 +19243,30 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>HBAN</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Huntington Bancshares</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>17.06</v>
+        <v>108.42</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>16.86</v>
+        <v>107.15</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>17.06</v>
+        <v>108.42</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>16.63</v>
+        <v>105.73</v>
       </c>
       <c r="H178" s="7" t="n">
         <v>-1.17</v>
@@ -19275,30 +19275,30 @@
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>HBAN</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Huntington Bancshares</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D179" s="5" t="n">
-        <v>108.42</v>
+        <v>17.06</v>
       </c>
       <c r="E179" s="5" t="n">
-        <v>107.15</v>
+        <v>16.86</v>
       </c>
       <c r="F179" s="5" t="n">
-        <v>108.42</v>
+        <v>17.06</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>105.73</v>
+        <v>16.63</v>
       </c>
       <c r="H179" s="7" t="n">
         <v>-1.17</v>
@@ -19467,30 +19467,30 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>271.65</v>
+        <v>217.15</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>268.16</v>
+        <v>214.38</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>271.65</v>
+        <v>217.72</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>263.99</v>
+        <v>212.66</v>
       </c>
       <c r="H185" s="7" t="n">
         <v>-1.28</v>
@@ -19499,30 +19499,30 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>217.15</v>
+        <v>271.65</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>214.38</v>
+        <v>268.16</v>
       </c>
       <c r="F186" s="5" t="n">
-        <v>217.72</v>
+        <v>271.65</v>
       </c>
       <c r="G186" s="5" t="n">
-        <v>212.66</v>
+        <v>263.99</v>
       </c>
       <c r="H186" s="7" t="n">
         <v>-1.28</v>
@@ -19659,30 +19659,30 @@
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>ALLE</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D191" s="5" t="n">
-        <v>106.41</v>
+        <v>155.56</v>
       </c>
       <c r="E191" s="5" t="n">
-        <v>104.9</v>
+        <v>153.35</v>
       </c>
       <c r="F191" s="5" t="n">
-        <v>106.73</v>
+        <v>157.12</v>
       </c>
       <c r="G191" s="5" t="n">
-        <v>104.9</v>
+        <v>151.27</v>
       </c>
       <c r="H191" s="7" t="n">
         <v>-1.42</v>
@@ -19691,30 +19691,30 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>ALLE</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>155.56</v>
+        <v>106.41</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>153.35</v>
+        <v>104.9</v>
       </c>
       <c r="F192" s="5" t="n">
-        <v>157.12</v>
+        <v>106.73</v>
       </c>
       <c r="G192" s="5" t="n">
-        <v>151.27</v>
+        <v>104.9</v>
       </c>
       <c r="H192" s="7" t="n">
         <v>-1.42</v>
@@ -20491,30 +20491,30 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>CI</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Cigna</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>286.26</v>
+        <v>73.81</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>280.76</v>
+        <v>72.39</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>286.26</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="G217" s="5" t="n">
-        <v>275.83</v>
+        <v>72.39</v>
       </c>
       <c r="H217" s="7" t="n">
         <v>-1.92</v>
@@ -20523,30 +20523,30 @@
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D218" s="5" t="n">
-        <v>73.81</v>
+        <v>286.26</v>
       </c>
       <c r="E218" s="5" t="n">
-        <v>72.39</v>
+        <v>280.76</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>74.23999999999999</v>
+        <v>286.26</v>
       </c>
       <c r="G218" s="5" t="n">
-        <v>72.39</v>
+        <v>275.83</v>
       </c>
       <c r="H218" s="7" t="n">
         <v>-1.92</v>
@@ -20683,30 +20683,30 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>American International Group</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>76.86</v>
+        <v>357.5</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>75.33</v>
+        <v>350.37</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>76.86</v>
+        <v>362.74</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>74.68000000000001</v>
+        <v>344.01</v>
       </c>
       <c r="H223" s="7" t="n">
         <v>-1.99</v>
@@ -20715,30 +20715,30 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>American International Group</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>357.5</v>
+        <v>76.86</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>350.37</v>
+        <v>75.33</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>362.74</v>
+        <v>76.86</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>344.01</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="H224" s="7" t="n">
         <v>-1.99</v>
@@ -20971,30 +20971,30 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Consolidated Edison</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D232" s="5" t="n">
-        <v>108.75</v>
+        <v>99.23</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>106.46</v>
+        <v>97.14</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>108.75</v>
+        <v>99.23</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>106.46</v>
+        <v>95.5</v>
       </c>
       <c r="H232" s="7" t="n">
         <v>-2.11</v>
@@ -21003,30 +21003,30 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Consolidated Edison</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>99.23</v>
+        <v>108.75</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>97.14</v>
+        <v>106.46</v>
       </c>
       <c r="F233" s="5" t="n">
-        <v>99.23</v>
+        <v>108.75</v>
       </c>
       <c r="G233" s="5" t="n">
-        <v>95.5</v>
+        <v>106.46</v>
       </c>
       <c r="H233" s="7" t="n">
         <v>-2.11</v>
@@ -21323,30 +21323,30 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Welltower</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>241.12</v>
+        <v>384.19</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>235.62</v>
+        <v>375.44</v>
       </c>
       <c r="F243" s="5" t="n">
-        <v>241.12</v>
+        <v>384.19</v>
       </c>
       <c r="G243" s="5" t="n">
-        <v>235.62</v>
+        <v>374.83</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>-2.28</v>
@@ -21355,30 +21355,30 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Welltower</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D244" s="5" t="n">
-        <v>384.19</v>
+        <v>241.12</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>375.44</v>
+        <v>235.62</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>384.19</v>
+        <v>241.12</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>374.83</v>
+        <v>235.62</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>-2.28</v>
@@ -21579,30 +21579,30 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>68.02</v>
+        <v>57.41</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>66.42</v>
+        <v>56.06</v>
       </c>
       <c r="F251" s="5" t="n">
-        <v>68.02</v>
+        <v>57.51</v>
       </c>
       <c r="G251" s="5" t="n">
-        <v>64.06</v>
+        <v>56.01</v>
       </c>
       <c r="H251" s="7" t="n">
         <v>-2.35</v>
@@ -21611,30 +21611,30 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>57.41</v>
+        <v>68.02</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>56.06</v>
+        <v>66.42</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>57.51</v>
+        <v>68.02</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>56.01</v>
+        <v>64.06</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>-2.35</v>
@@ -21867,30 +21867,30 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Steel Dynamics</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>246.03</v>
+        <v>207.63</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>239.79</v>
+        <v>202.36</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>246.03</v>
+        <v>209.61</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>237.08</v>
+        <v>202.18</v>
       </c>
       <c r="H260" s="7" t="n">
         <v>-2.54</v>
@@ -21899,30 +21899,30 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Steel Dynamics</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>16.94</v>
+        <v>246.03</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>16.51</v>
+        <v>239.79</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>16.94</v>
+        <v>246.03</v>
       </c>
       <c r="G261" s="5" t="n">
-        <v>16.38</v>
+        <v>237.08</v>
       </c>
       <c r="H261" s="7" t="n">
         <v>-2.54</v>
@@ -21931,30 +21931,30 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>207.63</v>
+        <v>16.94</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>202.36</v>
+        <v>16.51</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>209.61</v>
+        <v>16.94</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>202.18</v>
+        <v>16.38</v>
       </c>
       <c r="H262" s="7" t="n">
         <v>-2.54</v>
@@ -21963,12 +21963,12 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -21977,16 +21977,16 @@
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>118.36</v>
+        <v>140</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>115.28</v>
+        <v>136.36</v>
       </c>
       <c r="F263" s="5" t="n">
-        <v>118.36</v>
+        <v>140</v>
       </c>
       <c r="G263" s="5" t="n">
-        <v>114.47</v>
+        <v>135.66</v>
       </c>
       <c r="H263" s="7" t="n">
         <v>-2.6</v>
@@ -21995,12 +21995,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -22009,16 +22009,16 @@
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>140</v>
+        <v>118.36</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>136.36</v>
+        <v>115.28</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>140</v>
+        <v>118.36</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>135.66</v>
+        <v>114.47</v>
       </c>
       <c r="H264" s="7" t="n">
         <v>-2.6</v>
@@ -22187,30 +22187,30 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Deere &amp; Company</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>694.41</v>
+        <v>332.26</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>675.74</v>
+        <v>323.31</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>694.41</v>
+        <v>333.71</v>
       </c>
       <c r="G270" s="5" t="n">
-        <v>675.74</v>
+        <v>317.44</v>
       </c>
       <c r="H270" s="7" t="n">
         <v>-2.69</v>
@@ -22219,30 +22219,30 @@
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Deere &amp; Company</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D271" s="5" t="n">
-        <v>332.26</v>
+        <v>694.41</v>
       </c>
       <c r="E271" s="5" t="n">
-        <v>323.31</v>
+        <v>675.74</v>
       </c>
       <c r="F271" s="5" t="n">
-        <v>333.71</v>
+        <v>694.41</v>
       </c>
       <c r="G271" s="5" t="n">
-        <v>317.44</v>
+        <v>675.74</v>
       </c>
       <c r="H271" s="7" t="n">
         <v>-2.69</v>
@@ -22251,30 +22251,30 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>365.87</v>
+        <v>259.63</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>355.9</v>
+        <v>252.53</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>365.87</v>
+        <v>259.63</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>352.67</v>
+        <v>252.53</v>
       </c>
       <c r="H272" s="7" t="n">
         <v>-2.73</v>
@@ -22283,30 +22283,30 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>259.63</v>
+        <v>365.87</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>252.53</v>
+        <v>355.9</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>259.63</v>
+        <v>365.87</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>252.53</v>
+        <v>352.67</v>
       </c>
       <c r="H273" s="7" t="n">
         <v>-2.73</v>
@@ -22347,12 +22347,12 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -22361,16 +22361,16 @@
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>35.71</v>
+        <v>59.08</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>34.73</v>
+        <v>57.46</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>35.86</v>
+        <v>59.71</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>34.54</v>
+        <v>56.64</v>
       </c>
       <c r="H275" s="7" t="n">
         <v>-2.74</v>
@@ -22379,12 +22379,12 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
@@ -22393,16 +22393,16 @@
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>59.08</v>
+        <v>35.71</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>57.46</v>
+        <v>34.73</v>
       </c>
       <c r="F276" s="5" t="n">
-        <v>59.71</v>
+        <v>35.86</v>
       </c>
       <c r="G276" s="5" t="n">
-        <v>56.64</v>
+        <v>34.54</v>
       </c>
       <c r="H276" s="7" t="n">
         <v>-2.74</v>
@@ -22539,12 +22539,12 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -22553,16 +22553,16 @@
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>174.72</v>
+        <v>585.71</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>169.8</v>
+        <v>569.1900000000001</v>
       </c>
       <c r="F281" s="5" t="n">
-        <v>174.72</v>
+        <v>585.71</v>
       </c>
       <c r="G281" s="5" t="n">
-        <v>169.14</v>
+        <v>565.37</v>
       </c>
       <c r="H281" s="7" t="n">
         <v>-2.82</v>
@@ -22571,12 +22571,12 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
@@ -22585,16 +22585,16 @@
         </is>
       </c>
       <c r="D282" s="5" t="n">
-        <v>585.71</v>
+        <v>174.72</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>569.1900000000001</v>
+        <v>169.8</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>585.71</v>
+        <v>174.72</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>565.37</v>
+        <v>169.14</v>
       </c>
       <c r="H282" s="7" t="n">
         <v>-2.82</v>
@@ -22827,30 +22827,30 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>PPL Corporation</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D290" s="5" t="n">
-        <v>35.11</v>
+        <v>128.56</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>34.08</v>
+        <v>124.79</v>
       </c>
       <c r="F290" s="5" t="n">
-        <v>35.11</v>
+        <v>128.56</v>
       </c>
       <c r="G290" s="5" t="n">
-        <v>34.08</v>
+        <v>124.48</v>
       </c>
       <c r="H290" s="7" t="n">
         <v>-2.93</v>
@@ -22859,30 +22859,30 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>PPL Corporation</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>128.56</v>
+        <v>35.11</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>124.79</v>
+        <v>34.08</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>128.56</v>
+        <v>35.11</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>124.48</v>
+        <v>34.08</v>
       </c>
       <c r="H291" s="7" t="n">
         <v>-2.93</v>
@@ -23147,30 +23147,30 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D300" s="5" t="n">
-        <v>44.53</v>
+        <v>2968.04</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>43.16</v>
+        <v>2876.75</v>
       </c>
       <c r="F300" s="5" t="n">
-        <v>44.53</v>
+        <v>2983.29</v>
       </c>
       <c r="G300" s="5" t="n">
-        <v>43.16</v>
+        <v>2876.75</v>
       </c>
       <c r="H300" s="7" t="n">
         <v>-3.08</v>
@@ -23179,30 +23179,30 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>2968.04</v>
+        <v>44.53</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>2876.75</v>
+        <v>43.16</v>
       </c>
       <c r="F301" s="5" t="n">
-        <v>2983.29</v>
+        <v>44.53</v>
       </c>
       <c r="G301" s="5" t="n">
-        <v>2876.75</v>
+        <v>43.16</v>
       </c>
       <c r="H301" s="7" t="n">
         <v>-3.08</v>
@@ -23211,30 +23211,30 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>103.5</v>
+        <v>23.48</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>100.28</v>
+        <v>22.75</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>103.5</v>
+        <v>23.51</v>
       </c>
       <c r="G302" s="5" t="n">
-        <v>99.22</v>
+        <v>22.47</v>
       </c>
       <c r="H302" s="7" t="n">
         <v>-3.11</v>
@@ -23243,30 +23243,30 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>23.48</v>
+        <v>103.5</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>22.75</v>
+        <v>100.28</v>
       </c>
       <c r="F303" s="5" t="n">
-        <v>23.51</v>
+        <v>103.5</v>
       </c>
       <c r="G303" s="5" t="n">
-        <v>22.47</v>
+        <v>99.22</v>
       </c>
       <c r="H303" s="7" t="n">
         <v>-3.11</v>
@@ -23275,12 +23275,12 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>SBAC</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -23289,16 +23289,16 @@
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>191.52</v>
+        <v>211.52</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>185.47</v>
+        <v>204.83</v>
       </c>
       <c r="F304" s="5" t="n">
-        <v>191.52</v>
+        <v>211.88</v>
       </c>
       <c r="G304" s="5" t="n">
-        <v>181.42</v>
+        <v>204.53</v>
       </c>
       <c r="H304" s="7" t="n">
         <v>-3.16</v>
@@ -23307,30 +23307,30 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>SBAC</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>131.13</v>
+        <v>191.52</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>126.99</v>
+        <v>185.47</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>131.59</v>
+        <v>191.52</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>126.99</v>
+        <v>181.42</v>
       </c>
       <c r="H305" s="7" t="n">
         <v>-3.16</v>
@@ -23339,30 +23339,30 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>211.52</v>
+        <v>131.13</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>204.83</v>
+        <v>126.99</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>211.88</v>
+        <v>131.59</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>204.53</v>
+        <v>126.99</v>
       </c>
       <c r="H306" s="7" t="n">
         <v>-3.16</v>
@@ -23435,30 +23435,30 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>185.75</v>
+        <v>123.2</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>179.79</v>
+        <v>119.24</v>
       </c>
       <c r="F309" s="5" t="n">
-        <v>187.01</v>
+        <v>123.2</v>
       </c>
       <c r="G309" s="5" t="n">
-        <v>179.79</v>
+        <v>117.59</v>
       </c>
       <c r="H309" s="7" t="n">
         <v>-3.21</v>
@@ -23467,30 +23467,30 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>123.2</v>
+        <v>185.75</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>119.24</v>
+        <v>179.79</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>123.2</v>
+        <v>187.01</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>117.59</v>
+        <v>179.79</v>
       </c>
       <c r="H310" s="7" t="n">
         <v>-3.21</v>
@@ -23563,30 +23563,30 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>75.40000000000001</v>
+        <v>224.51</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>72.93000000000001</v>
+        <v>217.15</v>
       </c>
       <c r="F313" s="5" t="n">
-        <v>76.36</v>
+        <v>224.51</v>
       </c>
       <c r="G313" s="5" t="n">
-        <v>72.93000000000001</v>
+        <v>210.73</v>
       </c>
       <c r="H313" s="7" t="n">
         <v>-3.28</v>
@@ -23595,30 +23595,30 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>224.51</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>217.15</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>224.51</v>
+        <v>76.36</v>
       </c>
       <c r="G314" s="5" t="n">
-        <v>210.73</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="H314" s="7" t="n">
         <v>-3.28</v>
@@ -24075,30 +24075,30 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>IQVIA</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>271.62</v>
+        <v>61.74</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>261.77</v>
+        <v>59.5</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>271.62</v>
+        <v>61.74</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>256.98</v>
+        <v>59.5</v>
       </c>
       <c r="H329" s="7" t="n">
         <v>-3.63</v>
@@ -24107,30 +24107,30 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>IQV</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>IQVIA</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>61.74</v>
+        <v>271.62</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>59.5</v>
+        <v>261.77</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>61.74</v>
+        <v>271.62</v>
       </c>
       <c r="G330" s="5" t="n">
-        <v>59.5</v>
+        <v>256.98</v>
       </c>
       <c r="H330" s="7" t="n">
         <v>-3.63</v>
@@ -24491,30 +24491,30 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D342" s="5" t="n">
-        <v>91.77</v>
+        <v>1159.6</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>1115.7</v>
       </c>
       <c r="F342" s="5" t="n">
-        <v>92.54000000000001</v>
+        <v>1159.6</v>
       </c>
       <c r="G342" s="5" t="n">
-        <v>87.02</v>
+        <v>1115.7</v>
       </c>
       <c r="H342" s="7" t="n">
         <v>-3.79</v>
@@ -24555,30 +24555,30 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>1159.6</v>
+        <v>91.77</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>1115.7</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="F344" s="5" t="n">
-        <v>1159.6</v>
+        <v>92.54000000000001</v>
       </c>
       <c r="G344" s="5" t="n">
-        <v>1115.7</v>
+        <v>87.02</v>
       </c>
       <c r="H344" s="7" t="n">
         <v>-3.79</v>
@@ -24587,12 +24587,12 @@
     <row r="345">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Huntington Ingalls Industries</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -24601,16 +24601,16 @@
         </is>
       </c>
       <c r="D345" s="5" t="n">
-        <v>290.73</v>
+        <v>324.31</v>
       </c>
       <c r="E345" s="5" t="n">
-        <v>279.69</v>
+        <v>311.99</v>
       </c>
       <c r="F345" s="5" t="n">
-        <v>290.73</v>
+        <v>324.31</v>
       </c>
       <c r="G345" s="5" t="n">
-        <v>279.69</v>
+        <v>309.19</v>
       </c>
       <c r="H345" s="7" t="n">
         <v>-3.8</v>
@@ -24619,12 +24619,12 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Huntington Ingalls Industries</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
@@ -24633,16 +24633,16 @@
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>324.31</v>
+        <v>290.73</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>311.99</v>
+        <v>279.69</v>
       </c>
       <c r="F346" s="5" t="n">
-        <v>324.31</v>
+        <v>290.73</v>
       </c>
       <c r="G346" s="5" t="n">
-        <v>309.19</v>
+        <v>279.69</v>
       </c>
       <c r="H346" s="7" t="n">
         <v>-3.8</v>
@@ -25003,30 +25003,30 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BLK</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Eversource Energy</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>71.47</v>
+        <v>1126.15</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>68.52</v>
+        <v>1079.65</v>
       </c>
       <c r="F358" s="5" t="n">
-        <v>71.48999999999999</v>
+        <v>1126.15</v>
       </c>
       <c r="G358" s="5" t="n">
-        <v>68.52</v>
+        <v>1062.4</v>
       </c>
       <c r="H358" s="7" t="n">
         <v>-4.13</v>
@@ -25035,30 +25035,30 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>BLK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Eversource Energy</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>1126.15</v>
+        <v>71.47</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>1079.65</v>
+        <v>68.52</v>
       </c>
       <c r="F359" s="5" t="n">
-        <v>1126.15</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="G359" s="5" t="n">
-        <v>1062.4</v>
+        <v>68.52</v>
       </c>
       <c r="H359" s="7" t="n">
         <v>-4.13</v>
@@ -25067,30 +25067,30 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D360" s="5" t="n">
-        <v>110.88</v>
+        <v>177.49</v>
       </c>
       <c r="E360" s="5" t="n">
-        <v>106.29</v>
+        <v>170.15</v>
       </c>
       <c r="F360" s="5" t="n">
-        <v>110.88</v>
+        <v>177.49</v>
       </c>
       <c r="G360" s="5" t="n">
-        <v>106.29</v>
+        <v>169.99</v>
       </c>
       <c r="H360" s="7" t="n">
         <v>-4.14</v>
@@ -25099,30 +25099,30 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>177.49</v>
+        <v>110.88</v>
       </c>
       <c r="E361" s="5" t="n">
-        <v>170.15</v>
+        <v>106.29</v>
       </c>
       <c r="F361" s="5" t="n">
-        <v>177.49</v>
+        <v>110.88</v>
       </c>
       <c r="G361" s="5" t="n">
-        <v>169.99</v>
+        <v>106.29</v>
       </c>
       <c r="H361" s="7" t="n">
         <v>-4.14</v>
@@ -26635,12 +26635,12 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>LII</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>A. O. Smith</t>
+          <t>Lennox International</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
@@ -26649,16 +26649,16 @@
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>60.53</v>
+        <v>386.08</v>
       </c>
       <c r="E409" s="5" t="n">
-        <v>57.39</v>
+        <v>366.04</v>
       </c>
       <c r="F409" s="5" t="n">
-        <v>60.53</v>
+        <v>390.53</v>
       </c>
       <c r="G409" s="5" t="n">
-        <v>56.71</v>
+        <v>366.04</v>
       </c>
       <c r="H409" s="7" t="n">
         <v>-5.19</v>
@@ -26667,12 +26667,12 @@
     <row r="410">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>LII</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>Lennox International</t>
+          <t>A. O. Smith</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
@@ -26681,16 +26681,16 @@
         </is>
       </c>
       <c r="D410" s="5" t="n">
-        <v>386.08</v>
+        <v>60.53</v>
       </c>
       <c r="E410" s="5" t="n">
-        <v>366.04</v>
+        <v>57.39</v>
       </c>
       <c r="F410" s="5" t="n">
-        <v>390.53</v>
+        <v>60.53</v>
       </c>
       <c r="G410" s="5" t="n">
-        <v>366.04</v>
+        <v>56.71</v>
       </c>
       <c r="H410" s="7" t="n">
         <v>-5.19</v>
@@ -26987,30 +26987,30 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>148.74</v>
+        <v>220.5</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>140.51</v>
+        <v>208.3</v>
       </c>
       <c r="F420" s="5" t="n">
-        <v>148.74</v>
+        <v>220.5</v>
       </c>
       <c r="G420" s="5" t="n">
-        <v>137.99</v>
+        <v>207.11</v>
       </c>
       <c r="H420" s="7" t="n">
         <v>-5.53</v>
@@ -27019,30 +27019,30 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>220.5</v>
+        <v>148.74</v>
       </c>
       <c r="E421" s="5" t="n">
-        <v>208.3</v>
+        <v>140.51</v>
       </c>
       <c r="F421" s="5" t="n">
-        <v>220.5</v>
+        <v>148.74</v>
       </c>
       <c r="G421" s="5" t="n">
-        <v>207.11</v>
+        <v>137.99</v>
       </c>
       <c r="H421" s="7" t="n">
         <v>-5.53</v>
@@ -27051,30 +27051,30 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>75.95999999999999</v>
+        <v>248.61</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>71.67</v>
+        <v>234.57</v>
       </c>
       <c r="F422" s="5" t="n">
-        <v>75.95999999999999</v>
+        <v>248.61</v>
       </c>
       <c r="G422" s="5" t="n">
-        <v>71.08</v>
+        <v>234.57</v>
       </c>
       <c r="H422" s="7" t="n">
         <v>-5.65</v>
@@ -27083,30 +27083,30 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>248.61</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="E423" s="5" t="n">
-        <v>234.57</v>
+        <v>71.67</v>
       </c>
       <c r="F423" s="5" t="n">
-        <v>248.61</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="G423" s="5" t="n">
-        <v>234.57</v>
+        <v>71.08</v>
       </c>
       <c r="H423" s="7" t="n">
         <v>-5.65</v>
@@ -27179,30 +27179,30 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>128.51</v>
+        <v>60.02</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>121.14</v>
+        <v>56.58</v>
       </c>
       <c r="F426" s="5" t="n">
-        <v>128.51</v>
+        <v>60.21</v>
       </c>
       <c r="G426" s="5" t="n">
-        <v>121.07</v>
+        <v>56.58</v>
       </c>
       <c r="H426" s="7" t="n">
         <v>-5.73</v>
@@ -27211,30 +27211,30 @@
     <row r="427">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D427" s="5" t="n">
-        <v>60.02</v>
+        <v>128.51</v>
       </c>
       <c r="E427" s="5" t="n">
-        <v>56.58</v>
+        <v>121.14</v>
       </c>
       <c r="F427" s="5" t="n">
-        <v>60.21</v>
+        <v>128.51</v>
       </c>
       <c r="G427" s="5" t="n">
-        <v>56.58</v>
+        <v>121.07</v>
       </c>
       <c r="H427" s="7" t="n">
         <v>-5.73</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 10-&gt;Sep 11) and rolling 5-day  |  updated 2026-09-12 07:27</t>
+          <t>Daily (Sep 10-&gt;Sep 11) and rolling 5-day  |  updated 2026-09-13 07:48</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 10 close to Sep 11 close  |  503 companies  |  updated 2026-09-13 07:48</t>
+          <t>Sep 10 close to Sep 11 close  |  503 companies  |  updated 2026-09-14 08:19</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 03 close to Sep 11 close  |  503 companies  |  updated 2026-09-13 07:48</t>
+          <t>Sep 03 close to Sep 11 close  |  503 companies  |  updated 2026-09-14 08:19</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 10-&gt;Sep 11) and rolling 5-day  |  updated 2026-09-13 07:48</t>
+          <t>Daily (Sep 10-&gt;Sep 11) and rolling 5-day  |  updated 2026-09-14 08:19</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 24 close to Sep 25 close  |  503 companies  |  updated 2026-09-26 08:07</t>
+          <t>Sep 24 close to Sep 25 close  |  503 companies  |  updated 2026-09-27 08:43</t>
         </is>
       </c>
     </row>
@@ -1349,24 +1349,24 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>SHW</t>
+          <t>LUV</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>320.4</v>
+        <v>41.55</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>329.1</v>
+        <v>42.68</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>2.72</v>
@@ -1375,24 +1375,24 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>LUV</t>
+          <t>SHW</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>41.55</v>
+        <v>320.4</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>42.68</v>
+        <v>329.1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>2.72</v>
@@ -1505,24 +1505,24 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>GM</t>
+          <t>BDX</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>General Motors</t>
+          <t>Becton Dickinson</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>80.56999999999999</v>
+        <v>179.23</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>82.63</v>
+        <v>183.82</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>2.56</v>
@@ -1531,24 +1531,24 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>General Motors</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>179.23</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>183.82</v>
+        <v>82.63</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>2.56</v>
@@ -1739,12 +1739,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>MAS</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -1753,10 +1753,10 @@
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>67.31</v>
+        <v>319.78</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>68.84999999999999</v>
+        <v>327.09</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>2.29</v>
@@ -1765,12 +1765,12 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>MAS</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>319.78</v>
+        <v>67.31</v>
       </c>
       <c r="E52" s="5" t="n">
-        <v>327.09</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>2.29</v>
@@ -2077,12 +2077,12 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>183.66</v>
+        <v>92.05</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>187.46</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>2.07</v>
@@ -2103,12 +2103,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>92.05</v>
+        <v>183.66</v>
       </c>
       <c r="E65" s="5" t="n">
-        <v>93.95999999999999</v>
+        <v>187.46</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>2.07</v>
@@ -2207,12 +2207,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>JBL</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Jabil</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>122.31</v>
+        <v>310.69</v>
       </c>
       <c r="E69" s="5" t="n">
-        <v>124.69</v>
+        <v>316.74</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>1.95</v>
@@ -2233,12 +2233,12 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>JBL</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Jabil</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>310.69</v>
+        <v>122.31</v>
       </c>
       <c r="E70" s="5" t="n">
-        <v>316.74</v>
+        <v>124.69</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>1.95</v>
@@ -2493,24 +2493,24 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>SWKS</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Skyworks Solutions</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D80" s="5" t="n">
-        <v>87.81</v>
+        <v>74.78</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>89.34</v>
+        <v>76.08</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>1.74</v>
@@ -2519,24 +2519,24 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>SWKS</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
-        <v>74.78</v>
+        <v>87.81</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>76.08</v>
+        <v>89.34</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>1.74</v>
@@ -2571,12 +2571,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>132.1</v>
+        <v>202.17</v>
       </c>
       <c r="E83" s="5" t="n">
-        <v>134.28</v>
+        <v>205.5</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>1.65</v>
@@ -2597,24 +2597,24 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>AOS</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>A. O. Smith</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D84" s="5" t="n">
-        <v>202.17</v>
+        <v>57.7</v>
       </c>
       <c r="E84" s="5" t="n">
-        <v>205.5</v>
+        <v>58.65</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>1.65</v>
@@ -2623,24 +2623,24 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>AOS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>A. O. Smith</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
-        <v>57.7</v>
+        <v>132.1</v>
       </c>
       <c r="E85" s="5" t="n">
-        <v>58.65</v>
+        <v>134.28</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>1.65</v>
@@ -2935,24 +2935,24 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Franklin Resources</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>32.55</v>
+        <v>450.31</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>33.02</v>
+        <v>456.81</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>1.44</v>
@@ -2961,24 +2961,24 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Franklin Resources</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
-        <v>450.31</v>
+        <v>32.55</v>
       </c>
       <c r="E98" s="5" t="n">
-        <v>456.81</v>
+        <v>33.02</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>1.44</v>
@@ -2987,24 +2987,24 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Williams-Sonoma, Inc.</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
-        <v>399.52</v>
+        <v>228.66</v>
       </c>
       <c r="E99" s="5" t="n">
-        <v>405.18</v>
+        <v>231.9</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>1.42</v>
@@ -3013,24 +3013,24 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Williams-Sonoma, Inc.</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D100" s="5" t="n">
-        <v>228.66</v>
+        <v>399.52</v>
       </c>
       <c r="E100" s="5" t="n">
-        <v>231.9</v>
+        <v>405.18</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>1.42</v>
@@ -3065,24 +3065,24 @@
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>GPN</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D102" s="5" t="n">
-        <v>1753.62</v>
+        <v>85.31</v>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1777.8</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>1.38</v>
@@ -3091,24 +3091,24 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>GPN</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Global Payments</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>85.31</v>
+        <v>1753.62</v>
       </c>
       <c r="E103" s="5" t="n">
-        <v>86.48999999999999</v>
+        <v>1777.8</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>1.38</v>
@@ -3117,12 +3117,12 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Albemarle Corporation</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>241.7</v>
+        <v>108.25</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>245</v>
+        <v>109.73</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>1.37</v>
@@ -3143,24 +3143,24 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Carvana</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>64.18000000000001</v>
+        <v>241.7</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>65.06</v>
+        <v>245</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>1.37</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Albemarle Corporation</t>
+          <t>Carvana</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>108.25</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>109.73</v>
+        <v>65.06</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>1.37</v>
@@ -3221,24 +3221,24 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>929.04</v>
+        <v>751.96</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>941.65</v>
+        <v>762.21</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>1.36</v>
@@ -3247,24 +3247,24 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>751.96</v>
+        <v>929.04</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>762.21</v>
+        <v>941.65</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>1.36</v>
@@ -3273,24 +3273,24 @@
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D110" s="5" t="n">
-        <v>229.38</v>
+        <v>365.1</v>
       </c>
       <c r="E110" s="5" t="n">
-        <v>232.48</v>
+        <v>370.04</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>1.35</v>
@@ -3299,24 +3299,24 @@
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D111" s="5" t="n">
-        <v>365.1</v>
+        <v>229.38</v>
       </c>
       <c r="E111" s="5" t="n">
-        <v>370.04</v>
+        <v>232.48</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>1.35</v>
@@ -3377,12 +3377,12 @@
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="D114" s="5" t="n">
-        <v>27.26</v>
+        <v>923.29</v>
       </c>
       <c r="E114" s="5" t="n">
-        <v>27.62</v>
+        <v>935.45</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>1.32</v>
@@ -3403,12 +3403,12 @@
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="D115" s="5" t="n">
-        <v>923.29</v>
+        <v>27.26</v>
       </c>
       <c r="E115" s="5" t="n">
-        <v>935.45</v>
+        <v>27.62</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>1.32</v>
@@ -3481,24 +3481,24 @@
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D118" s="5" t="n">
-        <v>357.54</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="E118" s="5" t="n">
-        <v>362.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>1.29</v>
@@ -3507,24 +3507,24 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D119" s="5" t="n">
-        <v>83.95999999999999</v>
+        <v>357.54</v>
       </c>
       <c r="E119" s="5" t="n">
-        <v>85.04000000000001</v>
+        <v>362.15</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>1.29</v>
@@ -3715,24 +3715,24 @@
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D127" s="5" t="n">
-        <v>56.03</v>
+        <v>905.92</v>
       </c>
       <c r="E127" s="5" t="n">
-        <v>56.7</v>
+        <v>916.83</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>1.2</v>
@@ -3741,12 +3741,12 @@
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>AIZ</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="D128" s="5" t="n">
-        <v>261.86</v>
+        <v>34.99</v>
       </c>
       <c r="E128" s="5" t="n">
-        <v>265</v>
+        <v>35.41</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>1.2</v>
@@ -3767,24 +3767,24 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>905.92</v>
+        <v>56.03</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>916.83</v>
+        <v>56.7</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>1.2</v>
@@ -3819,12 +3819,12 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>AIZ</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Assurant</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -3833,10 +3833,10 @@
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>34.99</v>
+        <v>261.86</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>35.41</v>
+        <v>265</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>1.2</v>
@@ -3923,12 +3923,12 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>FERG</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ferguson Enterprises</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>220.17</v>
+        <v>55.44</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>222.74</v>
+        <v>56.09</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>1.17</v>
@@ -3949,12 +3949,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>FERG</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>Ferguson Enterprises</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>55.44</v>
+        <v>220.17</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>56.09</v>
+        <v>222.74</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>1.17</v>
@@ -3975,24 +3975,24 @@
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
         <is>
-          <t>MTB</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D137" s="5" t="n">
-        <v>218.66</v>
+        <v>80.19</v>
       </c>
       <c r="E137" s="5" t="n">
-        <v>221.19</v>
+        <v>81.12</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>1.16</v>
@@ -4001,24 +4001,24 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>MTB</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>80.19</v>
+        <v>218.66</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>81.12</v>
+        <v>221.19</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>1.16</v>
@@ -4105,24 +4105,24 @@
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D142" s="5" t="n">
-        <v>197.68</v>
+        <v>106.32</v>
       </c>
       <c r="E142" s="5" t="n">
-        <v>199.91</v>
+        <v>107.52</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>1.13</v>
@@ -4131,24 +4131,24 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Valero Energy</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>106.32</v>
+        <v>382.86</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>107.52</v>
+        <v>387.18</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>1.13</v>
@@ -4157,24 +4157,24 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Valero Energy</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>382.86</v>
+        <v>197.68</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>387.18</v>
+        <v>199.91</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>1.13</v>
@@ -4313,24 +4313,24 @@
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D150" s="5" t="n">
-        <v>305.66</v>
+        <v>176.99</v>
       </c>
       <c r="E150" s="5" t="n">
-        <v>308.89</v>
+        <v>178.86</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>1.06</v>
@@ -4339,24 +4339,24 @@
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D151" s="5" t="n">
-        <v>176.99</v>
+        <v>305.66</v>
       </c>
       <c r="E151" s="5" t="n">
-        <v>178.86</v>
+        <v>308.89</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>1.06</v>
@@ -4391,24 +4391,24 @@
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D153" s="5" t="n">
-        <v>88.59</v>
+        <v>23.27</v>
       </c>
       <c r="E153" s="5" t="n">
-        <v>89.5</v>
+        <v>23.51</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>1.03</v>
@@ -4417,12 +4417,12 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>PNC</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>PNC Financial Services</t>
+          <t>Blackstone Inc.</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -4431,10 +4431,10 @@
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>223.34</v>
+        <v>117.21</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>225.64</v>
+        <v>118.42</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>1.03</v>
@@ -4443,24 +4443,24 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Blackstone Inc.</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>117.21</v>
+        <v>88.59</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>118.42</v>
+        <v>89.5</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>1.03</v>
@@ -4469,24 +4469,24 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>23.27</v>
+        <v>42.67</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>23.51</v>
+        <v>43.11</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>1.03</v>
@@ -4495,24 +4495,24 @@
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>PNC</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>PNC Financial Services</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D157" s="5" t="n">
-        <v>42.67</v>
+        <v>223.34</v>
       </c>
       <c r="E157" s="5" t="n">
-        <v>43.11</v>
+        <v>225.64</v>
       </c>
       <c r="F157" s="6" t="n">
         <v>1.03</v>
@@ -4599,24 +4599,24 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>HSIC</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>Henry Schein</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>96.2</v>
+        <v>85.53</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>97.14</v>
+        <v>86.37</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>0.98</v>
@@ -4625,24 +4625,24 @@
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Henry Schein</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D162" s="5" t="n">
-        <v>85.53</v>
+        <v>96.2</v>
       </c>
       <c r="E162" s="5" t="n">
-        <v>86.37</v>
+        <v>97.14</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>0.98</v>
@@ -4651,24 +4651,24 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>AMCR</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Amcor</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>42.1</v>
+        <v>269.75</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>42.51</v>
+        <v>272.36</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>0.97</v>
@@ -4677,24 +4677,24 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>AMCR</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Amcor</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>269.75</v>
+        <v>42.1</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>272.36</v>
+        <v>42.51</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>0.97</v>
@@ -4755,24 +4755,24 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>BKR</t>
+          <t>FIX</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Baker Hughes</t>
+          <t>Comfort Systems USA</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>57.29</v>
+        <v>1643.39</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>57.83</v>
+        <v>1658.91</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -4781,24 +4781,24 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>BKR</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Baker Hughes</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>137.34</v>
+        <v>57.29</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>138.63</v>
+        <v>57.83</v>
       </c>
       <c r="F168" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -4807,24 +4807,24 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>FIX</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Comfort Systems USA</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>1643.39</v>
+        <v>137.34</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>1658.91</v>
+        <v>138.63</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0.9399999999999999</v>
@@ -4859,24 +4859,24 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>EXPE</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>28.41</v>
+        <v>261.75</v>
       </c>
       <c r="E171" s="5" t="n">
-        <v>28.67</v>
+        <v>264.17</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>0.92</v>
@@ -4885,24 +4885,24 @@
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>EXPE</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Expedia Group</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
-        <v>261.75</v>
+        <v>28.41</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>264.17</v>
+        <v>28.67</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>0.92</v>
@@ -4989,24 +4989,24 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
-        <v>480.1</v>
+        <v>643.5</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>484.3</v>
+        <v>649.13</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>0.87</v>
@@ -5015,24 +5015,24 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>643.5</v>
+        <v>12.6</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>649.13</v>
+        <v>12.71</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0.87</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Martin Marietta Materials</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>12.6</v>
+        <v>480.1</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>12.71</v>
+        <v>484.3</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>0.87</v>
@@ -5093,24 +5093,24 @@
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D180" s="5" t="n">
-        <v>272</v>
+        <v>22.25</v>
       </c>
       <c r="E180" s="5" t="n">
-        <v>274.32</v>
+        <v>22.44</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>0.85</v>
@@ -5119,24 +5119,24 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Extra Space Storage</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D181" s="5" t="n">
-        <v>132.23</v>
+        <v>272</v>
       </c>
       <c r="E181" s="5" t="n">
-        <v>133.35</v>
+        <v>274.32</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>0.85</v>
@@ -5145,12 +5145,12 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>Extra Space Storage</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>22.25</v>
+        <v>132.23</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>22.44</v>
+        <v>133.35</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>0.85</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>Gilead Sciences</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>338.25</v>
+        <v>149.69</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>341.07</v>
+        <v>150.93</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>0.83</v>
@@ -5197,24 +5197,24 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>DHI</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>D. R. Horton</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>156.15</v>
+        <v>140.35</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>157.45</v>
+        <v>141.51</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>0.83</v>
@@ -5223,24 +5223,24 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>CSGP</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>27.86</v>
+        <v>338.25</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>28.09</v>
+        <v>341.07</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>0.83</v>
@@ -5249,24 +5249,24 @@
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>DHI</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>D. R. Horton</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D186" s="5" t="n">
-        <v>140.35</v>
+        <v>156.15</v>
       </c>
       <c r="E186" s="5" t="n">
-        <v>141.51</v>
+        <v>157.45</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>0.83</v>
@@ -5275,24 +5275,24 @@
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>LEN</t>
+          <t>CSGP</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Lennar</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D187" s="5" t="n">
-        <v>81.47</v>
+        <v>27.86</v>
       </c>
       <c r="E187" s="5" t="n">
-        <v>82.15000000000001</v>
+        <v>28.09</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>0.83</v>
@@ -5301,24 +5301,24 @@
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>LEN</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Gilead Sciences</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D188" s="5" t="n">
-        <v>149.69</v>
+        <v>81.47</v>
       </c>
       <c r="E188" s="5" t="n">
-        <v>150.93</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>0.83</v>
@@ -5431,24 +5431,24 @@
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D193" s="5" t="n">
-        <v>323.26</v>
+        <v>30.68</v>
       </c>
       <c r="E193" s="5" t="n">
-        <v>325.77</v>
+        <v>30.92</v>
       </c>
       <c r="F193" s="6" t="n">
         <v>0.78</v>
@@ -5457,24 +5457,24 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>30.68</v>
+        <v>323.26</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>30.92</v>
+        <v>325.77</v>
       </c>
       <c r="F194" s="6" t="n">
         <v>0.78</v>
@@ -5483,24 +5483,24 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>521.0700000000001</v>
+        <v>39.12</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>525.0599999999999</v>
+        <v>39.42</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>0.77</v>
@@ -5509,24 +5509,24 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D196" s="5" t="n">
-        <v>39.12</v>
+        <v>521.0700000000001</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>39.42</v>
+        <v>525.0599999999999</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>0.77</v>
@@ -5561,24 +5561,24 @@
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>TXT</t>
+          <t>WAT</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D198" s="5" t="n">
-        <v>76.02</v>
+        <v>430.3</v>
       </c>
       <c r="E198" s="5" t="n">
-        <v>76.59</v>
+        <v>433.54</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>0.75</v>
@@ -5613,24 +5613,24 @@
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>WAT</t>
+          <t>TXT</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D200" s="5" t="n">
-        <v>430.3</v>
+        <v>76.02</v>
       </c>
       <c r="E200" s="5" t="n">
-        <v>433.54</v>
+        <v>76.59</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>0.75</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>RJF</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Raymond James Financial</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>350.36</v>
+        <v>158.76</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>352.81</v>
+        <v>159.87</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>0.7</v>
@@ -5743,12 +5743,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>RJF</t>
+          <t>NTRS</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Raymond James Financial</t>
+          <t>Northern Trust</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -5757,10 +5757,10 @@
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>158.76</v>
+        <v>174.5</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>159.87</v>
+        <v>175.73</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>0.7</v>
@@ -5795,24 +5795,24 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>NTRS</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Northern Trust</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>174.5</v>
+        <v>350.36</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>175.73</v>
+        <v>352.81</v>
       </c>
       <c r="F207" s="6" t="n">
         <v>0.7</v>
@@ -5951,24 +5951,24 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Marathon Petroleum</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>117.57</v>
+        <v>390.95</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>118.35</v>
+        <v>393.52</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>0.66</v>
@@ -5977,24 +5977,24 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Marathon Petroleum</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D214" s="5" t="n">
-        <v>390.95</v>
+        <v>117.57</v>
       </c>
       <c r="E214" s="5" t="n">
-        <v>393.52</v>
+        <v>118.35</v>
       </c>
       <c r="F214" s="6" t="n">
         <v>0.66</v>
@@ -6211,24 +6211,24 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>PRU</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Prudential Financial</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>312.13</v>
+        <v>118.75</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>313.96</v>
+        <v>119.45</v>
       </c>
       <c r="F223" s="6" t="n">
         <v>0.59</v>
@@ -6237,24 +6237,24 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>PRU</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Prudential Financial</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>118.75</v>
+        <v>312.13</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>119.45</v>
+        <v>313.96</v>
       </c>
       <c r="F224" s="6" t="n">
         <v>0.59</v>
@@ -6263,12 +6263,12 @@
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>PCAR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Paccar</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="D225" s="5" t="n">
-        <v>110.67</v>
+        <v>69.22</v>
       </c>
       <c r="E225" s="5" t="n">
-        <v>111.31</v>
+        <v>69.62</v>
       </c>
       <c r="F225" s="6" t="n">
         <v>0.58</v>
@@ -6289,12 +6289,12 @@
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>PCAR</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Paccar</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -6303,10 +6303,10 @@
         </is>
       </c>
       <c r="D226" s="5" t="n">
-        <v>69.22</v>
+        <v>110.67</v>
       </c>
       <c r="E226" s="5" t="n">
-        <v>69.62</v>
+        <v>111.31</v>
       </c>
       <c r="F226" s="6" t="n">
         <v>0.58</v>
@@ -6341,24 +6341,24 @@
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D228" s="5" t="n">
-        <v>100.9</v>
+        <v>226.36</v>
       </c>
       <c r="E228" s="5" t="n">
-        <v>101.45</v>
+        <v>227.6</v>
       </c>
       <c r="F228" s="6" t="n">
         <v>0.55</v>
@@ -6367,24 +6367,24 @@
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D229" s="5" t="n">
-        <v>226.36</v>
+        <v>100.9</v>
       </c>
       <c r="E229" s="5" t="n">
-        <v>227.6</v>
+        <v>101.45</v>
       </c>
       <c r="F229" s="6" t="n">
         <v>0.55</v>
@@ -6471,24 +6471,24 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>HPQ</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Atmos Energy</t>
+          <t>HP Inc.</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>156.42</v>
+        <v>31.14</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>157.21</v>
+        <v>31.3</v>
       </c>
       <c r="F233" s="6" t="n">
         <v>0.51</v>
@@ -6497,24 +6497,24 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>HPQ</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>HP Inc.</t>
+          <t>Atmos Energy</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>31.14</v>
+        <v>156.42</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>31.3</v>
+        <v>157.21</v>
       </c>
       <c r="F234" s="6" t="n">
         <v>0.51</v>
@@ -6575,27 +6575,27 @@
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>Alphabet Inc. (Class A)</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D237" s="5" t="n">
-        <v>463.7</v>
+        <v>342.36</v>
       </c>
       <c r="E237" s="5" t="n">
-        <v>465.88</v>
+        <v>343.92</v>
       </c>
       <c r="F237" s="6" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="238">
@@ -6627,24 +6627,24 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class A)</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>342.36</v>
+        <v>60.4</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>343.92</v>
+        <v>60.68</v>
       </c>
       <c r="F239" s="6" t="n">
         <v>0.46</v>
@@ -6653,12 +6653,12 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>LNT</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Alliant Energy</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>60.4</v>
+        <v>63.31</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>60.68</v>
+        <v>63.6</v>
       </c>
       <c r="F240" s="6" t="n">
         <v>0.46</v>
@@ -6679,53 +6679,53 @@
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
         <is>
-          <t>LNT</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Alliant Energy</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D241" s="5" t="n">
-        <v>63.31</v>
+        <v>26.5</v>
       </c>
       <c r="E241" s="5" t="n">
-        <v>63.6</v>
+        <v>26.62</v>
       </c>
       <c r="F241" s="6" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>26.5</v>
+        <v>187.11</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>26.62</v>
+        <v>187.92</v>
       </c>
       <c r="F242" s="6" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="243">
@@ -6757,24 +6757,24 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D244" s="5" t="n">
-        <v>187.11</v>
+        <v>72.92</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>187.92</v>
+        <v>73.23</v>
       </c>
       <c r="F244" s="6" t="n">
         <v>0.43</v>
@@ -6783,50 +6783,50 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>72.92</v>
+        <v>375.01</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>73.23</v>
+        <v>376.59</v>
       </c>
       <c r="F245" s="6" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>RTX Corporation</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>188.49</v>
+        <v>188.61</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>189.28</v>
+        <v>189.4</v>
       </c>
       <c r="F246" s="6" t="n">
         <v>0.42</v>
@@ -6835,24 +6835,24 @@
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>RTX Corporation</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D247" s="5" t="n">
-        <v>188.61</v>
+        <v>98.16</v>
       </c>
       <c r="E247" s="5" t="n">
-        <v>189.4</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F247" s="6" t="n">
         <v>0.42</v>
@@ -6861,24 +6861,24 @@
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D248" s="5" t="n">
-        <v>98.16</v>
+        <v>188.49</v>
       </c>
       <c r="E248" s="5" t="n">
-        <v>98.56999999999999</v>
+        <v>189.28</v>
       </c>
       <c r="F248" s="6" t="n">
         <v>0.42</v>
@@ -6887,50 +6887,50 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>375.01</v>
+        <v>367.71</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>376.59</v>
+        <v>369.2</v>
       </c>
       <c r="F249" s="6" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>367.71</v>
+        <v>205.7</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>369.2</v>
+        <v>206.55</v>
       </c>
       <c r="F250" s="6" t="n">
         <v>0.41</v>
@@ -6939,76 +6939,76 @@
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>International Paper</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D251" s="5" t="n">
-        <v>205.7</v>
+        <v>34.88</v>
       </c>
       <c r="E251" s="5" t="n">
-        <v>206.55</v>
+        <v>35.02</v>
       </c>
       <c r="F251" s="6" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>VST</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>International Paper</t>
+          <t>Vistra Corp.</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>34.88</v>
+        <v>137.94</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>35.02</v>
+        <v>138.46</v>
       </c>
       <c r="F252" s="6" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>VST</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Vistra Corp.</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>137.94</v>
+        <v>66.38</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>138.46</v>
+        <v>66.63</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0.38</v>
@@ -7017,24 +7017,24 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D254" s="5" t="n">
-        <v>66.38</v>
+        <v>145.68</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>66.63</v>
+        <v>146.23</v>
       </c>
       <c r="F254" s="6" t="n">
         <v>0.38</v>
@@ -7069,27 +7069,27 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>145.68</v>
+        <v>468.14</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>146.23</v>
+        <v>469.89</v>
       </c>
       <c r="F256" s="6" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="257">
@@ -7121,50 +7121,50 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>468.14</v>
+        <v>107.59</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>469.89</v>
+        <v>107.98</v>
       </c>
       <c r="F258" s="6" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>2861.75</v>
+        <v>211.79</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>2872.16</v>
+        <v>212.55</v>
       </c>
       <c r="F259" s="6" t="n">
         <v>0.36</v>
@@ -7173,24 +7173,24 @@
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D260" s="5" t="n">
-        <v>211.79</v>
+        <v>2861.75</v>
       </c>
       <c r="E260" s="5" t="n">
-        <v>212.55</v>
+        <v>2872.16</v>
       </c>
       <c r="F260" s="6" t="n">
         <v>0.36</v>
@@ -7199,50 +7199,50 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>TDY</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Teledyne Technologies</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>107.59</v>
+        <v>612.02</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>107.98</v>
+        <v>614.15</v>
       </c>
       <c r="F261" s="6" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Home Depot (The)</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>69.56</v>
+        <v>292.18</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>69.8</v>
+        <v>293.2</v>
       </c>
       <c r="F262" s="6" t="n">
         <v>0.35</v>
@@ -7251,24 +7251,24 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>40.2</v>
+        <v>78.19</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>40.34</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="F263" s="6" t="n">
         <v>0.35</v>
@@ -7277,24 +7277,24 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>TDY</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>612.02</v>
+        <v>69.56</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>614.15</v>
+        <v>69.8</v>
       </c>
       <c r="F264" s="6" t="n">
         <v>0.35</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>78.19</v>
+        <v>40.2</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>78.45999999999999</v>
+        <v>40.34</v>
       </c>
       <c r="F265" s="6" t="n">
         <v>0.35</v>
@@ -7329,38 +7329,38 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Home Depot (The)</t>
+          <t>Parker Hannifin</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>292.18</v>
+        <v>974.98</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>293.2</v>
+        <v>978.33</v>
       </c>
       <c r="F266" s="6" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Parker Hannifin</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -7369,39 +7369,39 @@
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>974.98</v>
+        <v>168.65</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>978.33</v>
+        <v>169.21</v>
       </c>
       <c r="F267" s="6" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>DHR</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Danaher Corporation</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D268" s="5" t="n">
-        <v>168.65</v>
+        <v>223.77</v>
       </c>
       <c r="E268" s="5" t="n">
-        <v>169.21</v>
+        <v>224.49</v>
       </c>
       <c r="F268" s="6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="269">
@@ -7433,27 +7433,27 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>DHR</t>
+          <t>ROST</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Danaher Corporation</t>
+          <t>Ross Stores</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>223.77</v>
+        <v>235.4</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>224.49</v>
+        <v>236.12</v>
       </c>
       <c r="F270" s="6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="271">
@@ -7485,50 +7485,50 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>ROST</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Ross Stores</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>235.4</v>
+        <v>56.66</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>236.12</v>
+        <v>56.83</v>
       </c>
       <c r="F272" s="6" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>56.66</v>
+        <v>508.98</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>56.83</v>
+        <v>510.52</v>
       </c>
       <c r="F273" s="6" t="n">
         <v>0.3</v>
@@ -7537,50 +7537,50 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>508.98</v>
+        <v>150.68</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>510.52</v>
+        <v>151.11</v>
       </c>
       <c r="F274" s="6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Moody's Corporation</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>467.35</v>
+        <v>62.77</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>468.7</v>
+        <v>62.95</v>
       </c>
       <c r="F275" s="6" t="n">
         <v>0.29</v>
@@ -7589,24 +7589,24 @@
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Moody's Corporation</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D276" s="5" t="n">
-        <v>62.77</v>
+        <v>467.35</v>
       </c>
       <c r="E276" s="5" t="n">
-        <v>62.95</v>
+        <v>468.7</v>
       </c>
       <c r="F276" s="6" t="n">
         <v>0.29</v>
@@ -7615,50 +7615,50 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>150.68</v>
+        <v>57.17</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>151.11</v>
+        <v>57.33</v>
       </c>
       <c r="F277" s="6" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>432.93</v>
+        <v>566.08</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>434.15</v>
+        <v>567.65</v>
       </c>
       <c r="F278" s="6" t="n">
         <v>0.28</v>
@@ -7693,24 +7693,24 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D280" s="5" t="n">
-        <v>57.17</v>
+        <v>432.93</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>57.33</v>
+        <v>434.15</v>
       </c>
       <c r="F280" s="6" t="n">
         <v>0.28</v>
@@ -7719,27 +7719,27 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>GPC</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Genuine Parts Company</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>566.08</v>
+        <v>129.26</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>567.65</v>
+        <v>129.61</v>
       </c>
       <c r="F281" s="6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="282">
@@ -7771,53 +7771,53 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>GPC</t>
+          <t>PODD</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Genuine Parts Company</t>
+          <t>Insulet Corporation</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>129.26</v>
+        <v>135.78</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>129.61</v>
+        <v>136.13</v>
       </c>
       <c r="F283" s="6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>PODD</t>
+          <t>MKC</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Insulet Corporation</t>
+          <t>McCormick &amp; Company</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D284" s="5" t="n">
-        <v>135.78</v>
+        <v>47.82</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>136.13</v>
+        <v>47.94</v>
       </c>
       <c r="F284" s="6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="285">
@@ -7849,102 +7849,102 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>MKC</t>
+          <t>SRE</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>McCormick &amp; Company</t>
+          <t>Sempra</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>47.82</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>47.94</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="F286" s="6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>SRE</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Sempra</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>77.73999999999999</v>
+        <v>55.41</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>77.93000000000001</v>
+        <v>55.54</v>
       </c>
       <c r="F287" s="6" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D288" s="5" t="n">
-        <v>55.41</v>
+        <v>629.26</v>
       </c>
       <c r="E288" s="5" t="n">
-        <v>55.54</v>
+        <v>630.63</v>
       </c>
       <c r="F288" s="6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D289" s="5" t="n">
-        <v>224.58</v>
+        <v>101.07</v>
       </c>
       <c r="E289" s="5" t="n">
-        <v>225.07</v>
+        <v>101.29</v>
       </c>
       <c r="F289" s="6" t="n">
         <v>0.22</v>
@@ -7953,12 +7953,12 @@
     <row r="290">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
@@ -7967,10 +7967,10 @@
         </is>
       </c>
       <c r="D290" s="5" t="n">
-        <v>629.26</v>
+        <v>224.58</v>
       </c>
       <c r="E290" s="5" t="n">
-        <v>630.63</v>
+        <v>225.07</v>
       </c>
       <c r="F290" s="6" t="n">
         <v>0.22</v>
@@ -7979,12 +7979,12 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>101.07</v>
+        <v>308.95</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>101.29</v>
+        <v>309.64</v>
       </c>
       <c r="F291" s="6" t="n">
         <v>0.22</v>
@@ -8005,38 +8005,38 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>308.95</v>
+        <v>123.35</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>309.64</v>
+        <v>123.61</v>
       </c>
       <c r="F292" s="6" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -8045,10 +8045,10 @@
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>52.54</v>
+        <v>121.18</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>52.65</v>
+        <v>121.44</v>
       </c>
       <c r="F293" s="6" t="n">
         <v>0.21</v>
@@ -8057,24 +8057,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>123.35</v>
+        <v>52.54</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>123.61</v>
+        <v>52.65</v>
       </c>
       <c r="F294" s="6" t="n">
         <v>0.21</v>
@@ -8135,50 +8135,50 @@
     <row r="297">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D297" s="5" t="n">
-        <v>121.18</v>
+        <v>158.46</v>
       </c>
       <c r="E297" s="5" t="n">
-        <v>121.44</v>
+        <v>158.78</v>
       </c>
       <c r="F297" s="6" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>SNPS</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D298" s="5" t="n">
-        <v>424.91</v>
+        <v>270.68</v>
       </c>
       <c r="E298" s="5" t="n">
-        <v>425.76</v>
+        <v>271.22</v>
       </c>
       <c r="F298" s="6" t="n">
         <v>0.2</v>
@@ -8213,24 +8213,24 @@
     <row r="300">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace</t>
+          <t>Synopsys</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D300" s="5" t="n">
-        <v>158.46</v>
+        <v>424.91</v>
       </c>
       <c r="E300" s="5" t="n">
-        <v>158.78</v>
+        <v>425.76</v>
       </c>
       <c r="F300" s="6" t="n">
         <v>0.2</v>
@@ -8239,27 +8239,27 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>270.68</v>
+        <v>99.2</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>271.22</v>
+        <v>99.39</v>
       </c>
       <c r="F301" s="6" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="302">
@@ -8291,24 +8291,24 @@
     <row r="303">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Allstate</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D303" s="5" t="n">
-        <v>99.2</v>
+        <v>227.17</v>
       </c>
       <c r="E303" s="5" t="n">
-        <v>99.39</v>
+        <v>227.6</v>
       </c>
       <c r="F303" s="6" t="n">
         <v>0.19</v>
@@ -8317,12 +8317,12 @@
     <row r="304">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Allstate</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -8331,13 +8331,13 @@
         </is>
       </c>
       <c r="D304" s="5" t="n">
-        <v>227.17</v>
+        <v>362.39</v>
       </c>
       <c r="E304" s="5" t="n">
-        <v>227.6</v>
+        <v>363.04</v>
       </c>
       <c r="F304" s="6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="305">
@@ -8369,50 +8369,50 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>PG&amp;E Corporation</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>362.39</v>
+        <v>12.32</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>363.04</v>
+        <v>12.34</v>
       </c>
       <c r="F306" s="6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>1080.53</v>
+        <v>465.88</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>1082.28</v>
+        <v>466.62</v>
       </c>
       <c r="F307" s="6" t="n">
         <v>0.16</v>
@@ -8421,24 +8421,24 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>PG&amp;E Corporation</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>12.32</v>
+        <v>1080.53</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>12.34</v>
+        <v>1082.28</v>
       </c>
       <c r="F308" s="6" t="n">
         <v>0.16</v>
@@ -8447,24 +8447,24 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>FRT</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Federal Realty Investment Trust</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>110.35</v>
+        <v>351.51</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>110.52</v>
+        <v>352.03</v>
       </c>
       <c r="F309" s="6" t="n">
         <v>0.15</v>
@@ -8499,24 +8499,24 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>FRT</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Federal Realty Investment Trust</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>351.51</v>
+        <v>110.35</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>352.03</v>
+        <v>110.52</v>
       </c>
       <c r="F311" s="6" t="n">
         <v>0.15</v>
@@ -8551,24 +8551,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>GD</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>336.29</v>
+        <v>1181.89</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>336.72</v>
+        <v>1183.46</v>
       </c>
       <c r="F313" s="6" t="n">
         <v>0.13</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Cincinnati Financial</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>162.33</v>
+        <v>14.85</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>162.54</v>
+        <v>14.87</v>
       </c>
       <c r="F314" s="6" t="n">
         <v>0.13</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Cincinnati Financial</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>14.85</v>
+        <v>162.33</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>14.87</v>
+        <v>162.54</v>
       </c>
       <c r="F315" s="6" t="n">
         <v>0.13</v>
@@ -8629,24 +8629,24 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>GD</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>1181.89</v>
+        <v>336.29</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>1183.46</v>
+        <v>336.72</v>
       </c>
       <c r="F316" s="6" t="n">
         <v>0.13</v>
@@ -8655,24 +8655,24 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>249.38</v>
+        <v>293.63</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>249.67</v>
+        <v>293.99</v>
       </c>
       <c r="F317" s="6" t="n">
         <v>0.12</v>
@@ -8681,24 +8681,24 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D318" s="5" t="n">
-        <v>293.63</v>
+        <v>249.38</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>293.99</v>
+        <v>249.67</v>
       </c>
       <c r="F318" s="6" t="n">
         <v>0.12</v>
@@ -8707,24 +8707,24 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>121.3</v>
+        <v>113.23</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>121.43</v>
+        <v>113.35</v>
       </c>
       <c r="F319" s="6" t="n">
         <v>0.11</v>
@@ -8733,24 +8733,24 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>113.23</v>
+        <v>121.3</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>113.35</v>
+        <v>121.43</v>
       </c>
       <c r="F320" s="6" t="n">
         <v>0.11</v>
@@ -8785,24 +8785,24 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>SPG</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Simon Property Group</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>204.7</v>
+        <v>107.83</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>204.82</v>
+        <v>107.9</v>
       </c>
       <c r="F322" s="6" t="n">
         <v>0.06</v>
@@ -8837,24 +8837,24 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>505.18</v>
+        <v>30.84</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>505.48</v>
+        <v>30.86</v>
       </c>
       <c r="F324" s="6" t="n">
         <v>0.06</v>
@@ -8863,24 +8863,24 @@
     <row r="325">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>SPG</t>
         </is>
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>Simon Property Group</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D325" s="5" t="n">
-        <v>107.83</v>
+        <v>204.7</v>
       </c>
       <c r="E325" s="5" t="n">
-        <v>107.9</v>
+        <v>204.82</v>
       </c>
       <c r="F325" s="6" t="n">
         <v>0.06</v>
@@ -8889,24 +8889,24 @@
     <row r="326">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>WBD</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Warner Bros. Discovery</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D326" s="5" t="n">
-        <v>30.84</v>
+        <v>505.18</v>
       </c>
       <c r="E326" s="5" t="n">
-        <v>30.86</v>
+        <v>505.48</v>
       </c>
       <c r="F326" s="6" t="n">
         <v>0.06</v>
@@ -8915,24 +8915,24 @@
     <row r="327">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D327" s="5" t="n">
-        <v>165.35</v>
+        <v>36.82</v>
       </c>
       <c r="E327" s="5" t="n">
-        <v>165.43</v>
+        <v>36.84</v>
       </c>
       <c r="F327" s="6" t="n">
         <v>0.05</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>36.82</v>
+        <v>165.35</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>36.84</v>
+        <v>165.43</v>
       </c>
       <c r="F329" s="6" t="n">
         <v>0.05</v>
@@ -9071,27 +9071,27 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>440</v>
+        <v>55.38</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>439.98</v>
+        <v>55.38</v>
       </c>
       <c r="F333" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
@@ -9123,50 +9123,50 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>55.38</v>
+        <v>440</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>55.38</v>
+        <v>439.98</v>
       </c>
       <c r="F335" s="6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>82.89</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>82.88</v>
+        <v>78.67</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-0.01</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>ESS</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>Essex Property Trust</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>196.32</v>
+        <v>271.65</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>196.31</v>
+        <v>271.61</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-0.01</v>
@@ -9201,24 +9201,24 @@
     <row r="338">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D338" s="5" t="n">
-        <v>78.68000000000001</v>
+        <v>82.89</v>
       </c>
       <c r="E338" s="5" t="n">
-        <v>78.67</v>
+        <v>82.88</v>
       </c>
       <c r="F338" s="7" t="n">
         <v>-0.01</v>
@@ -9227,24 +9227,24 @@
     <row r="339">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>ESS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>Essex Property Trust</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D339" s="5" t="n">
-        <v>271.65</v>
+        <v>196.32</v>
       </c>
       <c r="E339" s="5" t="n">
-        <v>271.61</v>
+        <v>196.31</v>
       </c>
       <c r="F339" s="7" t="n">
         <v>-0.01</v>
@@ -9331,24 +9331,24 @@
     <row r="343">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>PSX</t>
         </is>
       </c>
       <c r="B343" s="4" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D343" s="5" t="n">
-        <v>313.17</v>
+        <v>255.87</v>
       </c>
       <c r="E343" s="5" t="n">
-        <v>313</v>
+        <v>255.75</v>
       </c>
       <c r="F343" s="7" t="n">
         <v>-0.05</v>
@@ -9357,24 +9357,24 @@
     <row r="344">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D344" s="5" t="n">
-        <v>255.87</v>
+        <v>313.17</v>
       </c>
       <c r="E344" s="5" t="n">
-        <v>255.75</v>
+        <v>313</v>
       </c>
       <c r="F344" s="7" t="n">
         <v>-0.05</v>
@@ -9565,24 +9565,24 @@
     <row r="352">
       <c r="A352" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B352" s="4" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D352" s="5" t="n">
-        <v>367.98</v>
+        <v>61.92</v>
       </c>
       <c r="E352" s="5" t="n">
-        <v>367.38</v>
+        <v>61.82</v>
       </c>
       <c r="F352" s="7" t="n">
         <v>-0.16</v>
@@ -9591,24 +9591,24 @@
     <row r="353">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D353" s="5" t="n">
-        <v>61.92</v>
+        <v>367.98</v>
       </c>
       <c r="E353" s="5" t="n">
-        <v>61.82</v>
+        <v>367.38</v>
       </c>
       <c r="F353" s="7" t="n">
         <v>-0.16</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>MCD</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>McDonald's</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>237.02</v>
+        <v>101.59</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>236.5</v>
+        <v>101.37</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-0.22</v>
@@ -9721,24 +9721,24 @@
     <row r="358">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>MCD</t>
         </is>
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Paychex</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D358" s="5" t="n">
-        <v>101.59</v>
+        <v>237.02</v>
       </c>
       <c r="E358" s="5" t="n">
-        <v>101.37</v>
+        <v>236.5</v>
       </c>
       <c r="F358" s="7" t="n">
         <v>-0.22</v>
@@ -9773,24 +9773,24 @@
     <row r="360">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D360" s="5" t="n">
-        <v>106.97</v>
+        <v>114.01</v>
       </c>
       <c r="E360" s="5" t="n">
-        <v>106.7</v>
+        <v>113.72</v>
       </c>
       <c r="F360" s="7" t="n">
         <v>-0.25</v>
@@ -9799,24 +9799,24 @@
     <row r="361">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D361" s="5" t="n">
-        <v>114.01</v>
+        <v>106.97</v>
       </c>
       <c r="E361" s="5" t="n">
-        <v>113.72</v>
+        <v>106.7</v>
       </c>
       <c r="F361" s="7" t="n">
         <v>-0.25</v>
@@ -9825,24 +9825,24 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D362" s="5" t="n">
-        <v>86.83</v>
+        <v>25.45</v>
       </c>
       <c r="E362" s="5" t="n">
-        <v>86.59</v>
+        <v>25.38</v>
       </c>
       <c r="F362" s="7" t="n">
         <v>-0.28</v>
@@ -9851,24 +9851,24 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>25.45</v>
+        <v>86.83</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>25.38</v>
+        <v>86.59</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-0.28</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>247.96</v>
+        <v>265.12</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>247.25</v>
+        <v>264.34</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-0.29</v>
@@ -9903,24 +9903,24 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>265.12</v>
+        <v>247.96</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>264.34</v>
+        <v>247.25</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>-0.29</v>
@@ -9955,24 +9955,24 @@
     <row r="367">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D367" s="5" t="n">
-        <v>293.03</v>
+        <v>90.38</v>
       </c>
       <c r="E367" s="5" t="n">
-        <v>292.14</v>
+        <v>90.11</v>
       </c>
       <c r="F367" s="7" t="n">
         <v>-0.3</v>
@@ -9981,24 +9981,24 @@
     <row r="368">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B368" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D368" s="5" t="n">
-        <v>90.38</v>
+        <v>293.03</v>
       </c>
       <c r="E368" s="5" t="n">
-        <v>90.11</v>
+        <v>292.14</v>
       </c>
       <c r="F368" s="7" t="n">
         <v>-0.3</v>
@@ -10007,24 +10007,24 @@
     <row r="369">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D369" s="5" t="n">
-        <v>58.92</v>
+        <v>295.04</v>
       </c>
       <c r="E369" s="5" t="n">
-        <v>58.74</v>
+        <v>294.14</v>
       </c>
       <c r="F369" s="7" t="n">
         <v>-0.31</v>
@@ -10033,24 +10033,24 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>MCK</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>McKesson Corporation</t>
+          <t>Hershey Company (The)</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D370" s="5" t="n">
-        <v>869.36</v>
+        <v>166.88</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>866.64</v>
+        <v>166.37</v>
       </c>
       <c r="F370" s="7" t="n">
         <v>-0.31</v>
@@ -10059,12 +10059,12 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>Hershey Company (The)</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>166.88</v>
+        <v>58.92</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>166.37</v>
+        <v>58.74</v>
       </c>
       <c r="F371" s="7" t="n">
         <v>-0.31</v>
@@ -10085,24 +10085,24 @@
     <row r="372">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>MCK</t>
         </is>
       </c>
       <c r="B372" s="4" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>McKesson Corporation</t>
         </is>
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D372" s="5" t="n">
-        <v>295.04</v>
+        <v>869.36</v>
       </c>
       <c r="E372" s="5" t="n">
-        <v>294.14</v>
+        <v>866.64</v>
       </c>
       <c r="F372" s="7" t="n">
         <v>-0.31</v>
@@ -10111,24 +10111,24 @@
     <row r="373">
       <c r="A373" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Lululemon Athletica</t>
+          <t>Coca-Cola Company (The)</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D373" s="5" t="n">
-        <v>101.64</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E373" s="5" t="n">
-        <v>101.3</v>
+        <v>87.81</v>
       </c>
       <c r="F373" s="7" t="n">
         <v>-0.33</v>
@@ -10137,24 +10137,24 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola Company (The)</t>
+          <t>Lululemon Athletica</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>88.09999999999999</v>
+        <v>101.64</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>87.81</v>
+        <v>101.3</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>-0.33</v>
@@ -10293,24 +10293,24 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>XYZ</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>Block, Inc.</t>
+          <t>Ciena</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D380" s="5" t="n">
-        <v>76.73999999999999</v>
+        <v>358.43</v>
       </c>
       <c r="E380" s="5" t="n">
-        <v>76.42</v>
+        <v>356.91</v>
       </c>
       <c r="F380" s="7" t="n">
         <v>-0.42</v>
@@ -10319,24 +10319,24 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>XYZ</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>Ciena</t>
+          <t>Block, Inc.</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>358.43</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="E381" s="5" t="n">
-        <v>356.91</v>
+        <v>76.42</v>
       </c>
       <c r="F381" s="7" t="n">
         <v>-0.42</v>
@@ -10449,24 +10449,24 @@
     <row r="386">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>BAX</t>
         </is>
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>American Water Works</t>
+          <t>Baxter International</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D386" s="5" t="n">
-        <v>131.53</v>
+        <v>23.48</v>
       </c>
       <c r="E386" s="5" t="n">
-        <v>130.91</v>
+        <v>23.37</v>
       </c>
       <c r="F386" s="7" t="n">
         <v>-0.47</v>
@@ -10475,24 +10475,24 @@
     <row r="387">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>BAX</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Baxter International</t>
+          <t>American Water Works</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D387" s="5" t="n">
-        <v>23.48</v>
+        <v>131.53</v>
       </c>
       <c r="E387" s="5" t="n">
-        <v>23.37</v>
+        <v>130.91</v>
       </c>
       <c r="F387" s="7" t="n">
         <v>-0.47</v>
@@ -10579,24 +10579,24 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>STZ</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Verizon</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>114.21</v>
+        <v>47.32</v>
       </c>
       <c r="E391" s="5" t="n">
-        <v>113.63</v>
+        <v>47.08</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>-0.51</v>
@@ -10605,24 +10605,24 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>STZ</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Verizon</t>
+          <t>Constellation Brands</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>47.32</v>
+        <v>114.21</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>47.08</v>
+        <v>113.63</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>-0.51</v>
@@ -10683,24 +10683,24 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>ELV</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>398.25</v>
+        <v>207.96</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>396.09</v>
+        <v>206.83</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-0.54</v>
@@ -10709,12 +10709,12 @@
     <row r="396">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>CRL</t>
+          <t>ELV</t>
         </is>
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>Charles River Laboratories</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
@@ -10723,10 +10723,10 @@
         </is>
       </c>
       <c r="D396" s="5" t="n">
-        <v>294.44</v>
+        <v>398.25</v>
       </c>
       <c r="E396" s="5" t="n">
-        <v>292.84</v>
+        <v>396.09</v>
       </c>
       <c r="F396" s="7" t="n">
         <v>-0.54</v>
@@ -10735,24 +10735,24 @@
     <row r="397">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>CRL</t>
         </is>
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Charles River Laboratories</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D397" s="5" t="n">
-        <v>91</v>
+        <v>294.44</v>
       </c>
       <c r="E397" s="5" t="n">
-        <v>90.51000000000001</v>
+        <v>292.84</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>-0.54</v>
@@ -10761,24 +10761,24 @@
     <row r="398">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D398" s="5" t="n">
-        <v>207.96</v>
+        <v>91</v>
       </c>
       <c r="E398" s="5" t="n">
-        <v>206.83</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F398" s="7" t="n">
         <v>-0.54</v>
@@ -10787,24 +10787,24 @@
     <row r="399">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>FDXF</t>
         </is>
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>FedEx Freight</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D399" s="5" t="n">
-        <v>400.32</v>
+        <v>113.81</v>
       </c>
       <c r="E399" s="5" t="n">
-        <v>398.11</v>
+        <v>113.18</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>-0.55</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>FDXF</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>FedEx Freight</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>113.81</v>
+        <v>400.32</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>113.18</v>
+        <v>398.11</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-0.55</v>
@@ -10865,24 +10865,24 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>Prologis</t>
+          <t>Chevron Corporation</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D402" s="5" t="n">
-        <v>133.82</v>
+        <v>205.65</v>
       </c>
       <c r="E402" s="5" t="n">
-        <v>133.05</v>
+        <v>204.45</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>-0.58</v>
@@ -10891,24 +10891,24 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PLD</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>Chevron Corporation</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>205.65</v>
+        <v>133.82</v>
       </c>
       <c r="E403" s="5" t="n">
-        <v>204.45</v>
+        <v>133.05</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>-0.58</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Steel Dynamics</t>
+          <t>Ulta Beauty</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>235.2</v>
+        <v>548.78</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>233.66</v>
+        <v>545.2</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-0.65</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>20.14</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>20.01</v>
+        <v>89.23999999999999</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-0.65</v>
@@ -11021,24 +11021,24 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>89.81999999999999</v>
+        <v>20.14</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>89.23999999999999</v>
+        <v>20.01</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>-0.65</v>
@@ -11047,24 +11047,24 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>Ulta Beauty</t>
+          <t>Steel Dynamics</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>548.78</v>
+        <v>235.2</v>
       </c>
       <c r="E409" s="5" t="n">
-        <v>545.2</v>
+        <v>233.66</v>
       </c>
       <c r="F409" s="7" t="n">
         <v>-0.65</v>
@@ -11307,24 +11307,24 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>71.72</v>
+        <v>523.7</v>
       </c>
       <c r="E419" s="5" t="n">
-        <v>71.15000000000001</v>
+        <v>519.5599999999999</v>
       </c>
       <c r="F419" s="7" t="n">
         <v>-0.79</v>
@@ -11333,24 +11333,24 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>523.7</v>
+        <v>71.72</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>519.5599999999999</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>-0.79</v>
@@ -11385,24 +11385,24 @@
     <row r="422">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D422" s="5" t="n">
-        <v>373.6</v>
+        <v>556.08</v>
       </c>
       <c r="E422" s="5" t="n">
-        <v>370.44</v>
+        <v>551.36</v>
       </c>
       <c r="F422" s="7" t="n">
         <v>-0.85</v>
@@ -11411,24 +11411,24 @@
     <row r="423">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D423" s="5" t="n">
-        <v>556.08</v>
+        <v>373.6</v>
       </c>
       <c r="E423" s="5" t="n">
-        <v>551.36</v>
+        <v>370.44</v>
       </c>
       <c r="F423" s="7" t="n">
         <v>-0.85</v>
@@ -11645,24 +11645,24 @@
     <row r="432">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>APD</t>
+          <t>WELL</t>
         </is>
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>Air Products</t>
+          <t>Welltower</t>
         </is>
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D432" s="5" t="n">
-        <v>284.49</v>
+        <v>233.61</v>
       </c>
       <c r="E432" s="5" t="n">
-        <v>281.76</v>
+        <v>231.37</v>
       </c>
       <c r="F432" s="7" t="n">
         <v>-0.96</v>
@@ -11671,24 +11671,24 @@
     <row r="433">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>APD</t>
         </is>
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>Welltower</t>
+          <t>Air Products</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D433" s="5" t="n">
-        <v>233.61</v>
+        <v>284.49</v>
       </c>
       <c r="E433" s="5" t="n">
-        <v>231.37</v>
+        <v>281.76</v>
       </c>
       <c r="F433" s="7" t="n">
         <v>-0.96</v>
@@ -11697,24 +11697,24 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D434" s="5" t="n">
-        <v>162.14</v>
+        <v>23.86</v>
       </c>
       <c r="E434" s="5" t="n">
-        <v>160.59</v>
+        <v>23.63</v>
       </c>
       <c r="F434" s="7" t="n">
         <v>-0.96</v>
@@ -11723,24 +11723,24 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>23.86</v>
+        <v>162.14</v>
       </c>
       <c r="E435" s="5" t="n">
-        <v>23.63</v>
+        <v>160.59</v>
       </c>
       <c r="F435" s="7" t="n">
         <v>-0.96</v>
@@ -12269,24 +12269,24 @@
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>CBRE Group</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D456" s="5" t="n">
-        <v>136.53</v>
+        <v>238.93</v>
       </c>
       <c r="E456" s="5" t="n">
-        <v>134.55</v>
+        <v>235.47</v>
       </c>
       <c r="F456" s="7" t="n">
         <v>-1.45</v>
@@ -12295,24 +12295,24 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>Adobe Inc.</t>
+          <t>CBRE Group</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>238.93</v>
+        <v>136.53</v>
       </c>
       <c r="E457" s="5" t="n">
-        <v>235.47</v>
+        <v>134.55</v>
       </c>
       <c r="F457" s="7" t="n">
         <v>-1.45</v>
@@ -12685,24 +12685,24 @@
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>EOG Resources</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D472" s="5" t="n">
-        <v>142.86</v>
+        <v>238.22</v>
       </c>
       <c r="E472" s="5" t="n">
-        <v>140.35</v>
+        <v>234.02</v>
       </c>
       <c r="F472" s="7" t="n">
         <v>-1.76</v>
@@ -12711,24 +12711,24 @@
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>EOG Resources</t>
         </is>
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D473" s="5" t="n">
-        <v>238.22</v>
+        <v>142.86</v>
       </c>
       <c r="E473" s="5" t="n">
-        <v>234.02</v>
+        <v>140.35</v>
       </c>
       <c r="F473" s="7" t="n">
         <v>-1.76</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 18 close to Sep 25 close  |  503 companies  |  updated 2026-09-26 08:07</t>
+          <t>Sep 18 close to Sep 25 close  |  503 companies  |  updated 2026-09-27 08:43</t>
         </is>
       </c>
     </row>
@@ -14539,12 +14539,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -14553,16 +14553,16 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>371.47</v>
+        <v>244.25</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>398.38</v>
+        <v>261.94</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>398.69</v>
+        <v>262.36</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>371.47</v>
+        <v>244.25</v>
       </c>
       <c r="H31" s="6" t="n">
         <v>7.24</v>
@@ -14571,12 +14571,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -14585,16 +14585,16 @@
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>244.25</v>
+        <v>371.47</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>261.94</v>
+        <v>398.38</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>262.36</v>
+        <v>398.69</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>244.25</v>
+        <v>371.47</v>
       </c>
       <c r="H32" s="6" t="n">
         <v>7.24</v>
@@ -15243,76 +15243,76 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>HUBB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Hubbell Incorporated</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>443.23</v>
+        <v>52.41</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>465.88</v>
+        <v>55.04</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>465.88</v>
+        <v>55.04</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>443.23</v>
+        <v>52.41</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>5.11</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>52.41</v>
+        <v>108.71</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>55.04</v>
+        <v>113.99</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>55.04</v>
+        <v>115.21</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>52.41</v>
+        <v>108.71</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>5.02</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>JCI</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -15321,126 +15321,126 @@
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>108.71</v>
+        <v>143.28</v>
       </c>
       <c r="E55" s="5" t="n">
-        <v>113.99</v>
+        <v>150.2</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>115.21</v>
+        <v>150.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>108.71</v>
+        <v>143.28</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>JCI</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Johnson Controls</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>143.28</v>
+        <v>375.72</v>
       </c>
       <c r="E56" s="5" t="n">
-        <v>150.2</v>
+        <v>393.6</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>150.2</v>
+        <v>393.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>143.28</v>
+        <v>375.72</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>4.83</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>SW</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Smurfit Westrock</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>375.72</v>
+        <v>44.33</v>
       </c>
       <c r="E57" s="5" t="n">
-        <v>393.6</v>
+        <v>46.41</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>393.6</v>
+        <v>46.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>375.72</v>
+        <v>44.33</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Smurfit Westrock</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>44.33</v>
+        <v>53.88</v>
       </c>
       <c r="E58" s="5" t="n">
-        <v>46.41</v>
+        <v>56.37</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>46.49</v>
+        <v>56.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>44.33</v>
+        <v>53.88</v>
       </c>
       <c r="H58" s="6" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -15449,147 +15449,147 @@
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>53.88</v>
+        <v>311.57</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>56.37</v>
+        <v>325.77</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>56.37</v>
+        <v>325.77</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>53.88</v>
+        <v>311.57</v>
       </c>
       <c r="H59" s="6" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>311.57</v>
+        <v>493.78</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>325.77</v>
+        <v>516.17</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>325.77</v>
+        <v>516.17</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>311.57</v>
+        <v>493.78</v>
       </c>
       <c r="H60" s="6" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>493.78</v>
+        <v>415.62</v>
       </c>
       <c r="E61" s="5" t="n">
-        <v>516.17</v>
+        <v>434.15</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>516.17</v>
+        <v>434.15</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>493.78</v>
+        <v>415.62</v>
       </c>
       <c r="H61" s="6" t="n">
-        <v>4.53</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>NXPI</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>NXP Semiconductors</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>415.62</v>
+        <v>227.99</v>
       </c>
       <c r="E62" s="5" t="n">
-        <v>434.15</v>
+        <v>238.08</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>434.15</v>
+        <v>238.08</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>415.62</v>
+        <v>227.99</v>
       </c>
       <c r="H62" s="6" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>NXPI</t>
+          <t>HUBB</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>NXP Semiconductors</t>
+          <t>Hubbell Incorporated</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>227.99</v>
+        <v>446.92</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>238.08</v>
+        <v>466.62</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>238.08</v>
+        <v>466.62</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>227.99</v>
+        <v>446.92</v>
       </c>
       <c r="H63" s="6" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="64">
@@ -15851,30 +15851,30 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>338.92</v>
+        <v>120.05</v>
       </c>
       <c r="E72" s="5" t="n">
-        <v>352.03</v>
+        <v>124.69</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>352.03</v>
+        <v>124.86</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>338.92</v>
+        <v>120.05</v>
       </c>
       <c r="H72" s="6" t="n">
         <v>3.87</v>
@@ -15883,30 +15883,30 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>120.05</v>
+        <v>338.92</v>
       </c>
       <c r="E73" s="5" t="n">
-        <v>124.69</v>
+        <v>352.03</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>124.86</v>
+        <v>352.03</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>120.05</v>
+        <v>338.92</v>
       </c>
       <c r="H73" s="6" t="n">
         <v>3.87</v>
@@ -16043,12 +16043,12 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>ANET</t>
+          <t>HPE</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Hewlett Packard Enterprise</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
@@ -16057,16 +16057,16 @@
         </is>
       </c>
       <c r="D78" s="5" t="n">
-        <v>199.39</v>
+        <v>60.76</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>206.55</v>
+        <v>62.94</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>206.55</v>
+        <v>63.52</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>199.39</v>
+        <v>60.76</v>
       </c>
       <c r="H78" s="6" t="n">
         <v>3.59</v>
@@ -16075,12 +16075,12 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>HPE</t>
+          <t>ANET</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise</t>
+          <t>Arista Networks</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -16089,16 +16089,16 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>60.76</v>
+        <v>199.39</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>62.94</v>
+        <v>206.55</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>63.52</v>
+        <v>206.55</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>60.76</v>
+        <v>199.39</v>
       </c>
       <c r="H79" s="6" t="n">
         <v>3.59</v>
@@ -16459,30 +16459,30 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Costco</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>895.3099999999999</v>
+        <v>363.58</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>922.77</v>
+        <v>374.74</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>922.77</v>
+        <v>393.3</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>895.3099999999999</v>
+        <v>363.58</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>3.07</v>
@@ -16491,30 +16491,30 @@
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>363.58</v>
+        <v>895.3099999999999</v>
       </c>
       <c r="E92" s="5" t="n">
-        <v>374.74</v>
+        <v>922.77</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>393.3</v>
+        <v>922.77</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>363.58</v>
+        <v>895.3099999999999</v>
       </c>
       <c r="H92" s="6" t="n">
         <v>3.07</v>
@@ -17675,30 +17675,30 @@
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>STE</t>
         </is>
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Steris</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D129" s="5" t="n">
-        <v>131.77</v>
+        <v>205.04</v>
       </c>
       <c r="E129" s="5" t="n">
-        <v>134.28</v>
+        <v>208.93</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>135.05</v>
+        <v>209.98</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>131.77</v>
+        <v>205.04</v>
       </c>
       <c r="H129" s="6" t="n">
         <v>1.9</v>
@@ -17707,30 +17707,30 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>STE</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Steris</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>205.04</v>
+        <v>131.77</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>208.93</v>
+        <v>134.28</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>209.98</v>
+        <v>135.05</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>205.04</v>
+        <v>131.77</v>
       </c>
       <c r="H130" s="6" t="n">
         <v>1.9</v>
@@ -18155,30 +18155,30 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>EQT</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>EQT Corporation</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>50</v>
+        <v>750.09</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>50.81</v>
+        <v>762.21</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>51.87</v>
+        <v>762.21</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>50</v>
+        <v>750.09</v>
       </c>
       <c r="H144" s="6" t="n">
         <v>1.62</v>
@@ -18187,30 +18187,30 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>EQT</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>EQT Corporation</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>750.09</v>
+        <v>50</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>762.21</v>
+        <v>50.81</v>
       </c>
       <c r="F145" s="5" t="n">
-        <v>762.21</v>
+        <v>51.87</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>750.09</v>
+        <v>50</v>
       </c>
       <c r="H145" s="6" t="n">
         <v>1.62</v>
@@ -18283,12 +18283,12 @@
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -18297,16 +18297,16 @@
         </is>
       </c>
       <c r="D148" s="5" t="n">
-        <v>249.39</v>
+        <v>808.99</v>
       </c>
       <c r="E148" s="5" t="n">
-        <v>253.28</v>
+        <v>821.58</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>253.46</v>
+        <v>821.58</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>245.3</v>
+        <v>805.25</v>
       </c>
       <c r="H148" s="6" t="n">
         <v>1.56</v>
@@ -18315,12 +18315,12 @@
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -18329,16 +18329,16 @@
         </is>
       </c>
       <c r="D149" s="5" t="n">
-        <v>808.99</v>
+        <v>249.39</v>
       </c>
       <c r="E149" s="5" t="n">
-        <v>821.58</v>
+        <v>253.28</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>821.58</v>
+        <v>253.46</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>805.25</v>
+        <v>245.3</v>
       </c>
       <c r="H149" s="6" t="n">
         <v>1.56</v>
@@ -18891,30 +18891,30 @@
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>CTAS</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Cintas</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D167" s="5" t="n">
-        <v>197.64</v>
+        <v>930.91</v>
       </c>
       <c r="E167" s="5" t="n">
-        <v>199.91</v>
+        <v>941.65</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>199.91</v>
+        <v>954.49</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>191.97</v>
+        <v>929.04</v>
       </c>
       <c r="H167" s="6" t="n">
         <v>1.15</v>
@@ -18923,30 +18923,30 @@
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>CTAS</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Cintas</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D168" s="5" t="n">
-        <v>930.91</v>
+        <v>197.64</v>
       </c>
       <c r="E168" s="5" t="n">
-        <v>941.65</v>
+        <v>199.91</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>954.49</v>
+        <v>199.91</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>929.04</v>
+        <v>191.97</v>
       </c>
       <c r="H168" s="6" t="n">
         <v>1.15</v>
@@ -19755,30 +19755,30 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>269.99</v>
+        <v>137.99</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>271.22</v>
+        <v>138.63</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>271.22</v>
+        <v>140.63</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>269.17</v>
+        <v>137.34</v>
       </c>
       <c r="H194" s="6" t="n">
         <v>0.46</v>
@@ -19787,30 +19787,30 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>137.99</v>
+        <v>269.99</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>138.63</v>
+        <v>271.22</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>140.63</v>
+        <v>271.22</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>137.34</v>
+        <v>269.17</v>
       </c>
       <c r="H195" s="6" t="n">
         <v>0.46</v>
@@ -20075,12 +20075,12 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -20089,16 +20089,16 @@
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>72.37</v>
+        <v>88.84</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>72.61</v>
+        <v>89.13</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>72.61</v>
+        <v>89.13</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>72.37</v>
+        <v>85.05</v>
       </c>
       <c r="H204" s="6" t="n">
         <v>0.33</v>
@@ -20107,12 +20107,12 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -20121,16 +20121,16 @@
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>88.84</v>
+        <v>72.37</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>89.13</v>
+        <v>72.61</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>89.13</v>
+        <v>72.61</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>85.05</v>
+        <v>72.37</v>
       </c>
       <c r="H205" s="6" t="n">
         <v>0.33</v>
@@ -20331,30 +20331,30 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CASY</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D212" s="5" t="n">
-        <v>55.29</v>
+        <v>597.48</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>55.38</v>
+        <v>598.46</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>56.07</v>
+        <v>598.85</v>
       </c>
       <c r="G212" s="5" t="n">
-        <v>54.12</v>
+        <v>584.83</v>
       </c>
       <c r="H212" s="6" t="n">
         <v>0.16</v>
@@ -20363,30 +20363,30 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>CASY</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>597.48</v>
+        <v>55.29</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>598.46</v>
+        <v>55.38</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>598.85</v>
+        <v>56.07</v>
       </c>
       <c r="G213" s="5" t="n">
-        <v>584.83</v>
+        <v>54.12</v>
       </c>
       <c r="H213" s="6" t="n">
         <v>0.16</v>
@@ -20651,30 +20651,30 @@
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>CVNA</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Carvana</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D222" s="5" t="n">
-        <v>65.11</v>
+        <v>376.9</v>
       </c>
       <c r="E222" s="5" t="n">
-        <v>65.06</v>
+        <v>376.59</v>
       </c>
       <c r="F222" s="5" t="n">
-        <v>67.18000000000001</v>
+        <v>377.56</v>
       </c>
       <c r="G222" s="5" t="n">
-        <v>63.95</v>
+        <v>371.29</v>
       </c>
       <c r="H222" s="7" t="n">
         <v>-0.08</v>
@@ -20683,30 +20683,30 @@
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>CVNA</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Carvana</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D223" s="5" t="n">
-        <v>25.4</v>
+        <v>65.11</v>
       </c>
       <c r="E223" s="5" t="n">
-        <v>25.38</v>
+        <v>65.06</v>
       </c>
       <c r="F223" s="5" t="n">
-        <v>25.45</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="G223" s="5" t="n">
-        <v>25.1</v>
+        <v>63.95</v>
       </c>
       <c r="H223" s="7" t="n">
         <v>-0.08</v>
@@ -20715,30 +20715,30 @@
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D224" s="5" t="n">
-        <v>376.9</v>
+        <v>25.4</v>
       </c>
       <c r="E224" s="5" t="n">
-        <v>376.59</v>
+        <v>25.38</v>
       </c>
       <c r="F224" s="5" t="n">
-        <v>377.56</v>
+        <v>25.45</v>
       </c>
       <c r="G224" s="5" t="n">
-        <v>371.29</v>
+        <v>25.1</v>
       </c>
       <c r="H224" s="7" t="n">
         <v>-0.08</v>
@@ -21323,30 +21323,30 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Coca-Cola Company (The)</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>405.32</v>
+        <v>88.25</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>403.3</v>
+        <v>87.81</v>
       </c>
       <c r="F243" s="5" t="n">
-        <v>406.5</v>
+        <v>88.61</v>
       </c>
       <c r="G243" s="5" t="n">
-        <v>402.44</v>
+        <v>87.12</v>
       </c>
       <c r="H243" s="7" t="n">
         <v>-0.5</v>
@@ -21355,30 +21355,30 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola Company (The)</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D244" s="5" t="n">
-        <v>88.25</v>
+        <v>405.32</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>87.81</v>
+        <v>403.3</v>
       </c>
       <c r="F244" s="5" t="n">
-        <v>88.61</v>
+        <v>406.5</v>
       </c>
       <c r="G244" s="5" t="n">
-        <v>87.12</v>
+        <v>402.44</v>
       </c>
       <c r="H244" s="7" t="n">
         <v>-0.5</v>
@@ -21611,30 +21611,30 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>942</v>
+        <v>294.2</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>935.45</v>
+        <v>292.14</v>
       </c>
       <c r="F252" s="5" t="n">
-        <v>959.39</v>
+        <v>297.12</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>923.29</v>
+        <v>292.14</v>
       </c>
       <c r="H252" s="7" t="n">
         <v>-0.7</v>
@@ -21643,30 +21643,30 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>294.2</v>
+        <v>942</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>292.14</v>
+        <v>935.45</v>
       </c>
       <c r="F253" s="5" t="n">
-        <v>297.12</v>
+        <v>959.39</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>292.14</v>
+        <v>923.29</v>
       </c>
       <c r="H253" s="7" t="n">
         <v>-0.7</v>
@@ -21995,30 +21995,30 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>VICI</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Vici Properties</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>23.72</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>23.51</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F264" s="5" t="n">
-        <v>24.05</v>
+        <v>73.36</v>
       </c>
       <c r="G264" s="5" t="n">
-        <v>23.27</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="H264" s="7" t="n">
         <v>-0.89</v>
@@ -22027,30 +22027,30 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>VICI</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Vici Properties</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>71.79000000000001</v>
+        <v>23.72</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>71.15000000000001</v>
+        <v>23.51</v>
       </c>
       <c r="F265" s="5" t="n">
-        <v>73.36</v>
+        <v>24.05</v>
       </c>
       <c r="G265" s="5" t="n">
-        <v>71.15000000000001</v>
+        <v>23.27</v>
       </c>
       <c r="H265" s="7" t="n">
         <v>-0.89</v>
@@ -22155,30 +22155,30 @@
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Alphabet Inc. (Class C)</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D269" s="5" t="n">
-        <v>344.41</v>
+        <v>115</v>
       </c>
       <c r="E269" s="5" t="n">
-        <v>341.08</v>
+        <v>113.88</v>
       </c>
       <c r="F269" s="5" t="n">
-        <v>350.87</v>
+        <v>115</v>
       </c>
       <c r="G269" s="5" t="n">
-        <v>334.98</v>
+        <v>110.51</v>
       </c>
       <c r="H269" s="7" t="n">
         <v>-0.97</v>
@@ -22187,30 +22187,30 @@
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Alphabet Inc. (Class C)</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D270" s="5" t="n">
-        <v>115</v>
+        <v>344.41</v>
       </c>
       <c r="E270" s="5" t="n">
-        <v>113.88</v>
+        <v>341.08</v>
       </c>
       <c r="F270" s="5" t="n">
-        <v>115</v>
+        <v>350.87</v>
       </c>
       <c r="G270" s="5" t="n">
-        <v>110.51</v>
+        <v>334.98</v>
       </c>
       <c r="H270" s="7" t="n">
         <v>-0.97</v>
@@ -22283,30 +22283,30 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>CPT</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Altria</t>
+          <t>Camden Property Trust</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>69.52</v>
+        <v>99.12</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>68.81999999999999</v>
+        <v>98.12</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>69.52</v>
+        <v>99.31</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>68.53</v>
+        <v>97.41</v>
       </c>
       <c r="H273" s="7" t="n">
         <v>-1.01</v>
@@ -22347,30 +22347,30 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>CPT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Camden Property Trust</t>
+          <t>Altria</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>99.12</v>
+        <v>69.52</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>98.12</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="F275" s="5" t="n">
-        <v>99.31</v>
+        <v>69.52</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>97.41</v>
+        <v>68.53</v>
       </c>
       <c r="H275" s="7" t="n">
         <v>-1.01</v>
@@ -22699,30 +22699,30 @@
     <row r="286">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D286" s="5" t="n">
-        <v>102.61</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E286" s="5" t="n">
-        <v>101.29</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="F286" s="5" t="n">
-        <v>103.69</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="G286" s="5" t="n">
-        <v>101.07</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="H286" s="7" t="n">
         <v>-1.29</v>
@@ -22731,30 +22731,30 @@
     <row r="287">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D287" s="5" t="n">
-        <v>86.15000000000001</v>
+        <v>102.61</v>
       </c>
       <c r="E287" s="5" t="n">
-        <v>85.04000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="F287" s="5" t="n">
-        <v>88.04000000000001</v>
+        <v>103.69</v>
       </c>
       <c r="G287" s="5" t="n">
-        <v>83.95999999999999</v>
+        <v>101.07</v>
       </c>
       <c r="H287" s="7" t="n">
         <v>-1.29</v>
@@ -23403,30 +23403,30 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>TMUS</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>T-Mobile US</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>168.18</v>
+        <v>237.92</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>165.43</v>
+        <v>234.02</v>
       </c>
       <c r="F308" s="5" t="n">
-        <v>168.18</v>
+        <v>238.22</v>
       </c>
       <c r="G308" s="5" t="n">
-        <v>162.41</v>
+        <v>233.28</v>
       </c>
       <c r="H308" s="7" t="n">
         <v>-1.64</v>
@@ -23435,30 +23435,30 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>TMUS</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>T-Mobile US</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>237.92</v>
+        <v>168.18</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>234.02</v>
+        <v>165.43</v>
       </c>
       <c r="F309" s="5" t="n">
-        <v>238.22</v>
+        <v>168.18</v>
       </c>
       <c r="G309" s="5" t="n">
-        <v>233.28</v>
+        <v>162.41</v>
       </c>
       <c r="H309" s="7" t="n">
         <v>-1.64</v>
@@ -23467,30 +23467,30 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>103.17</v>
+        <v>192.49</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>101.45</v>
+        <v>189.28</v>
       </c>
       <c r="F310" s="5" t="n">
-        <v>103.48</v>
+        <v>196.08</v>
       </c>
       <c r="G310" s="5" t="n">
-        <v>100.9</v>
+        <v>188.49</v>
       </c>
       <c r="H310" s="7" t="n">
         <v>-1.67</v>
@@ -23499,30 +23499,30 @@
     <row r="311">
       <c r="A311" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D311" s="5" t="n">
-        <v>192.49</v>
+        <v>103.17</v>
       </c>
       <c r="E311" s="5" t="n">
-        <v>189.28</v>
+        <v>101.45</v>
       </c>
       <c r="F311" s="5" t="n">
-        <v>196.08</v>
+        <v>103.48</v>
       </c>
       <c r="G311" s="5" t="n">
-        <v>188.49</v>
+        <v>100.9</v>
       </c>
       <c r="H311" s="7" t="n">
         <v>-1.67</v>
@@ -23755,30 +23755,30 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>DLR</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Atmos Energy</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>160.3</v>
+        <v>182.12</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>157.21</v>
+        <v>178.61</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>160.3</v>
+        <v>186.33</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>156.24</v>
+        <v>178.61</v>
       </c>
       <c r="H319" s="7" t="n">
         <v>-1.93</v>
@@ -23787,30 +23787,30 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>DLR</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Atmos Energy</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>182.12</v>
+        <v>160.3</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>178.61</v>
+        <v>157.21</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>186.33</v>
+        <v>160.3</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>178.61</v>
+        <v>156.24</v>
       </c>
       <c r="H320" s="7" t="n">
         <v>-1.93</v>
@@ -25131,30 +25131,30 @@
     <row r="362">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Loews Corporation</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D362" s="5" t="n">
-        <v>218.07</v>
+        <v>107.77</v>
       </c>
       <c r="E362" s="5" t="n">
-        <v>212.1</v>
+        <v>104.82</v>
       </c>
       <c r="F362" s="5" t="n">
-        <v>218.07</v>
+        <v>107.77</v>
       </c>
       <c r="G362" s="5" t="n">
-        <v>212.1</v>
+        <v>104.82</v>
       </c>
       <c r="H362" s="7" t="n">
         <v>-2.74</v>
@@ -25163,30 +25163,30 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Loews Corporation</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>107.77</v>
+        <v>218.07</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>104.82</v>
+        <v>212.1</v>
       </c>
       <c r="F363" s="5" t="n">
-        <v>107.77</v>
+        <v>218.07</v>
       </c>
       <c r="G363" s="5" t="n">
-        <v>104.82</v>
+        <v>212.1</v>
       </c>
       <c r="H363" s="7" t="n">
         <v>-2.74</v>
@@ -25195,30 +25195,30 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>271.22</v>
+        <v>102.23</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>263.67</v>
+        <v>99.39</v>
       </c>
       <c r="F364" s="5" t="n">
-        <v>271.22</v>
+        <v>102.23</v>
       </c>
       <c r="G364" s="5" t="n">
-        <v>263.11</v>
+        <v>99.2</v>
       </c>
       <c r="H364" s="7" t="n">
         <v>-2.78</v>
@@ -25227,30 +25227,30 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>102.23</v>
+        <v>271.22</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>99.39</v>
+        <v>263.67</v>
       </c>
       <c r="F365" s="5" t="n">
-        <v>102.23</v>
+        <v>271.22</v>
       </c>
       <c r="G365" s="5" t="n">
-        <v>99.2</v>
+        <v>263.11</v>
       </c>
       <c r="H365" s="7" t="n">
         <v>-2.78</v>
@@ -25387,30 +25387,30 @@
     <row r="370">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B370" s="4" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D370" s="5" t="n">
-        <v>40.58</v>
+        <v>181.29</v>
       </c>
       <c r="E370" s="5" t="n">
-        <v>39.42</v>
+        <v>176.11</v>
       </c>
       <c r="F370" s="5" t="n">
-        <v>40.58</v>
+        <v>186.11</v>
       </c>
       <c r="G370" s="5" t="n">
-        <v>39.12</v>
+        <v>176.11</v>
       </c>
       <c r="H370" s="7" t="n">
         <v>-2.86</v>
@@ -25419,30 +25419,30 @@
     <row r="371">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D371" s="5" t="n">
-        <v>181.29</v>
+        <v>40.58</v>
       </c>
       <c r="E371" s="5" t="n">
-        <v>176.11</v>
+        <v>39.42</v>
       </c>
       <c r="F371" s="5" t="n">
-        <v>186.11</v>
+        <v>40.58</v>
       </c>
       <c r="G371" s="5" t="n">
-        <v>176.11</v>
+        <v>39.12</v>
       </c>
       <c r="H371" s="7" t="n">
         <v>-2.86</v>
@@ -25643,30 +25643,30 @@
     <row r="378">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="B378" s="4" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Travelers Companies (The)</t>
         </is>
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D378" s="5" t="n">
-        <v>85.52</v>
+        <v>374.62</v>
       </c>
       <c r="E378" s="5" t="n">
-        <v>82.88</v>
+        <v>363.04</v>
       </c>
       <c r="F378" s="5" t="n">
-        <v>85.52</v>
+        <v>374.62</v>
       </c>
       <c r="G378" s="5" t="n">
-        <v>82.88</v>
+        <v>360.39</v>
       </c>
       <c r="H378" s="7" t="n">
         <v>-3.09</v>
@@ -25675,30 +25675,30 @@
     <row r="379">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>Travelers Companies (The)</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D379" s="5" t="n">
-        <v>374.62</v>
+        <v>85.52</v>
       </c>
       <c r="E379" s="5" t="n">
-        <v>363.04</v>
+        <v>82.88</v>
       </c>
       <c r="F379" s="5" t="n">
-        <v>374.62</v>
+        <v>85.52</v>
       </c>
       <c r="G379" s="5" t="n">
-        <v>360.39</v>
+        <v>82.88</v>
       </c>
       <c r="H379" s="7" t="n">
         <v>-3.09</v>
@@ -25835,12 +25835,12 @@
     <row r="384">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>NOC</t>
         </is>
       </c>
       <c r="B384" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Northrop Grumman</t>
         </is>
       </c>
       <c r="C384" s="4" t="inlineStr">
@@ -25849,16 +25849,16 @@
         </is>
       </c>
       <c r="D384" s="5" t="n">
-        <v>127.69</v>
+        <v>527.39</v>
       </c>
       <c r="E384" s="5" t="n">
-        <v>123.61</v>
+        <v>510.52</v>
       </c>
       <c r="F384" s="5" t="n">
-        <v>128.23</v>
+        <v>527.39</v>
       </c>
       <c r="G384" s="5" t="n">
-        <v>123.31</v>
+        <v>508.98</v>
       </c>
       <c r="H384" s="7" t="n">
         <v>-3.2</v>
@@ -25867,12 +25867,12 @@
     <row r="385">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>NOC</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>Northrop Grumman</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
@@ -25881,16 +25881,16 @@
         </is>
       </c>
       <c r="D385" s="5" t="n">
-        <v>527.39</v>
+        <v>127.69</v>
       </c>
       <c r="E385" s="5" t="n">
-        <v>510.52</v>
+        <v>123.61</v>
       </c>
       <c r="F385" s="5" t="n">
-        <v>527.39</v>
+        <v>128.23</v>
       </c>
       <c r="G385" s="5" t="n">
-        <v>508.98</v>
+        <v>123.31</v>
       </c>
       <c r="H385" s="7" t="n">
         <v>-3.2</v>
@@ -26091,30 +26091,30 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>ETR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Entergy</t>
+          <t>Occidental Petroleum</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>102.01</v>
+        <v>58.84</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>98.56999999999999</v>
+        <v>56.86</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>102.01</v>
+        <v>58.84</v>
       </c>
       <c r="G392" s="5" t="n">
-        <v>98.16</v>
+        <v>56.31</v>
       </c>
       <c r="H392" s="7" t="n">
         <v>-3.37</v>
@@ -26123,30 +26123,30 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ETR</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Occidental Petroleum</t>
+          <t>Entergy</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>58.84</v>
+        <v>102.01</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>56.86</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="F393" s="5" t="n">
-        <v>58.84</v>
+        <v>102.01</v>
       </c>
       <c r="G393" s="5" t="n">
-        <v>56.31</v>
+        <v>98.16</v>
       </c>
       <c r="H393" s="7" t="n">
         <v>-3.37</v>
@@ -26475,30 +26475,30 @@
     <row r="404">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>TYL</t>
         </is>
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D404" s="5" t="n">
-        <v>175.41</v>
+        <v>337.5</v>
       </c>
       <c r="E404" s="5" t="n">
-        <v>169.21</v>
+        <v>325.57</v>
       </c>
       <c r="F404" s="5" t="n">
-        <v>175.41</v>
+        <v>337.5</v>
       </c>
       <c r="G404" s="5" t="n">
-        <v>168.65</v>
+        <v>325.57</v>
       </c>
       <c r="H404" s="7" t="n">
         <v>-3.53</v>
@@ -26507,30 +26507,30 @@
     <row r="405">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>TYL</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D405" s="5" t="n">
-        <v>337.5</v>
+        <v>175.41</v>
       </c>
       <c r="E405" s="5" t="n">
-        <v>325.57</v>
+        <v>169.21</v>
       </c>
       <c r="F405" s="5" t="n">
-        <v>337.5</v>
+        <v>175.41</v>
       </c>
       <c r="G405" s="5" t="n">
-        <v>325.57</v>
+        <v>168.65</v>
       </c>
       <c r="H405" s="7" t="n">
         <v>-3.53</v>
@@ -26603,30 +26603,30 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>ECHO</t>
+          <t>MNST</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Monster Beverage</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>93.45999999999999</v>
+        <v>44.71</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>90.11</v>
+        <v>43.11</v>
       </c>
       <c r="F408" s="5" t="n">
-        <v>95.45999999999999</v>
+        <v>44.71</v>
       </c>
       <c r="G408" s="5" t="n">
-        <v>90.11</v>
+        <v>42.67</v>
       </c>
       <c r="H408" s="7" t="n">
         <v>-3.58</v>
@@ -26635,30 +26635,30 @@
     <row r="409">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>MNST</t>
+          <t>ECHO</t>
         </is>
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>Monster Beverage</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D409" s="5" t="n">
-        <v>44.71</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="E409" s="5" t="n">
-        <v>43.11</v>
+        <v>90.11</v>
       </c>
       <c r="F409" s="5" t="n">
-        <v>44.71</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="G409" s="5" t="n">
-        <v>42.67</v>
+        <v>90.11</v>
       </c>
       <c r="H409" s="7" t="n">
         <v>-3.58</v>
@@ -26763,30 +26763,30 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>65.34</v>
+        <v>86.12</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>62.95</v>
+        <v>82.97</v>
       </c>
       <c r="F413" s="5" t="n">
-        <v>65.34</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="G413" s="5" t="n">
-        <v>62.77</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H413" s="7" t="n">
         <v>-3.66</v>
@@ -26795,30 +26795,30 @@
     <row r="414">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D414" s="5" t="n">
-        <v>86.12</v>
+        <v>65.34</v>
       </c>
       <c r="E414" s="5" t="n">
-        <v>82.97</v>
+        <v>62.95</v>
       </c>
       <c r="F414" s="5" t="n">
-        <v>86.54000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="G414" s="5" t="n">
-        <v>81.90000000000001</v>
+        <v>62.77</v>
       </c>
       <c r="H414" s="7" t="n">
         <v>-3.66</v>
@@ -26987,30 +26987,30 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>92.13</v>
+        <v>13.21</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>88.64</v>
+        <v>12.71</v>
       </c>
       <c r="F420" s="5" t="n">
-        <v>92.13</v>
+        <v>13.21</v>
       </c>
       <c r="G420" s="5" t="n">
-        <v>88.51000000000001</v>
+        <v>12.6</v>
       </c>
       <c r="H420" s="7" t="n">
         <v>-3.79</v>
@@ -27019,30 +27019,30 @@
     <row r="421">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D421" s="5" t="n">
-        <v>13.21</v>
+        <v>92.13</v>
       </c>
       <c r="E421" s="5" t="n">
-        <v>12.71</v>
+        <v>88.64</v>
       </c>
       <c r="F421" s="5" t="n">
-        <v>13.21</v>
+        <v>92.13</v>
       </c>
       <c r="G421" s="5" t="n">
-        <v>12.6</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="H421" s="7" t="n">
         <v>-3.79</v>
@@ -27307,30 +27307,30 @@
     <row r="430">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D430" s="5" t="n">
-        <v>447.76</v>
+        <v>69.77</v>
       </c>
       <c r="E430" s="5" t="n">
-        <v>430.11</v>
+        <v>67.02</v>
       </c>
       <c r="F430" s="5" t="n">
-        <v>459.32</v>
+        <v>69.77</v>
       </c>
       <c r="G430" s="5" t="n">
-        <v>430.11</v>
+        <v>66.56</v>
       </c>
       <c r="H430" s="7" t="n">
         <v>-3.94</v>
@@ -27339,30 +27339,30 @@
     <row r="431">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D431" s="5" t="n">
-        <v>69.77</v>
+        <v>447.76</v>
       </c>
       <c r="E431" s="5" t="n">
-        <v>67.02</v>
+        <v>430.11</v>
       </c>
       <c r="F431" s="5" t="n">
-        <v>69.77</v>
+        <v>459.32</v>
       </c>
       <c r="G431" s="5" t="n">
-        <v>66.56</v>
+        <v>430.11</v>
       </c>
       <c r="H431" s="7" t="n">
         <v>-3.94</v>
@@ -27435,30 +27435,30 @@
     <row r="434">
       <c r="A434" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>DGX</t>
         </is>
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D434" s="5" t="n">
-        <v>42.07</v>
+        <v>246.45</v>
       </c>
       <c r="E434" s="5" t="n">
-        <v>40.34</v>
+        <v>236.32</v>
       </c>
       <c r="F434" s="5" t="n">
-        <v>42.07</v>
+        <v>246.45</v>
       </c>
       <c r="G434" s="5" t="n">
-        <v>40.2</v>
+        <v>233</v>
       </c>
       <c r="H434" s="7" t="n">
         <v>-4.11</v>
@@ -27467,30 +27467,30 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>DGX</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>246.45</v>
+        <v>42.07</v>
       </c>
       <c r="E435" s="5" t="n">
-        <v>236.32</v>
+        <v>40.34</v>
       </c>
       <c r="F435" s="5" t="n">
-        <v>246.45</v>
+        <v>42.07</v>
       </c>
       <c r="G435" s="5" t="n">
-        <v>233</v>
+        <v>40.2</v>
       </c>
       <c r="H435" s="7" t="n">
         <v>-4.11</v>
@@ -27595,30 +27595,30 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>News Corp (Class A)</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>29.78</v>
+        <v>45.26</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>28.49</v>
+        <v>43.3</v>
       </c>
       <c r="F439" s="5" t="n">
-        <v>29.78</v>
+        <v>45.26</v>
       </c>
       <c r="G439" s="5" t="n">
-        <v>28.12</v>
+        <v>43.19</v>
       </c>
       <c r="H439" s="7" t="n">
         <v>-4.33</v>
@@ -27627,30 +27627,30 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>News Corp (Class A)</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D440" s="5" t="n">
-        <v>45.26</v>
+        <v>29.78</v>
       </c>
       <c r="E440" s="5" t="n">
-        <v>43.3</v>
+        <v>28.49</v>
       </c>
       <c r="F440" s="5" t="n">
-        <v>45.26</v>
+        <v>29.78</v>
       </c>
       <c r="G440" s="5" t="n">
-        <v>43.19</v>
+        <v>28.12</v>
       </c>
       <c r="H440" s="7" t="n">
         <v>-4.33</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 24-&gt;Sep 25) and rolling 5-day  |  updated 2026-09-26 08:07</t>
+          <t>Daily (Sep 24-&gt;Sep 25) and rolling 5-day  |  updated 2026-09-27 08:43</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 24 close to Sep 25 close  |  503 companies  |  updated 2026-09-27 08:43</t>
+          <t>Sep 24 close to Sep 25 close  |  503 companies  |  updated 2026-09-28 09:08</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 18 close to Sep 25 close  |  503 companies  |  updated 2026-09-27 08:43</t>
+          <t>Sep 18 close to Sep 25 close  |  503 companies  |  updated 2026-09-28 09:08</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Sep 24-&gt;Sep 25) and rolling 5-day  |  updated 2026-09-27 08:43</t>
+          <t>Daily (Sep 24-&gt;Sep 25) and rolling 5-day  |  updated 2026-09-28 09:08</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 01 close to Oct 02 close  |  503 companies  |  updated 2026-10-03 08:44</t>
+          <t>Oct 01 close to Oct 02 close  |  503 companies  |  updated 2026-10-04 08:59</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 25 close to Oct 02 close  |  503 companies  |  updated 2026-10-03 08:44</t>
+          <t>Sep 25 close to Oct 02 close  |  503 companies  |  updated 2026-10-04 08:59</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 01-&gt;Oct 02) and rolling 5-day  |  updated 2026-10-03 08:44</t>
+          <t>Daily (Oct 01-&gt;Oct 02) and rolling 5-day  |  updated 2026-10-04 08:59</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 01 close to Oct 02 close  |  503 companies  |  updated 2026-10-04 08:59</t>
+          <t>Oct 01 close to Oct 02 close  |  503 companies  |  updated 2026-10-05 09:49</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sep 25 close to Oct 02 close  |  503 companies  |  updated 2026-10-04 08:59</t>
+          <t>Sep 25 close to Oct 02 close  |  503 companies  |  updated 2026-10-05 09:49</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 01-&gt;Oct 02) and rolling 5-day  |  updated 2026-10-04 08:59</t>
+          <t>Daily (Oct 01-&gt;Oct 02) and rolling 5-day  |  updated 2026-10-05 09:49</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 08 close to Oct 09 close  |  503 companies  |  updated 2026-10-10 09:13</t>
+          <t>Oct 08 close to Oct 09 close  |  503 companies  |  updated 2026-10-11 09:30</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>73.08</v>
+        <v>64.22</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>74.81</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>2.37</v>
@@ -1817,12 +1817,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>64.22</v>
+        <v>73.08</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>74.81</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>2.37</v>
@@ -1947,24 +1947,24 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>22.75</v>
+        <v>156.47</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>23.25</v>
+        <v>159.91</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>2.2</v>
@@ -1973,24 +1973,24 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>156.47</v>
+        <v>22.75</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>159.91</v>
+        <v>23.25</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>2.2</v>
@@ -2051,24 +2051,24 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>119.22</v>
+        <v>415.41</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>121.68</v>
+        <v>423.96</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>2.06</v>
@@ -2077,24 +2077,24 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>415.41</v>
+        <v>119.22</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>423.96</v>
+        <v>121.68</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>2.06</v>
@@ -2129,12 +2129,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>297.79</v>
+        <v>574.55</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>303.74</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>2</v>
@@ -2155,12 +2155,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>574.55</v>
+        <v>297.79</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>586.0599999999999</v>
+        <v>303.74</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>2</v>
@@ -2675,24 +2675,24 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>27.82</v>
+        <v>280.8</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>28.28</v>
+        <v>285.43</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>1.65</v>
@@ -2701,24 +2701,24 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>280.8</v>
+        <v>27.82</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>285.43</v>
+        <v>28.28</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>1.65</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>272.42</v>
+        <v>56.42</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>276.47</v>
+        <v>57.26</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>1.49</v>
@@ -3221,24 +3221,24 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>56.42</v>
+        <v>272.42</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>57.26</v>
+        <v>276.47</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>1.49</v>
@@ -3533,24 +3533,24 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>503.25</v>
+        <v>112.97</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>510.08</v>
+        <v>114.51</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>1.36</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>112.97</v>
+        <v>503.25</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>114.51</v>
+        <v>510.08</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>1.36</v>
@@ -3585,24 +3585,24 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>417.31</v>
+        <v>1529.46</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>422.89</v>
+        <v>1549.99</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>1.34</v>
@@ -3611,24 +3611,24 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>1529.46</v>
+        <v>417.31</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>1549.99</v>
+        <v>422.89</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>1.34</v>
@@ -3637,24 +3637,24 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>361.08</v>
+        <v>152.16</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>365.88</v>
+        <v>154.18</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>1.33</v>
@@ -3663,24 +3663,24 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>152.16</v>
+        <v>361.08</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>154.18</v>
+        <v>365.88</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>1.33</v>
@@ -3793,24 +3793,24 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>143</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>65.36</v>
+        <v>144.82</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>1.27</v>
@@ -3819,24 +3819,24 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>143</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>144.82</v>
+        <v>65.36</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>1.27</v>
@@ -3897,24 +3897,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>175.49</v>
+        <v>128.08</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>177.63</v>
+        <v>129.64</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>1.22</v>
@@ -3923,24 +3923,24 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>128.08</v>
+        <v>175.49</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>129.64</v>
+        <v>177.63</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>1.22</v>
@@ -3949,12 +3949,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>424.51</v>
+        <v>222.56</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>429.65</v>
+        <v>225.26</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>1.21</v>
@@ -4001,12 +4001,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>222.56</v>
+        <v>424.51</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>225.26</v>
+        <v>429.65</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>1.21</v>
@@ -4131,24 +4131,24 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Extra Space Storage</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>133.12</v>
+        <v>17.44</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>134.65</v>
+        <v>17.64</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>1.15</v>
@@ -4183,24 +4183,24 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Extra Space Storage</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>17.44</v>
+        <v>133.12</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>17.64</v>
+        <v>134.65</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>1.15</v>
@@ -4547,12 +4547,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>323.29</v>
+        <v>2910.54</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>326.56</v>
+        <v>2939.85</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>1.01</v>
@@ -4573,24 +4573,24 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
-        <v>393.31</v>
+        <v>323.29</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>397.28</v>
+        <v>326.56</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>1.01</v>
@@ -4599,24 +4599,24 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>2910.54</v>
+        <v>393.31</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>2939.85</v>
+        <v>397.28</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>1.01</v>
@@ -4677,24 +4677,24 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>97.98</v>
+        <v>78</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>98.92</v>
+        <v>78.75</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>0.96</v>
@@ -4703,24 +4703,24 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Pinnacle West Capital</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>78</v>
+        <v>97.98</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>78.75</v>
+        <v>98.92</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>0.96</v>
@@ -4807,24 +4807,24 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>55.02</v>
+        <v>175.72</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>55.53</v>
+        <v>177.35</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0.93</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>175.72</v>
+        <v>55.02</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>177.35</v>
+        <v>55.53</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>0.93</v>
@@ -4963,24 +4963,24 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>511.05</v>
+        <v>357.78</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>515.62</v>
+        <v>360.98</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>0.89</v>
@@ -4989,24 +4989,24 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
-        <v>357.78</v>
+        <v>104.23</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>360.98</v>
+        <v>105.16</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>0.89</v>
@@ -5015,24 +5015,24 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>104.23</v>
+        <v>92.5</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>105.16</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0.89</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>92.5</v>
+        <v>511.05</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>515.62</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>0.89</v>
@@ -5145,24 +5145,24 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>305.62</v>
+        <v>26.13</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>308.2</v>
+        <v>26.35</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>0.84</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>26.13</v>
+        <v>305.62</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>26.35</v>
+        <v>308.2</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>0.84</v>
@@ -5353,24 +5353,24 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>International Paper</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>31.88</v>
+        <v>363.27</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>32.12</v>
+        <v>366</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>0.75</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>International Paper</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>363.27</v>
+        <v>31.88</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>366</v>
+        <v>32.12</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>0.75</v>
@@ -5509,24 +5509,24 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D196" s="5" t="n">
-        <v>110.56</v>
+        <v>101.99</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>111.35</v>
+        <v>102.71</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>0.71</v>
@@ -5535,24 +5535,24 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
-        <v>101.99</v>
+        <v>110.56</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>102.71</v>
+        <v>111.35</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>0.71</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>71.84</v>
+        <v>561.67</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>72.28</v>
+        <v>565.12</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>0.61</v>
@@ -5743,24 +5743,24 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>561.67</v>
+        <v>71.84</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>565.12</v>
+        <v>72.28</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>0.61</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>116.19</v>
+        <v>227.8</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>116.86</v>
+        <v>229.13</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>0.58</v>
@@ -5873,24 +5873,24 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>227.8</v>
+        <v>116.19</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>229.13</v>
+        <v>116.86</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>0.58</v>
@@ -5899,24 +5899,24 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>73.36</v>
+        <v>520.4</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>73.78</v>
+        <v>523.39</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>0.57</v>
@@ -5925,12 +5925,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D212" s="5" t="n">
-        <v>40.53</v>
+        <v>73.36</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>40.76</v>
+        <v>73.78</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>0.57</v>
@@ -5951,24 +5951,24 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>520.4</v>
+        <v>40.53</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>523.39</v>
+        <v>40.76</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>0.57</v>
@@ -6003,24 +6003,24 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>American Water Works</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
-        <v>128.18</v>
+        <v>206.6</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>128.88</v>
+        <v>207.73</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>0.55</v>
@@ -6029,12 +6029,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>American Water Works</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>80.52</v>
+        <v>128.18</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>128.88</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>0.55</v>
@@ -6055,24 +6055,24 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>206.6</v>
+        <v>80.52</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>207.73</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F217" s="6" t="n">
         <v>0.55</v>
@@ -6107,24 +6107,24 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>155.35</v>
+        <v>999.35</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>156.19</v>
+        <v>1004.73</v>
       </c>
       <c r="F219" s="6" t="n">
         <v>0.54</v>
@@ -6133,24 +6133,24 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>796.1799999999999</v>
+        <v>155.35</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>800.47</v>
+        <v>156.19</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>0.54</v>
@@ -6159,12 +6159,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>999.35</v>
+        <v>796.1799999999999</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>1004.73</v>
+        <v>800.47</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>0.54</v>
@@ -6471,12 +6471,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>96.48</v>
+        <v>94.13</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>96.93000000000001</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F233" s="6" t="n">
         <v>0.47</v>
@@ -6497,12 +6497,12 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>94.13</v>
+        <v>96.48</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>94.56999999999999</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="F234" s="6" t="n">
         <v>0.47</v>
@@ -6627,24 +6627,24 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>481.7</v>
+        <v>358.88</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>483.73</v>
+        <v>360.37</v>
       </c>
       <c r="F239" s="6" t="n">
         <v>0.42</v>
@@ -6653,24 +6653,24 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>150.59</v>
+        <v>481.7</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>151.23</v>
+        <v>483.73</v>
       </c>
       <c r="F240" s="6" t="n">
         <v>0.42</v>
@@ -6705,24 +6705,24 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>358.88</v>
+        <v>150.59</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>360.37</v>
+        <v>151.23</v>
       </c>
       <c r="F242" s="6" t="n">
         <v>0.42</v>
@@ -6731,24 +6731,24 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>122.32</v>
+        <v>326.87</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>122.81</v>
+        <v>328.17</v>
       </c>
       <c r="F243" s="6" t="n">
         <v>0.4</v>
@@ -6757,24 +6757,24 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D244" s="5" t="n">
-        <v>326.87</v>
+        <v>82.56</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>328.17</v>
+        <v>82.89</v>
       </c>
       <c r="F244" s="6" t="n">
         <v>0.4</v>
@@ -6783,24 +6783,24 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>138.59</v>
+        <v>122.32</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>139.15</v>
+        <v>122.81</v>
       </c>
       <c r="F245" s="6" t="n">
         <v>0.4</v>
@@ -6809,24 +6809,24 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>82.56</v>
+        <v>138.59</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>82.89</v>
+        <v>139.15</v>
       </c>
       <c r="F246" s="6" t="n">
         <v>0.4</v>
@@ -6887,24 +6887,24 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>97.73</v>
+        <v>360.14</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>98.11</v>
+        <v>361.54</v>
       </c>
       <c r="F249" s="6" t="n">
         <v>0.39</v>
@@ -6913,24 +6913,24 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>360.14</v>
+        <v>97.73</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>361.54</v>
+        <v>98.11</v>
       </c>
       <c r="F250" s="6" t="n">
         <v>0.39</v>
@@ -6965,24 +6965,24 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>193.73</v>
+        <v>61.41</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>194.45</v>
+        <v>61.64</v>
       </c>
       <c r="F252" s="6" t="n">
         <v>0.37</v>
@@ -6991,24 +6991,24 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>61.41</v>
+        <v>228.42</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>61.64</v>
+        <v>229.26</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0.37</v>
@@ -7017,24 +7017,24 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D254" s="5" t="n">
-        <v>228.42</v>
+        <v>193.73</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>229.26</v>
+        <v>194.45</v>
       </c>
       <c r="F254" s="6" t="n">
         <v>0.37</v>
@@ -7043,24 +7043,24 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Altria</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>71.42</v>
+        <v>115.82</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>71.68000000000001</v>
+        <v>116.24</v>
       </c>
       <c r="F255" s="6" t="n">
         <v>0.36</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Altria</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>115.82</v>
+        <v>71.42</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>116.24</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="F256" s="6" t="n">
         <v>0.36</v>
@@ -7121,24 +7121,24 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>81.76000000000001</v>
+        <v>208.36</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>82.04000000000001</v>
+        <v>209.06</v>
       </c>
       <c r="F258" s="6" t="n">
         <v>0.34</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>200.5</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>201.19</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F259" s="6" t="n">
         <v>0.34</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>208.36</v>
+        <v>200.5</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>209.06</v>
+        <v>201.19</v>
       </c>
       <c r="F261" s="6" t="n">
         <v>0.34</v>
@@ -7251,24 +7251,24 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>44.85</v>
+        <v>507.89</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>45</v>
+        <v>509.59</v>
       </c>
       <c r="F263" s="6" t="n">
         <v>0.33</v>
@@ -7277,12 +7277,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>507.89</v>
+        <v>52.3</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>509.59</v>
+        <v>52.47</v>
       </c>
       <c r="F264" s="6" t="n">
         <v>0.33</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>52.3</v>
+        <v>44.85</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>52.47</v>
+        <v>45</v>
       </c>
       <c r="F265" s="6" t="n">
         <v>0.33</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>Coca-Cola Company (The)</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>22.09</v>
+        <v>87.77</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>22.16</v>
+        <v>88.05</v>
       </c>
       <c r="F266" s="6" t="n">
         <v>0.32</v>
@@ -7355,24 +7355,24 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola Company (The)</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>87.77</v>
+        <v>22.09</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>88.05</v>
+        <v>22.16</v>
       </c>
       <c r="F267" s="6" t="n">
         <v>0.32</v>
@@ -7537,24 +7537,24 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Packaging Corporation of America</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>316.99</v>
+        <v>229.94</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>317.79</v>
+        <v>230.51</v>
       </c>
       <c r="F274" s="6" t="n">
         <v>0.25</v>
@@ -7563,24 +7563,24 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Packaging Corporation of America</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>229.94</v>
+        <v>316.99</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>230.51</v>
+        <v>317.79</v>
       </c>
       <c r="F275" s="6" t="n">
         <v>0.25</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>191.68</v>
+        <v>65.34</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>192.13</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F277" s="6" t="n">
         <v>0.23</v>
@@ -7641,24 +7641,24 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>308.65</v>
+        <v>191.68</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>309.36</v>
+        <v>192.13</v>
       </c>
       <c r="F278" s="6" t="n">
         <v>0.23</v>
@@ -7667,24 +7667,24 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
-        <v>65.34</v>
+        <v>286.52</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>65.48999999999999</v>
+        <v>287.18</v>
       </c>
       <c r="F279" s="6" t="n">
         <v>0.23</v>
@@ -7693,24 +7693,24 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D280" s="5" t="n">
-        <v>274.66</v>
+        <v>159.97</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>275.28</v>
+        <v>160.34</v>
       </c>
       <c r="F280" s="6" t="n">
         <v>0.23</v>
@@ -7719,24 +7719,24 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>286.52</v>
+        <v>274.66</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>287.18</v>
+        <v>275.28</v>
       </c>
       <c r="F281" s="6" t="n">
         <v>0.23</v>
@@ -7771,12 +7771,12 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>159.97</v>
+        <v>308.65</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>160.34</v>
+        <v>309.36</v>
       </c>
       <c r="F283" s="6" t="n">
         <v>0.23</v>
@@ -8005,24 +8005,24 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>165.21</v>
+        <v>58.37</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>165.45</v>
+        <v>58.46</v>
       </c>
       <c r="F292" s="6" t="n">
         <v>0.15</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Broadridge Financial Solutions</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>58.37</v>
+        <v>165.21</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>58.46</v>
+        <v>165.45</v>
       </c>
       <c r="F293" s="6" t="n">
         <v>0.15</v>
@@ -8057,24 +8057,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>54.3</v>
+        <v>103.61</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>54.37</v>
+        <v>103.74</v>
       </c>
       <c r="F294" s="6" t="n">
         <v>0.13</v>
@@ -8083,24 +8083,24 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>103.61</v>
+        <v>276.97</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>103.74</v>
+        <v>277.33</v>
       </c>
       <c r="F295" s="6" t="n">
         <v>0.13</v>
@@ -8109,12 +8109,12 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="D296" s="5" t="n">
-        <v>276.97</v>
+        <v>54.3</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>277.33</v>
+        <v>54.37</v>
       </c>
       <c r="F296" s="6" t="n">
         <v>0.13</v>
@@ -8239,12 +8239,12 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>14.93</v>
+        <v>41.73</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>14.94</v>
+        <v>41.76</v>
       </c>
       <c r="F301" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8265,12 +8265,12 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>41.73</v>
+        <v>14.93</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>41.76</v>
+        <v>14.94</v>
       </c>
       <c r="F302" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8395,24 +8395,24 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>281.69</v>
+        <v>278.2</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>281.83</v>
+        <v>278.34</v>
       </c>
       <c r="F307" s="6" t="n">
         <v>0.05</v>
@@ -8421,24 +8421,24 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>278.2</v>
+        <v>281.69</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>278.34</v>
+        <v>281.83</v>
       </c>
       <c r="F308" s="6" t="n">
         <v>0.05</v>
@@ -8447,24 +8447,24 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>75.52</v>
+        <v>82.14</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>75.55</v>
+        <v>82.17</v>
       </c>
       <c r="F309" s="6" t="n">
         <v>0.04</v>
@@ -8473,24 +8473,24 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Omnicom Group</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>82.14</v>
+        <v>76.45</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>82.17</v>
+        <v>76.48</v>
       </c>
       <c r="F310" s="6" t="n">
         <v>0.04</v>
@@ -8525,24 +8525,24 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Omnicom Group</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>76.45</v>
+        <v>75.52</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>76.48</v>
+        <v>75.55</v>
       </c>
       <c r="F312" s="6" t="n">
         <v>0.04</v>
@@ -8551,24 +8551,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>118.62</v>
+        <v>107.44</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>118.64</v>
+        <v>107.46</v>
       </c>
       <c r="F313" s="6" t="n">
         <v>0.02</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>54.17</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>54.18</v>
+        <v>86.17</v>
       </c>
       <c r="F314" s="6" t="n">
         <v>0.02</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>107.44</v>
+        <v>308.1</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>107.46</v>
+        <v>308.17</v>
       </c>
       <c r="F315" s="6" t="n">
         <v>0.02</v>
@@ -8629,24 +8629,24 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>86.15000000000001</v>
+        <v>118.62</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>86.17</v>
+        <v>118.64</v>
       </c>
       <c r="F316" s="6" t="n">
         <v>0.02</v>
@@ -8655,24 +8655,24 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>216.84</v>
+        <v>54.17</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>216.88</v>
+        <v>54.18</v>
       </c>
       <c r="F317" s="6" t="n">
         <v>0.02</v>
@@ -8681,12 +8681,12 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D318" s="5" t="n">
-        <v>236.92</v>
+        <v>216.84</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>236.97</v>
+        <v>216.88</v>
       </c>
       <c r="F318" s="6" t="n">
         <v>0.02</v>
@@ -8707,24 +8707,24 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>308.1</v>
+        <v>236.92</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>308.17</v>
+        <v>236.97</v>
       </c>
       <c r="F319" s="6" t="n">
         <v>0.02</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>72.45</v>
+        <v>138.75</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>72.45999999999999</v>
+        <v>138.76</v>
       </c>
       <c r="F321" s="6" t="n">
         <v>0.01</v>
@@ -8785,24 +8785,24 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>138.75</v>
+        <v>72.45</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>138.76</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F322" s="6" t="n">
         <v>0.01</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>126.68</v>
+        <v>48.98</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>126.6</v>
+        <v>48.95</v>
       </c>
       <c r="F329" s="7" t="n">
         <v>-0.06</v>
@@ -8993,24 +8993,24 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>32.57</v>
+        <v>126.68</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>32.55</v>
+        <v>126.6</v>
       </c>
       <c r="F330" s="7" t="n">
         <v>-0.06</v>
@@ -9019,12 +9019,12 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>48.98</v>
+        <v>32.57</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>48.95</v>
+        <v>32.55</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>-0.06</v>
@@ -9045,24 +9045,24 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>199.4</v>
+        <v>134.19</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>199.26</v>
+        <v>134.1</v>
       </c>
       <c r="F332" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>188.96</v>
+        <v>175.09</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>188.83</v>
+        <v>174.96</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9097,24 +9097,24 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D334" s="5" t="n">
-        <v>175.09</v>
+        <v>188.96</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>174.96</v>
+        <v>188.83</v>
       </c>
       <c r="F334" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9123,24 +9123,24 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>134.19</v>
+        <v>199.4</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>134.1</v>
+        <v>199.26</v>
       </c>
       <c r="F335" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Huntington Ingalls Industries</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>78.2</v>
+        <v>265.02</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>78.14</v>
+        <v>264.8</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-0.08</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Huntington Ingalls Industries</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>265.02</v>
+        <v>78.2</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>264.8</v>
+        <v>78.14</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-0.08</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>84.65000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>84.55</v>
+        <v>50.64</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-0.12</v>
@@ -9305,24 +9305,24 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>International Flavors &amp; Fragrances</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D342" s="5" t="n">
-        <v>50.7</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>50.64</v>
+        <v>84.55</v>
       </c>
       <c r="F342" s="7" t="n">
         <v>-0.12</v>
@@ -9409,24 +9409,24 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>27.07</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>27.03</v>
+        <v>97.59</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>-0.15</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>97.73999999999999</v>
+        <v>27.07</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>97.59</v>
+        <v>27.03</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-0.15</v>
@@ -9617,24 +9617,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>61.75</v>
+        <v>96.87</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>61.64</v>
+        <v>96.7</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>-0.18</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>96.87</v>
+        <v>61.75</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>96.7</v>
+        <v>61.64</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-0.18</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>72.05</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>71.91</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-0.19</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>75.29000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>75.15000000000001</v>
+        <v>71.91</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-0.19</v>
@@ -9851,12 +9851,12 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>66.11</v>
+        <v>193.71</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>65.95</v>
+        <v>193.24</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-0.24</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>EOG Resources</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>148.51</v>
+        <v>66.11</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>148.16</v>
+        <v>65.95</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-0.24</v>
@@ -9903,24 +9903,24 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>EOG Resources</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>193.71</v>
+        <v>148.51</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>193.24</v>
+        <v>148.16</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>-0.24</v>
@@ -10137,24 +10137,24 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>434.14</v>
+        <v>84.41</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>432.59</v>
+        <v>84.11</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>-0.36</v>
@@ -10163,24 +10163,24 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>84.41</v>
+        <v>434.14</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>84.11</v>
+        <v>432.59</v>
       </c>
       <c r="F375" s="7" t="n">
         <v>-0.36</v>
@@ -10189,24 +10189,24 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D376" s="5" t="n">
-        <v>303.88</v>
+        <v>19.17</v>
       </c>
       <c r="E376" s="5" t="n">
-        <v>302.75</v>
+        <v>19.1</v>
       </c>
       <c r="F376" s="7" t="n">
         <v>-0.37</v>
@@ -10215,24 +10215,24 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>19.17</v>
+        <v>303.88</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>19.1</v>
+        <v>302.75</v>
       </c>
       <c r="F377" s="7" t="n">
         <v>-0.37</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>234.05</v>
+        <v>178.85</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>232.7</v>
+        <v>177.82</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-0.58</v>
@@ -10865,12 +10865,12 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D402" s="5" t="n">
-        <v>178.85</v>
+        <v>196.72</v>
       </c>
       <c r="E402" s="5" t="n">
-        <v>177.82</v>
+        <v>195.57</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>-0.58</v>
@@ -10891,24 +10891,24 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>196.72</v>
+        <v>234.05</v>
       </c>
       <c r="E403" s="5" t="n">
-        <v>195.57</v>
+        <v>232.7</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>-0.58</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Dow Inc.</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>28.59</v>
+        <v>171.34</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>28.42</v>
+        <v>170.33</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-0.59</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Dow Inc.</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>218.73</v>
+        <v>28.59</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>217.43</v>
+        <v>28.42</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-0.59</v>
@@ -11021,24 +11021,24 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>171.34</v>
+        <v>218.73</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>170.33</v>
+        <v>217.43</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>-0.59</v>
@@ -11125,24 +11125,24 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>314.2</v>
+        <v>12.25</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>312.15</v>
+        <v>12.17</v>
       </c>
       <c r="F412" s="7" t="n">
         <v>-0.65</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>12.25</v>
+        <v>314.2</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>12.17</v>
+        <v>312.15</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-0.65</v>
@@ -11281,24 +11281,24 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D418" s="5" t="n">
-        <v>481.57</v>
+        <v>89.17</v>
       </c>
       <c r="E418" s="5" t="n">
-        <v>478.35</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F418" s="7" t="n">
         <v>-0.67</v>
@@ -11333,24 +11333,24 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Martin Marietta Materials</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>89.17</v>
+        <v>481.57</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>88.56999999999999</v>
+        <v>478.35</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>-0.67</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>154.76</v>
+        <v>88.86</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>153.64</v>
+        <v>88.22</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-0.72</v>
@@ -11489,24 +11489,24 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>88.86</v>
+        <v>154.76</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>88.22</v>
+        <v>153.64</v>
       </c>
       <c r="F426" s="7" t="n">
         <v>-0.72</v>
@@ -11723,24 +11723,24 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>34.34</v>
+        <v>32.26</v>
       </c>
       <c r="E435" s="5" t="n">
-        <v>34.04</v>
+        <v>31.98</v>
       </c>
       <c r="F435" s="7" t="n">
         <v>-0.87</v>
@@ -11749,24 +11749,24 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D436" s="5" t="n">
-        <v>32.26</v>
+        <v>34.34</v>
       </c>
       <c r="E436" s="5" t="n">
-        <v>31.98</v>
+        <v>34.04</v>
       </c>
       <c r="F436" s="7" t="n">
         <v>-0.87</v>
@@ -12295,24 +12295,24 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>48.92</v>
+        <v>60.01</v>
       </c>
       <c r="E457" s="5" t="n">
-        <v>48.26</v>
+        <v>59.2</v>
       </c>
       <c r="F457" s="7" t="n">
         <v>-1.35</v>
@@ -12321,24 +12321,24 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D458" s="5" t="n">
-        <v>60.01</v>
+        <v>48.92</v>
       </c>
       <c r="E458" s="5" t="n">
-        <v>59.2</v>
+        <v>48.26</v>
       </c>
       <c r="F458" s="7" t="n">
         <v>-1.35</v>
@@ -12607,24 +12607,24 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>6002.55</v>
+        <v>1609.46</v>
       </c>
       <c r="E469" s="5" t="n">
-        <v>5899.16</v>
+        <v>1581.82</v>
       </c>
       <c r="F469" s="7" t="n">
         <v>-1.72</v>
@@ -12633,24 +12633,24 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D470" s="5" t="n">
-        <v>1609.46</v>
+        <v>6002.55</v>
       </c>
       <c r="E470" s="5" t="n">
-        <v>1581.82</v>
+        <v>5899.16</v>
       </c>
       <c r="F470" s="7" t="n">
         <v>-1.72</v>
@@ -12789,24 +12789,24 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D476" s="5" t="n">
-        <v>132.48</v>
+        <v>87.8</v>
       </c>
       <c r="E476" s="5" t="n">
-        <v>130</v>
+        <v>86.16</v>
       </c>
       <c r="F476" s="7" t="n">
         <v>-1.87</v>
@@ -12815,24 +12815,24 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D477" s="5" t="n">
-        <v>87.8</v>
+        <v>132.48</v>
       </c>
       <c r="E477" s="5" t="n">
-        <v>86.16</v>
+        <v>130</v>
       </c>
       <c r="F477" s="7" t="n">
         <v>-1.87</v>
@@ -12893,24 +12893,24 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>181.63</v>
+        <v>226.54</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>178.01</v>
+        <v>222.04</v>
       </c>
       <c r="F480" s="7" t="n">
         <v>-1.99</v>
@@ -12919,24 +12919,24 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>226.54</v>
+        <v>181.63</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>222.04</v>
+        <v>178.01</v>
       </c>
       <c r="F481" s="7" t="n">
         <v>-1.99</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 02 close to Oct 09 close  |  503 companies  |  updated 2026-10-10 09:13</t>
+          <t>Oct 02 close to Oct 09 close  |  503 companies  |  updated 2026-10-11 09:30</t>
         </is>
       </c>
     </row>
@@ -14187,30 +14187,30 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>31.09</v>
+        <v>163.88</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>33.7</v>
+        <v>177.63</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>33.7</v>
+        <v>177.63</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>31.09</v>
+        <v>163.28</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>8.390000000000001</v>
@@ -14219,30 +14219,30 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>163.88</v>
+        <v>31.09</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>177.63</v>
+        <v>33.7</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>177.63</v>
+        <v>33.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>163.28</v>
+        <v>31.09</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>8.390000000000001</v>
@@ -15435,30 +15435,30 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>106.4</v>
+        <v>535.95</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>112.19</v>
+        <v>565.12</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>112.19</v>
+        <v>565.12</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>106.4</v>
+        <v>535.95</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>5.44</v>
@@ -15467,30 +15467,30 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>535.95</v>
+        <v>106.4</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>565.12</v>
+        <v>112.19</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>565.12</v>
+        <v>112.19</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>535.95</v>
+        <v>106.4</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>5.44</v>
@@ -16427,30 +16427,30 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>30.37</v>
+        <v>132.68</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>31.76</v>
+        <v>138.76</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>31.76</v>
+        <v>138.8</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>30.37</v>
+        <v>132.68</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>4.58</v>
@@ -16459,30 +16459,30 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>132.68</v>
+        <v>30.37</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>138.76</v>
+        <v>31.76</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>138.8</v>
+        <v>31.76</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>132.68</v>
+        <v>30.37</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>4.58</v>
@@ -16875,30 +16875,30 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>80.41</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>83.8</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>83.8</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>80.41</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>4.22</v>
@@ -16907,30 +16907,30 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="H105" s="6" t="n">
         <v>4.22</v>
@@ -16971,30 +16971,30 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>240.39</v>
+        <v>140</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>250.33</v>
+        <v>145.78</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>251.41</v>
+        <v>145.78</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>240.39</v>
+        <v>140</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>4.13</v>
@@ -17003,30 +17003,30 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>240.39</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>98.33</v>
+        <v>250.33</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>98.47</v>
+        <v>251.41</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>240.39</v>
       </c>
       <c r="H108" s="6" t="n">
         <v>4.13</v>
@@ -17035,30 +17035,30 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>140</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>145.78</v>
+        <v>98.33</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>145.78</v>
+        <v>98.47</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>140</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="H109" s="6" t="n">
         <v>4.13</v>
@@ -17131,30 +17131,30 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>114.02</v>
+        <v>228.3</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>118.65</v>
+        <v>237.57</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>118.65</v>
+        <v>238.96</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>114.02</v>
+        <v>228.3</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>4.06</v>
@@ -17163,30 +17163,30 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>228.3</v>
+        <v>114.02</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>237.57</v>
+        <v>118.65</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>238.96</v>
+        <v>118.65</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>228.3</v>
+        <v>114.02</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>4.06</v>
@@ -17483,30 +17483,30 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>80.45</v>
+        <v>403.24</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>83.55</v>
+        <v>418.78</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>83.55</v>
+        <v>419.91</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>80.26000000000001</v>
+        <v>398.5</v>
       </c>
       <c r="H123" s="6" t="n">
         <v>3.85</v>
@@ -17515,30 +17515,30 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>403.24</v>
+        <v>80.45</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>418.78</v>
+        <v>83.55</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>419.91</v>
+        <v>83.55</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>398.5</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="H124" s="6" t="n">
         <v>3.85</v>
@@ -18027,30 +18027,30 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>210.31</v>
+        <v>517.53</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>217.43</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>218.73</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>210.31</v>
+        <v>517.53</v>
       </c>
       <c r="H140" s="6" t="n">
         <v>3.39</v>
@@ -18059,30 +18059,30 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>517.53</v>
+        <v>210.31</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>535.0700000000001</v>
+        <v>217.43</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>535.0700000000001</v>
+        <v>218.73</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>517.53</v>
+        <v>210.31</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>3.39</v>
@@ -18123,30 +18123,30 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>170.06</v>
+        <v>117.74</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>175.76</v>
+        <v>121.68</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>176.67</v>
+        <v>121.68</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>170.06</v>
+        <v>113.55</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>3.35</v>
@@ -18155,30 +18155,30 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>117.74</v>
+        <v>170.06</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>121.68</v>
+        <v>175.76</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>121.68</v>
+        <v>176.67</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>113.55</v>
+        <v>170.06</v>
       </c>
       <c r="H144" s="6" t="n">
         <v>3.35</v>
@@ -18475,30 +18475,30 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>164.01</v>
+        <v>375.86</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>168.94</v>
+        <v>387.18</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>168.94</v>
+        <v>387.18</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>164</v>
+        <v>375.66</v>
       </c>
       <c r="H154" s="6" t="n">
         <v>3.01</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>375.86</v>
+        <v>164.01</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>387.18</v>
+        <v>168.94</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>387.18</v>
+        <v>168.94</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>375.66</v>
+        <v>164</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>3.01</v>
@@ -18539,30 +18539,30 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>51.89</v>
+        <v>64.05</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>53.43</v>
+        <v>65.95</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>53.43</v>
+        <v>66.45</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
       <c r="H156" s="6" t="n">
         <v>2.97</v>
@@ -18603,30 +18603,30 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>64.05</v>
+        <v>51.89</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>65.95</v>
+        <v>53.43</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>66.45</v>
+        <v>53.43</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>64.05</v>
+        <v>51.7</v>
       </c>
       <c r="H158" s="6" t="n">
         <v>2.97</v>
@@ -18763,30 +18763,30 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>26.04</v>
+        <v>180.8</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>26.79</v>
+        <v>186</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>26.79</v>
+        <v>188.85</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>25.86</v>
+        <v>179.5</v>
       </c>
       <c r="H163" s="6" t="n">
         <v>2.88</v>
@@ -18795,30 +18795,30 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>180.8</v>
+        <v>26.04</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>186</v>
+        <v>26.79</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>188.85</v>
+        <v>26.79</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>179.5</v>
+        <v>25.86</v>
       </c>
       <c r="H164" s="6" t="n">
         <v>2.88</v>
@@ -18827,30 +18827,30 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Atmos Energy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>157.17</v>
+        <v>44.36</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>161.66</v>
+        <v>45.63</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>161.66</v>
+        <v>46.14</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>157.17</v>
+        <v>44.36</v>
       </c>
       <c r="H165" s="6" t="n">
         <v>2.86</v>
@@ -18859,30 +18859,30 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Atmos Energy</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
-        <v>44.36</v>
+        <v>157.17</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>45.63</v>
+        <v>161.66</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>46.14</v>
+        <v>161.66</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>44.36</v>
+        <v>157.17</v>
       </c>
       <c r="H166" s="6" t="n">
         <v>2.86</v>
@@ -19115,12 +19115,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -19129,16 +19129,16 @@
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>354.32</v>
+        <v>116.61</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>364.09</v>
+        <v>119.83</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>364.23</v>
+        <v>121.38</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>354.32</v>
+        <v>114.74</v>
       </c>
       <c r="H174" s="6" t="n">
         <v>2.76</v>
@@ -19147,12 +19147,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -19161,16 +19161,16 @@
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>116.61</v>
+        <v>354.32</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>119.83</v>
+        <v>364.09</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>121.38</v>
+        <v>364.23</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>114.74</v>
+        <v>354.32</v>
       </c>
       <c r="H175" s="6" t="n">
         <v>2.76</v>
@@ -19371,30 +19371,30 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>288.61</v>
+        <v>219.88</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>296.26</v>
+        <v>225.71</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>297.86</v>
+        <v>225.71</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>288.11</v>
+        <v>218.43</v>
       </c>
       <c r="H182" s="6" t="n">
         <v>2.65</v>
@@ -19403,30 +19403,30 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>219.88</v>
+        <v>288.61</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>225.71</v>
+        <v>296.26</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>225.71</v>
+        <v>297.86</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>218.43</v>
+        <v>288.11</v>
       </c>
       <c r="H183" s="6" t="n">
         <v>2.65</v>
@@ -19435,12 +19435,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Consolidated Edison</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -19449,16 +19449,16 @@
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>53.89</v>
+        <v>103.39</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>55.3</v>
+        <v>106.1</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>55.3</v>
+        <v>106.1</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>53.89</v>
+        <v>103.38</v>
       </c>
       <c r="H184" s="6" t="n">
         <v>2.62</v>
@@ -19467,12 +19467,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Consolidated Edison</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -19481,16 +19481,16 @@
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>103.39</v>
+        <v>53.89</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>106.1</v>
+        <v>55.3</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>106.1</v>
+        <v>55.3</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>103.38</v>
+        <v>53.89</v>
       </c>
       <c r="H185" s="6" t="n">
         <v>2.62</v>
@@ -19755,30 +19755,30 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>126.05</v>
+        <v>86.38</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>129.11</v>
+        <v>88.48</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>129.48</v>
+        <v>88.48</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>126.05</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="H194" s="6" t="n">
         <v>2.43</v>
@@ -19787,30 +19787,30 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>86.38</v>
+        <v>126.05</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>88.48</v>
+        <v>129.11</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>88.48</v>
+        <v>129.48</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>85.51000000000001</v>
+        <v>126.05</v>
       </c>
       <c r="H195" s="6" t="n">
         <v>2.43</v>
@@ -20075,30 +20075,30 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Vivmark Residential</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>72.04000000000001</v>
+        <v>59.79</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>73.69</v>
+        <v>61.16</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>73.69</v>
+        <v>61.16</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>71.14</v>
+        <v>59.29</v>
       </c>
       <c r="H204" s="6" t="n">
         <v>2.29</v>
@@ -20107,30 +20107,30 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Vivmark Residential</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>59.79</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>61.16</v>
+        <v>73.69</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>61.16</v>
+        <v>73.69</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>59.29</v>
+        <v>71.14</v>
       </c>
       <c r="H205" s="6" t="n">
         <v>2.29</v>
@@ -20171,30 +20171,30 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>79.17</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F207" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>79.09</v>
+        <v>64.22</v>
       </c>
       <c r="H207" s="6" t="n">
         <v>2.26</v>
@@ -20203,30 +20203,30 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>64.29000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>64.22</v>
+        <v>79.09</v>
       </c>
       <c r="H208" s="6" t="n">
         <v>2.26</v>
@@ -20235,30 +20235,30 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>117.19</v>
+        <v>319.36</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>119.83</v>
+        <v>326.56</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>119.83</v>
+        <v>326.56</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>115.93</v>
+        <v>316.12</v>
       </c>
       <c r="H209" s="6" t="n">
         <v>2.25</v>
@@ -20267,30 +20267,30 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>319.36</v>
+        <v>99.94</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>326.56</v>
+        <v>102.19</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>326.56</v>
+        <v>102.19</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>316.12</v>
+        <v>99.7</v>
       </c>
       <c r="H210" s="6" t="n">
         <v>2.25</v>
@@ -20299,30 +20299,30 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>99.94</v>
+        <v>117.19</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>102.19</v>
+        <v>119.83</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>102.19</v>
+        <v>119.83</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>99.7</v>
+        <v>115.93</v>
       </c>
       <c r="H211" s="6" t="n">
         <v>2.25</v>
@@ -20555,30 +20555,30 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>37.79</v>
+        <v>154.63</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>38.6</v>
+        <v>157.94</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>38.6</v>
+        <v>157.94</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>37.75</v>
+        <v>153.07</v>
       </c>
       <c r="H219" s="6" t="n">
         <v>2.14</v>
@@ -20587,30 +20587,30 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>204.45</v>
+        <v>37.79</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>208.83</v>
+        <v>38.6</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>210.1</v>
+        <v>38.6</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>204.45</v>
+        <v>37.75</v>
       </c>
       <c r="H220" s="6" t="n">
         <v>2.14</v>
@@ -20619,12 +20619,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -20633,16 +20633,16 @@
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>154.63</v>
+        <v>204.45</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>157.94</v>
+        <v>208.83</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>157.94</v>
+        <v>210.1</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>153.07</v>
+        <v>204.45</v>
       </c>
       <c r="H221" s="6" t="n">
         <v>2.14</v>
@@ -20939,30 +20939,30 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>115.56</v>
+        <v>124.45</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>117.84</v>
+        <v>126.9</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>117.84</v>
+        <v>128.22</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>113.54</v>
+        <v>124.45</v>
       </c>
       <c r="H231" s="6" t="n">
         <v>1.97</v>
@@ -20971,30 +20971,30 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D232" s="5" t="n">
-        <v>124.45</v>
+        <v>115.56</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>126.9</v>
+        <v>117.84</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>128.22</v>
+        <v>117.84</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>124.45</v>
+        <v>113.54</v>
       </c>
       <c r="H232" s="6" t="n">
         <v>1.97</v>
@@ -21515,30 +21515,30 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>167.78</v>
+        <v>1085.42</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>170.54</v>
+        <v>1103.36</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>171.29</v>
+        <v>1133.4</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>167.78</v>
+        <v>1048.6</v>
       </c>
       <c r="H249" s="6" t="n">
         <v>1.65</v>
@@ -21547,30 +21547,30 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>1085.42</v>
+        <v>167.78</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>1103.36</v>
+        <v>170.54</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>1133.4</v>
+        <v>171.29</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>1048.6</v>
+        <v>167.78</v>
       </c>
       <c r="H250" s="6" t="n">
         <v>1.65</v>
@@ -21931,30 +21931,30 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>175.58</v>
+        <v>115.27</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>178.01</v>
+        <v>116.86</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>181.63</v>
+        <v>116.99</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>175.58</v>
+        <v>114.21</v>
       </c>
       <c r="H262" s="6" t="n">
         <v>1.38</v>
@@ -21963,30 +21963,30 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>115.27</v>
+        <v>175.58</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>116.86</v>
+        <v>178.01</v>
       </c>
       <c r="F263" s="5" t="n">
-        <v>116.99</v>
+        <v>181.63</v>
       </c>
       <c r="G263" s="5" t="n">
-        <v>114.21</v>
+        <v>175.58</v>
       </c>
       <c r="H263" s="6" t="n">
         <v>1.38</v>
@@ -22251,30 +22251,30 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>53.75</v>
+        <v>504.73</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>54.32</v>
+        <v>510.08</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>54.32</v>
+        <v>510.08</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>53.52</v>
+        <v>502.31</v>
       </c>
       <c r="H272" s="6" t="n">
         <v>1.06</v>
@@ -22283,30 +22283,30 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>504.73</v>
+        <v>53.75</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>510.08</v>
+        <v>54.32</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>510.08</v>
+        <v>54.32</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>502.31</v>
+        <v>53.52</v>
       </c>
       <c r="H273" s="6" t="n">
         <v>1.06</v>
@@ -22411,30 +22411,30 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>661.25</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>89.14</v>
+        <v>667.58</v>
       </c>
       <c r="F277" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>707.4299999999999</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>661.25</v>
       </c>
       <c r="H277" s="6" t="n">
         <v>0.96</v>
@@ -22443,30 +22443,30 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Fair Isaac</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>661.25</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>667.58</v>
+        <v>89.14</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>707.4299999999999</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>661.25</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="H278" s="6" t="n">
         <v>0.96</v>
@@ -22571,30 +22571,30 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D282" s="5" t="n">
-        <v>101.79</v>
+        <v>144.3</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>102.71</v>
+        <v>145.6</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>104.57</v>
+        <v>145.6</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>101.79</v>
+        <v>139.54</v>
       </c>
       <c r="H282" s="6" t="n">
         <v>0.9</v>
@@ -22603,30 +22603,30 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Merck &amp; Co.</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>144.3</v>
+        <v>101.79</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>145.6</v>
+        <v>102.71</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>145.6</v>
+        <v>104.57</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>139.54</v>
+        <v>101.79</v>
       </c>
       <c r="H283" s="6" t="n">
         <v>0.9</v>
@@ -22635,30 +22635,30 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D284" s="5" t="n">
-        <v>128.5</v>
+        <v>479.48</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>129.64</v>
+        <v>483.73</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>129.64</v>
+        <v>489.95</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>127.32</v>
+        <v>479.48</v>
       </c>
       <c r="H284" s="6" t="n">
         <v>0.89</v>
@@ -22667,30 +22667,30 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
-        <v>479.48</v>
+        <v>128.5</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>483.73</v>
+        <v>129.64</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>489.95</v>
+        <v>129.64</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>479.48</v>
+        <v>127.32</v>
       </c>
       <c r="H285" s="6" t="n">
         <v>0.89</v>
@@ -22859,30 +22859,30 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>77.48999999999999</v>
+        <v>394.6</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>78.14</v>
+        <v>397.92</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>78.2</v>
+        <v>406.79</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>76.38</v>
+        <v>394.6</v>
       </c>
       <c r="H291" s="6" t="n">
         <v>0.84</v>
@@ -22891,30 +22891,30 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>394.6</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>397.92</v>
+        <v>78.14</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>406.79</v>
+        <v>78.2</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>394.6</v>
+        <v>76.38</v>
       </c>
       <c r="H292" s="6" t="n">
         <v>0.84</v>
@@ -22923,30 +22923,30 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>505.41</v>
+        <v>159.02</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>509.59</v>
+        <v>160.34</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>510.12</v>
+        <v>160.34</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>499.22</v>
+        <v>155.87</v>
       </c>
       <c r="H293" s="6" t="n">
         <v>0.83</v>
@@ -22955,12 +22955,12 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -22969,16 +22969,16 @@
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>180.48</v>
+        <v>505.41</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>181.97</v>
+        <v>509.59</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>181.97</v>
+        <v>510.12</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>175.61</v>
+        <v>499.22</v>
       </c>
       <c r="H294" s="6" t="n">
         <v>0.83</v>
@@ -22987,30 +22987,30 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>159.02</v>
+        <v>180.48</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>160.34</v>
+        <v>181.97</v>
       </c>
       <c r="F295" s="5" t="n">
-        <v>160.34</v>
+        <v>181.97</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>155.87</v>
+        <v>175.61</v>
       </c>
       <c r="H295" s="6" t="n">
         <v>0.83</v>
@@ -23307,30 +23307,30 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>243.06</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>72.05</v>
+        <v>244.58</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>72.05</v>
+        <v>248.85</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>70.8</v>
+        <v>243.06</v>
       </c>
       <c r="H305" s="6" t="n">
         <v>0.63</v>
@@ -23339,30 +23339,30 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>243.06</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>244.58</v>
+        <v>72.05</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>248.85</v>
+        <v>72.05</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>243.06</v>
+        <v>70.8</v>
       </c>
       <c r="H306" s="6" t="n">
         <v>0.63</v>
@@ -23755,12 +23755,12 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -23769,16 +23769,16 @@
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>290.36</v>
+        <v>262.92</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>291.71</v>
+        <v>264.13</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>291.73</v>
+        <v>267.14</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>289.03</v>
+        <v>261.15</v>
       </c>
       <c r="H319" s="6" t="n">
         <v>0.46</v>
@@ -23787,12 +23787,12 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -23801,16 +23801,16 @@
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>262.92</v>
+        <v>290.36</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>264.13</v>
+        <v>291.71</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>267.14</v>
+        <v>291.73</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>261.15</v>
+        <v>289.03</v>
       </c>
       <c r="H320" s="6" t="n">
         <v>0.46</v>
@@ -23883,30 +23883,30 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>48.74</v>
+        <v>221.09</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>48.95</v>
+        <v>222.04</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>50.28</v>
+        <v>226.54</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>47.96</v>
+        <v>217.77</v>
       </c>
       <c r="H323" s="6" t="n">
         <v>0.43</v>
@@ -23915,30 +23915,30 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>221.09</v>
+        <v>48.74</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>222.04</v>
+        <v>48.95</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>226.54</v>
+        <v>50.28</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>217.77</v>
+        <v>47.96</v>
       </c>
       <c r="H324" s="6" t="n">
         <v>0.43</v>
@@ -24075,30 +24075,30 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>22.19</v>
+        <v>786.61</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>22.27</v>
+        <v>789.45</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>22.48</v>
+        <v>824.52</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>21.84</v>
+        <v>778.24</v>
       </c>
       <c r="H329" s="6" t="n">
         <v>0.36</v>
@@ -24107,30 +24107,30 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>786.61</v>
+        <v>22.19</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>789.45</v>
+        <v>22.27</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>824.52</v>
+        <v>22.48</v>
       </c>
       <c r="G330" s="5" t="n">
-        <v>778.24</v>
+        <v>21.84</v>
       </c>
       <c r="H330" s="6" t="n">
         <v>0.36</v>
@@ -24203,12 +24203,12 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -24217,16 +24217,16 @@
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>42.6</v>
+        <v>178.69</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>42.73</v>
+        <v>179.25</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>42.73</v>
+        <v>180.4</v>
       </c>
       <c r="G333" s="5" t="n">
-        <v>41.58</v>
+        <v>176.78</v>
       </c>
       <c r="H333" s="6" t="n">
         <v>0.31</v>
@@ -24267,12 +24267,12 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -24281,16 +24281,16 @@
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>178.69</v>
+        <v>42.6</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>179.25</v>
+        <v>42.73</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>180.4</v>
+        <v>42.73</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>176.78</v>
+        <v>41.58</v>
       </c>
       <c r="H335" s="6" t="n">
         <v>0.31</v>
@@ -24971,30 +24971,30 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>96.7</v>
+        <v>50.75</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>96.7</v>
+        <v>50.75</v>
       </c>
       <c r="F357" s="5" t="n">
-        <v>97.95999999999999</v>
+        <v>50.81</v>
       </c>
       <c r="G357" s="5" t="n">
-        <v>95.58</v>
+        <v>49.83</v>
       </c>
       <c r="H357" s="6" t="n">
         <v>0</v>
@@ -25035,30 +25035,30 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Fastenal</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>50.75</v>
+        <v>96.7</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>50.75</v>
+        <v>96.7</v>
       </c>
       <c r="F359" s="5" t="n">
-        <v>50.81</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="G359" s="5" t="n">
-        <v>49.83</v>
+        <v>95.58</v>
       </c>
       <c r="H359" s="6" t="n">
         <v>0</v>
@@ -25515,30 +25515,30 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>22.24</v>
+        <v>47.43</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>22.16</v>
+        <v>47.26</v>
       </c>
       <c r="F374" s="5" t="n">
-        <v>22.24</v>
+        <v>47.5</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>21.85</v>
+        <v>46.81</v>
       </c>
       <c r="H374" s="7" t="n">
         <v>-0.36</v>
@@ -25547,30 +25547,30 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>47.43</v>
+        <v>22.24</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>47.26</v>
+        <v>22.16</v>
       </c>
       <c r="F375" s="5" t="n">
-        <v>47.5</v>
+        <v>22.24</v>
       </c>
       <c r="G375" s="5" t="n">
-        <v>46.81</v>
+        <v>21.85</v>
       </c>
       <c r="H375" s="7" t="n">
         <v>-0.36</v>
@@ -25707,30 +25707,30 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D380" s="5" t="n">
-        <v>88.3</v>
+        <v>81.94</v>
       </c>
       <c r="E380" s="5" t="n">
-        <v>87.87</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F380" s="5" t="n">
-        <v>90.58</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G380" s="5" t="n">
-        <v>86.47</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H380" s="7" t="n">
         <v>-0.49</v>
@@ -25739,30 +25739,30 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>384.64</v>
+        <v>88.3</v>
       </c>
       <c r="E381" s="5" t="n">
-        <v>382.75</v>
+        <v>87.87</v>
       </c>
       <c r="F381" s="5" t="n">
-        <v>388.03</v>
+        <v>90.58</v>
       </c>
       <c r="G381" s="5" t="n">
-        <v>374.67</v>
+        <v>86.47</v>
       </c>
       <c r="H381" s="7" t="n">
         <v>-0.49</v>
@@ -25771,30 +25771,30 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D382" s="5" t="n">
-        <v>81.94</v>
+        <v>384.64</v>
       </c>
       <c r="E382" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>382.75</v>
       </c>
       <c r="F382" s="5" t="n">
-        <v>83.59999999999999</v>
+        <v>388.03</v>
       </c>
       <c r="G382" s="5" t="n">
-        <v>81.45999999999999</v>
+        <v>374.67</v>
       </c>
       <c r="H382" s="7" t="n">
         <v>-0.49</v>
@@ -26091,30 +26091,30 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Align Technology</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>143.74</v>
+        <v>447.41</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>142.71</v>
+        <v>444.18</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>143.74</v>
+        <v>456.28</v>
       </c>
       <c r="G392" s="5" t="n">
-        <v>139.87</v>
+        <v>444.18</v>
       </c>
       <c r="H392" s="7" t="n">
         <v>-0.72</v>
@@ -26123,30 +26123,30 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Align Technology</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>447.41</v>
+        <v>143.74</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>444.18</v>
+        <v>142.71</v>
       </c>
       <c r="F393" s="5" t="n">
-        <v>456.28</v>
+        <v>143.74</v>
       </c>
       <c r="G393" s="5" t="n">
-        <v>444.18</v>
+        <v>139.87</v>
       </c>
       <c r="H393" s="7" t="n">
         <v>-0.72</v>
@@ -26923,30 +26923,30 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Ametek</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D418" s="5" t="n">
-        <v>200.33</v>
+        <v>251.93</v>
       </c>
       <c r="E418" s="5" t="n">
-        <v>197.66</v>
+        <v>248.58</v>
       </c>
       <c r="F418" s="5" t="n">
-        <v>203.14</v>
+        <v>253.72</v>
       </c>
       <c r="G418" s="5" t="n">
-        <v>197.66</v>
+        <v>247.52</v>
       </c>
       <c r="H418" s="7" t="n">
         <v>-1.33</v>
@@ -26955,30 +26955,30 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Ametek</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>251.93</v>
+        <v>200.33</v>
       </c>
       <c r="E419" s="5" t="n">
-        <v>248.58</v>
+        <v>197.66</v>
       </c>
       <c r="F419" s="5" t="n">
-        <v>253.72</v>
+        <v>203.14</v>
       </c>
       <c r="G419" s="5" t="n">
-        <v>247.52</v>
+        <v>197.66</v>
       </c>
       <c r="H419" s="7" t="n">
         <v>-1.33</v>
@@ -28363,12 +28363,12 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
@@ -28377,16 +28377,16 @@
         </is>
       </c>
       <c r="D463" s="5" t="n">
-        <v>1439.73</v>
+        <v>131.48</v>
       </c>
       <c r="E463" s="5" t="n">
-        <v>1386.29</v>
+        <v>126.6</v>
       </c>
       <c r="F463" s="5" t="n">
-        <v>1479.89</v>
+        <v>133.63</v>
       </c>
       <c r="G463" s="5" t="n">
-        <v>1369.8</v>
+        <v>126.6</v>
       </c>
       <c r="H463" s="7" t="n">
         <v>-3.71</v>
@@ -28395,12 +28395,12 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
@@ -28409,16 +28409,16 @@
         </is>
       </c>
       <c r="D464" s="5" t="n">
-        <v>131.48</v>
+        <v>1439.73</v>
       </c>
       <c r="E464" s="5" t="n">
-        <v>126.6</v>
+        <v>1386.29</v>
       </c>
       <c r="F464" s="5" t="n">
-        <v>133.63</v>
+        <v>1479.89</v>
       </c>
       <c r="G464" s="5" t="n">
-        <v>126.6</v>
+        <v>1369.8</v>
       </c>
       <c r="H464" s="7" t="n">
         <v>-3.71</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 08-&gt;Oct 09) and rolling 5-day  |  updated 2026-10-10 09:13</t>
+          <t>Daily (Oct 08-&gt;Oct 09) and rolling 5-day  |  updated 2026-10-11 09:30</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 08 close to Oct 09 close  |  503 companies  |  updated 2026-10-11 09:30</t>
+          <t>Oct 08 close to Oct 09 close  |  503 companies  |  updated 2026-10-12 10:00</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>ZTS</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>64.22</v>
+        <v>73.08</v>
       </c>
       <c r="E53" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>74.81</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>2.37</v>
@@ -1817,12 +1817,12 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>ZTS</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -1831,10 +1831,10 @@
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>73.08</v>
+        <v>64.22</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>74.81</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>2.37</v>
@@ -1947,24 +1947,24 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>RDDT</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Gen Digital</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>156.47</v>
+        <v>22.75</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>159.91</v>
+        <v>23.25</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>2.2</v>
@@ -1973,24 +1973,24 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>RDDT</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Gen Digital</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>22.75</v>
+        <v>156.47</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>23.25</v>
+        <v>159.91</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>2.2</v>
@@ -2051,24 +2051,24 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Intuitive Surgical</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>415.41</v>
+        <v>119.22</v>
       </c>
       <c r="E63" s="5" t="n">
-        <v>423.96</v>
+        <v>121.68</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>2.06</v>
@@ -2077,24 +2077,24 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>ISRG</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Intuitive Surgical</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>119.22</v>
+        <v>415.41</v>
       </c>
       <c r="E64" s="5" t="n">
-        <v>121.68</v>
+        <v>423.96</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>2.06</v>
@@ -2129,12 +2129,12 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Dell Technologies</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>574.55</v>
+        <v>297.79</v>
       </c>
       <c r="E66" s="5" t="n">
-        <v>586.0599999999999</v>
+        <v>303.74</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>2</v>
@@ -2155,12 +2155,12 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>297.79</v>
+        <v>574.55</v>
       </c>
       <c r="E67" s="5" t="n">
-        <v>303.74</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>2</v>
@@ -2675,24 +2675,24 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>WAB</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Wabtec</t>
+          <t>Pfizer</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>280.8</v>
+        <v>27.82</v>
       </c>
       <c r="E87" s="5" t="n">
-        <v>285.43</v>
+        <v>28.28</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>1.65</v>
@@ -2701,24 +2701,24 @@
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>WAB</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>Wabtec</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D88" s="5" t="n">
-        <v>27.82</v>
+        <v>280.8</v>
       </c>
       <c r="E88" s="5" t="n">
-        <v>28.28</v>
+        <v>285.43</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>1.65</v>
@@ -3169,24 +3169,24 @@
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>FTV</t>
+          <t>ABBV</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Fortive</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D106" s="5" t="n">
-        <v>56.42</v>
+        <v>272.42</v>
       </c>
       <c r="E106" s="5" t="n">
-        <v>57.26</v>
+        <v>276.47</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>1.49</v>
@@ -3221,24 +3221,24 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>ABBV</t>
+          <t>FTV</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Fortive</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>272.42</v>
+        <v>56.42</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>276.47</v>
+        <v>57.26</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>1.49</v>
@@ -3533,24 +3533,24 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>IRM</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Iron Mountain</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D120" s="5" t="n">
-        <v>112.97</v>
+        <v>503.25</v>
       </c>
       <c r="E120" s="5" t="n">
-        <v>114.51</v>
+        <v>510.08</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>1.36</v>
@@ -3559,24 +3559,24 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>IRM</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Iron Mountain</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D121" s="5" t="n">
-        <v>503.25</v>
+        <v>112.97</v>
       </c>
       <c r="E121" s="5" t="n">
-        <v>510.08</v>
+        <v>114.51</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>1.36</v>
@@ -3585,24 +3585,24 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>MTD</t>
+          <t>AXON</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Mettler Toledo</t>
+          <t>Axon Enterprise</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D122" s="5" t="n">
-        <v>1529.46</v>
+        <v>417.31</v>
       </c>
       <c r="E122" s="5" t="n">
-        <v>1549.99</v>
+        <v>422.89</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>1.34</v>
@@ -3611,24 +3611,24 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>AXON</t>
+          <t>MTD</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Axon Enterprise</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>417.31</v>
+        <v>1529.46</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>422.89</v>
+        <v>1549.99</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>1.34</v>
@@ -3637,24 +3637,24 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Revvity</t>
+          <t>Marriott International</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>152.16</v>
+        <v>361.08</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>154.18</v>
+        <v>365.88</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>1.33</v>
@@ -3663,24 +3663,24 @@
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>RVTY</t>
         </is>
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Marriott International</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D125" s="5" t="n">
-        <v>361.08</v>
+        <v>152.16</v>
       </c>
       <c r="E125" s="5" t="n">
-        <v>365.88</v>
+        <v>154.18</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>1.33</v>
@@ -3793,24 +3793,24 @@
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Yum! Brands</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D130" s="5" t="n">
-        <v>143</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E130" s="5" t="n">
-        <v>144.82</v>
+        <v>65.36</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>1.27</v>
@@ -3819,24 +3819,24 @@
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
         <is>
-          <t>CNC</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Centene Corporation</t>
+          <t>Yum! Brands</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D131" s="5" t="n">
-        <v>64.54000000000001</v>
+        <v>143</v>
       </c>
       <c r="E131" s="5" t="n">
-        <v>65.36</v>
+        <v>144.82</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>1.27</v>
@@ -3897,24 +3897,24 @@
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D134" s="5" t="n">
-        <v>128.08</v>
+        <v>175.49</v>
       </c>
       <c r="E134" s="5" t="n">
-        <v>129.64</v>
+        <v>177.63</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>1.22</v>
@@ -3923,24 +3923,24 @@
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D135" s="5" t="n">
-        <v>175.49</v>
+        <v>128.08</v>
       </c>
       <c r="E135" s="5" t="n">
-        <v>177.63</v>
+        <v>129.64</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>1.22</v>
@@ -3949,12 +3949,12 @@
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>HWM</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Howmet Aerospace</t>
+          <t>Eaton Corporation</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="D136" s="5" t="n">
-        <v>222.56</v>
+        <v>424.51</v>
       </c>
       <c r="E136" s="5" t="n">
-        <v>225.26</v>
+        <v>429.65</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>1.21</v>
@@ -4001,12 +4001,12 @@
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>HWM</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Eaton Corporation</t>
+          <t>Howmet Aerospace</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="D138" s="5" t="n">
-        <v>424.51</v>
+        <v>222.56</v>
       </c>
       <c r="E138" s="5" t="n">
-        <v>429.65</v>
+        <v>225.26</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>1.21</v>
@@ -4131,24 +4131,24 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>VTRS</t>
+          <t>EXR</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>Extra Space Storage</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>17.44</v>
+        <v>133.12</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>17.64</v>
+        <v>134.65</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>1.15</v>
@@ -4183,24 +4183,24 @@
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>EXR</t>
+          <t>VTRS</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Extra Space Storage</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D145" s="5" t="n">
-        <v>133.12</v>
+        <v>17.44</v>
       </c>
       <c r="E145" s="5" t="n">
-        <v>134.65</v>
+        <v>17.64</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>1.15</v>
@@ -4547,12 +4547,12 @@
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>AutoZone</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4561,10 +4561,10 @@
         </is>
       </c>
       <c r="D159" s="5" t="n">
-        <v>2910.54</v>
+        <v>323.29</v>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2939.85</v>
+        <v>326.56</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>1.01</v>
@@ -4573,24 +4573,24 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D160" s="5" t="n">
-        <v>323.29</v>
+        <v>393.31</v>
       </c>
       <c r="E160" s="5" t="n">
-        <v>326.56</v>
+        <v>397.28</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>1.01</v>
@@ -4599,24 +4599,24 @@
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>AZO</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D161" s="5" t="n">
-        <v>393.31</v>
+        <v>2910.54</v>
       </c>
       <c r="E161" s="5" t="n">
-        <v>397.28</v>
+        <v>2939.85</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>1.01</v>
@@ -4677,24 +4677,24 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>PNW</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Ingersoll Rand</t>
+          <t>Pinnacle West Capital</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>78</v>
+        <v>97.98</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>78.75</v>
+        <v>98.92</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>0.96</v>
@@ -4703,24 +4703,24 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>PNW</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Pinnacle West Capital</t>
+          <t>Ingersoll Rand</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>97.98</v>
+        <v>78</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>98.92</v>
+        <v>78.75</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>0.96</v>
@@ -4807,24 +4807,24 @@
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D169" s="5" t="n">
-        <v>175.72</v>
+        <v>55.02</v>
       </c>
       <c r="E169" s="5" t="n">
-        <v>177.35</v>
+        <v>55.53</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>0.93</v>
@@ -4833,24 +4833,24 @@
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D170" s="5" t="n">
-        <v>55.02</v>
+        <v>175.72</v>
       </c>
       <c r="E170" s="5" t="n">
-        <v>55.53</v>
+        <v>177.35</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>0.93</v>
@@ -4963,24 +4963,24 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>BRK.B</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Texas Pacific Land Corporation</t>
+          <t>Berkshire Hathaway</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>357.78</v>
+        <v>511.05</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>360.98</v>
+        <v>515.62</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>0.89</v>
@@ -4989,24 +4989,24 @@
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>TROW</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>T. Rowe Price</t>
+          <t>Texas Pacific Land Corporation</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D176" s="5" t="n">
-        <v>104.23</v>
+        <v>357.78</v>
       </c>
       <c r="E176" s="5" t="n">
-        <v>105.16</v>
+        <v>360.98</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>0.89</v>
@@ -5015,24 +5015,24 @@
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>TROW</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>T. Rowe Price</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D177" s="5" t="n">
-        <v>92.5</v>
+        <v>104.23</v>
       </c>
       <c r="E177" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>105.16</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>0.89</v>
@@ -5041,24 +5041,24 @@
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>BRK.B</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D178" s="5" t="n">
-        <v>511.05</v>
+        <v>92.5</v>
       </c>
       <c r="E178" s="5" t="n">
-        <v>515.62</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>0.89</v>
@@ -5145,24 +5145,24 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Carnival Corporation</t>
+          <t>GE Aerospace</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>26.13</v>
+        <v>305.62</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>26.35</v>
+        <v>308.2</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>0.84</v>
@@ -5171,24 +5171,24 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>GE Aerospace</t>
+          <t>Carnival Corporation</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>305.62</v>
+        <v>26.13</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>308.2</v>
+        <v>26.35</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>0.84</v>
@@ -5353,24 +5353,24 @@
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>IP</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>International Paper</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D190" s="5" t="n">
-        <v>363.27</v>
+        <v>31.88</v>
       </c>
       <c r="E190" s="5" t="n">
-        <v>366</v>
+        <v>32.12</v>
       </c>
       <c r="F190" s="6" t="n">
         <v>0.75</v>
@@ -5405,24 +5405,24 @@
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>IP</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>International Paper</t>
+          <t>West Pharmaceutical Services</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D192" s="5" t="n">
-        <v>31.88</v>
+        <v>363.27</v>
       </c>
       <c r="E192" s="5" t="n">
-        <v>32.12</v>
+        <v>366</v>
       </c>
       <c r="F192" s="6" t="n">
         <v>0.75</v>
@@ -5509,24 +5509,24 @@
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>WMT</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D196" s="5" t="n">
-        <v>101.99</v>
+        <v>110.56</v>
       </c>
       <c r="E196" s="5" t="n">
-        <v>102.71</v>
+        <v>111.35</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>0.71</v>
@@ -5535,24 +5535,24 @@
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D197" s="5" t="n">
-        <v>110.56</v>
+        <v>101.99</v>
       </c>
       <c r="E197" s="5" t="n">
-        <v>111.35</v>
+        <v>102.71</v>
       </c>
       <c r="F197" s="6" t="n">
         <v>0.71</v>
@@ -5717,24 +5717,24 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>PEG</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>Public Service Enterprise Group</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>561.67</v>
+        <v>71.84</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>565.12</v>
+        <v>72.28</v>
       </c>
       <c r="F204" s="6" t="n">
         <v>0.61</v>
@@ -5743,24 +5743,24 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>PEG</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Public Service Enterprise Group</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>71.84</v>
+        <v>561.67</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>72.28</v>
+        <v>565.12</v>
       </c>
       <c r="F205" s="6" t="n">
         <v>0.61</v>
@@ -5847,24 +5847,24 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>227.8</v>
+        <v>116.19</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>229.13</v>
+        <v>116.86</v>
       </c>
       <c r="F209" s="6" t="n">
         <v>0.58</v>
@@ -5873,24 +5873,24 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>116.19</v>
+        <v>227.8</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>116.86</v>
+        <v>229.13</v>
       </c>
       <c r="F210" s="6" t="n">
         <v>0.58</v>
@@ -5899,24 +5899,24 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>CMI</t>
+          <t>XEL</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Xcel Energy</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>520.4</v>
+        <v>73.36</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>523.39</v>
+        <v>73.78</v>
       </c>
       <c r="F211" s="6" t="n">
         <v>0.57</v>
@@ -5925,12 +5925,12 @@
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>XEL</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Xcel Energy</t>
+          <t>NiSource</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="D212" s="5" t="n">
-        <v>73.36</v>
+        <v>40.53</v>
       </c>
       <c r="E212" s="5" t="n">
-        <v>73.78</v>
+        <v>40.76</v>
       </c>
       <c r="F212" s="6" t="n">
         <v>0.57</v>
@@ -5951,24 +5951,24 @@
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>CMI</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>NiSource</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D213" s="5" t="n">
-        <v>40.53</v>
+        <v>520.4</v>
       </c>
       <c r="E213" s="5" t="n">
-        <v>40.76</v>
+        <v>523.39</v>
       </c>
       <c r="F213" s="6" t="n">
         <v>0.57</v>
@@ -6003,24 +6003,24 @@
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>HON</t>
+          <t>AWK</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Technologies</t>
+          <t>American Water Works</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D215" s="5" t="n">
-        <v>206.6</v>
+        <v>128.18</v>
       </c>
       <c r="E215" s="5" t="n">
-        <v>207.73</v>
+        <v>128.88</v>
       </c>
       <c r="F215" s="6" t="n">
         <v>0.55</v>
@@ -6029,12 +6029,12 @@
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>AWK</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>American Water Works</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
@@ -6043,10 +6043,10 @@
         </is>
       </c>
       <c r="D216" s="5" t="n">
-        <v>128.18</v>
+        <v>80.52</v>
       </c>
       <c r="E216" s="5" t="n">
-        <v>128.88</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F216" s="6" t="n">
         <v>0.55</v>
@@ -6055,24 +6055,24 @@
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>HON</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>Honeywell Technologies</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D217" s="5" t="n">
-        <v>80.52</v>
+        <v>206.6</v>
       </c>
       <c r="E217" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>207.73</v>
       </c>
       <c r="F217" s="6" t="n">
         <v>0.55</v>
@@ -6107,24 +6107,24 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>999.35</v>
+        <v>155.35</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>1004.73</v>
+        <v>156.19</v>
       </c>
       <c r="F219" s="6" t="n">
         <v>0.54</v>
@@ -6133,24 +6133,24 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>155.35</v>
+        <v>796.1799999999999</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>156.19</v>
+        <v>800.47</v>
       </c>
       <c r="F220" s="6" t="n">
         <v>0.54</v>
@@ -6159,12 +6159,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -6173,10 +6173,10 @@
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>796.1799999999999</v>
+        <v>999.35</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>800.47</v>
+        <v>1004.73</v>
       </c>
       <c r="F221" s="6" t="n">
         <v>0.54</v>
@@ -6471,12 +6471,12 @@
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>VLTO</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>United Parcel Service</t>
+          <t>Veralto</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="D233" s="5" t="n">
-        <v>94.13</v>
+        <v>96.48</v>
       </c>
       <c r="E233" s="5" t="n">
-        <v>94.56999999999999</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="F233" s="6" t="n">
         <v>0.47</v>
@@ -6497,12 +6497,12 @@
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>VLTO</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Veralto</t>
+          <t>United Parcel Service</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="D234" s="5" t="n">
-        <v>96.48</v>
+        <v>94.13</v>
       </c>
       <c r="E234" s="5" t="n">
-        <v>96.93000000000001</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F234" s="6" t="n">
         <v>0.47</v>
@@ -6627,24 +6627,24 @@
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Snap-on</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D239" s="5" t="n">
-        <v>358.88</v>
+        <v>481.7</v>
       </c>
       <c r="E239" s="5" t="n">
-        <v>360.37</v>
+        <v>483.73</v>
       </c>
       <c r="F239" s="6" t="n">
         <v>0.42</v>
@@ -6653,24 +6653,24 @@
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D240" s="5" t="n">
-        <v>481.7</v>
+        <v>150.59</v>
       </c>
       <c r="E240" s="5" t="n">
-        <v>483.73</v>
+        <v>151.23</v>
       </c>
       <c r="F240" s="6" t="n">
         <v>0.42</v>
@@ -6705,24 +6705,24 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Snap-on</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D242" s="5" t="n">
-        <v>150.59</v>
+        <v>358.88</v>
       </c>
       <c r="E242" s="5" t="n">
-        <v>151.23</v>
+        <v>360.37</v>
       </c>
       <c r="F242" s="6" t="n">
         <v>0.42</v>
@@ -6731,24 +6731,24 @@
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>AEP</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Nordson Corporation</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D243" s="5" t="n">
-        <v>326.87</v>
+        <v>122.32</v>
       </c>
       <c r="E243" s="5" t="n">
-        <v>328.17</v>
+        <v>122.81</v>
       </c>
       <c r="F243" s="6" t="n">
         <v>0.4</v>
@@ -6757,24 +6757,24 @@
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>DECK</t>
+          <t>NDSN</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Deckers Brands</t>
+          <t>Nordson Corporation</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D244" s="5" t="n">
-        <v>82.56</v>
+        <v>326.87</v>
       </c>
       <c r="E244" s="5" t="n">
-        <v>82.89</v>
+        <v>328.17</v>
       </c>
       <c r="F244" s="6" t="n">
         <v>0.4</v>
@@ -6783,24 +6783,24 @@
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>AEP</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Jacobs Solutions</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D245" s="5" t="n">
-        <v>122.32</v>
+        <v>138.59</v>
       </c>
       <c r="E245" s="5" t="n">
-        <v>122.81</v>
+        <v>139.15</v>
       </c>
       <c r="F245" s="6" t="n">
         <v>0.4</v>
@@ -6809,24 +6809,24 @@
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>DECK</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Jacobs Solutions</t>
+          <t>Deckers Brands</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D246" s="5" t="n">
-        <v>138.59</v>
+        <v>82.56</v>
       </c>
       <c r="E246" s="5" t="n">
-        <v>139.15</v>
+        <v>82.89</v>
       </c>
       <c r="F246" s="6" t="n">
         <v>0.4</v>
@@ -6887,24 +6887,24 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>CHD</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>Church &amp; Dwight</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>360.14</v>
+        <v>97.73</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>361.54</v>
+        <v>98.11</v>
       </c>
       <c r="F249" s="6" t="n">
         <v>0.39</v>
@@ -6913,24 +6913,24 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>CHD</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>97.73</v>
+        <v>360.14</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>98.11</v>
+        <v>361.54</v>
       </c>
       <c r="F250" s="6" t="n">
         <v>0.39</v>
@@ -6965,24 +6965,24 @@
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>PTC Inc.</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D252" s="5" t="n">
-        <v>61.41</v>
+        <v>193.73</v>
       </c>
       <c r="E252" s="5" t="n">
-        <v>61.64</v>
+        <v>194.45</v>
       </c>
       <c r="F252" s="6" t="n">
         <v>0.37</v>
@@ -6991,24 +6991,24 @@
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>Kroger</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D253" s="5" t="n">
-        <v>228.42</v>
+        <v>61.41</v>
       </c>
       <c r="E253" s="5" t="n">
-        <v>229.26</v>
+        <v>61.64</v>
       </c>
       <c r="F253" s="6" t="n">
         <v>0.37</v>
@@ -7017,24 +7017,24 @@
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>PTC Inc.</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D254" s="5" t="n">
-        <v>193.73</v>
+        <v>228.42</v>
       </c>
       <c r="E254" s="5" t="n">
-        <v>194.45</v>
+        <v>229.26</v>
       </c>
       <c r="F254" s="6" t="n">
         <v>0.37</v>
@@ -7043,24 +7043,24 @@
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>TPR</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Tapestry, Inc.</t>
+          <t>Altria</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D255" s="5" t="n">
-        <v>115.82</v>
+        <v>71.42</v>
       </c>
       <c r="E255" s="5" t="n">
-        <v>116.24</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="F255" s="6" t="n">
         <v>0.36</v>
@@ -7069,24 +7069,24 @@
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TPR</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Altria</t>
+          <t>Tapestry, Inc.</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D256" s="5" t="n">
-        <v>71.42</v>
+        <v>115.82</v>
       </c>
       <c r="E256" s="5" t="n">
-        <v>71.68000000000001</v>
+        <v>116.24</v>
       </c>
       <c r="F256" s="6" t="n">
         <v>0.36</v>
@@ -7121,24 +7121,24 @@
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VTR</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Ventas</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D258" s="5" t="n">
-        <v>208.36</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="E258" s="5" t="n">
-        <v>209.06</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F258" s="6" t="n">
         <v>0.34</v>
@@ -7147,24 +7147,24 @@
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>VTR</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Ventas</t>
+          <t>Philip Morris International</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D259" s="5" t="n">
-        <v>81.76000000000001</v>
+        <v>200.5</v>
       </c>
       <c r="E259" s="5" t="n">
-        <v>82.04000000000001</v>
+        <v>201.19</v>
       </c>
       <c r="F259" s="6" t="n">
         <v>0.34</v>
@@ -7199,24 +7199,24 @@
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Philip Morris International</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D261" s="5" t="n">
-        <v>200.5</v>
+        <v>208.36</v>
       </c>
       <c r="E261" s="5" t="n">
-        <v>201.19</v>
+        <v>209.06</v>
       </c>
       <c r="F261" s="6" t="n">
         <v>0.34</v>
@@ -7251,24 +7251,24 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>FE</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>FirstEnergy</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>507.89</v>
+        <v>44.85</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>509.59</v>
+        <v>45</v>
       </c>
       <c r="F263" s="6" t="n">
         <v>0.33</v>
@@ -7277,12 +7277,12 @@
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="D264" s="5" t="n">
-        <v>52.3</v>
+        <v>507.89</v>
       </c>
       <c r="E264" s="5" t="n">
-        <v>52.47</v>
+        <v>509.59</v>
       </c>
       <c r="F264" s="6" t="n">
         <v>0.33</v>
@@ -7303,24 +7303,24 @@
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>FE</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>FirstEnergy</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D265" s="5" t="n">
-        <v>44.85</v>
+        <v>52.3</v>
       </c>
       <c r="E265" s="5" t="n">
-        <v>45</v>
+        <v>52.47</v>
       </c>
       <c r="F265" s="6" t="n">
         <v>0.33</v>
@@ -7329,24 +7329,24 @@
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Coca-Cola Company (The)</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D266" s="5" t="n">
-        <v>87.77</v>
+        <v>22.09</v>
       </c>
       <c r="E266" s="5" t="n">
-        <v>88.05</v>
+        <v>22.16</v>
       </c>
       <c r="F266" s="6" t="n">
         <v>0.32</v>
@@ -7355,24 +7355,24 @@
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>Coca-Cola Company (The)</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D267" s="5" t="n">
-        <v>22.09</v>
+        <v>87.77</v>
       </c>
       <c r="E267" s="5" t="n">
-        <v>22.16</v>
+        <v>88.05</v>
       </c>
       <c r="F267" s="6" t="n">
         <v>0.32</v>
@@ -7537,24 +7537,24 @@
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>PKG</t>
+          <t>NSC</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Packaging Corporation of America</t>
+          <t>Norfolk Southern</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D274" s="5" t="n">
-        <v>229.94</v>
+        <v>316.99</v>
       </c>
       <c r="E274" s="5" t="n">
-        <v>230.51</v>
+        <v>317.79</v>
       </c>
       <c r="F274" s="6" t="n">
         <v>0.25</v>
@@ -7563,24 +7563,24 @@
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>PKG</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Norfolk Southern</t>
+          <t>Packaging Corporation of America</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D275" s="5" t="n">
-        <v>316.99</v>
+        <v>229.94</v>
       </c>
       <c r="E275" s="5" t="n">
-        <v>317.79</v>
+        <v>230.51</v>
       </c>
       <c r="F275" s="6" t="n">
         <v>0.25</v>
@@ -7615,24 +7615,24 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>CMS Energy</t>
+          <t>Diamondback Energy</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>65.34</v>
+        <v>191.68</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>65.48999999999999</v>
+        <v>192.13</v>
       </c>
       <c r="F277" s="6" t="n">
         <v>0.23</v>
@@ -7641,24 +7641,24 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>DPZ</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Diamondback Energy</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>191.68</v>
+        <v>308.65</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>192.13</v>
+        <v>309.36</v>
       </c>
       <c r="F278" s="6" t="n">
         <v>0.23</v>
@@ -7667,24 +7667,24 @@
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>CMS Energy</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D279" s="5" t="n">
-        <v>286.52</v>
+        <v>65.34</v>
       </c>
       <c r="E279" s="5" t="n">
-        <v>287.18</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F279" s="6" t="n">
         <v>0.23</v>
@@ -7693,24 +7693,24 @@
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D280" s="5" t="n">
-        <v>159.97</v>
+        <v>274.66</v>
       </c>
       <c r="E280" s="5" t="n">
-        <v>160.34</v>
+        <v>275.28</v>
       </c>
       <c r="F280" s="6" t="n">
         <v>0.23</v>
@@ -7719,24 +7719,24 @@
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D281" s="5" t="n">
-        <v>274.66</v>
+        <v>286.52</v>
       </c>
       <c r="E281" s="5" t="n">
-        <v>275.28</v>
+        <v>287.18</v>
       </c>
       <c r="F281" s="6" t="n">
         <v>0.23</v>
@@ -7771,12 +7771,12 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>DPZ</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -7785,10 +7785,10 @@
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>308.65</v>
+        <v>159.97</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>309.36</v>
+        <v>160.34</v>
       </c>
       <c r="F283" s="6" t="n">
         <v>0.23</v>
@@ -8005,24 +8005,24 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>BALL</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Ball Corporation</t>
+          <t>Broadridge Financial Solutions</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>58.37</v>
+        <v>165.21</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>58.46</v>
+        <v>165.45</v>
       </c>
       <c r="F292" s="6" t="n">
         <v>0.15</v>
@@ -8031,24 +8031,24 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BALL</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions</t>
+          <t>Ball Corporation</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>165.21</v>
+        <v>58.37</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>165.45</v>
+        <v>58.46</v>
       </c>
       <c r="F293" s="6" t="n">
         <v>0.15</v>
@@ -8057,24 +8057,24 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>WEC</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>WEC Energy Group</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>103.61</v>
+        <v>54.3</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>103.74</v>
+        <v>54.37</v>
       </c>
       <c r="F294" s="6" t="n">
         <v>0.13</v>
@@ -8083,24 +8083,24 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>SYK</t>
+          <t>WEC</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Stryker Corporation</t>
+          <t>WEC Energy Group</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>276.97</v>
+        <v>103.61</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>277.33</v>
+        <v>103.74</v>
       </c>
       <c r="F295" s="6" t="n">
         <v>0.13</v>
@@ -8109,12 +8109,12 @@
     <row r="296">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>SYK</t>
         </is>
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Cooper Companies (The)</t>
+          <t>Stryker Corporation</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -8123,10 +8123,10 @@
         </is>
       </c>
       <c r="D296" s="5" t="n">
-        <v>54.3</v>
+        <v>276.97</v>
       </c>
       <c r="E296" s="5" t="n">
-        <v>54.37</v>
+        <v>277.33</v>
       </c>
       <c r="F296" s="6" t="n">
         <v>0.13</v>
@@ -8239,12 +8239,12 @@
     <row r="301">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>AES</t>
         </is>
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Exelon</t>
+          <t>AES Corporation</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -8253,10 +8253,10 @@
         </is>
       </c>
       <c r="D301" s="5" t="n">
-        <v>41.73</v>
+        <v>14.93</v>
       </c>
       <c r="E301" s="5" t="n">
-        <v>41.76</v>
+        <v>14.94</v>
       </c>
       <c r="F301" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8265,12 +8265,12 @@
     <row r="302">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>AES</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>AES Corporation</t>
+          <t>Exelon</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
@@ -8279,10 +8279,10 @@
         </is>
       </c>
       <c r="D302" s="5" t="n">
-        <v>14.93</v>
+        <v>41.73</v>
       </c>
       <c r="E302" s="5" t="n">
-        <v>14.94</v>
+        <v>41.76</v>
       </c>
       <c r="F302" s="6" t="n">
         <v>0.07000000000000001</v>
@@ -8395,24 +8395,24 @@
     <row r="307">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Union Pacific Corporation</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D307" s="5" t="n">
-        <v>278.2</v>
+        <v>281.69</v>
       </c>
       <c r="E307" s="5" t="n">
-        <v>278.34</v>
+        <v>281.83</v>
       </c>
       <c r="F307" s="6" t="n">
         <v>0.05</v>
@@ -8421,24 +8421,24 @@
     <row r="308">
       <c r="A308" s="4" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>UNP</t>
         </is>
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Union Pacific Corporation</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D308" s="5" t="n">
-        <v>281.69</v>
+        <v>278.2</v>
       </c>
       <c r="E308" s="5" t="n">
-        <v>281.83</v>
+        <v>278.34</v>
       </c>
       <c r="F308" s="6" t="n">
         <v>0.05</v>
@@ -8447,24 +8447,24 @@
     <row r="309">
       <c r="A309" s="4" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D309" s="5" t="n">
-        <v>82.14</v>
+        <v>75.52</v>
       </c>
       <c r="E309" s="5" t="n">
-        <v>82.17</v>
+        <v>75.55</v>
       </c>
       <c r="F309" s="6" t="n">
         <v>0.04</v>
@@ -8473,24 +8473,24 @@
     <row r="310">
       <c r="A310" s="4" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Omnicom Group</t>
+          <t>Delta Air Lines</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D310" s="5" t="n">
-        <v>76.45</v>
+        <v>82.14</v>
       </c>
       <c r="E310" s="5" t="n">
-        <v>76.48</v>
+        <v>82.17</v>
       </c>
       <c r="F310" s="6" t="n">
         <v>0.04</v>
@@ -8525,24 +8525,24 @@
     <row r="312">
       <c r="A312" s="4" t="inlineStr">
         <is>
-          <t>MCHP</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Omnicom Group</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D312" s="5" t="n">
-        <v>75.52</v>
+        <v>76.45</v>
       </c>
       <c r="E312" s="5" t="n">
-        <v>75.55</v>
+        <v>76.48</v>
       </c>
       <c r="F312" s="6" t="n">
         <v>0.04</v>
@@ -8551,24 +8551,24 @@
     <row r="313">
       <c r="A313" s="4" t="inlineStr">
         <is>
-          <t>UAL</t>
+          <t>DLTR</t>
         </is>
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>United Airlines Holdings</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D313" s="5" t="n">
-        <v>107.44</v>
+        <v>118.62</v>
       </c>
       <c r="E313" s="5" t="n">
-        <v>107.46</v>
+        <v>118.64</v>
       </c>
       <c r="F313" s="6" t="n">
         <v>0.02</v>
@@ -8577,24 +8577,24 @@
     <row r="314">
       <c r="A314" s="4" t="inlineStr">
         <is>
-          <t>SO</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D314" s="5" t="n">
-        <v>86.15000000000001</v>
+        <v>54.17</v>
       </c>
       <c r="E314" s="5" t="n">
-        <v>86.17</v>
+        <v>54.18</v>
       </c>
       <c r="F314" s="6" t="n">
         <v>0.02</v>
@@ -8603,24 +8603,24 @@
     <row r="315">
       <c r="A315" s="4" t="inlineStr">
         <is>
-          <t>AXP</t>
+          <t>UAL</t>
         </is>
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>United Airlines Holdings</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D315" s="5" t="n">
-        <v>308.1</v>
+        <v>107.44</v>
       </c>
       <c r="E315" s="5" t="n">
-        <v>308.17</v>
+        <v>107.46</v>
       </c>
       <c r="F315" s="6" t="n">
         <v>0.02</v>
@@ -8629,24 +8629,24 @@
     <row r="316">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>SO</t>
         </is>
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Dollar Tree</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D316" s="5" t="n">
-        <v>118.62</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E316" s="5" t="n">
-        <v>118.64</v>
+        <v>86.17</v>
       </c>
       <c r="F316" s="6" t="n">
         <v>0.02</v>
@@ -8655,24 +8655,24 @@
     <row r="317">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Republic Services</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D317" s="5" t="n">
-        <v>54.17</v>
+        <v>216.84</v>
       </c>
       <c r="E317" s="5" t="n">
-        <v>54.18</v>
+        <v>216.88</v>
       </c>
       <c r="F317" s="6" t="n">
         <v>0.02</v>
@@ -8681,12 +8681,12 @@
     <row r="318">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>LHX</t>
         </is>
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Republic Services</t>
+          <t>L3Harris</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
@@ -8695,10 +8695,10 @@
         </is>
       </c>
       <c r="D318" s="5" t="n">
-        <v>216.84</v>
+        <v>236.92</v>
       </c>
       <c r="E318" s="5" t="n">
-        <v>216.88</v>
+        <v>236.97</v>
       </c>
       <c r="F318" s="6" t="n">
         <v>0.02</v>
@@ -8707,24 +8707,24 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>LHX</t>
+          <t>AXP</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>L3Harris</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>236.92</v>
+        <v>308.1</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>236.97</v>
+        <v>308.17</v>
       </c>
       <c r="F319" s="6" t="n">
         <v>0.02</v>
@@ -8759,24 +8759,24 @@
     <row r="321">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>TECH</t>
         </is>
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Bio-Techne</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D321" s="5" t="n">
-        <v>138.75</v>
+        <v>72.45</v>
       </c>
       <c r="E321" s="5" t="n">
-        <v>138.76</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="F321" s="6" t="n">
         <v>0.01</v>
@@ -8785,24 +8785,24 @@
     <row r="322">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>TECH</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D322" s="5" t="n">
-        <v>72.45</v>
+        <v>138.75</v>
       </c>
       <c r="E322" s="5" t="n">
-        <v>72.45999999999999</v>
+        <v>138.76</v>
       </c>
       <c r="F322" s="6" t="n">
         <v>0.01</v>
@@ -8967,24 +8967,24 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>48.98</v>
+        <v>126.68</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>48.95</v>
+        <v>126.6</v>
       </c>
       <c r="F329" s="7" t="n">
         <v>-0.06</v>
@@ -8993,24 +8993,24 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>126.68</v>
+        <v>32.57</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>126.6</v>
+        <v>32.55</v>
       </c>
       <c r="F330" s="7" t="n">
         <v>-0.06</v>
@@ -9019,12 +9019,12 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
@@ -9033,10 +9033,10 @@
         </is>
       </c>
       <c r="D331" s="5" t="n">
-        <v>32.57</v>
+        <v>48.98</v>
       </c>
       <c r="E331" s="5" t="n">
-        <v>32.55</v>
+        <v>48.95</v>
       </c>
       <c r="F331" s="7" t="n">
         <v>-0.06</v>
@@ -9045,24 +9045,24 @@
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>COF</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D332" s="5" t="n">
-        <v>134.19</v>
+        <v>199.4</v>
       </c>
       <c r="E332" s="5" t="n">
-        <v>134.1</v>
+        <v>199.26</v>
       </c>
       <c r="F332" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9071,24 +9071,24 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>DOV</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>State Street Corporation</t>
+          <t>Dover Corporation</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>175.09</v>
+        <v>188.96</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>174.96</v>
+        <v>188.83</v>
       </c>
       <c r="F333" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9097,24 +9097,24 @@
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>DOV</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Dover Corporation</t>
+          <t>State Street Corporation</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D334" s="5" t="n">
-        <v>188.96</v>
+        <v>175.09</v>
       </c>
       <c r="E334" s="5" t="n">
-        <v>188.83</v>
+        <v>174.96</v>
       </c>
       <c r="F334" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9123,24 +9123,24 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>COF</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>199.4</v>
+        <v>134.19</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>199.26</v>
+        <v>134.1</v>
       </c>
       <c r="F335" s="7" t="n">
         <v>-0.07000000000000001</v>
@@ -9149,24 +9149,24 @@
     <row r="336">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>HII</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Huntington Ingalls Industries</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D336" s="5" t="n">
-        <v>265.02</v>
+        <v>78.2</v>
       </c>
       <c r="E336" s="5" t="n">
-        <v>264.8</v>
+        <v>78.14</v>
       </c>
       <c r="F336" s="7" t="n">
         <v>-0.08</v>
@@ -9175,24 +9175,24 @@
     <row r="337">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>HII</t>
         </is>
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Huntington Ingalls Industries</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D337" s="5" t="n">
-        <v>78.2</v>
+        <v>265.02</v>
       </c>
       <c r="E337" s="5" t="n">
-        <v>78.14</v>
+        <v>264.8</v>
       </c>
       <c r="F337" s="7" t="n">
         <v>-0.08</v>
@@ -9279,24 +9279,24 @@
     <row r="341">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>IFF</t>
         </is>
       </c>
       <c r="B341" s="4" t="inlineStr">
         <is>
-          <t>Fifth Third Bancorp</t>
+          <t>International Flavors &amp; Fragrances</t>
         </is>
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D341" s="5" t="n">
-        <v>50.7</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="E341" s="5" t="n">
-        <v>50.64</v>
+        <v>84.55</v>
       </c>
       <c r="F341" s="7" t="n">
         <v>-0.12</v>
@@ -9305,24 +9305,24 @@
     <row r="342">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>IFF</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="B342" s="4" t="inlineStr">
         <is>
-          <t>International Flavors &amp; Fragrances</t>
+          <t>Fifth Third Bancorp</t>
         </is>
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D342" s="5" t="n">
-        <v>84.65000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="E342" s="5" t="n">
-        <v>84.55</v>
+        <v>50.64</v>
       </c>
       <c r="F342" s="7" t="n">
         <v>-0.12</v>
@@ -9409,24 +9409,24 @@
     <row r="346">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Regions Financial Corporation</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D346" s="5" t="n">
-        <v>97.73999999999999</v>
+        <v>27.07</v>
       </c>
       <c r="E346" s="5" t="n">
-        <v>97.59</v>
+        <v>27.03</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>-0.15</v>
@@ -9435,24 +9435,24 @@
     <row r="347">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Regions Financial Corporation</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D347" s="5" t="n">
-        <v>27.07</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="E347" s="5" t="n">
-        <v>27.03</v>
+        <v>97.59</v>
       </c>
       <c r="F347" s="7" t="n">
         <v>-0.15</v>
@@ -9617,24 +9617,24 @@
     <row r="354">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B354" s="4" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D354" s="5" t="n">
-        <v>96.87</v>
+        <v>61.75</v>
       </c>
       <c r="E354" s="5" t="n">
-        <v>96.7</v>
+        <v>61.64</v>
       </c>
       <c r="F354" s="7" t="n">
         <v>-0.18</v>
@@ -9643,24 +9643,24 @@
     <row r="355">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D355" s="5" t="n">
-        <v>61.75</v>
+        <v>96.87</v>
       </c>
       <c r="E355" s="5" t="n">
-        <v>61.64</v>
+        <v>96.7</v>
       </c>
       <c r="F355" s="7" t="n">
         <v>-0.18</v>
@@ -9669,24 +9669,24 @@
     <row r="356">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>WYNN</t>
+          <t>WRB</t>
         </is>
       </c>
       <c r="B356" s="4" t="inlineStr">
         <is>
-          <t>Wynn Resorts</t>
+          <t>W. R. Berkley Corporation</t>
         </is>
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D356" s="5" t="n">
-        <v>75.29000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="E356" s="5" t="n">
-        <v>75.15000000000001</v>
+        <v>71.91</v>
       </c>
       <c r="F356" s="7" t="n">
         <v>-0.19</v>
@@ -9695,24 +9695,24 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>WRB</t>
+          <t>WYNN</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>W. R. Berkley Corporation</t>
+          <t>Wynn Resorts</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>72.05</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>71.91</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F357" s="7" t="n">
         <v>-0.19</v>
@@ -9851,12 +9851,12 @@
     <row r="363">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Expeditors International</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
@@ -9865,10 +9865,10 @@
         </is>
       </c>
       <c r="D363" s="5" t="n">
-        <v>193.71</v>
+        <v>66.11</v>
       </c>
       <c r="E363" s="5" t="n">
-        <v>193.24</v>
+        <v>65.95</v>
       </c>
       <c r="F363" s="7" t="n">
         <v>-0.24</v>
@@ -9877,24 +9877,24 @@
     <row r="364">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="B364" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>EOG Resources</t>
         </is>
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D364" s="5" t="n">
-        <v>66.11</v>
+        <v>148.51</v>
       </c>
       <c r="E364" s="5" t="n">
-        <v>65.95</v>
+        <v>148.16</v>
       </c>
       <c r="F364" s="7" t="n">
         <v>-0.24</v>
@@ -9903,24 +9903,24 @@
     <row r="365">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>EOG Resources</t>
+          <t>Expeditors International</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D365" s="5" t="n">
-        <v>148.51</v>
+        <v>193.71</v>
       </c>
       <c r="E365" s="5" t="n">
-        <v>148.16</v>
+        <v>193.24</v>
       </c>
       <c r="F365" s="7" t="n">
         <v>-0.24</v>
@@ -10137,24 +10137,24 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>ROK</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>Dexcom</t>
+          <t>Rockwell Automation</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>84.41</v>
+        <v>434.14</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>84.11</v>
+        <v>432.59</v>
       </c>
       <c r="F374" s="7" t="n">
         <v>-0.36</v>
@@ -10163,24 +10163,24 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>ROK</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>Rockwell Automation</t>
+          <t>Dexcom</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>434.14</v>
+        <v>84.41</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>432.59</v>
+        <v>84.11</v>
       </c>
       <c r="F375" s="7" t="n">
         <v>-0.36</v>
@@ -10189,24 +10189,24 @@
     <row r="376">
       <c r="A376" s="4" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B376" s="4" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D376" s="5" t="n">
-        <v>19.17</v>
+        <v>303.88</v>
       </c>
       <c r="E376" s="5" t="n">
-        <v>19.1</v>
+        <v>302.75</v>
       </c>
       <c r="F376" s="7" t="n">
         <v>-0.37</v>
@@ -10215,24 +10215,24 @@
     <row r="377">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D377" s="5" t="n">
-        <v>303.88</v>
+        <v>19.17</v>
       </c>
       <c r="E377" s="5" t="n">
-        <v>302.75</v>
+        <v>19.1</v>
       </c>
       <c r="F377" s="7" t="n">
         <v>-0.37</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>AJG</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>Arthur J. Gallagher &amp; Co.</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>178.85</v>
+        <v>234.05</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>177.82</v>
+        <v>232.7</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-0.58</v>
@@ -10865,12 +10865,12 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>First Solar</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D402" s="5" t="n">
-        <v>196.72</v>
+        <v>178.85</v>
       </c>
       <c r="E402" s="5" t="n">
-        <v>195.57</v>
+        <v>177.82</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>-0.58</v>
@@ -10891,24 +10891,24 @@
     <row r="403">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>AJG</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>Arthur J. Gallagher &amp; Co.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D403" s="5" t="n">
-        <v>234.05</v>
+        <v>196.72</v>
       </c>
       <c r="E403" s="5" t="n">
-        <v>232.7</v>
+        <v>195.57</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>-0.58</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>LYV</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Live Nation Entertainment</t>
+          <t>Dow Inc.</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>171.34</v>
+        <v>28.59</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>170.33</v>
+        <v>28.42</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-0.59</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Dow Inc.</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>28.59</v>
+        <v>218.73</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>28.42</v>
+        <v>217.43</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-0.59</v>
@@ -11021,24 +11021,24 @@
     <row r="408">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>LYV</t>
         </is>
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Live Nation Entertainment</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D408" s="5" t="n">
-        <v>218.73</v>
+        <v>171.34</v>
       </c>
       <c r="E408" s="5" t="n">
-        <v>217.43</v>
+        <v>170.33</v>
       </c>
       <c r="F408" s="7" t="n">
         <v>-0.59</v>
@@ -11125,24 +11125,24 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>LH</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>12.25</v>
+        <v>314.2</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>12.17</v>
+        <v>312.15</v>
       </c>
       <c r="F412" s="7" t="n">
         <v>-0.65</v>
@@ -11203,24 +11203,24 @@
     <row r="415">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>LH</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D415" s="5" t="n">
-        <v>314.2</v>
+        <v>12.25</v>
       </c>
       <c r="E415" s="5" t="n">
-        <v>312.15</v>
+        <v>12.17</v>
       </c>
       <c r="F415" s="7" t="n">
         <v>-0.65</v>
@@ -11281,24 +11281,24 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>SWK</t>
+          <t>MLM</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Stanley Black &amp; Decker</t>
+          <t>Martin Marietta Materials</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D418" s="5" t="n">
-        <v>89.17</v>
+        <v>481.57</v>
       </c>
       <c r="E418" s="5" t="n">
-        <v>88.56999999999999</v>
+        <v>478.35</v>
       </c>
       <c r="F418" s="7" t="n">
         <v>-0.67</v>
@@ -11333,24 +11333,24 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>MLM</t>
+          <t>SWK</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Martin Marietta Materials</t>
+          <t>Stanley Black &amp; Decker</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>481.57</v>
+        <v>89.17</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>478.35</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>-0.67</v>
@@ -11463,24 +11463,24 @@
     <row r="425">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>EXE</t>
+          <t>TGT</t>
         </is>
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Expand Energy</t>
+          <t>Target Corporation</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D425" s="5" t="n">
-        <v>88.86</v>
+        <v>154.76</v>
       </c>
       <c r="E425" s="5" t="n">
-        <v>88.22</v>
+        <v>153.64</v>
       </c>
       <c r="F425" s="7" t="n">
         <v>-0.72</v>
@@ -11489,24 +11489,24 @@
     <row r="426">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>EXE</t>
         </is>
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>Target Corporation</t>
+          <t>Expand Energy</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D426" s="5" t="n">
-        <v>154.76</v>
+        <v>88.86</v>
       </c>
       <c r="E426" s="5" t="n">
-        <v>153.64</v>
+        <v>88.22</v>
       </c>
       <c r="F426" s="7" t="n">
         <v>-0.72</v>
@@ -11723,24 +11723,24 @@
     <row r="435">
       <c r="A435" s="4" t="inlineStr">
         <is>
-          <t>ROL</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Rollins, Inc.</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D435" s="5" t="n">
-        <v>32.26</v>
+        <v>34.34</v>
       </c>
       <c r="E435" s="5" t="n">
-        <v>31.98</v>
+        <v>34.04</v>
       </c>
       <c r="F435" s="7" t="n">
         <v>-0.87</v>
@@ -11749,24 +11749,24 @@
     <row r="436">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>ROL</t>
         </is>
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>Rollins, Inc.</t>
         </is>
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D436" s="5" t="n">
-        <v>34.34</v>
+        <v>32.26</v>
       </c>
       <c r="E436" s="5" t="n">
-        <v>34.04</v>
+        <v>31.98</v>
       </c>
       <c r="F436" s="7" t="n">
         <v>-0.87</v>
@@ -12295,24 +12295,24 @@
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Devon Energy</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D457" s="5" t="n">
-        <v>60.01</v>
+        <v>48.92</v>
       </c>
       <c r="E457" s="5" t="n">
-        <v>59.2</v>
+        <v>48.26</v>
       </c>
       <c r="F457" s="7" t="n">
         <v>-1.35</v>
@@ -12321,24 +12321,24 @@
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>Devon Energy</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D458" s="5" t="n">
-        <v>48.92</v>
+        <v>60.01</v>
       </c>
       <c r="E458" s="5" t="n">
-        <v>48.26</v>
+        <v>59.2</v>
       </c>
       <c r="F458" s="7" t="n">
         <v>-1.35</v>
@@ -12607,24 +12607,24 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVR</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>Sandisk</t>
+          <t>NVR, Inc.</t>
         </is>
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D469" s="5" t="n">
-        <v>1609.46</v>
+        <v>6002.55</v>
       </c>
       <c r="E469" s="5" t="n">
-        <v>1581.82</v>
+        <v>5899.16</v>
       </c>
       <c r="F469" s="7" t="n">
         <v>-1.72</v>
@@ -12633,24 +12633,24 @@
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>NVR</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>NVR, Inc.</t>
+          <t>Sandisk</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D470" s="5" t="n">
-        <v>6002.55</v>
+        <v>1609.46</v>
       </c>
       <c r="E470" s="5" t="n">
-        <v>5899.16</v>
+        <v>1581.82</v>
       </c>
       <c r="F470" s="7" t="n">
         <v>-1.72</v>
@@ -12789,24 +12789,24 @@
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
-          <t>CVS</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>DuPont</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D476" s="5" t="n">
-        <v>87.8</v>
+        <v>132.48</v>
       </c>
       <c r="E476" s="5" t="n">
-        <v>86.16</v>
+        <v>130</v>
       </c>
       <c r="F476" s="7" t="n">
         <v>-1.87</v>
@@ -12815,24 +12815,24 @@
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>CVS</t>
         </is>
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>DuPont</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D477" s="5" t="n">
-        <v>132.48</v>
+        <v>87.8</v>
       </c>
       <c r="E477" s="5" t="n">
-        <v>130</v>
+        <v>86.16</v>
       </c>
       <c r="F477" s="7" t="n">
         <v>-1.87</v>
@@ -12893,24 +12893,24 @@
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D480" s="5" t="n">
-        <v>226.54</v>
+        <v>181.63</v>
       </c>
       <c r="E480" s="5" t="n">
-        <v>222.04</v>
+        <v>178.01</v>
       </c>
       <c r="F480" s="7" t="n">
         <v>-1.99</v>
@@ -12919,24 +12919,24 @@
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D481" s="5" t="n">
-        <v>181.63</v>
+        <v>226.54</v>
       </c>
       <c r="E481" s="5" t="n">
-        <v>178.01</v>
+        <v>222.04</v>
       </c>
       <c r="F481" s="7" t="n">
         <v>-1.99</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 02 close to Oct 09 close  |  503 companies  |  updated 2026-10-11 09:30</t>
+          <t>Oct 02 close to Oct 09 close  |  503 companies  |  updated 2026-10-12 10:00</t>
         </is>
       </c>
     </row>
@@ -14187,30 +14187,30 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>TSCO</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>Tractor Supply</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>163.88</v>
+        <v>31.09</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>177.63</v>
+        <v>33.7</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>177.63</v>
+        <v>33.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>163.28</v>
+        <v>31.09</v>
       </c>
       <c r="H20" s="6" t="n">
         <v>8.390000000000001</v>
@@ -14219,30 +14219,30 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>TSCO</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Tractor Supply</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>31.09</v>
+        <v>163.88</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>33.7</v>
+        <v>177.63</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>33.7</v>
+        <v>177.63</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>31.09</v>
+        <v>163.28</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>8.390000000000001</v>
@@ -15435,30 +15435,30 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>EBAY</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>MSCI</t>
+          <t>eBay Inc.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>535.95</v>
+        <v>106.4</v>
       </c>
       <c r="E59" s="5" t="n">
-        <v>565.12</v>
+        <v>112.19</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>565.12</v>
+        <v>112.19</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>535.95</v>
+        <v>106.4</v>
       </c>
       <c r="H59" s="6" t="n">
         <v>5.44</v>
@@ -15467,30 +15467,30 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>eBay Inc.</t>
+          <t>MSCI</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>106.4</v>
+        <v>535.95</v>
       </c>
       <c r="E60" s="5" t="n">
-        <v>112.19</v>
+        <v>565.12</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>112.19</v>
+        <v>565.12</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>106.4</v>
+        <v>535.95</v>
       </c>
       <c r="H60" s="6" t="n">
         <v>5.44</v>
@@ -16427,30 +16427,30 @@
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>TJX</t>
+          <t>KDP</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>TJX Companies</t>
+          <t>Keurig Dr Pepper</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>132.68</v>
+        <v>30.37</v>
       </c>
       <c r="E90" s="5" t="n">
-        <v>138.76</v>
+        <v>31.76</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>138.8</v>
+        <v>31.76</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>132.68</v>
+        <v>30.37</v>
       </c>
       <c r="H90" s="6" t="n">
         <v>4.58</v>
@@ -16459,30 +16459,30 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>KDP</t>
+          <t>TJX</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Keurig Dr Pepper</t>
+          <t>TJX Companies</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>30.37</v>
+        <v>132.68</v>
       </c>
       <c r="E91" s="5" t="n">
-        <v>31.76</v>
+        <v>138.76</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>31.76</v>
+        <v>138.8</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>30.37</v>
+        <v>132.68</v>
       </c>
       <c r="H91" s="6" t="n">
         <v>4.58</v>
@@ -16875,30 +16875,30 @@
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Hasbro</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D104" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="E104" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>93.31999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>89.54000000000001</v>
+        <v>80.41</v>
       </c>
       <c r="H104" s="6" t="n">
         <v>4.22</v>
@@ -16907,30 +16907,30 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Hasbro</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>80.41</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="E105" s="5" t="n">
-        <v>83.8</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>83.8</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>80.41</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="H105" s="6" t="n">
         <v>4.22</v>
@@ -16971,30 +16971,30 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>140</v>
+        <v>240.39</v>
       </c>
       <c r="E107" s="5" t="n">
-        <v>145.78</v>
+        <v>250.33</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>145.78</v>
+        <v>251.41</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>140</v>
+        <v>240.39</v>
       </c>
       <c r="H107" s="6" t="n">
         <v>4.13</v>
@@ -17003,30 +17003,30 @@
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>MET</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D108" s="5" t="n">
-        <v>240.39</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="E108" s="5" t="n">
-        <v>250.33</v>
+        <v>98.33</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>251.41</v>
+        <v>98.47</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>240.39</v>
+        <v>94.43000000000001</v>
       </c>
       <c r="H108" s="6" t="n">
         <v>4.13</v>
@@ -17035,30 +17035,30 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>MET</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>140</v>
       </c>
       <c r="E109" s="5" t="n">
-        <v>98.33</v>
+        <v>145.78</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>98.47</v>
+        <v>145.78</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>94.43000000000001</v>
+        <v>140</v>
       </c>
       <c r="H109" s="6" t="n">
         <v>4.13</v>
@@ -17131,30 +17131,30 @@
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>CAH</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D112" s="5" t="n">
-        <v>228.3</v>
+        <v>114.02</v>
       </c>
       <c r="E112" s="5" t="n">
-        <v>237.57</v>
+        <v>118.65</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>238.96</v>
+        <v>118.65</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>228.3</v>
+        <v>114.02</v>
       </c>
       <c r="H112" s="6" t="n">
         <v>4.06</v>
@@ -17163,30 +17163,30 @@
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>CAH</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D113" s="5" t="n">
-        <v>114.02</v>
+        <v>228.3</v>
       </c>
       <c r="E113" s="5" t="n">
-        <v>118.65</v>
+        <v>237.57</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>118.65</v>
+        <v>238.96</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>114.02</v>
+        <v>228.3</v>
       </c>
       <c r="H113" s="6" t="n">
         <v>4.06</v>
@@ -17483,30 +17483,30 @@
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>WFC</t>
         </is>
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D123" s="5" t="n">
-        <v>403.24</v>
+        <v>80.45</v>
       </c>
       <c r="E123" s="5" t="n">
-        <v>418.78</v>
+        <v>83.55</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>419.91</v>
+        <v>83.55</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>398.5</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="H123" s="6" t="n">
         <v>3.85</v>
@@ -17515,30 +17515,30 @@
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>WFC</t>
+          <t>PANW</t>
         </is>
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D124" s="5" t="n">
-        <v>80.45</v>
+        <v>403.24</v>
       </c>
       <c r="E124" s="5" t="n">
-        <v>83.55</v>
+        <v>418.78</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>83.55</v>
+        <v>419.91</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>80.26000000000001</v>
+        <v>398.5</v>
       </c>
       <c r="H124" s="6" t="n">
         <v>3.85</v>
@@ -18027,30 +18027,30 @@
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PGR</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Progressive Corporation</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D140" s="5" t="n">
-        <v>517.53</v>
+        <v>210.31</v>
       </c>
       <c r="E140" s="5" t="n">
-        <v>535.0700000000001</v>
+        <v>217.43</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>535.0700000000001</v>
+        <v>218.73</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>517.53</v>
+        <v>210.31</v>
       </c>
       <c r="H140" s="6" t="n">
         <v>3.39</v>
@@ -18059,30 +18059,30 @@
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
         <is>
-          <t>PGR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Progressive Corporation</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D141" s="5" t="n">
-        <v>210.31</v>
+        <v>517.53</v>
       </c>
       <c r="E141" s="5" t="n">
-        <v>217.43</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>218.73</v>
+        <v>535.0700000000001</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>210.31</v>
+        <v>517.53</v>
       </c>
       <c r="H141" s="6" t="n">
         <v>3.39</v>
@@ -18123,30 +18123,30 @@
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>LDOS</t>
+          <t>MRSH</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Leidos</t>
+          <t>Marsh McLennan</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D143" s="5" t="n">
-        <v>117.74</v>
+        <v>170.06</v>
       </c>
       <c r="E143" s="5" t="n">
-        <v>121.68</v>
+        <v>175.76</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>121.68</v>
+        <v>176.67</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>113.55</v>
+        <v>170.06</v>
       </c>
       <c r="H143" s="6" t="n">
         <v>3.35</v>
@@ -18155,30 +18155,30 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>MRSH</t>
+          <t>LDOS</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Marsh McLennan</t>
+          <t>Leidos</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D144" s="5" t="n">
-        <v>170.06</v>
+        <v>117.74</v>
       </c>
       <c r="E144" s="5" t="n">
-        <v>175.76</v>
+        <v>121.68</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>176.67</v>
+        <v>121.68</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>170.06</v>
+        <v>113.55</v>
       </c>
       <c r="H144" s="6" t="n">
         <v>3.35</v>
@@ -18475,30 +18475,30 @@
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>ZBRA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D154" s="5" t="n">
-        <v>375.86</v>
+        <v>164.01</v>
       </c>
       <c r="E154" s="5" t="n">
-        <v>387.18</v>
+        <v>168.94</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>387.18</v>
+        <v>168.94</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>375.66</v>
+        <v>164</v>
       </c>
       <c r="H154" s="6" t="n">
         <v>3.01</v>
@@ -18507,30 +18507,30 @@
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>ZBRA</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D155" s="5" t="n">
-        <v>164.01</v>
+        <v>375.86</v>
       </c>
       <c r="E155" s="5" t="n">
-        <v>168.94</v>
+        <v>387.18</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>168.94</v>
+        <v>387.18</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>164</v>
+        <v>375.66</v>
       </c>
       <c r="H155" s="6" t="n">
         <v>3.01</v>
@@ -18539,30 +18539,30 @@
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>OTIS</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Otis Worldwide</t>
+          <t>Tyson Foods</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D156" s="5" t="n">
-        <v>64.05</v>
+        <v>51.89</v>
       </c>
       <c r="E156" s="5" t="n">
-        <v>65.95</v>
+        <v>53.43</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>66.45</v>
+        <v>53.43</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>64.05</v>
+        <v>51.7</v>
       </c>
       <c r="H156" s="6" t="n">
         <v>2.97</v>
@@ -18603,30 +18603,30 @@
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>TSN</t>
+          <t>OTIS</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Tyson Foods</t>
+          <t>Otis Worldwide</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D158" s="5" t="n">
-        <v>51.89</v>
+        <v>64.05</v>
       </c>
       <c r="E158" s="5" t="n">
-        <v>53.43</v>
+        <v>65.95</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>53.43</v>
+        <v>66.45</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>51.7</v>
+        <v>64.05</v>
       </c>
       <c r="H158" s="6" t="n">
         <v>2.97</v>
@@ -18763,30 +18763,30 @@
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>INVH</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Invitation Homes</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D163" s="5" t="n">
-        <v>180.8</v>
+        <v>26.04</v>
       </c>
       <c r="E163" s="5" t="n">
-        <v>186</v>
+        <v>26.79</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>188.85</v>
+        <v>26.79</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>179.5</v>
+        <v>25.86</v>
       </c>
       <c r="H163" s="6" t="n">
         <v>2.88</v>
@@ -18795,30 +18795,30 @@
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>INVH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Invitation Homes</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D164" s="5" t="n">
-        <v>26.04</v>
+        <v>180.8</v>
       </c>
       <c r="E164" s="5" t="n">
-        <v>26.79</v>
+        <v>186</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>26.79</v>
+        <v>188.85</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>25.86</v>
+        <v>179.5</v>
       </c>
       <c r="H164" s="6" t="n">
         <v>2.88</v>
@@ -18827,30 +18827,30 @@
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>ATO</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Atmos Energy</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D165" s="5" t="n">
-        <v>44.36</v>
+        <v>157.17</v>
       </c>
       <c r="E165" s="5" t="n">
-        <v>45.63</v>
+        <v>161.66</v>
       </c>
       <c r="F165" s="5" t="n">
-        <v>46.14</v>
+        <v>161.66</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>44.36</v>
+        <v>157.17</v>
       </c>
       <c r="H165" s="6" t="n">
         <v>2.86</v>
@@ -18859,30 +18859,30 @@
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>ATO</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Atmos Energy</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D166" s="5" t="n">
-        <v>157.17</v>
+        <v>44.36</v>
       </c>
       <c r="E166" s="5" t="n">
-        <v>161.66</v>
+        <v>45.63</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>161.66</v>
+        <v>46.14</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>157.17</v>
+        <v>44.36</v>
       </c>
       <c r="H166" s="6" t="n">
         <v>2.86</v>
@@ -19115,12 +19115,12 @@
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>FLEX</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Flex Ltd.</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -19129,16 +19129,16 @@
         </is>
       </c>
       <c r="D174" s="5" t="n">
-        <v>116.61</v>
+        <v>354.32</v>
       </c>
       <c r="E174" s="5" t="n">
-        <v>119.83</v>
+        <v>364.09</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>121.38</v>
+        <v>364.23</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>114.74</v>
+        <v>354.32</v>
       </c>
       <c r="H174" s="6" t="n">
         <v>2.76</v>
@@ -19147,12 +19147,12 @@
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>FLEX</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -19161,16 +19161,16 @@
         </is>
       </c>
       <c r="D175" s="5" t="n">
-        <v>354.32</v>
+        <v>116.61</v>
       </c>
       <c r="E175" s="5" t="n">
-        <v>364.09</v>
+        <v>119.83</v>
       </c>
       <c r="F175" s="5" t="n">
-        <v>364.23</v>
+        <v>121.38</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>354.32</v>
+        <v>114.74</v>
       </c>
       <c r="H175" s="6" t="n">
         <v>2.76</v>
@@ -19371,30 +19371,30 @@
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>WTW</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Willis Towers Watson</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D182" s="5" t="n">
-        <v>219.88</v>
+        <v>288.61</v>
       </c>
       <c r="E182" s="5" t="n">
-        <v>225.71</v>
+        <v>296.26</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>225.71</v>
+        <v>297.86</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>218.43</v>
+        <v>288.11</v>
       </c>
       <c r="H182" s="6" t="n">
         <v>2.65</v>
@@ -19403,30 +19403,30 @@
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>WTW</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Willis Towers Watson</t>
+          <t>Biogen</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D183" s="5" t="n">
-        <v>288.61</v>
+        <v>219.88</v>
       </c>
       <c r="E183" s="5" t="n">
-        <v>296.26</v>
+        <v>225.71</v>
       </c>
       <c r="F183" s="5" t="n">
-        <v>297.86</v>
+        <v>225.71</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>288.11</v>
+        <v>218.43</v>
       </c>
       <c r="H183" s="6" t="n">
         <v>2.65</v>
@@ -19435,12 +19435,12 @@
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Consolidated Edison</t>
+          <t>Edison International</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -19449,16 +19449,16 @@
         </is>
       </c>
       <c r="D184" s="5" t="n">
-        <v>103.39</v>
+        <v>53.89</v>
       </c>
       <c r="E184" s="5" t="n">
-        <v>106.1</v>
+        <v>55.3</v>
       </c>
       <c r="F184" s="5" t="n">
-        <v>106.1</v>
+        <v>55.3</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>103.38</v>
+        <v>53.89</v>
       </c>
       <c r="H184" s="6" t="n">
         <v>2.62</v>
@@ -19467,12 +19467,12 @@
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Edison International</t>
+          <t>Consolidated Edison</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -19481,16 +19481,16 @@
         </is>
       </c>
       <c r="D185" s="5" t="n">
-        <v>53.89</v>
+        <v>103.39</v>
       </c>
       <c r="E185" s="5" t="n">
-        <v>55.3</v>
+        <v>106.1</v>
       </c>
       <c r="F185" s="5" t="n">
-        <v>55.3</v>
+        <v>106.1</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>53.89</v>
+        <v>103.38</v>
       </c>
       <c r="H185" s="6" t="n">
         <v>2.62</v>
@@ -19755,30 +19755,30 @@
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Medtronic</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D194" s="5" t="n">
-        <v>86.38</v>
+        <v>126.05</v>
       </c>
       <c r="E194" s="5" t="n">
-        <v>88.48</v>
+        <v>129.11</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>88.48</v>
+        <v>129.48</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>85.51000000000001</v>
+        <v>126.05</v>
       </c>
       <c r="H194" s="6" t="n">
         <v>2.43</v>
@@ -19787,30 +19787,30 @@
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>Medtronic</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D195" s="5" t="n">
-        <v>126.05</v>
+        <v>86.38</v>
       </c>
       <c r="E195" s="5" t="n">
-        <v>129.11</v>
+        <v>88.48</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>129.48</v>
+        <v>88.48</v>
       </c>
       <c r="G195" s="5" t="n">
-        <v>126.05</v>
+        <v>85.51000000000001</v>
       </c>
       <c r="H195" s="6" t="n">
         <v>2.43</v>
@@ -20075,30 +20075,30 @@
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>VMRK</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Vivmark Residential</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D204" s="5" t="n">
-        <v>59.79</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E204" s="5" t="n">
-        <v>61.16</v>
+        <v>73.69</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>61.16</v>
+        <v>73.69</v>
       </c>
       <c r="G204" s="5" t="n">
-        <v>59.29</v>
+        <v>71.14</v>
       </c>
       <c r="H204" s="6" t="n">
         <v>2.29</v>
@@ -20107,30 +20107,30 @@
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>VMRK</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Vivmark Residential</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D205" s="5" t="n">
-        <v>72.04000000000001</v>
+        <v>59.79</v>
       </c>
       <c r="E205" s="5" t="n">
-        <v>73.69</v>
+        <v>61.16</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>73.69</v>
+        <v>61.16</v>
       </c>
       <c r="G205" s="5" t="n">
-        <v>71.14</v>
+        <v>59.29</v>
       </c>
       <c r="H205" s="6" t="n">
         <v>2.29</v>
@@ -20171,30 +20171,30 @@
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>GEHC</t>
+          <t>EVRG</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>Evergy</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D207" s="5" t="n">
-        <v>64.29000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="E207" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="F207" s="5" t="n">
-        <v>65.73999999999999</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>64.22</v>
+        <v>79.09</v>
       </c>
       <c r="H207" s="6" t="n">
         <v>2.26</v>
@@ -20203,30 +20203,30 @@
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>EVRG</t>
+          <t>GEHC</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Evergy</t>
+          <t>GE HealthCare</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D208" s="5" t="n">
-        <v>79.17</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E208" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="G208" s="5" t="n">
-        <v>79.09</v>
+        <v>64.22</v>
       </c>
       <c r="H208" s="6" t="n">
         <v>2.26</v>
@@ -20235,30 +20235,30 @@
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>HLT</t>
+          <t>SJM</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Hilton Worldwide</t>
+          <t>J.M. Smucker Company (The)</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D209" s="5" t="n">
-        <v>319.36</v>
+        <v>117.19</v>
       </c>
       <c r="E209" s="5" t="n">
-        <v>326.56</v>
+        <v>119.83</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>326.56</v>
+        <v>119.83</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>316.12</v>
+        <v>115.93</v>
       </c>
       <c r="H209" s="6" t="n">
         <v>2.25</v>
@@ -20267,30 +20267,30 @@
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>AEE</t>
+          <t>HLT</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Ameren</t>
+          <t>Hilton Worldwide</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D210" s="5" t="n">
-        <v>99.94</v>
+        <v>319.36</v>
       </c>
       <c r="E210" s="5" t="n">
-        <v>102.19</v>
+        <v>326.56</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>102.19</v>
+        <v>326.56</v>
       </c>
       <c r="G210" s="5" t="n">
-        <v>99.7</v>
+        <v>316.12</v>
       </c>
       <c r="H210" s="6" t="n">
         <v>2.25</v>
@@ -20299,30 +20299,30 @@
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>AEE</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>J.M. Smucker Company (The)</t>
+          <t>Ameren</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D211" s="5" t="n">
-        <v>117.19</v>
+        <v>99.94</v>
       </c>
       <c r="E211" s="5" t="n">
-        <v>119.83</v>
+        <v>102.19</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>119.83</v>
+        <v>102.19</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>115.93</v>
+        <v>99.7</v>
       </c>
       <c r="H211" s="6" t="n">
         <v>2.25</v>
@@ -20555,30 +20555,30 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>HONA</t>
+          <t>CNP</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Honeywell Aerospace</t>
+          <t>CenterPoint Energy</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D219" s="5" t="n">
-        <v>154.63</v>
+        <v>37.79</v>
       </c>
       <c r="E219" s="5" t="n">
-        <v>157.94</v>
+        <v>38.6</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>157.94</v>
+        <v>38.6</v>
       </c>
       <c r="G219" s="5" t="n">
-        <v>153.07</v>
+        <v>37.75</v>
       </c>
       <c r="H219" s="6" t="n">
         <v>2.14</v>
@@ -20587,30 +20587,30 @@
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>CNP</t>
+          <t>WM</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>CenterPoint Energy</t>
+          <t>Waste Management</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D220" s="5" t="n">
-        <v>37.79</v>
+        <v>204.45</v>
       </c>
       <c r="E220" s="5" t="n">
-        <v>38.6</v>
+        <v>208.83</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>38.6</v>
+        <v>210.1</v>
       </c>
       <c r="G220" s="5" t="n">
-        <v>37.75</v>
+        <v>204.45</v>
       </c>
       <c r="H220" s="6" t="n">
         <v>2.14</v>
@@ -20619,12 +20619,12 @@
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>WM</t>
+          <t>HONA</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Waste Management</t>
+          <t>Honeywell Aerospace</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -20633,16 +20633,16 @@
         </is>
       </c>
       <c r="D221" s="5" t="n">
-        <v>204.45</v>
+        <v>154.63</v>
       </c>
       <c r="E221" s="5" t="n">
-        <v>208.83</v>
+        <v>157.94</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>210.1</v>
+        <v>157.94</v>
       </c>
       <c r="G221" s="5" t="n">
-        <v>204.45</v>
+        <v>153.07</v>
       </c>
       <c r="H221" s="6" t="n">
         <v>2.14</v>
@@ -20939,30 +20939,30 @@
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>DTE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>DTE Energy</t>
+          <t>Newmont</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D231" s="5" t="n">
-        <v>124.45</v>
+        <v>115.56</v>
       </c>
       <c r="E231" s="5" t="n">
-        <v>126.9</v>
+        <v>117.84</v>
       </c>
       <c r="F231" s="5" t="n">
-        <v>128.22</v>
+        <v>117.84</v>
       </c>
       <c r="G231" s="5" t="n">
-        <v>124.45</v>
+        <v>113.54</v>
       </c>
       <c r="H231" s="6" t="n">
         <v>1.97</v>
@@ -20971,30 +20971,30 @@
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>DTE</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Newmont</t>
+          <t>DTE Energy</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D232" s="5" t="n">
-        <v>115.56</v>
+        <v>124.45</v>
       </c>
       <c r="E232" s="5" t="n">
-        <v>117.84</v>
+        <v>126.9</v>
       </c>
       <c r="F232" s="5" t="n">
-        <v>117.84</v>
+        <v>128.22</v>
       </c>
       <c r="G232" s="5" t="n">
-        <v>113.54</v>
+        <v>124.45</v>
       </c>
       <c r="H232" s="6" t="n">
         <v>1.97</v>
@@ -21515,30 +21515,30 @@
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Lumentum</t>
+          <t>Agilent Technologies</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D249" s="5" t="n">
-        <v>1085.42</v>
+        <v>167.78</v>
       </c>
       <c r="E249" s="5" t="n">
-        <v>1103.36</v>
+        <v>170.54</v>
       </c>
       <c r="F249" s="5" t="n">
-        <v>1133.4</v>
+        <v>171.29</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>1048.6</v>
+        <v>167.78</v>
       </c>
       <c r="H249" s="6" t="n">
         <v>1.65</v>
@@ -21547,30 +21547,30 @@
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D250" s="5" t="n">
-        <v>167.78</v>
+        <v>1085.42</v>
       </c>
       <c r="E250" s="5" t="n">
-        <v>170.54</v>
+        <v>1103.36</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>171.29</v>
+        <v>1133.4</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>167.78</v>
+        <v>1048.6</v>
       </c>
       <c r="H250" s="6" t="n">
         <v>1.65</v>
@@ -21931,30 +21931,30 @@
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>MAA</t>
+          <t>TKO</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Mid-America Apartment Communities</t>
+          <t>TKO Group Holdings</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D262" s="5" t="n">
-        <v>115.27</v>
+        <v>175.58</v>
       </c>
       <c r="E262" s="5" t="n">
-        <v>116.86</v>
+        <v>178.01</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>116.99</v>
+        <v>181.63</v>
       </c>
       <c r="G262" s="5" t="n">
-        <v>114.21</v>
+        <v>175.58</v>
       </c>
       <c r="H262" s="6" t="n">
         <v>1.38</v>
@@ -21963,30 +21963,30 @@
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>TKO</t>
+          <t>MAA</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>TKO Group Holdings</t>
+          <t>Mid-America Apartment Communities</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D263" s="5" t="n">
-        <v>175.58</v>
+        <v>115.27</v>
       </c>
       <c r="E263" s="5" t="n">
-        <v>178.01</v>
+        <v>116.86</v>
       </c>
       <c r="F263" s="5" t="n">
-        <v>181.63</v>
+        <v>116.99</v>
       </c>
       <c r="G263" s="5" t="n">
-        <v>175.58</v>
+        <v>114.21</v>
       </c>
       <c r="H263" s="6" t="n">
         <v>1.38</v>
@@ -22251,30 +22251,30 @@
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D272" s="5" t="n">
-        <v>504.73</v>
+        <v>53.75</v>
       </c>
       <c r="E272" s="5" t="n">
-        <v>510.08</v>
+        <v>54.32</v>
       </c>
       <c r="F272" s="5" t="n">
-        <v>510.08</v>
+        <v>54.32</v>
       </c>
       <c r="G272" s="5" t="n">
-        <v>502.31</v>
+        <v>53.52</v>
       </c>
       <c r="H272" s="6" t="n">
         <v>1.06</v>
@@ -22283,30 +22283,30 @@
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>BAC</t>
+          <t>VRTX</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Vertex Pharmaceuticals</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D273" s="5" t="n">
-        <v>53.75</v>
+        <v>504.73</v>
       </c>
       <c r="E273" s="5" t="n">
-        <v>54.32</v>
+        <v>510.08</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>54.32</v>
+        <v>510.08</v>
       </c>
       <c r="G273" s="5" t="n">
-        <v>53.52</v>
+        <v>502.31</v>
       </c>
       <c r="H273" s="6" t="n">
         <v>1.06</v>
@@ -22411,30 +22411,30 @@
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>ZBH</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Fair Isaac</t>
+          <t>Zimmer Biomet</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D277" s="5" t="n">
-        <v>661.25</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="E277" s="5" t="n">
-        <v>667.58</v>
+        <v>89.14</v>
       </c>
       <c r="F277" s="5" t="n">
-        <v>707.4299999999999</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="G277" s="5" t="n">
-        <v>661.25</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="H277" s="6" t="n">
         <v>0.96</v>
@@ -22443,30 +22443,30 @@
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>ZBH</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D278" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>661.25</v>
       </c>
       <c r="E278" s="5" t="n">
-        <v>89.14</v>
+        <v>667.58</v>
       </c>
       <c r="F278" s="5" t="n">
-        <v>91.56999999999999</v>
+        <v>707.4299999999999</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>88.29000000000001</v>
+        <v>661.25</v>
       </c>
       <c r="H278" s="6" t="n">
         <v>0.96</v>
@@ -22571,30 +22571,30 @@
     <row r="282">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>XYL</t>
         </is>
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Merck &amp; Co.</t>
+          <t>Xylem Inc.</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D282" s="5" t="n">
-        <v>144.3</v>
+        <v>101.79</v>
       </c>
       <c r="E282" s="5" t="n">
-        <v>145.6</v>
+        <v>102.71</v>
       </c>
       <c r="F282" s="5" t="n">
-        <v>145.6</v>
+        <v>104.57</v>
       </c>
       <c r="G282" s="5" t="n">
-        <v>139.54</v>
+        <v>101.79</v>
       </c>
       <c r="H282" s="6" t="n">
         <v>0.9</v>
@@ -22603,30 +22603,30 @@
     <row r="283">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>XYL</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Xylem Inc.</t>
+          <t>Merck &amp; Co.</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D283" s="5" t="n">
-        <v>101.79</v>
+        <v>144.3</v>
       </c>
       <c r="E283" s="5" t="n">
-        <v>102.71</v>
+        <v>145.6</v>
       </c>
       <c r="F283" s="5" t="n">
-        <v>104.57</v>
+        <v>145.6</v>
       </c>
       <c r="G283" s="5" t="n">
-        <v>101.79</v>
+        <v>139.54</v>
       </c>
       <c r="H283" s="6" t="n">
         <v>0.9</v>
@@ -22635,30 +22635,30 @@
     <row r="284">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>LIN</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Linde plc</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D284" s="5" t="n">
-        <v>479.48</v>
+        <v>128.5</v>
       </c>
       <c r="E284" s="5" t="n">
-        <v>483.73</v>
+        <v>129.64</v>
       </c>
       <c r="F284" s="5" t="n">
-        <v>489.95</v>
+        <v>129.64</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>479.48</v>
+        <v>127.32</v>
       </c>
       <c r="H284" s="6" t="n">
         <v>0.89</v>
@@ -22667,30 +22667,30 @@
     <row r="285">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Linde plc</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D285" s="5" t="n">
-        <v>128.5</v>
+        <v>479.48</v>
       </c>
       <c r="E285" s="5" t="n">
-        <v>129.64</v>
+        <v>483.73</v>
       </c>
       <c r="F285" s="5" t="n">
-        <v>129.64</v>
+        <v>489.95</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>127.32</v>
+        <v>479.48</v>
       </c>
       <c r="H285" s="6" t="n">
         <v>0.89</v>
@@ -22859,30 +22859,30 @@
     <row r="291">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>CPAY</t>
+          <t>SYY</t>
         </is>
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Corpay</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D291" s="5" t="n">
-        <v>394.6</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E291" s="5" t="n">
-        <v>397.92</v>
+        <v>78.14</v>
       </c>
       <c r="F291" s="5" t="n">
-        <v>406.79</v>
+        <v>78.2</v>
       </c>
       <c r="G291" s="5" t="n">
-        <v>394.6</v>
+        <v>76.38</v>
       </c>
       <c r="H291" s="6" t="n">
         <v>0.84</v>
@@ -22891,30 +22891,30 @@
     <row r="292">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>SYY</t>
+          <t>CPAY</t>
         </is>
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Corpay</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D292" s="5" t="n">
-        <v>77.48999999999999</v>
+        <v>394.6</v>
       </c>
       <c r="E292" s="5" t="n">
-        <v>78.14</v>
+        <v>397.92</v>
       </c>
       <c r="F292" s="5" t="n">
-        <v>78.2</v>
+        <v>406.79</v>
       </c>
       <c r="G292" s="5" t="n">
-        <v>76.38</v>
+        <v>394.6</v>
       </c>
       <c r="H292" s="6" t="n">
         <v>0.84</v>
@@ -22923,30 +22923,30 @@
     <row r="293">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>BKNG</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Booking Holdings</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D293" s="5" t="n">
-        <v>159.02</v>
+        <v>505.41</v>
       </c>
       <c r="E293" s="5" t="n">
-        <v>160.34</v>
+        <v>509.59</v>
       </c>
       <c r="F293" s="5" t="n">
-        <v>160.34</v>
+        <v>510.12</v>
       </c>
       <c r="G293" s="5" t="n">
-        <v>155.87</v>
+        <v>499.22</v>
       </c>
       <c r="H293" s="6" t="n">
         <v>0.83</v>
@@ -22955,12 +22955,12 @@
     <row r="294">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>ODFL</t>
         </is>
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Old Dominion</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -22969,16 +22969,16 @@
         </is>
       </c>
       <c r="D294" s="5" t="n">
-        <v>505.41</v>
+        <v>180.48</v>
       </c>
       <c r="E294" s="5" t="n">
-        <v>509.59</v>
+        <v>181.97</v>
       </c>
       <c r="F294" s="5" t="n">
-        <v>510.12</v>
+        <v>181.97</v>
       </c>
       <c r="G294" s="5" t="n">
-        <v>499.22</v>
+        <v>175.61</v>
       </c>
       <c r="H294" s="6" t="n">
         <v>0.83</v>
@@ -22987,30 +22987,30 @@
     <row r="295">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>ODFL</t>
+          <t>BKNG</t>
         </is>
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Old Dominion</t>
+          <t>Booking Holdings</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D295" s="5" t="n">
-        <v>180.48</v>
+        <v>159.02</v>
       </c>
       <c r="E295" s="5" t="n">
-        <v>181.97</v>
+        <v>160.34</v>
       </c>
       <c r="F295" s="5" t="n">
-        <v>181.97</v>
+        <v>160.34</v>
       </c>
       <c r="G295" s="5" t="n">
-        <v>175.61</v>
+        <v>155.87</v>
       </c>
       <c r="H295" s="6" t="n">
         <v>0.83</v>
@@ -23307,30 +23307,30 @@
     <row r="305">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>VMC</t>
+          <t>REG</t>
         </is>
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Vulcan Materials Company</t>
+          <t>Regency Centers</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D305" s="5" t="n">
-        <v>243.06</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E305" s="5" t="n">
-        <v>244.58</v>
+        <v>72.05</v>
       </c>
       <c r="F305" s="5" t="n">
-        <v>248.85</v>
+        <v>72.05</v>
       </c>
       <c r="G305" s="5" t="n">
-        <v>243.06</v>
+        <v>70.8</v>
       </c>
       <c r="H305" s="6" t="n">
         <v>0.63</v>
@@ -23339,30 +23339,30 @@
     <row r="306">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>REG</t>
+          <t>VMC</t>
         </is>
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Regency Centers</t>
+          <t>Vulcan Materials Company</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D306" s="5" t="n">
-        <v>71.59999999999999</v>
+        <v>243.06</v>
       </c>
       <c r="E306" s="5" t="n">
-        <v>72.05</v>
+        <v>244.58</v>
       </c>
       <c r="F306" s="5" t="n">
-        <v>72.05</v>
+        <v>248.85</v>
       </c>
       <c r="G306" s="5" t="n">
-        <v>70.8</v>
+        <v>243.06</v>
       </c>
       <c r="H306" s="6" t="n">
         <v>0.63</v>
@@ -23755,12 +23755,12 @@
     <row r="319">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>ITW</t>
+          <t>FDX</t>
         </is>
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>FedEx</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -23769,16 +23769,16 @@
         </is>
       </c>
       <c r="D319" s="5" t="n">
-        <v>262.92</v>
+        <v>290.36</v>
       </c>
       <c r="E319" s="5" t="n">
-        <v>264.13</v>
+        <v>291.71</v>
       </c>
       <c r="F319" s="5" t="n">
-        <v>267.14</v>
+        <v>291.73</v>
       </c>
       <c r="G319" s="5" t="n">
-        <v>261.15</v>
+        <v>289.03</v>
       </c>
       <c r="H319" s="6" t="n">
         <v>0.46</v>
@@ -23787,12 +23787,12 @@
     <row r="320">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>FDX</t>
+          <t>ITW</t>
         </is>
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>FedEx</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -23801,16 +23801,16 @@
         </is>
       </c>
       <c r="D320" s="5" t="n">
-        <v>290.36</v>
+        <v>262.92</v>
       </c>
       <c r="E320" s="5" t="n">
-        <v>291.71</v>
+        <v>264.13</v>
       </c>
       <c r="F320" s="5" t="n">
-        <v>291.73</v>
+        <v>267.14</v>
       </c>
       <c r="G320" s="5" t="n">
-        <v>289.03</v>
+        <v>261.15</v>
       </c>
       <c r="H320" s="6" t="n">
         <v>0.46</v>
@@ -23883,30 +23883,30 @@
     <row r="323">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Schlumberger</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D323" s="5" t="n">
-        <v>221.09</v>
+        <v>48.74</v>
       </c>
       <c r="E323" s="5" t="n">
-        <v>222.04</v>
+        <v>48.95</v>
       </c>
       <c r="F323" s="5" t="n">
-        <v>226.54</v>
+        <v>50.28</v>
       </c>
       <c r="G323" s="5" t="n">
-        <v>217.77</v>
+        <v>47.96</v>
       </c>
       <c r="H323" s="6" t="n">
         <v>0.43</v>
@@ -23915,30 +23915,30 @@
     <row r="324">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Schlumberger</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D324" s="5" t="n">
-        <v>48.74</v>
+        <v>221.09</v>
       </c>
       <c r="E324" s="5" t="n">
-        <v>48.95</v>
+        <v>222.04</v>
       </c>
       <c r="F324" s="5" t="n">
-        <v>50.28</v>
+        <v>226.54</v>
       </c>
       <c r="G324" s="5" t="n">
-        <v>47.96</v>
+        <v>217.77</v>
       </c>
       <c r="H324" s="6" t="n">
         <v>0.43</v>
@@ -24075,30 +24075,30 @@
     <row r="329">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>KHC</t>
         </is>
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>Kraft Heinz</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D329" s="5" t="n">
-        <v>786.61</v>
+        <v>22.19</v>
       </c>
       <c r="E329" s="5" t="n">
-        <v>789.45</v>
+        <v>22.27</v>
       </c>
       <c r="F329" s="5" t="n">
-        <v>824.52</v>
+        <v>22.48</v>
       </c>
       <c r="G329" s="5" t="n">
-        <v>778.24</v>
+        <v>21.84</v>
       </c>
       <c r="H329" s="6" t="n">
         <v>0.36</v>
@@ -24107,30 +24107,30 @@
     <row r="330">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>KHC</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Kraft Heinz</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D330" s="5" t="n">
-        <v>22.19</v>
+        <v>786.61</v>
       </c>
       <c r="E330" s="5" t="n">
-        <v>22.27</v>
+        <v>789.45</v>
       </c>
       <c r="F330" s="5" t="n">
-        <v>22.48</v>
+        <v>824.52</v>
       </c>
       <c r="G330" s="5" t="n">
-        <v>21.84</v>
+        <v>778.24</v>
       </c>
       <c r="H330" s="6" t="n">
         <v>0.36</v>
@@ -24203,12 +24203,12 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>DVA</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>DaVita</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -24217,16 +24217,16 @@
         </is>
       </c>
       <c r="D333" s="5" t="n">
-        <v>178.69</v>
+        <v>42.6</v>
       </c>
       <c r="E333" s="5" t="n">
-        <v>179.25</v>
+        <v>42.73</v>
       </c>
       <c r="F333" s="5" t="n">
-        <v>180.4</v>
+        <v>42.73</v>
       </c>
       <c r="G333" s="5" t="n">
-        <v>176.78</v>
+        <v>41.58</v>
       </c>
       <c r="H333" s="6" t="n">
         <v>0.31</v>
@@ -24267,12 +24267,12 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>DVA</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -24281,16 +24281,16 @@
         </is>
       </c>
       <c r="D335" s="5" t="n">
-        <v>42.6</v>
+        <v>178.69</v>
       </c>
       <c r="E335" s="5" t="n">
-        <v>42.73</v>
+        <v>179.25</v>
       </c>
       <c r="F335" s="5" t="n">
-        <v>42.73</v>
+        <v>180.4</v>
       </c>
       <c r="G335" s="5" t="n">
-        <v>41.58</v>
+        <v>176.78</v>
       </c>
       <c r="H335" s="6" t="n">
         <v>0.31</v>
@@ -24971,30 +24971,30 @@
     <row r="357">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>SCHW</t>
         </is>
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Fastenal</t>
+          <t>Charles Schwab Corporation</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D357" s="5" t="n">
-        <v>50.75</v>
+        <v>96.7</v>
       </c>
       <c r="E357" s="5" t="n">
-        <v>50.75</v>
+        <v>96.7</v>
       </c>
       <c r="F357" s="5" t="n">
-        <v>50.81</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="G357" s="5" t="n">
-        <v>49.83</v>
+        <v>95.58</v>
       </c>
       <c r="H357" s="6" t="n">
         <v>0</v>
@@ -25035,30 +25035,30 @@
     <row r="359">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>SCHW</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Charles Schwab Corporation</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D359" s="5" t="n">
-        <v>96.7</v>
+        <v>50.75</v>
       </c>
       <c r="E359" s="5" t="n">
-        <v>96.7</v>
+        <v>50.75</v>
       </c>
       <c r="F359" s="5" t="n">
-        <v>97.95999999999999</v>
+        <v>50.81</v>
       </c>
       <c r="G359" s="5" t="n">
-        <v>95.58</v>
+        <v>49.83</v>
       </c>
       <c r="H359" s="6" t="n">
         <v>0</v>
@@ -25515,30 +25515,30 @@
     <row r="374">
       <c r="A374" s="4" t="inlineStr">
         <is>
-          <t>CSX</t>
+          <t>KIM</t>
         </is>
       </c>
       <c r="B374" s="4" t="inlineStr">
         <is>
-          <t>CSX Corporation</t>
+          <t>Kimco Realty</t>
         </is>
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D374" s="5" t="n">
-        <v>47.43</v>
+        <v>22.24</v>
       </c>
       <c r="E374" s="5" t="n">
-        <v>47.26</v>
+        <v>22.16</v>
       </c>
       <c r="F374" s="5" t="n">
-        <v>47.5</v>
+        <v>22.24</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>46.81</v>
+        <v>21.85</v>
       </c>
       <c r="H374" s="7" t="n">
         <v>-0.36</v>
@@ -25547,30 +25547,30 @@
     <row r="375">
       <c r="A375" s="4" t="inlineStr">
         <is>
-          <t>KIM</t>
+          <t>CSX</t>
         </is>
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>Kimco Realty</t>
+          <t>CSX Corporation</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D375" s="5" t="n">
-        <v>22.24</v>
+        <v>47.43</v>
       </c>
       <c r="E375" s="5" t="n">
-        <v>22.16</v>
+        <v>47.26</v>
       </c>
       <c r="F375" s="5" t="n">
-        <v>22.24</v>
+        <v>47.5</v>
       </c>
       <c r="G375" s="5" t="n">
-        <v>21.85</v>
+        <v>46.81</v>
       </c>
       <c r="H375" s="7" t="n">
         <v>-0.36</v>
@@ -25707,30 +25707,30 @@
     <row r="380">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>CRH</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="B380" s="4" t="inlineStr">
         <is>
-          <t>CRH plc</t>
+          <t>Interactive Brokers</t>
         </is>
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D380" s="5" t="n">
-        <v>81.94</v>
+        <v>88.3</v>
       </c>
       <c r="E380" s="5" t="n">
-        <v>81.54000000000001</v>
+        <v>87.87</v>
       </c>
       <c r="F380" s="5" t="n">
-        <v>83.59999999999999</v>
+        <v>90.58</v>
       </c>
       <c r="G380" s="5" t="n">
-        <v>81.45999999999999</v>
+        <v>86.47</v>
       </c>
       <c r="H380" s="7" t="n">
         <v>-0.49</v>
@@ -25739,30 +25739,30 @@
     <row r="381">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>Interactive Brokers</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D381" s="5" t="n">
-        <v>88.3</v>
+        <v>384.64</v>
       </c>
       <c r="E381" s="5" t="n">
-        <v>87.87</v>
+        <v>382.75</v>
       </c>
       <c r="F381" s="5" t="n">
-        <v>90.58</v>
+        <v>388.03</v>
       </c>
       <c r="G381" s="5" t="n">
-        <v>86.47</v>
+        <v>374.67</v>
       </c>
       <c r="H381" s="7" t="n">
         <v>-0.49</v>
@@ -25771,30 +25771,30 @@
     <row r="382">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>CRH</t>
         </is>
       </c>
       <c r="B382" s="4" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>CRH plc</t>
         </is>
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D382" s="5" t="n">
-        <v>384.64</v>
+        <v>81.94</v>
       </c>
       <c r="E382" s="5" t="n">
-        <v>382.75</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="F382" s="5" t="n">
-        <v>388.03</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G382" s="5" t="n">
-        <v>374.67</v>
+        <v>81.45999999999999</v>
       </c>
       <c r="H382" s="7" t="n">
         <v>-0.49</v>
@@ -26091,30 +26091,30 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>ALGN</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Align Technology</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>447.41</v>
+        <v>143.74</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>444.18</v>
+        <v>142.71</v>
       </c>
       <c r="F392" s="5" t="n">
-        <v>456.28</v>
+        <v>143.74</v>
       </c>
       <c r="G392" s="5" t="n">
-        <v>444.18</v>
+        <v>139.87</v>
       </c>
       <c r="H392" s="7" t="n">
         <v>-0.72</v>
@@ -26123,30 +26123,30 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>ALGN</t>
+          <t>MSI</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Align Technology</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>143.74</v>
+        <v>447.41</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>142.71</v>
+        <v>444.18</v>
       </c>
       <c r="F393" s="5" t="n">
-        <v>143.74</v>
+        <v>456.28</v>
       </c>
       <c r="G393" s="5" t="n">
-        <v>139.87</v>
+        <v>444.18</v>
       </c>
       <c r="H393" s="7" t="n">
         <v>-0.72</v>
@@ -26923,30 +26923,30 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Ametek</t>
+          <t>Darden Restaurants</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D418" s="5" t="n">
-        <v>251.93</v>
+        <v>200.33</v>
       </c>
       <c r="E418" s="5" t="n">
-        <v>248.58</v>
+        <v>197.66</v>
       </c>
       <c r="F418" s="5" t="n">
-        <v>253.72</v>
+        <v>203.14</v>
       </c>
       <c r="G418" s="5" t="n">
-        <v>247.52</v>
+        <v>197.66</v>
       </c>
       <c r="H418" s="7" t="n">
         <v>-1.33</v>
@@ -26955,30 +26955,30 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Darden Restaurants</t>
+          <t>Ametek</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>200.33</v>
+        <v>251.93</v>
       </c>
       <c r="E419" s="5" t="n">
-        <v>197.66</v>
+        <v>248.58</v>
       </c>
       <c r="F419" s="5" t="n">
-        <v>203.14</v>
+        <v>253.72</v>
       </c>
       <c r="G419" s="5" t="n">
-        <v>197.66</v>
+        <v>247.52</v>
       </c>
       <c r="H419" s="7" t="n">
         <v>-1.33</v>
@@ -28363,12 +28363,12 @@
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>Qnity Electronics</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
@@ -28377,16 +28377,16 @@
         </is>
       </c>
       <c r="D463" s="5" t="n">
-        <v>131.48</v>
+        <v>1439.73</v>
       </c>
       <c r="E463" s="5" t="n">
-        <v>126.6</v>
+        <v>1386.29</v>
       </c>
       <c r="F463" s="5" t="n">
-        <v>133.63</v>
+        <v>1479.89</v>
       </c>
       <c r="G463" s="5" t="n">
-        <v>126.6</v>
+        <v>1369.8</v>
       </c>
       <c r="H463" s="7" t="n">
         <v>-3.71</v>
@@ -28395,12 +28395,12 @@
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Qnity Electronics</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
@@ -28409,16 +28409,16 @@
         </is>
       </c>
       <c r="D464" s="5" t="n">
-        <v>1439.73</v>
+        <v>131.48</v>
       </c>
       <c r="E464" s="5" t="n">
-        <v>1386.29</v>
+        <v>126.6</v>
       </c>
       <c r="F464" s="5" t="n">
-        <v>1479.89</v>
+        <v>133.63</v>
       </c>
       <c r="G464" s="5" t="n">
-        <v>1369.8</v>
+        <v>126.6</v>
       </c>
       <c r="H464" s="7" t="n">
         <v>-3.71</v>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 08-&gt;Oct 09) and rolling 5-day  |  updated 2026-10-11 09:30</t>
+          <t>Daily (Oct 08-&gt;Oct 09) and rolling 5-day  |  updated 2026-10-12 10:00</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 15 close to Oct 16 close  |  503 companies  |  updated 2026-10-17 07:19</t>
+          <t>Oct 15 close to Oct 16 close  |  503 companies  |  updated 2026-10-18 07:34</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 09 close to Oct 16 close  |  503 companies  |  updated 2026-10-17 07:19</t>
+          <t>Oct 09 close to Oct 16 close  |  503 companies  |  updated 2026-10-18 07:34</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 15-&gt;Oct 16) and rolling 5-day  |  updated 2026-10-17 07:19</t>
+          <t>Daily (Oct 15-&gt;Oct 16) and rolling 5-day  |  updated 2026-10-18 07:34</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 15 close to Oct 16 close  |  503 companies  |  updated 2026-10-18 07:34</t>
+          <t>Oct 15 close to Oct 16 close  |  503 companies  |  updated 2026-10-19 08:17</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 09 close to Oct 16 close  |  503 companies  |  updated 2026-10-18 07:34</t>
+          <t>Oct 09 close to Oct 16 close  |  503 companies  |  updated 2026-10-19 08:17</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 15-&gt;Oct 16) and rolling 5-day  |  updated 2026-10-18 07:34</t>
+          <t>Daily (Oct 15-&gt;Oct 16) and rolling 5-day  |  updated 2026-10-19 08:17</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 22 close to Oct 23 close  |  503 companies  |  updated 2026-10-24 07:45</t>
+          <t>Oct 22 close to Oct 23 close  |  503 companies  |  updated 2026-10-25 07:56</t>
         </is>
       </c>
     </row>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 16 close to Oct 23 close  |  503 companies  |  updated 2026-10-24 07:45</t>
+          <t>Oct 16 close to Oct 23 close  |  503 companies  |  updated 2026-10-25 07:56</t>
         </is>
       </c>
     </row>
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 22-&gt;Oct 23) and rolling 5-day  |  updated 2026-10-24 07:45</t>
+          <t>Daily (Oct 22-&gt;Oct 23) and rolling 5-day  |  updated 2026-10-25 07:56</t>
         </is>
       </c>
     </row>

--- a/SP500_Weekly_Performance.xlsx
+++ b/SP500_Weekly_Performance.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 22 close to Oct 23 close  |  503 companies  |  updated 2026-10-25 07:56</t>
+          <t>Oct 22 close to Oct 23 close  |  503 companies  |  updated 2026-10-26 08:17</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Skydance Corporation</t>
+          <t>Skydance</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -10527,24 +10527,24 @@
     <row r="389">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>EME</t>
         </is>
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Emcor</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D389" s="5" t="n">
-        <v>112.32</v>
+        <v>660.41</v>
       </c>
       <c r="E389" s="5" t="n">
-        <v>110.15</v>
+        <v>647.66</v>
       </c>
       <c r="F389" s="7" t="n">
         <v>-1.93</v>
@@ -10579,24 +10579,24 @@
     <row r="391">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>EME</t>
+          <t>HIG</t>
         </is>
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>Emcor</t>
+          <t>Hartford (The)</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D391" s="5" t="n">
-        <v>660.41</v>
+        <v>139.45</v>
       </c>
       <c r="E391" s="5" t="n">
-        <v>647.66</v>
+        <v>136.76</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>-1.93</v>
@@ -10605,24 +10605,24 @@
     <row r="392">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>HIG</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Hartford (The)</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D392" s="5" t="n">
-        <v>139.45</v>
+        <v>112.32</v>
       </c>
       <c r="E392" s="5" t="n">
-        <v>136.76</v>
+        <v>110.15</v>
       </c>
       <c r="F392" s="7" t="n">
         <v>-1.93</v>
@@ -10631,24 +10631,24 @@
     <row r="393">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>TTWO</t>
+          <t>FIS</t>
         </is>
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Take-Two Interactive</t>
+          <t>Fidelity National Information Services</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D393" s="5" t="n">
-        <v>207.81</v>
+        <v>38.29</v>
       </c>
       <c r="E393" s="5" t="n">
-        <v>203.69</v>
+        <v>37.53</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>-1.98</v>
@@ -10657,24 +10657,24 @@
     <row r="394">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>FIS</t>
+          <t>JBHT</t>
         </is>
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>Fidelity National Information Services</t>
+          <t>J.B. Hunt</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D394" s="5" t="n">
-        <v>38.29</v>
+        <v>230.59</v>
       </c>
       <c r="E394" s="5" t="n">
-        <v>37.53</v>
+        <v>226.03</v>
       </c>
       <c r="F394" s="7" t="n">
         <v>-1.98</v>
@@ -10683,24 +10683,24 @@
     <row r="395">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>JBHT</t>
+          <t>TTWO</t>
         </is>
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>J.B. Hunt</t>
+          <t>Take-Two Interactive</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D395" s="5" t="n">
-        <v>230.59</v>
+        <v>207.81</v>
       </c>
       <c r="E395" s="5" t="n">
-        <v>226.03</v>
+        <v>203.69</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>-1.98</v>
@@ -10839,24 +10839,24 @@
     <row r="401">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>American International Group</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D401" s="5" t="n">
-        <v>175.76</v>
+        <v>83.03</v>
       </c>
       <c r="E401" s="5" t="n">
-        <v>172.01</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>-2.13</v>
@@ -10865,24 +10865,24 @@
     <row r="402">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>American International Group</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D402" s="5" t="n">
-        <v>83.03</v>
+        <v>175.76</v>
       </c>
       <c r="E402" s="5" t="n">
-        <v>81.26000000000001</v>
+        <v>172.01</v>
       </c>
       <c r="F402" s="7" t="n">
         <v>-2.13</v>
@@ -10969,24 +10969,24 @@
     <row r="406">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>PPG</t>
+          <t>NRG</t>
         </is>
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>NRG Energy</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D406" s="5" t="n">
-        <v>113.09</v>
+        <v>94.38</v>
       </c>
       <c r="E406" s="5" t="n">
-        <v>110.61</v>
+        <v>92.31</v>
       </c>
       <c r="F406" s="7" t="n">
         <v>-2.19</v>
@@ -10995,24 +10995,24 @@
     <row r="407">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>NRG</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>NRG Energy</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D407" s="5" t="n">
-        <v>94.38</v>
+        <v>113.09</v>
       </c>
       <c r="E407" s="5" t="n">
-        <v>92.31</v>
+        <v>110.61</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>-2.19</v>
@@ -11125,24 +11125,24 @@
     <row r="412">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Fox Corporation (Class B)</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D412" s="5" t="n">
-        <v>60.82</v>
+        <v>123.27</v>
       </c>
       <c r="E412" s="5" t="n">
-        <v>59.46</v>
+        <v>120.51</v>
       </c>
       <c r="F412" s="7" t="n">
         <v>-2.24</v>
@@ -11151,24 +11151,24 @@
     <row r="413">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Fox Corporation (Class B)</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D413" s="5" t="n">
-        <v>123.27</v>
+        <v>60.82</v>
       </c>
       <c r="E413" s="5" t="n">
-        <v>120.51</v>
+        <v>59.46</v>
       </c>
       <c r="F413" s="7" t="n">
         <v>-2.24</v>
@@ -11255,24 +11255,24 @@
     <row r="417">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>Altria</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D417" s="5" t="n">
-        <v>76.06999999999999</v>
+        <v>33.72</v>
       </c>
       <c r="E417" s="5" t="n">
-        <v>74.31</v>
+        <v>32.94</v>
       </c>
       <c r="F417" s="7" t="n">
         <v>-2.31</v>
@@ -11281,24 +11281,24 @@
     <row r="418">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Supermicro</t>
+          <t>Altria</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D418" s="5" t="n">
-        <v>33.72</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="E418" s="5" t="n">
-        <v>32.94</v>
+        <v>74.31</v>
       </c>
       <c r="F418" s="7" t="n">
         <v>-2.31</v>
@@ -11307,24 +11307,24 @@
     <row r="419">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>LVS</t>
         </is>
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Solventum</t>
+          <t>Las Vegas Sands</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D419" s="5" t="n">
-        <v>87.45</v>
+        <v>36.53</v>
       </c>
       <c r="E419" s="5" t="n">
-        <v>85.41</v>
+        <v>35.68</v>
       </c>
       <c r="F419" s="7" t="n">
         <v>-2.33</v>
@@ -11333,24 +11333,24 @@
     <row r="420">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>LVS</t>
+          <t>SOLV</t>
         </is>
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Las Vegas Sands</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D420" s="5" t="n">
-        <v>36.53</v>
+        <v>87.45</v>
       </c>
       <c r="E420" s="5" t="n">
-        <v>35.68</v>
+        <v>85.41</v>
       </c>
       <c r="F420" s="7" t="n">
         <v>-2.33</v>
@@ -11775,24 +11775,24 @@
     <row r="437">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>IVZ</t>
         </is>
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>Lilly (Eli)</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D437" s="5" t="n">
-        <v>1306.69</v>
+        <v>28.79</v>
       </c>
       <c r="E437" s="5" t="n">
-        <v>1273.46</v>
+        <v>28.06</v>
       </c>
       <c r="F437" s="7" t="n">
         <v>-2.54</v>
@@ -11801,24 +11801,24 @@
     <row r="438">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>IVZ</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>Invesco</t>
+          <t>Lilly (Eli)</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="D438" s="5" t="n">
-        <v>28.79</v>
+        <v>1306.69</v>
       </c>
       <c r="E438" s="5" t="n">
-        <v>28.06</v>
+        <v>1273.46</v>
       </c>
       <c r="F438" s="7" t="n">
         <v>-2.54</v>
@@ -11827,12 +11827,12 @@
     <row r="439">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>BF.B</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Brown–Forman</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
@@ -11841,10 +11841,10 @@
         </is>
       </c>
       <c r="D439" s="5" t="n">
-        <v>30.18</v>
+        <v>88.66</v>
       </c>
       <c r="E439" s="5" t="n">
-        <v>29.41</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F439" s="7" t="n">
         <v>-2.55</v>
@@ -11853,12 +11853,12 @@
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>CLX</t>
+          <t>BF.B</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>Clorox</t>
+          <t>Brown–Forman</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
@@ -11867,10 +11867,10 @@
         </is>
       </c>
       <c r="D440" s="5" t="n">
-        <v>88.66</v>
+        <v>30.18</v>
       </c>
       <c r="E440" s="5" t="n">
-        <v>86.40000000000001</v>
+        <v>29.41</v>
       </c>
       <c r="F440" s="7" t="n">
         <v>-2.55</v>
@@ -13626,7 +13626,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Oct 16 close to Oct 23 close  |  503 companies  |  updated 2026-10-25 07:56</t>
+          <t>Oct 16 close to Oct 23 close  |  503 companies  |  updated 2026-10-26 08:17</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13872,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Skydance Corporation</t>
+          <t>Skydance</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -29797,7 +29797,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Daily (Oct 22-&gt;Oct 23) and rolling 5-day  |  updated 2026-10-25 07:56</t>
+          <t>Daily (Oct 22-&gt;Oct 23) and rolling 5-day  |  updated 2026-10-26 08:17</t>
         </is>
       </c>
     </row>
